--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="138">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -427,6 +427,9 @@
   <si>
     <t>alto_cm</t>
   </si>
+  <si>
+    <t>110_40</t>
+  </si>
 </sst>
 </file>
 
@@ -7177,7 +7180,7 @@
         <v>115</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>116</v>
@@ -7186,7 +7189,7 @@
         <v>1098</v>
       </c>
       <c r="E145" s="21">
-        <v>597</v>
+        <v>397</v>
       </c>
       <c r="F145" s="21"/>
       <c r="G145" s="22" t="s">
@@ -7194,10 +7197,10 @@
       </c>
       <c r="H145" s="9">
         <f t="shared" si="8"/>
-        <v>699.3</v>
+        <v>1639.3999999999999</v>
       </c>
       <c r="I145" s="21">
-        <v>999</v>
+        <v>2342</v>
       </c>
       <c r="J145" s="21">
         <v>30</v>
@@ -7215,27 +7218,46 @@
       <c r="U145" s="10"/>
     </row>
     <row r="146" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A146" s="10"/>
-      <c r="B146" s="10"/>
-      <c r="C146" s="10"/>
-      <c r="D146" s="10"/>
-      <c r="E146" s="10"/>
-      <c r="F146" s="10"/>
-      <c r="G146" s="10"/>
-      <c r="H146" s="10"/>
-      <c r="I146" s="10"/>
-      <c r="J146" s="10"/>
-      <c r="K146" s="10"/>
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
-      <c r="N146" s="10"/>
-      <c r="O146" s="10"/>
-      <c r="P146" s="10"/>
-      <c r="Q146" s="10"/>
-      <c r="R146" s="10"/>
-      <c r="S146" s="10"/>
-      <c r="T146" s="10"/>
-      <c r="U146" s="10"/>
+      <c r="A146" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C146" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D146" s="23">
+        <v>1098</v>
+      </c>
+      <c r="E146" s="23">
+        <v>597</v>
+      </c>
+      <c r="F146" s="23"/>
+      <c r="G146" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H146" s="9">
+        <f t="shared" ref="H146" si="9">I146*((100-J146)/100)</f>
+        <v>16396.099999999999</v>
+      </c>
+      <c r="I146" s="23">
+        <v>23423</v>
+      </c>
+      <c r="J146" s="23">
+        <v>30</v>
+      </c>
+      <c r="K146" s="23"/>
+      <c r="L146" s="23"/>
+      <c r="M146" s="23"/>
+      <c r="N146" s="23"/>
+      <c r="O146" s="23"/>
+      <c r="P146" s="23"/>
+      <c r="Q146" s="23"/>
+      <c r="R146" s="23"/>
+      <c r="S146" s="23"/>
+      <c r="T146" s="23"/>
+      <c r="U146" s="23"/>
     </row>
     <row r="147" spans="1:21" ht="15.75" customHeight="1">
       <c r="A147" s="10"/>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="142">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -430,6 +430,18 @@
   <si>
     <t>110_40</t>
   </si>
+  <si>
+    <t>Colgador mueble alto</t>
+  </si>
+  <si>
+    <t>PATA_H10</t>
+  </si>
+  <si>
+    <t>PATA_H15</t>
+  </si>
+  <si>
+    <t>BISAGRA_SENSYS</t>
+  </si>
 </sst>
 </file>
 
@@ -798,7 +810,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U975"/>
+  <dimension ref="A1:U976"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.90625" customWidth="1"/>
@@ -895,11 +907,11 @@
         <v>1</v>
       </c>
       <c r="L2" s="10">
-        <f>D131</f>
+        <f>D132</f>
         <v>698</v>
       </c>
       <c r="M2" s="10">
-        <f>E131</f>
+        <f>E132</f>
         <v>147</v>
       </c>
       <c r="N2" s="10"/>
@@ -947,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="23">
-        <f t="shared" ref="L3:M3" si="1">D132</f>
+        <f t="shared" ref="L3:M3" si="1">D133</f>
         <v>698</v>
       </c>
       <c r="M3" s="23">
@@ -999,7 +1011,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="23">
-        <f t="shared" ref="L4:M4" si="2">D133</f>
+        <f t="shared" ref="L4:M4" si="2">D134</f>
         <v>698</v>
       </c>
       <c r="M4" s="23">
@@ -1051,7 +1063,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="23">
-        <f t="shared" ref="L5:M5" si="3">D134</f>
+        <f t="shared" ref="L5:M5" si="3">D135</f>
         <v>698</v>
       </c>
       <c r="M5" s="23">
@@ -1103,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="23">
-        <f t="shared" ref="L6:M6" si="4">D135</f>
+        <f t="shared" ref="L6:M6" si="4">D136</f>
         <v>698</v>
       </c>
       <c r="M6" s="23">
@@ -1155,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="23">
-        <f t="shared" ref="L7:M7" si="5">D136</f>
+        <f t="shared" ref="L7:M7" si="5">D137</f>
         <v>698</v>
       </c>
       <c r="M7" s="23">
@@ -1207,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="23">
-        <f t="shared" ref="L8:M8" si="6">D137</f>
+        <f t="shared" ref="L8:M8" si="6">D138</f>
         <v>698</v>
       </c>
       <c r="M8" s="23">
@@ -6694,9 +6706,12 @@
       <c r="A128" s="25" t="s">
         <v>114</v>
       </c>
+      <c r="C128" s="7" t="s">
+        <v>141</v>
+      </c>
       <c r="F128" s="23"/>
       <c r="H128" s="9">
-        <f t="shared" ref="H128:H130" si="7">I128*((100-J128)/100)</f>
+        <f t="shared" ref="H128:H131" si="7">I128*((100-J128)/100)</f>
         <v>3.0352396694214878</v>
       </c>
       <c r="I128" s="23">
@@ -6712,10 +6727,12 @@
       <c r="A129" s="25" t="s">
         <v>114</v>
       </c>
+      <c r="C129" s="7" t="s">
+        <v>139</v>
+      </c>
       <c r="F129" s="23"/>
       <c r="H129" s="9">
-        <f t="shared" si="7"/>
-        <v>1.8722809917355372</v>
+        <v>1</v>
       </c>
       <c r="I129" s="23">
         <f>2.27/1.21</f>
@@ -6729,47 +6746,33 @@
       <c r="A130" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="F130" s="21"/>
+      <c r="C130" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F130" s="23"/>
       <c r="H130" s="9">
+        <v>1</v>
+      </c>
+      <c r="I130" s="23"/>
+      <c r="J130" s="24"/>
+    </row>
+    <row r="131" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A131" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F131" s="21"/>
+      <c r="H131" s="9">
         <f t="shared" si="7"/>
         <v>3.992</v>
       </c>
-      <c r="I130" s="21">
+      <c r="I131" s="21">
         <v>4</v>
       </c>
-      <c r="J130" s="24">
+      <c r="J131" s="24">
         <v>0.2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A131" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B131" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C131" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D131" s="21">
-        <v>698</v>
-      </c>
-      <c r="E131" s="21">
-        <v>147</v>
-      </c>
-      <c r="F131" s="21"/>
-      <c r="G131" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="H131" s="9">
-        <f t="shared" ref="H131:H145" si="8">I131*((100-J131)/100)</f>
-        <v>700</v>
-      </c>
-      <c r="I131" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J131" s="21">
-        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:10" ht="15.75" customHeight="1">
@@ -6777,7 +6780,7 @@
         <v>115</v>
       </c>
       <c r="B132" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C132" s="22" t="s">
         <v>116</v>
@@ -6786,14 +6789,14 @@
         <v>698</v>
       </c>
       <c r="E132" s="21">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="F132" s="21"/>
       <c r="G132" s="22" t="s">
         <v>117</v>
       </c>
       <c r="H132" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="H132:H146" si="8">I132*((100-J132)/100)</f>
         <v>700</v>
       </c>
       <c r="I132" s="21">
@@ -6808,7 +6811,7 @@
         <v>115</v>
       </c>
       <c r="B133" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C133" s="22" t="s">
         <v>116</v>
@@ -6817,7 +6820,7 @@
         <v>698</v>
       </c>
       <c r="E133" s="21">
-        <v>347</v>
+        <v>297</v>
       </c>
       <c r="F133" s="21"/>
       <c r="G133" s="22" t="s">
@@ -6839,7 +6842,7 @@
         <v>115</v>
       </c>
       <c r="B134" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C134" s="22" t="s">
         <v>116</v>
@@ -6848,7 +6851,7 @@
         <v>698</v>
       </c>
       <c r="E134" s="21">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="F134" s="21"/>
       <c r="G134" s="22" t="s">
@@ -6870,7 +6873,7 @@
         <v>115</v>
       </c>
       <c r="B135" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C135" s="22" t="s">
         <v>116</v>
@@ -6879,7 +6882,7 @@
         <v>698</v>
       </c>
       <c r="E135" s="21">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="F135" s="21"/>
       <c r="G135" s="22" t="s">
@@ -6901,7 +6904,7 @@
         <v>115</v>
       </c>
       <c r="B136" s="22" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C136" s="22" t="s">
         <v>116</v>
@@ -6910,7 +6913,7 @@
         <v>698</v>
       </c>
       <c r="E136" s="21">
-        <v>497</v>
+        <v>447</v>
       </c>
       <c r="F136" s="21"/>
       <c r="G136" s="22" t="s">
@@ -6932,7 +6935,7 @@
         <v>115</v>
       </c>
       <c r="B137" s="22" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C137" s="22" t="s">
         <v>116</v>
@@ -6941,7 +6944,7 @@
         <v>698</v>
       </c>
       <c r="E137" s="21">
-        <v>597</v>
+        <v>497</v>
       </c>
       <c r="F137" s="21"/>
       <c r="G137" s="22" t="s">
@@ -6963,16 +6966,16 @@
         <v>115</v>
       </c>
       <c r="B138" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C138" s="22" t="s">
         <v>116</v>
       </c>
       <c r="D138" s="21">
-        <v>798</v>
+        <v>698</v>
       </c>
       <c r="E138" s="21">
-        <v>147</v>
+        <v>597</v>
       </c>
       <c r="F138" s="21"/>
       <c r="G138" s="22" t="s">
@@ -6994,7 +6997,7 @@
         <v>115</v>
       </c>
       <c r="B139" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C139" s="22" t="s">
         <v>116</v>
@@ -7003,7 +7006,7 @@
         <v>798</v>
       </c>
       <c r="E139" s="21">
-        <v>297</v>
+        <v>147</v>
       </c>
       <c r="F139" s="21"/>
       <c r="G139" s="22" t="s">
@@ -7025,7 +7028,7 @@
         <v>115</v>
       </c>
       <c r="B140" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C140" s="22" t="s">
         <v>116</v>
@@ -7034,7 +7037,7 @@
         <v>798</v>
       </c>
       <c r="E140" s="21">
-        <v>347</v>
+        <v>297</v>
       </c>
       <c r="F140" s="21"/>
       <c r="G140" s="22" t="s">
@@ -7056,7 +7059,7 @@
         <v>115</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C141" s="22" t="s">
         <v>116</v>
@@ -7065,7 +7068,7 @@
         <v>798</v>
       </c>
       <c r="E141" s="21">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="F141" s="21"/>
       <c r="G141" s="22" t="s">
@@ -7087,7 +7090,7 @@
         <v>115</v>
       </c>
       <c r="B142" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C142" s="22" t="s">
         <v>116</v>
@@ -7096,7 +7099,7 @@
         <v>798</v>
       </c>
       <c r="E142" s="21">
-        <v>447</v>
+        <v>397</v>
       </c>
       <c r="F142" s="21"/>
       <c r="G142" s="22" t="s">
@@ -7118,7 +7121,7 @@
         <v>115</v>
       </c>
       <c r="B143" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C143" s="22" t="s">
         <v>116</v>
@@ -7127,7 +7130,7 @@
         <v>798</v>
       </c>
       <c r="E143" s="21">
-        <v>497</v>
+        <v>447</v>
       </c>
       <c r="F143" s="21"/>
       <c r="G143" s="22" t="s">
@@ -7149,7 +7152,7 @@
         <v>115</v>
       </c>
       <c r="B144" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C144" s="22" t="s">
         <v>116</v>
@@ -7158,7 +7161,7 @@
         <v>798</v>
       </c>
       <c r="E144" s="21">
-        <v>597</v>
+        <v>497</v>
       </c>
       <c r="F144" s="21"/>
       <c r="G144" s="22" t="s">
@@ -7180,16 +7183,16 @@
         <v>115</v>
       </c>
       <c r="B145" s="22" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C145" s="22" t="s">
         <v>116</v>
       </c>
       <c r="D145" s="21">
-        <v>1098</v>
+        <v>798</v>
       </c>
       <c r="E145" s="21">
-        <v>397</v>
+        <v>597</v>
       </c>
       <c r="F145" s="21"/>
       <c r="G145" s="22" t="s">
@@ -7197,90 +7200,98 @@
       </c>
       <c r="H145" s="9">
         <f t="shared" si="8"/>
-        <v>1639.3999999999999</v>
+        <v>700</v>
       </c>
       <c r="I145" s="21">
-        <v>2342</v>
+        <v>1000</v>
       </c>
       <c r="J145" s="21">
         <v>30</v>
       </c>
-      <c r="K145" s="10"/>
-      <c r="L145" s="10"/>
-      <c r="M145" s="10"/>
-      <c r="N145" s="10"/>
-      <c r="O145" s="10"/>
-      <c r="P145" s="10"/>
-      <c r="Q145" s="10"/>
-      <c r="R145" s="10"/>
-      <c r="S145" s="10"/>
-      <c r="T145" s="10"/>
-      <c r="U145" s="10"/>
     </row>
     <row r="146" spans="1:21" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
         <v>115</v>
       </c>
       <c r="B146" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C146" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="D146" s="23">
+      <c r="D146" s="21">
         <v>1098</v>
       </c>
-      <c r="E146" s="23">
-        <v>597</v>
-      </c>
-      <c r="F146" s="23"/>
+      <c r="E146" s="21">
+        <v>397</v>
+      </c>
+      <c r="F146" s="21"/>
       <c r="G146" s="22" t="s">
         <v>117</v>
       </c>
       <c r="H146" s="9">
-        <f t="shared" ref="H146" si="9">I146*((100-J146)/100)</f>
+        <f t="shared" si="8"/>
+        <v>1639.3999999999999</v>
+      </c>
+      <c r="I146" s="21">
+        <v>2342</v>
+      </c>
+      <c r="J146" s="21">
+        <v>30</v>
+      </c>
+      <c r="K146" s="10"/>
+      <c r="L146" s="10"/>
+      <c r="M146" s="10"/>
+      <c r="N146" s="10"/>
+      <c r="O146" s="10"/>
+      <c r="P146" s="10"/>
+      <c r="Q146" s="10"/>
+      <c r="R146" s="10"/>
+      <c r="S146" s="10"/>
+      <c r="T146" s="10"/>
+      <c r="U146" s="10"/>
+    </row>
+    <row r="147" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A147" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="D147" s="23">
+        <v>1098</v>
+      </c>
+      <c r="E147" s="23">
+        <v>597</v>
+      </c>
+      <c r="F147" s="23"/>
+      <c r="G147" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H147" s="9">
+        <f t="shared" ref="H147" si="9">I147*((100-J147)/100)</f>
         <v>16396.099999999999</v>
       </c>
-      <c r="I146" s="23">
+      <c r="I147" s="23">
         <v>23423</v>
       </c>
-      <c r="J146" s="23">
+      <c r="J147" s="23">
         <v>30</v>
       </c>
-      <c r="K146" s="23"/>
-      <c r="L146" s="23"/>
-      <c r="M146" s="23"/>
-      <c r="N146" s="23"/>
-      <c r="O146" s="23"/>
-      <c r="P146" s="23"/>
-      <c r="Q146" s="23"/>
-      <c r="R146" s="23"/>
-      <c r="S146" s="23"/>
-      <c r="T146" s="23"/>
-      <c r="U146" s="23"/>
-    </row>
-    <row r="147" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A147" s="10"/>
-      <c r="B147" s="10"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="10"/>
-      <c r="E147" s="10"/>
-      <c r="F147" s="10"/>
-      <c r="G147" s="10"/>
-      <c r="H147" s="10"/>
-      <c r="I147" s="10"/>
-      <c r="J147" s="10"/>
-      <c r="K147" s="10"/>
-      <c r="L147" s="10"/>
-      <c r="M147" s="10"/>
-      <c r="N147" s="10"/>
-      <c r="O147" s="10"/>
-      <c r="P147" s="10"/>
-      <c r="Q147" s="10"/>
-      <c r="R147" s="10"/>
-      <c r="S147" s="10"/>
-      <c r="T147" s="10"/>
-      <c r="U147" s="10"/>
+      <c r="K147" s="23"/>
+      <c r="L147" s="23"/>
+      <c r="M147" s="23"/>
+      <c r="N147" s="23"/>
+      <c r="O147" s="23"/>
+      <c r="P147" s="23"/>
+      <c r="Q147" s="23"/>
+      <c r="R147" s="23"/>
+      <c r="S147" s="23"/>
+      <c r="T147" s="23"/>
+      <c r="U147" s="23"/>
     </row>
     <row r="148" spans="1:21" ht="15.75" customHeight="1">
       <c r="A148" s="10"/>
@@ -26326,6 +26337,29 @@
       <c r="T975" s="10"/>
       <c r="U975" s="10"/>
     </row>
+    <row r="976" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A976" s="10"/>
+      <c r="B976" s="10"/>
+      <c r="C976" s="10"/>
+      <c r="D976" s="10"/>
+      <c r="E976" s="10"/>
+      <c r="F976" s="10"/>
+      <c r="G976" s="10"/>
+      <c r="H976" s="10"/>
+      <c r="I976" s="10"/>
+      <c r="J976" s="10"/>
+      <c r="K976" s="10"/>
+      <c r="L976" s="10"/>
+      <c r="M976" s="10"/>
+      <c r="N976" s="10"/>
+      <c r="O976" s="10"/>
+      <c r="P976" s="10"/>
+      <c r="Q976" s="10"/>
+      <c r="R976" s="10"/>
+      <c r="S976" s="10"/>
+      <c r="T976" s="10"/>
+      <c r="U976" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="144">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -442,6 +442,12 @@
   <si>
     <t>BISAGRA_SENSYS</t>
   </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>1s</t>
+  </si>
 </sst>
 </file>
 
@@ -533,7 +539,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -596,6 +602,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3306,7 +3313,7 @@
         <v>94</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>75</v>
@@ -3928,8 +3935,8 @@
       <c r="J67" s="9">
         <v>30</v>
       </c>
-      <c r="K67" s="23">
-        <v>1</v>
+      <c r="K67" s="23" t="s">
+        <v>142</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -4526,8 +4533,8 @@
       <c r="J80" s="9">
         <v>30</v>
       </c>
-      <c r="K80" s="23">
-        <v>1</v>
+      <c r="K80" s="23" t="s">
+        <v>143</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -6723,7 +6730,7 @@
       </c>
       <c r="K128" s="20"/>
     </row>
-    <row r="129" spans="1:10" ht="15.75" customHeight="1">
+    <row r="129" spans="1:12" ht="15.75" customHeight="1">
       <c r="A129" s="25" t="s">
         <v>114</v>
       </c>
@@ -6735,14 +6742,13 @@
         <v>1</v>
       </c>
       <c r="I129" s="23">
-        <f>2.27/1.21</f>
-        <v>1.8760330578512396</v>
+        <v>1</v>
       </c>
       <c r="J129" s="24">
         <v>0.2</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15.75" customHeight="1">
+    <row r="130" spans="1:12" ht="15.75" customHeight="1">
       <c r="A130" s="25" t="s">
         <v>114</v>
       </c>
@@ -6753,10 +6759,13 @@
       <c r="H130" s="9">
         <v>1</v>
       </c>
-      <c r="I130" s="23"/>
+      <c r="I130" s="23">
+        <v>1.2</v>
+      </c>
       <c r="J130" s="24"/>
-    </row>
-    <row r="131" spans="1:10" ht="15.75" customHeight="1">
+      <c r="L130" s="26"/>
+    </row>
+    <row r="131" spans="1:12" ht="15.75" customHeight="1">
       <c r="A131" s="25" t="s">
         <v>114</v>
       </c>
@@ -6775,7 +6784,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15.75" customHeight="1">
+    <row r="132" spans="1:12" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
         <v>115</v>
       </c>
@@ -6806,7 +6815,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15.75" customHeight="1">
+    <row r="133" spans="1:12" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
         <v>115</v>
       </c>
@@ -6837,7 +6846,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15.75" customHeight="1">
+    <row r="134" spans="1:12" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
         <v>115</v>
       </c>
@@ -6868,7 +6877,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15.75" customHeight="1">
+    <row r="135" spans="1:12" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
         <v>115</v>
       </c>
@@ -6899,7 +6908,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15.75" customHeight="1">
+    <row r="136" spans="1:12" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
         <v>115</v>
       </c>
@@ -6930,7 +6939,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15.75" customHeight="1">
+    <row r="137" spans="1:12" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
         <v>115</v>
       </c>
@@ -6961,7 +6970,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15.75" customHeight="1">
+    <row r="138" spans="1:12" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
         <v>115</v>
       </c>
@@ -6992,7 +7001,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15.75" customHeight="1">
+    <row r="139" spans="1:12" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
         <v>115</v>
       </c>
@@ -7023,7 +7032,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15.75" customHeight="1">
+    <row r="140" spans="1:12" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
         <v>115</v>
       </c>
@@ -7054,7 +7063,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15.75" customHeight="1">
+    <row r="141" spans="1:12" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
         <v>115</v>
       </c>
@@ -7085,7 +7094,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15.75" customHeight="1">
+    <row r="142" spans="1:12" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
         <v>115</v>
       </c>
@@ -7116,7 +7125,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15.75" customHeight="1">
+    <row r="143" spans="1:12" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
         <v>115</v>
       </c>
@@ -7147,7 +7156,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15.75" customHeight="1">
+    <row r="144" spans="1:12" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
         <v>115</v>
       </c>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="86">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -65,103 +65,37 @@
     <t>BLANCO</t>
   </si>
   <si>
-    <t>30.99</t>
-  </si>
-  <si>
     <t>300</t>
   </si>
   <si>
     <t>340</t>
   </si>
   <si>
-    <t>32.85</t>
-  </si>
-  <si>
     <t>400</t>
-  </si>
-  <si>
-    <t>34.65</t>
   </si>
   <si>
     <t>450</t>
   </si>
   <si>
-    <t>36.29</t>
-  </si>
-  <si>
     <t>500</t>
-  </si>
-  <si>
-    <t>38.14</t>
   </si>
   <si>
     <t>600</t>
   </si>
   <si>
-    <t>41.84</t>
-  </si>
-  <si>
-    <t>45.33</t>
-  </si>
-  <si>
     <t>800</t>
-  </si>
-  <si>
-    <t>48.89</t>
   </si>
   <si>
     <t>900</t>
   </si>
   <si>
-    <t>52.30</t>
-  </si>
-  <si>
     <t>1000</t>
-  </si>
-  <si>
-    <t>55.93</t>
   </si>
   <si>
     <t>1200</t>
   </si>
   <si>
-    <t>60.44</t>
-  </si>
-  <si>
     <t>BAJOS ALMACENAJE altura 80</t>
-  </si>
-  <si>
-    <t>34.58</t>
-  </si>
-  <si>
-    <t>36.42</t>
-  </si>
-  <si>
-    <t>38.69</t>
-  </si>
-  <si>
-    <t>40.48</t>
-  </si>
-  <si>
-    <t>42.45</t>
-  </si>
-  <si>
-    <t>46.53</t>
-  </si>
-  <si>
-    <t>51.01</t>
-  </si>
-  <si>
-    <t>54.97</t>
-  </si>
-  <si>
-    <t>58.93</t>
-  </si>
-  <si>
-    <t>63.02</t>
-  </si>
-  <si>
-    <t>65.64</t>
   </si>
   <si>
     <t>FREGDERO DE 70</t>
@@ -170,55 +104,7 @@
     <t>BAJOS_FREGADERO</t>
   </si>
   <si>
-    <t>31.18</t>
-  </si>
-  <si>
-    <t>31.99</t>
-  </si>
-  <si>
-    <t>33.65</t>
-  </si>
-  <si>
-    <t>36.77</t>
-  </si>
-  <si>
-    <t>38.16</t>
-  </si>
-  <si>
-    <t>40.24</t>
-  </si>
-  <si>
-    <t>46.40</t>
-  </si>
-  <si>
-    <t>52.69</t>
-  </si>
-  <si>
     <t>FREGADEROS 80</t>
-  </si>
-  <si>
-    <t>31.66</t>
-  </si>
-  <si>
-    <t>35.77</t>
-  </si>
-  <si>
-    <t>37,11</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>42.15</t>
-  </si>
-  <si>
-    <t>46,74</t>
-  </si>
-  <si>
-    <t>51,60</t>
-  </si>
-  <si>
-    <t>57,42</t>
   </si>
   <si>
     <t>BAJO RINCON L</t>
@@ -228,12 +114,6 @@
   </si>
   <si>
     <t>930</t>
-  </si>
-  <si>
-    <t>122,28</t>
-  </si>
-  <si>
-    <t>138,76</t>
   </si>
   <si>
     <t>COLUMNA ESCOBERO 2000</t>
@@ -251,25 +131,10 @@
     <t>2200</t>
   </si>
   <si>
-    <t>75,93</t>
-  </si>
-  <si>
     <t>COLUMNA ESCOBERO 2300</t>
   </si>
   <si>
     <t>2300</t>
-  </si>
-  <si>
-    <t>79,18</t>
-  </si>
-  <si>
-    <t>76,44</t>
-  </si>
-  <si>
-    <t>84,19</t>
-  </si>
-  <si>
-    <t>88,13</t>
   </si>
   <si>
     <t>KIT 3 BALDAS</t>
@@ -278,25 +143,13 @@
     <t>BALDAS</t>
   </si>
   <si>
-    <t>22,77</t>
-  </si>
-  <si>
-    <t>27,86</t>
-  </si>
-  <si>
     <t>HORNO altura 70</t>
   </si>
   <si>
     <t>BAJO_HORNO</t>
   </si>
   <si>
-    <t>36,83</t>
-  </si>
-  <si>
     <t>HORNO altura 80</t>
-  </si>
-  <si>
-    <t>40,62</t>
   </si>
   <si>
     <t>COLUMNA HM 2000</t>
@@ -305,19 +158,10 @@
     <t>COLUMNA_HM</t>
   </si>
   <si>
-    <t>90,14</t>
-  </si>
-  <si>
     <t>COLUMNA HM 2200</t>
   </si>
   <si>
-    <t>94,65</t>
-  </si>
-  <si>
     <t>COLUMNA HM 2300</t>
-  </si>
-  <si>
-    <t>97,26</t>
   </si>
   <si>
     <t>ALTO H=70</t>
@@ -329,34 +173,13 @@
     <t>330</t>
   </si>
   <si>
-    <t>40,83</t>
-  </si>
-  <si>
     <t>ALTO H=80</t>
-  </si>
-  <si>
-    <t>40.83</t>
-  </si>
-  <si>
-    <t>45</t>
   </si>
   <si>
     <t>ALTO H=90</t>
   </si>
   <si>
-    <t>45646</t>
-  </si>
-  <si>
-    <t>36345</t>
-  </si>
-  <si>
     <t>GRAFITO</t>
-  </si>
-  <si>
-    <t>444</t>
-  </si>
-  <si>
-    <t>54</t>
   </si>
   <si>
     <t>HERRAJE</t>
@@ -448,6 +271,9 @@
   <si>
     <t>1s</t>
   </si>
+  <si>
+    <t>5</t>
+  </si>
 </sst>
 </file>
 
@@ -509,7 +335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -526,20 +352,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -569,9 +386,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -839,8 +653,8 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>136</v>
+      <c r="D1" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -861,13 +675,13 @@
         <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>133</v>
+        <v>74</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>134</v>
+        <v>75</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>135</v>
+        <v>76</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -900,12 +714,12 @@
       <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9" t="e">
+      <c r="H2" s="9">
         <f t="shared" ref="H2:H127" si="0">I2*((100-J2)/100)</f>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="J2" s="9">
         <v>30</v>
@@ -944,7 +758,7 @@
         <v>12</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>14</v>
@@ -952,24 +766,24 @@
       <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="9" t="e">
+      <c r="H3" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="J3" s="9">
         <v>30</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="22">
         <v>1</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="22">
         <f t="shared" ref="L3:M3" si="1">D133</f>
         <v>698</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="22">
         <f t="shared" si="1"/>
         <v>297</v>
       </c>
@@ -996,7 +810,7 @@
         <v>12</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="8" t="s">
         <v>14</v>
@@ -1004,24 +818,24 @@
       <c r="G4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="9" t="e">
+      <c r="H4" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="J4" s="9">
         <v>30</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="22">
         <v>1</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="22">
         <f t="shared" ref="L4:M4" si="2">D134</f>
         <v>698</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="22">
         <f t="shared" si="2"/>
         <v>347</v>
       </c>
@@ -1048,7 +862,7 @@
         <v>12</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>14</v>
@@ -1056,24 +870,24 @@
       <c r="G5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="9" t="e">
+      <c r="H5" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="J5" s="9">
         <v>30</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="22">
         <v>1</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="22">
         <f t="shared" ref="L5:M5" si="3">D135</f>
         <v>698</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="22">
         <f t="shared" si="3"/>
         <v>397</v>
       </c>
@@ -1100,7 +914,7 @@
         <v>12</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>14</v>
@@ -1108,24 +922,24 @@
       <c r="G6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="9" t="e">
+      <c r="H6" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="22">
         <v>1</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="22">
         <f t="shared" ref="L6:M6" si="4">D136</f>
         <v>698</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="22">
         <f t="shared" si="4"/>
         <v>447</v>
       </c>
@@ -1152,7 +966,7 @@
         <v>12</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -1160,24 +974,24 @@
       <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="9" t="e">
+      <c r="H7" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="J7" s="9">
         <v>30</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="22">
         <v>1</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="22">
         <f t="shared" ref="L7:M7" si="5">D137</f>
         <v>698</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="22">
         <f t="shared" si="5"/>
         <v>497</v>
       </c>
@@ -1204,7 +1018,7 @@
         <v>12</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>14</v>
@@ -1212,24 +1026,24 @@
       <c r="G8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="9" t="e">
+      <c r="H8" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="J8" s="9">
         <v>30</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="22">
         <v>1</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="22">
         <f t="shared" ref="L8:M8" si="6">D138</f>
         <v>698</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="22">
         <f t="shared" si="6"/>
         <v>597</v>
       </c>
@@ -1264,12 +1078,12 @@
       <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="9" t="e">
+      <c r="H9" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="J9" s="9">
         <v>30</v>
@@ -1302,7 +1116,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>14</v>
@@ -1310,12 +1124,12 @@
       <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="9" t="e">
+      <c r="H10" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="J10" s="9">
         <v>30</v>
@@ -1348,7 +1162,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F11" s="8" t="s">
         <v>14</v>
@@ -1356,12 +1170,12 @@
       <c r="G11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="9" t="e">
+      <c r="H11" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="J11" s="9">
         <v>30</v>
@@ -1394,7 +1208,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>14</v>
@@ -1402,12 +1216,12 @@
       <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="9" t="e">
+      <c r="H12" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="J12" s="9">
         <v>30</v>
@@ -1440,7 +1254,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>14</v>
@@ -1448,12 +1262,12 @@
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="9" t="e">
+      <c r="H13" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>36</v>
+        <v>3.5</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J13" s="9">
         <v>30</v>
@@ -1477,13 +1291,13 @@
         <v>9</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E14" s="8" t="s">
         <v>13</v>
@@ -1494,17 +1308,17 @@
       <c r="G14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="9" t="e">
+      <c r="H14" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J14" s="9">
         <v>30</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="22">
         <v>1</v>
       </c>
       <c r="L14" s="10"/>
@@ -1523,16 +1337,16 @@
         <v>9</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>14</v>
@@ -1540,17 +1354,17 @@
       <c r="G15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="9" t="e">
+      <c r="H15" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J15" s="9">
         <v>30</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="22">
         <v>1</v>
       </c>
       <c r="L15" s="10"/>
@@ -1569,16 +1383,16 @@
         <v>9</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>14</v>
@@ -1586,17 +1400,17 @@
       <c r="G16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="9" t="e">
+      <c r="H16" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>39</v>
+        <v>85</v>
       </c>
       <c r="J16" s="9">
         <v>30</v>
       </c>
-      <c r="K16" s="23">
+      <c r="K16" s="22">
         <v>1</v>
       </c>
       <c r="L16" s="10"/>
@@ -1615,16 +1429,16 @@
         <v>9</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>14</v>
@@ -1632,17 +1446,17 @@
       <c r="G17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="9" t="e">
+      <c r="H17" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="J17" s="9">
         <v>30</v>
       </c>
-      <c r="K17" s="23">
+      <c r="K17" s="22">
         <v>1</v>
       </c>
       <c r="L17" s="10"/>
@@ -1661,16 +1475,16 @@
         <v>9</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>14</v>
@@ -1678,17 +1492,17 @@
       <c r="G18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="9" t="e">
+      <c r="H18" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>41</v>
+        <v>85</v>
       </c>
       <c r="J18" s="9">
         <v>30</v>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="22">
         <v>1</v>
       </c>
       <c r="L18" s="10"/>
@@ -1707,16 +1521,16 @@
         <v>9</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>14</v>
@@ -1724,17 +1538,17 @@
       <c r="G19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="9" t="e">
+      <c r="H19" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="J19" s="9">
         <v>30</v>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="22">
         <v>1</v>
       </c>
       <c r="L19" s="10"/>
@@ -1753,16 +1567,16 @@
         <v>9</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>14</v>
@@ -1770,17 +1584,17 @@
       <c r="G20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="9" t="e">
+      <c r="H20" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="J20" s="9">
         <v>30</v>
       </c>
-      <c r="K20" s="23">
+      <c r="K20" s="22">
         <v>1</v>
       </c>
       <c r="L20" s="10"/>
@@ -1799,13 +1613,13 @@
         <v>9</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>12</v>
@@ -1816,12 +1630,12 @@
       <c r="G21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="9" t="e">
+      <c r="H21" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="J21" s="9">
         <v>30</v>
@@ -1845,16 +1659,16 @@
         <v>9</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>14</v>
@@ -1862,12 +1676,12 @@
       <c r="G22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="9" t="e">
+      <c r="H22" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="J22" s="9">
         <v>30</v>
@@ -1891,16 +1705,16 @@
         <v>9</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>14</v>
@@ -1908,12 +1722,12 @@
       <c r="G23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="9" t="e">
+      <c r="H23" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="J23" s="9">
         <v>30</v>
@@ -1937,16 +1751,16 @@
         <v>9</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>14</v>
@@ -1954,12 +1768,12 @@
       <c r="G24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="9" t="e">
+      <c r="H24" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="J24" s="9">
         <v>30</v>
@@ -1983,16 +1797,16 @@
         <v>9</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>14</v>
@@ -2000,12 +1814,12 @@
       <c r="G25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="9" t="e">
+      <c r="H25" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="J25" s="9">
         <v>30</v>
@@ -2028,17 +1842,17 @@
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>50</v>
+      <c r="B26" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>14</v>
@@ -2046,12 +1860,12 @@
       <c r="G26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="9" t="e">
+      <c r="H26" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="J26" s="9">
         <v>30</v>
@@ -2074,17 +1888,17 @@
       <c r="A27" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>50</v>
+      <c r="B27" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>14</v>
@@ -2092,12 +1906,12 @@
       <c r="G27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="9" t="e">
+      <c r="H27" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="J27" s="9">
         <v>30</v>
@@ -2120,17 +1934,17 @@
       <c r="A28" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>50</v>
+      <c r="B28" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>14</v>
@@ -2138,12 +1952,12 @@
       <c r="G28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="9" t="e">
+      <c r="H28" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="J28" s="9">
         <v>30</v>
@@ -2166,11 +1980,11 @@
       <c r="A29" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B29" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>50</v>
+      <c r="B29" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>12</v>
@@ -2184,12 +1998,12 @@
       <c r="G29" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H29" s="9" t="e">
+      <c r="H29" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="J29" s="9">
         <v>30</v>
@@ -2212,17 +2026,17 @@
       <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B30" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>50</v>
+      <c r="B30" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F30" s="8" t="s">
         <v>14</v>
@@ -2230,12 +2044,12 @@
       <c r="G30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="9" t="e">
+      <c r="H30" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J30" s="9">
         <v>30</v>
@@ -2258,17 +2072,17 @@
       <c r="A31" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B31" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>50</v>
+      <c r="B31" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>14</v>
@@ -2276,12 +2090,12 @@
       <c r="G31" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="9" t="e">
+      <c r="H31" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2304,17 +2118,17 @@
       <c r="A32" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>50</v>
+      <c r="B32" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F32" s="8" t="s">
         <v>14</v>
@@ -2322,12 +2136,12 @@
       <c r="G32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="9" t="e">
+      <c r="H32" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="J32" s="9">
         <v>30</v>
@@ -2350,17 +2164,17 @@
       <c r="A33" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B33" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>50</v>
+      <c r="B33" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F33" s="8" t="s">
         <v>14</v>
@@ -2368,12 +2182,12 @@
       <c r="G33" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="9" t="e">
+      <c r="H33" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="J33" s="9">
         <v>30</v>
@@ -2396,17 +2210,17 @@
       <c r="A34" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>50</v>
+      <c r="B34" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F34" s="8" t="s">
         <v>14</v>
@@ -2414,12 +2228,12 @@
       <c r="G34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="9" t="e">
+      <c r="H34" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="J34" s="9">
         <v>30</v>
@@ -2442,17 +2256,17 @@
       <c r="A35" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>50</v>
+      <c r="B35" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>14</v>
@@ -2460,12 +2274,12 @@
       <c r="G35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="9" t="e">
+      <c r="H35" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="J35" s="9">
         <v>30</v>
@@ -2488,17 +2302,17 @@
       <c r="A36" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B36" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>50</v>
+      <c r="B36" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>14</v>
@@ -2508,10 +2322,10 @@
       </c>
       <c r="H36" s="9">
         <f t="shared" si="0"/>
-        <v>25.976999999999997</v>
+        <v>3.5</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>62</v>
+        <v>85</v>
       </c>
       <c r="J36" s="9">
         <v>30</v>
@@ -2534,14 +2348,14 @@
       <c r="A37" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>50</v>
+      <c r="B37" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>12</v>
@@ -2554,10 +2368,10 @@
       </c>
       <c r="H37" s="9">
         <f t="shared" si="0"/>
-        <v>28.454999999999998</v>
+        <v>3.5</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="J37" s="9">
         <v>30</v>
@@ -2580,17 +2394,17 @@
       <c r="A38" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>50</v>
+      <c r="B38" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>14</v>
@@ -2598,12 +2412,12 @@
       <c r="G38" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="9" t="e">
+      <c r="H38" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
+        <v>3.5</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="J38" s="9">
         <v>30</v>
@@ -2626,17 +2440,17 @@
       <c r="A39" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B39" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>50</v>
+      <c r="B39" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>14</v>
@@ -2646,10 +2460,10 @@
       </c>
       <c r="H39" s="9">
         <f t="shared" si="0"/>
-        <v>32.717999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J39" s="9">
         <v>30</v>
@@ -2672,17 +2486,17 @@
       <c r="A40" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B40" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>50</v>
+      <c r="B40" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F40" s="8" t="s">
         <v>14</v>
@@ -2692,10 +2506,10 @@
       </c>
       <c r="H40" s="9">
         <f t="shared" si="0"/>
-        <v>36.119999999999997</v>
+        <v>3.5</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="J40" s="9">
         <v>30</v>
@@ -2718,17 +2532,17 @@
       <c r="A41" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B41" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>50</v>
+      <c r="B41" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>14</v>
@@ -2738,10 +2552,10 @@
       </c>
       <c r="H41" s="9">
         <f t="shared" si="0"/>
-        <v>40.193999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="J41" s="9">
         <v>30</v>
@@ -2764,17 +2578,17 @@
       <c r="A42" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B42" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>69</v>
+      <c r="B42" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>14</v>
@@ -2784,10 +2598,10 @@
       </c>
       <c r="H42" s="9">
         <f t="shared" si="0"/>
-        <v>85.595999999999989</v>
+        <v>3.5</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="J42" s="9">
         <v>30</v>
@@ -2810,17 +2624,17 @@
       <c r="A43" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B43" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>69</v>
+      <c r="B43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>14</v>
@@ -2830,10 +2644,10 @@
       </c>
       <c r="H43" s="9">
         <f t="shared" si="0"/>
-        <v>97.131999999999991</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="J43" s="9">
         <v>30</v>
@@ -2857,16 +2671,16 @@
         <v>9</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>14</v>
@@ -2876,11 +2690,10 @@
       </c>
       <c r="H44" s="9">
         <f t="shared" si="0"/>
-        <v>51.574380165289263</v>
-      </c>
-      <c r="I44" s="8">
-        <f>89.15/1.21</f>
-        <v>73.677685950413235</v>
+        <v>3.5</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J44" s="9">
         <v>30</v>
@@ -2904,16 +2717,16 @@
         <v>9</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>14</v>
@@ -2923,10 +2736,10 @@
       </c>
       <c r="H45" s="9">
         <f t="shared" si="0"/>
-        <v>53.151000000000003</v>
+        <v>3.5</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J45" s="9">
         <v>30</v>
@@ -2950,16 +2763,16 @@
         <v>9</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>14</v>
@@ -2969,10 +2782,10 @@
       </c>
       <c r="H46" s="9">
         <f t="shared" si="0"/>
-        <v>55.426000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="J46" s="9">
         <v>30</v>
@@ -2996,16 +2809,16 @@
         <v>9</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>14</v>
@@ -3015,10 +2828,10 @@
       </c>
       <c r="H47" s="9">
         <f t="shared" si="0"/>
-        <v>53.507999999999996</v>
+        <v>3.5</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J47" s="9">
         <v>30</v>
@@ -3042,16 +2855,16 @@
         <v>9</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>14</v>
@@ -3061,10 +2874,10 @@
       </c>
       <c r="H48" s="9">
         <f t="shared" si="0"/>
-        <v>58.932999999999993</v>
+        <v>3.5</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J48" s="9">
         <v>30</v>
@@ -3088,16 +2901,16 @@
         <v>9</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F49" s="8" t="s">
         <v>14</v>
@@ -3107,10 +2920,10 @@
       </c>
       <c r="H49" s="9">
         <f t="shared" si="0"/>
-        <v>61.690999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J49" s="9">
         <v>30</v>
@@ -3133,15 +2946,15 @@
       <c r="A50" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B50" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>86</v>
+      <c r="B50" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F50" s="8" t="s">
         <v>14</v>
@@ -3151,10 +2964,10 @@
       </c>
       <c r="H50" s="9">
         <f t="shared" si="0"/>
-        <v>15.938999999999998</v>
+        <v>3.5</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J50" s="9">
         <v>30</v>
@@ -3175,15 +2988,15 @@
       <c r="A51" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B51" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>86</v>
+      <c r="B51" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>41</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F51" s="8" t="s">
         <v>14</v>
@@ -3193,10 +3006,10 @@
       </c>
       <c r="H51" s="9">
         <f t="shared" si="0"/>
-        <v>19.501999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="J51" s="9">
         <v>30</v>
@@ -3217,17 +3030,17 @@
       <c r="A52" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>90</v>
+      <c r="B52" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>14</v>
@@ -3237,10 +3050,10 @@
       </c>
       <c r="H52" s="9">
         <f t="shared" si="0"/>
-        <v>25.780999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J52" s="9">
         <v>30</v>
@@ -3263,17 +3076,17 @@
       <c r="A53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>90</v>
+      <c r="B53" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>14</v>
@@ -3283,10 +3096,10 @@
       </c>
       <c r="H53" s="9">
         <f t="shared" si="0"/>
-        <v>28.433999999999997</v>
+        <v>3.5</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J53" s="9">
         <v>30</v>
@@ -3309,17 +3122,17 @@
       <c r="A54" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B54" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>142</v>
+      <c r="B54" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>83</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>14</v>
@@ -3329,10 +3142,10 @@
       </c>
       <c r="H54" s="9">
         <f t="shared" si="0"/>
-        <v>63.097999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J54" s="9">
         <v>30</v>
@@ -3355,17 +3168,17 @@
       <c r="A55" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B55" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>95</v>
+      <c r="B55" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>14</v>
@@ -3375,10 +3188,10 @@
       </c>
       <c r="H55" s="9">
         <f t="shared" si="0"/>
-        <v>66.254999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="J55" s="9">
         <v>30</v>
@@ -3401,17 +3214,17 @@
       <c r="A56" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B56" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>95</v>
+      <c r="B56" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>14</v>
@@ -3421,10 +3234,10 @@
       </c>
       <c r="H56" s="9">
         <f t="shared" si="0"/>
-        <v>68.081999999999994</v>
+        <v>3.5</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J56" s="9">
         <v>30</v>
@@ -3448,29 +3261,29 @@
         <v>9</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="14" t="s">
-        <v>103</v>
+        <v>16</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H57" s="9">
         <f t="shared" si="0"/>
-        <v>28.580999999999996</v>
-      </c>
-      <c r="I57" s="14" t="s">
-        <v>104</v>
+        <v>3.5</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J57" s="9">
         <v>30</v>
@@ -3494,29 +3307,29 @@
         <v>9</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F58" s="14" t="s">
-        <v>103</v>
+        <v>19</v>
+      </c>
+      <c r="F58" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H58" s="9">
         <f t="shared" si="0"/>
-        <v>28.580999999999996</v>
-      </c>
-      <c r="I58" s="14" t="s">
-        <v>104</v>
+        <v>3.5</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J58" s="9">
         <v>30</v>
@@ -3540,29 +3353,29 @@
         <v>9</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" s="14" t="s">
-        <v>103</v>
+        <v>21</v>
+      </c>
+      <c r="F59" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="9">
         <f t="shared" si="0"/>
-        <v>28.580999999999996</v>
-      </c>
-      <c r="I59" s="14" t="s">
-        <v>104</v>
+        <v>3.5</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J59" s="9">
         <v>30</v>
@@ -3586,29 +3399,29 @@
         <v>9</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="14" t="s">
-        <v>103</v>
+        <v>16</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H60" s="9">
         <f t="shared" si="0"/>
-        <v>28.580999999999996</v>
-      </c>
-      <c r="I60" s="14" t="s">
-        <v>104</v>
+        <v>3.5</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J60" s="9">
         <v>30</v>
@@ -3632,29 +3445,29 @@
         <v>9</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>103</v>
+        <v>19</v>
+      </c>
+      <c r="F61" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="9" t="e">
+      <c r="H61" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I61" s="14" t="s">
-        <v>106</v>
+        <v>3.5</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J61" s="9">
         <v>30</v>
@@ -3678,29 +3491,29 @@
         <v>9</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>105</v>
+        <v>52</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>103</v>
+        <v>21</v>
+      </c>
+      <c r="F62" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H62" s="9">
         <f t="shared" si="0"/>
-        <v>31.499999999999996</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>107</v>
+        <v>3.5</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J62" s="9">
         <v>30</v>
@@ -3724,29 +3537,29 @@
         <v>9</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="14" t="s">
-        <v>103</v>
+        <v>16</v>
+      </c>
+      <c r="F63" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H63" s="9">
         <f t="shared" si="0"/>
-        <v>31952.199999999997</v>
-      </c>
-      <c r="I63" s="14" t="s">
-        <v>109</v>
+        <v>3.5</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J63" s="9">
         <v>30</v>
@@ -3770,29 +3583,29 @@
         <v>9</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="F64" s="14" t="s">
-        <v>103</v>
+        <v>19</v>
+      </c>
+      <c r="F64" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H64" s="9">
         <f t="shared" si="0"/>
-        <v>25441.5</v>
-      </c>
-      <c r="I64" s="14" t="s">
-        <v>110</v>
+        <v>3.5</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J64" s="9">
         <v>30</v>
@@ -3816,29 +3629,29 @@
         <v>9</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F65" s="14" t="s">
-        <v>103</v>
+        <v>21</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="9" t="e">
+      <c r="H65" s="9">
         <f t="shared" si="0"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="I65" s="14" t="s">
-        <v>106</v>
+        <v>3.5</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J65" s="9">
         <v>30</v>
@@ -3877,19 +3690,19 @@
         <v>14</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H66" s="9">
         <f t="shared" si="0"/>
-        <v>28.580999999999996</v>
-      </c>
-      <c r="I66" s="14" t="s">
-        <v>104</v>
+        <v>3.5</v>
+      </c>
+      <c r="I66" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="J66" s="9">
         <v>30</v>
       </c>
-      <c r="K66" s="23">
+      <c r="K66" s="22">
         <v>1</v>
       </c>
       <c r="L66" s="10"/>
@@ -3917,26 +3730,26 @@
         <v>12</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H67" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J67" s="9">
         <v>30</v>
       </c>
-      <c r="K67" s="23" t="s">
-        <v>142</v>
+      <c r="K67" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -3963,25 +3776,25 @@
         <v>12</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H68" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J68" s="9">
         <v>30</v>
       </c>
-      <c r="K68" s="23">
+      <c r="K68" s="22">
         <v>1</v>
       </c>
       <c r="L68" s="10"/>
@@ -4009,25 +3822,25 @@
         <v>12</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H69" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J69" s="9">
         <v>30</v>
       </c>
-      <c r="K69" s="23">
+      <c r="K69" s="22">
         <v>1</v>
       </c>
       <c r="L69" s="10"/>
@@ -4055,25 +3868,25 @@
         <v>12</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H70" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J70" s="9">
         <v>30</v>
       </c>
-      <c r="K70" s="23">
+      <c r="K70" s="22">
         <v>1</v>
       </c>
       <c r="L70" s="10"/>
@@ -4101,25 +3914,25 @@
         <v>12</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F71" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H71" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J71" s="9">
         <v>30</v>
       </c>
-      <c r="K71" s="23">
+      <c r="K71" s="22">
         <v>1</v>
       </c>
       <c r="L71" s="10"/>
@@ -4147,25 +3960,25 @@
         <v>12</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F72" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H72" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J72" s="9">
         <v>30</v>
       </c>
-      <c r="K72" s="23">
+      <c r="K72" s="22">
         <v>1</v>
       </c>
       <c r="L72" s="10"/>
@@ -4199,19 +4012,19 @@
         <v>14</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H73" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J73" s="9">
         <v>30</v>
       </c>
-      <c r="K73" s="23">
+      <c r="K73" s="22">
         <v>2</v>
       </c>
       <c r="L73" s="10"/>
@@ -4239,25 +4052,25 @@
         <v>12</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H74" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J74" s="9">
         <v>30</v>
       </c>
-      <c r="K74" s="23">
+      <c r="K74" s="22">
         <v>2</v>
       </c>
       <c r="L74" s="10"/>
@@ -4285,25 +4098,25 @@
         <v>12</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H75" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J75" s="9">
         <v>30</v>
       </c>
-      <c r="K75" s="23">
+      <c r="K75" s="22">
         <v>2</v>
       </c>
       <c r="L75" s="10"/>
@@ -4331,25 +4144,25 @@
         <v>12</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H76" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J76" s="9">
         <v>30</v>
       </c>
-      <c r="K76" s="23">
+      <c r="K76" s="22">
         <v>2</v>
       </c>
       <c r="L76" s="10"/>
@@ -4377,25 +4190,25 @@
         <v>12</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H77" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J77" s="9">
         <v>30</v>
       </c>
-      <c r="K77" s="23">
+      <c r="K77" s="22">
         <v>2</v>
       </c>
       <c r="L77" s="10"/>
@@ -4414,13 +4227,13 @@
         <v>9</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E78" s="8" t="s">
         <v>13</v>
@@ -4429,19 +4242,19 @@
         <v>14</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H78" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J78" s="9">
         <v>30</v>
       </c>
-      <c r="K78" s="23">
+      <c r="K78" s="22">
         <v>1</v>
       </c>
       <c r="L78" s="10"/>
@@ -4460,34 +4273,34 @@
         <v>9</v>
       </c>
       <c r="B79" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H79" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J79" s="9">
         <v>30</v>
       </c>
-      <c r="K79" s="23">
+      <c r="K79" s="22">
         <v>1</v>
       </c>
       <c r="L79" s="10"/>
@@ -4506,35 +4319,35 @@
         <v>9</v>
       </c>
       <c r="B80" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E80" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F80" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H80" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J80" s="9">
         <v>30</v>
       </c>
-      <c r="K80" s="23" t="s">
-        <v>143</v>
+      <c r="K80" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -4552,34 +4365,34 @@
         <v>9</v>
       </c>
       <c r="B81" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C81" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E81" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F81" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H81" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J81" s="9">
         <v>30</v>
       </c>
-      <c r="K81" s="23">
+      <c r="K81" s="22">
         <v>1</v>
       </c>
       <c r="L81" s="10"/>
@@ -4598,34 +4411,34 @@
         <v>9</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C82" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H82" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J82" s="9">
         <v>30</v>
       </c>
-      <c r="K82" s="23">
+      <c r="K82" s="22">
         <v>1</v>
       </c>
       <c r="L82" s="10"/>
@@ -4644,34 +4457,34 @@
         <v>9</v>
       </c>
       <c r="B83" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C83" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H83" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J83" s="9">
         <v>30</v>
       </c>
-      <c r="K83" s="23">
+      <c r="K83" s="22">
         <v>1</v>
       </c>
       <c r="L83" s="10"/>
@@ -4690,34 +4503,34 @@
         <v>9</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C84" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H84" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J84" s="9">
         <v>30</v>
       </c>
-      <c r="K84" s="23">
+      <c r="K84" s="22">
         <v>1</v>
       </c>
       <c r="L84" s="10"/>
@@ -4736,13 +4549,13 @@
         <v>9</v>
       </c>
       <c r="B85" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C85" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E85" s="8" t="s">
         <v>12</v>
@@ -4751,19 +4564,19 @@
         <v>14</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H85" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J85" s="9">
         <v>30</v>
       </c>
-      <c r="K85" s="23">
+      <c r="K85" s="22">
         <v>2</v>
       </c>
       <c r="L85" s="10"/>
@@ -4782,34 +4595,34 @@
         <v>9</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C86" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H86" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J86" s="9">
         <v>30</v>
       </c>
-      <c r="K86" s="23">
+      <c r="K86" s="22">
         <v>2</v>
       </c>
       <c r="L86" s="10"/>
@@ -4828,34 +4641,34 @@
         <v>9</v>
       </c>
       <c r="B87" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C87" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H87" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J87" s="9">
         <v>30</v>
       </c>
-      <c r="K87" s="23">
+      <c r="K87" s="22">
         <v>2</v>
       </c>
       <c r="L87" s="10"/>
@@ -4874,34 +4687,34 @@
         <v>9</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F88" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H88" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J88" s="9">
         <v>30</v>
       </c>
-      <c r="K88" s="23">
+      <c r="K88" s="22">
         <v>2</v>
       </c>
       <c r="L88" s="10"/>
@@ -4920,34 +4733,34 @@
         <v>9</v>
       </c>
       <c r="B89" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H89" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J89" s="9">
         <v>30</v>
       </c>
-      <c r="K89" s="23">
+      <c r="K89" s="22">
         <v>2</v>
       </c>
       <c r="L89" s="10"/>
@@ -4965,35 +4778,35 @@
       <c r="A90" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B90" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C90" s="12" t="s">
-        <v>50</v>
+      <c r="B90" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F90" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H90" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J90" s="9">
         <v>30</v>
       </c>
-      <c r="K90" s="23">
+      <c r="K90" s="22">
         <v>1</v>
       </c>
       <c r="L90" s="10"/>
@@ -5011,35 +4824,35 @@
       <c r="A91" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B91" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C91" s="12" t="s">
-        <v>50</v>
+      <c r="B91" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F91" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H91" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J91" s="9">
         <v>30</v>
       </c>
-      <c r="K91" s="23">
+      <c r="K91" s="22">
         <v>1</v>
       </c>
       <c r="L91" s="10"/>
@@ -5057,35 +4870,35 @@
       <c r="A92" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B92" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C92" s="12" t="s">
-        <v>50</v>
+      <c r="B92" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F92" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H92" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J92" s="9">
         <v>30</v>
       </c>
-      <c r="K92" s="23">
+      <c r="K92" s="22">
         <v>1</v>
       </c>
       <c r="L92" s="10"/>
@@ -5103,11 +4916,11 @@
       <c r="A93" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B93" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>50</v>
+      <c r="B93" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>12</v>
@@ -5119,19 +4932,19 @@
         <v>14</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H93" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J93" s="9">
         <v>30</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K93" s="22">
         <v>2</v>
       </c>
       <c r="L93" s="10"/>
@@ -5149,35 +4962,35 @@
       <c r="A94" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B94" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C94" s="12" t="s">
-        <v>50</v>
+      <c r="B94" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E94" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F94" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H94" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J94" s="9">
         <v>30</v>
       </c>
-      <c r="K94" s="23">
+      <c r="K94" s="22">
         <v>2</v>
       </c>
       <c r="L94" s="10"/>
@@ -5195,35 +5008,35 @@
       <c r="A95" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B95" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>50</v>
+      <c r="B95" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E95" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H95" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J95" s="9">
         <v>30</v>
       </c>
-      <c r="K95" s="23">
+      <c r="K95" s="22">
         <v>2</v>
       </c>
       <c r="L95" s="10"/>
@@ -5241,35 +5054,35 @@
       <c r="A96" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B96" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C96" s="12" t="s">
-        <v>50</v>
+      <c r="B96" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>111</v>
+        <v>54</v>
       </c>
       <c r="H96" s="9">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J96" s="9">
         <v>30</v>
       </c>
-      <c r="K96" s="23">
+      <c r="K96" s="22">
         <v>2</v>
       </c>
       <c r="L96" s="10"/>
@@ -5287,35 +5100,35 @@
       <c r="A97" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B97" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>50</v>
+      <c r="B97" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H97" s="15">
+        <v>54</v>
+      </c>
+      <c r="H97" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J97" s="9">
         <v>30</v>
       </c>
-      <c r="K97" s="23">
+      <c r="K97" s="22">
         <v>2</v>
       </c>
       <c r="L97" s="10"/>
@@ -5333,35 +5146,35 @@
       <c r="A98" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B98" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C98" s="12" t="s">
-        <v>50</v>
+      <c r="B98" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E98" s="8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H98" s="15">
+        <v>54</v>
+      </c>
+      <c r="H98" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J98" s="9">
         <v>30</v>
       </c>
-      <c r="K98" s="23">
+      <c r="K98" s="22">
         <v>1</v>
       </c>
       <c r="L98" s="10"/>
@@ -5379,35 +5192,35 @@
       <c r="A99" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B99" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>50</v>
+      <c r="B99" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E99" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H99" s="15">
+        <v>54</v>
+      </c>
+      <c r="H99" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J99" s="9">
         <v>30</v>
       </c>
-      <c r="K99" s="23">
+      <c r="K99" s="22">
         <v>1</v>
       </c>
       <c r="L99" s="10"/>
@@ -5425,35 +5238,35 @@
       <c r="A100" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B100" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C100" s="12" t="s">
-        <v>50</v>
+      <c r="B100" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H100" s="15">
+        <v>54</v>
+      </c>
+      <c r="H100" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J100" s="9">
         <v>30</v>
       </c>
-      <c r="K100" s="23">
+      <c r="K100" s="22">
         <v>1</v>
       </c>
       <c r="L100" s="10"/>
@@ -5471,14 +5284,14 @@
       <c r="A101" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B101" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>50</v>
+      <c r="B101" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E101" s="8" t="s">
         <v>12</v>
@@ -5487,19 +5300,19 @@
         <v>14</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H101" s="15">
+        <v>54</v>
+      </c>
+      <c r="H101" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J101" s="9">
         <v>30</v>
       </c>
-      <c r="K101" s="23">
+      <c r="K101" s="22">
         <v>2</v>
       </c>
       <c r="L101" s="10"/>
@@ -5517,35 +5330,35 @@
       <c r="A102" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B102" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C102" s="12" t="s">
-        <v>50</v>
+      <c r="B102" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E102" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H102" s="15">
+        <v>54</v>
+      </c>
+      <c r="H102" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J102" s="9">
         <v>30</v>
       </c>
-      <c r="K102" s="23">
+      <c r="K102" s="22">
         <v>2</v>
       </c>
       <c r="L102" s="10"/>
@@ -5563,35 +5376,35 @@
       <c r="A103" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B103" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>50</v>
+      <c r="B103" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H103" s="15">
+        <v>54</v>
+      </c>
+      <c r="H103" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J103" s="9">
         <v>30</v>
       </c>
-      <c r="K103" s="23">
+      <c r="K103" s="22">
         <v>2</v>
       </c>
       <c r="L103" s="10"/>
@@ -5609,35 +5422,35 @@
       <c r="A104" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B104" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C104" s="12" t="s">
-        <v>50</v>
+      <c r="B104" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H104" s="15">
+        <v>54</v>
+      </c>
+      <c r="H104" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J104" s="9">
         <v>30</v>
       </c>
-      <c r="K104" s="23">
+      <c r="K104" s="22">
         <v>2</v>
       </c>
       <c r="L104" s="10"/>
@@ -5655,35 +5468,35 @@
       <c r="A105" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B105" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>50</v>
+      <c r="B105" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>28</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E105" s="8" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H105" s="15">
+        <v>54</v>
+      </c>
+      <c r="H105" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J105" s="9">
         <v>30</v>
       </c>
-      <c r="K105" s="23">
+      <c r="K105" s="22">
         <v>2</v>
       </c>
       <c r="L105" s="10"/>
@@ -5701,35 +5514,35 @@
       <c r="A106" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B106" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C106" s="12" t="s">
-        <v>69</v>
+      <c r="B106" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H106" s="15">
+        <v>54</v>
+      </c>
+      <c r="H106" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J106" s="9">
         <v>30</v>
       </c>
-      <c r="K106" s="23">
+      <c r="K106" s="22">
         <v>2</v>
       </c>
       <c r="L106" s="10"/>
@@ -5747,35 +5560,35 @@
       <c r="A107" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B107" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>69</v>
+      <c r="B107" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C107" s="11" t="s">
+        <v>31</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H107" s="15">
+        <v>54</v>
+      </c>
+      <c r="H107" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J107" s="9">
         <v>30</v>
       </c>
-      <c r="K107" s="23">
+      <c r="K107" s="22">
         <v>2</v>
       </c>
       <c r="L107" s="10"/>
@@ -5794,34 +5607,34 @@
         <v>9</v>
       </c>
       <c r="B108" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E108" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F108" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H108" s="15">
+        <v>54</v>
+      </c>
+      <c r="H108" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J108" s="9">
         <v>30</v>
       </c>
-      <c r="K108" s="23">
+      <c r="K108" s="22">
         <v>2</v>
       </c>
       <c r="L108" s="10"/>
@@ -5840,34 +5653,34 @@
         <v>9</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F109" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H109" s="15">
+        <v>54</v>
+      </c>
+      <c r="H109" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J109" s="9">
         <v>30</v>
       </c>
-      <c r="K109" s="23">
+      <c r="K109" s="22">
         <v>2</v>
       </c>
       <c r="L109" s="10"/>
@@ -5886,34 +5699,34 @@
         <v>9</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F110" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H110" s="15">
+        <v>54</v>
+      </c>
+      <c r="H110" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J110" s="9">
         <v>30</v>
       </c>
-      <c r="K110" s="23">
+      <c r="K110" s="22">
         <v>2</v>
       </c>
       <c r="L110" s="10"/>
@@ -5932,34 +5745,34 @@
         <v>9</v>
       </c>
       <c r="B111" s="7" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H111" s="15">
+        <v>54</v>
+      </c>
+      <c r="H111" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J111" s="9">
         <v>30</v>
       </c>
-      <c r="K111" s="23">
+      <c r="K111" s="22">
         <v>2</v>
       </c>
       <c r="L111" s="10"/>
@@ -5978,34 +5791,34 @@
         <v>9</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>76</v>
+        <v>36</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H112" s="15">
+        <v>54</v>
+      </c>
+      <c r="H112" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J112" s="9">
         <v>30</v>
       </c>
-      <c r="K112" s="23">
+      <c r="K112" s="22">
         <v>2</v>
       </c>
       <c r="L112" s="10"/>
@@ -6024,34 +5837,34 @@
         <v>9</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>74</v>
+        <v>34</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E113" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F113" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H113" s="15">
+        <v>54</v>
+      </c>
+      <c r="H113" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J113" s="9">
         <v>30</v>
       </c>
-      <c r="K113" s="23">
+      <c r="K113" s="22">
         <v>2</v>
       </c>
       <c r="L113" s="10"/>
@@ -6069,30 +5882,30 @@
       <c r="A114" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B114" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C114" s="13" t="s">
-        <v>90</v>
+      <c r="B114" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E114" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F114" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H114" s="15">
+        <v>54</v>
+      </c>
+      <c r="H114" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J114" s="9">
         <v>30</v>
@@ -6115,30 +5928,30 @@
       <c r="A115" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B115" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>90</v>
+      <c r="B115" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H115" s="15">
+        <v>54</v>
+      </c>
+      <c r="H115" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J115" s="9">
         <v>30</v>
@@ -6161,35 +5974,35 @@
       <c r="A116" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B116" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C116" s="12" t="s">
-        <v>95</v>
+      <c r="B116" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="E116" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H116" s="15">
+        <v>54</v>
+      </c>
+      <c r="H116" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J116" s="9">
         <v>30</v>
       </c>
-      <c r="K116" s="23">
+      <c r="K116" s="22">
         <v>2</v>
       </c>
       <c r="L116" s="10"/>
@@ -6207,30 +6020,30 @@
       <c r="A117" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B117" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C117" s="12" t="s">
-        <v>95</v>
+      <c r="B117" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
       <c r="E117" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H117" s="15">
+        <v>54</v>
+      </c>
+      <c r="H117" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J117" s="9">
         <v>30</v>
@@ -6253,30 +6066,30 @@
       <c r="A118" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B118" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C118" s="12" t="s">
-        <v>95</v>
+      <c r="B118" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H118" s="15">
+        <v>54</v>
+      </c>
+      <c r="H118" s="14">
         <f t="shared" si="0"/>
-        <v>310.79999999999995</v>
+        <v>3.5</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="J118" s="9">
         <v>30</v>
@@ -6299,953 +6112,952 @@
       <c r="A119" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B119" s="16" t="s">
-        <v>101</v>
+      <c r="B119" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D119" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D119" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E119" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F119" s="18" t="s">
-        <v>103</v>
+      <c r="E119" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F119" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H119" s="15">
+        <v>54</v>
+      </c>
+      <c r="H119" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I119" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J119" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J119" s="18">
         <v>30</v>
       </c>
-      <c r="K119" s="20">
+      <c r="K119" s="19">
         <v>1</v>
       </c>
-      <c r="L119" s="20"/>
-      <c r="M119" s="20"/>
-      <c r="N119" s="20"/>
-      <c r="O119" s="20"/>
-      <c r="P119" s="20"/>
-      <c r="Q119" s="20"/>
-      <c r="R119" s="20"/>
-      <c r="S119" s="20"/>
-      <c r="T119" s="20"/>
-      <c r="U119" s="20"/>
+      <c r="L119" s="19"/>
+      <c r="M119" s="19"/>
+      <c r="N119" s="19"/>
+      <c r="O119" s="19"/>
+      <c r="P119" s="19"/>
+      <c r="Q119" s="19"/>
+      <c r="R119" s="19"/>
+      <c r="S119" s="19"/>
+      <c r="T119" s="19"/>
+      <c r="U119" s="19"/>
     </row>
     <row r="120" spans="1:21" ht="15.75" customHeight="1">
       <c r="A120" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B120" s="16" t="s">
-        <v>101</v>
+      <c r="B120" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D120" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D120" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E120" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F120" s="18" t="s">
-        <v>103</v>
+      <c r="E120" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F120" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H120" s="15">
+        <v>54</v>
+      </c>
+      <c r="H120" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I120" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J120" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J120" s="18">
         <v>30</v>
       </c>
-      <c r="K120" s="20">
+      <c r="K120" s="19">
         <v>1</v>
       </c>
-      <c r="L120" s="20"/>
-      <c r="M120" s="20"/>
-      <c r="N120" s="20"/>
-      <c r="O120" s="20"/>
-      <c r="P120" s="20"/>
-      <c r="Q120" s="20"/>
-      <c r="R120" s="20"/>
-      <c r="S120" s="20"/>
-      <c r="T120" s="20"/>
-      <c r="U120" s="20"/>
+      <c r="L120" s="19"/>
+      <c r="M120" s="19"/>
+      <c r="N120" s="19"/>
+      <c r="O120" s="19"/>
+      <c r="P120" s="19"/>
+      <c r="Q120" s="19"/>
+      <c r="R120" s="19"/>
+      <c r="S120" s="19"/>
+      <c r="T120" s="19"/>
+      <c r="U120" s="19"/>
     </row>
     <row r="121" spans="1:21" ht="15.75" customHeight="1">
       <c r="A121" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B121" s="16" t="s">
-        <v>101</v>
+      <c r="B121" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D121" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E121" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F121" s="18" t="s">
-        <v>103</v>
+      <c r="E121" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F121" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H121" s="15">
+        <v>54</v>
+      </c>
+      <c r="H121" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I121" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J121" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J121" s="18">
         <v>30</v>
       </c>
-      <c r="K121" s="20">
+      <c r="K121" s="19">
         <v>1</v>
       </c>
-      <c r="L121" s="20"/>
-      <c r="M121" s="20"/>
-      <c r="N121" s="20"/>
-      <c r="O121" s="20"/>
-      <c r="P121" s="20"/>
-      <c r="Q121" s="20"/>
-      <c r="R121" s="20"/>
-      <c r="S121" s="20"/>
-      <c r="T121" s="20"/>
-      <c r="U121" s="20"/>
+      <c r="L121" s="19"/>
+      <c r="M121" s="19"/>
+      <c r="N121" s="19"/>
+      <c r="O121" s="19"/>
+      <c r="P121" s="19"/>
+      <c r="Q121" s="19"/>
+      <c r="R121" s="19"/>
+      <c r="S121" s="19"/>
+      <c r="T121" s="19"/>
+      <c r="U121" s="19"/>
     </row>
     <row r="122" spans="1:21" ht="15.75" customHeight="1">
       <c r="A122" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B122" s="16" t="s">
-        <v>105</v>
+      <c r="B122" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D122" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E122" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F122" s="18" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="D122" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F122" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H122" s="15">
+        <v>54</v>
+      </c>
+      <c r="H122" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I122" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J122" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J122" s="18">
         <v>30</v>
       </c>
-      <c r="K122" s="20">
+      <c r="K122" s="19">
         <v>1</v>
       </c>
-      <c r="L122" s="20"/>
-      <c r="M122" s="20"/>
-      <c r="N122" s="20"/>
-      <c r="O122" s="20"/>
-      <c r="P122" s="20"/>
-      <c r="Q122" s="20"/>
-      <c r="R122" s="20"/>
-      <c r="S122" s="20"/>
-      <c r="T122" s="20"/>
-      <c r="U122" s="20"/>
+      <c r="L122" s="19"/>
+      <c r="M122" s="19"/>
+      <c r="N122" s="19"/>
+      <c r="O122" s="19"/>
+      <c r="P122" s="19"/>
+      <c r="Q122" s="19"/>
+      <c r="R122" s="19"/>
+      <c r="S122" s="19"/>
+      <c r="T122" s="19"/>
+      <c r="U122" s="19"/>
     </row>
     <row r="123" spans="1:21" ht="15.75" customHeight="1">
       <c r="A123" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B123" s="16" t="s">
-        <v>105</v>
+      <c r="B123" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D123" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E123" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D123" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F123" s="18" t="s">
-        <v>103</v>
+      <c r="E123" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H123" s="15">
+        <v>54</v>
+      </c>
+      <c r="H123" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I123" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J123" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J123" s="18">
         <v>30</v>
       </c>
-      <c r="K123" s="20">
+      <c r="K123" s="19">
         <v>1</v>
       </c>
-      <c r="L123" s="20"/>
-      <c r="M123" s="20"/>
-      <c r="N123" s="20"/>
-      <c r="O123" s="20"/>
-      <c r="P123" s="20"/>
-      <c r="Q123" s="20"/>
-      <c r="R123" s="20"/>
-      <c r="S123" s="20"/>
-      <c r="T123" s="20"/>
-      <c r="U123" s="20"/>
+      <c r="L123" s="19"/>
+      <c r="M123" s="19"/>
+      <c r="N123" s="19"/>
+      <c r="O123" s="19"/>
+      <c r="P123" s="19"/>
+      <c r="Q123" s="19"/>
+      <c r="R123" s="19"/>
+      <c r="S123" s="19"/>
+      <c r="T123" s="19"/>
+      <c r="U123" s="19"/>
     </row>
     <row r="124" spans="1:21" ht="15.75" customHeight="1">
       <c r="A124" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>105</v>
+      <c r="B124" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D124" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E124" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F124" s="18" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="D124" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E124" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F124" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H124" s="15">
+        <v>54</v>
+      </c>
+      <c r="H124" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I124" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J124" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J124" s="18">
         <v>30</v>
       </c>
-      <c r="K124" s="20">
+      <c r="K124" s="19">
         <v>1</v>
       </c>
-      <c r="L124" s="20"/>
-      <c r="M124" s="20"/>
-      <c r="N124" s="20"/>
-      <c r="O124" s="20"/>
-      <c r="P124" s="20"/>
-      <c r="Q124" s="20"/>
-      <c r="R124" s="20"/>
-      <c r="S124" s="20"/>
-      <c r="T124" s="20"/>
-      <c r="U124" s="20"/>
+      <c r="L124" s="19"/>
+      <c r="M124" s="19"/>
+      <c r="N124" s="19"/>
+      <c r="O124" s="19"/>
+      <c r="P124" s="19"/>
+      <c r="Q124" s="19"/>
+      <c r="R124" s="19"/>
+      <c r="S124" s="19"/>
+      <c r="T124" s="19"/>
+      <c r="U124" s="19"/>
     </row>
     <row r="125" spans="1:21" ht="15.75" customHeight="1">
       <c r="A125" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>108</v>
+      <c r="B125" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D125" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E125" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="18" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="D125" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F125" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H125" s="15">
+        <v>54</v>
+      </c>
+      <c r="H125" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I125" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J125" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J125" s="18">
         <v>30</v>
       </c>
-      <c r="K125" s="20">
+      <c r="K125" s="19">
         <v>1</v>
       </c>
-      <c r="L125" s="20"/>
-      <c r="M125" s="20"/>
-      <c r="N125" s="20"/>
-      <c r="O125" s="20"/>
-      <c r="P125" s="20"/>
-      <c r="Q125" s="20"/>
-      <c r="R125" s="20"/>
-      <c r="S125" s="20"/>
-      <c r="T125" s="20"/>
-      <c r="U125" s="20"/>
+      <c r="L125" s="19"/>
+      <c r="M125" s="19"/>
+      <c r="N125" s="19"/>
+      <c r="O125" s="19"/>
+      <c r="P125" s="19"/>
+      <c r="Q125" s="19"/>
+      <c r="R125" s="19"/>
+      <c r="S125" s="19"/>
+      <c r="T125" s="19"/>
+      <c r="U125" s="19"/>
     </row>
     <row r="126" spans="1:21" ht="15.75" customHeight="1">
       <c r="A126" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B126" s="16" t="s">
-        <v>108</v>
+      <c r="B126" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D126" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E126" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F126" s="18" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="D126" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F126" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H126" s="15">
+        <v>54</v>
+      </c>
+      <c r="H126" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I126" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J126" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J126" s="18">
         <v>30</v>
       </c>
-      <c r="K126" s="20">
+      <c r="K126" s="19">
         <v>1</v>
       </c>
-      <c r="L126" s="20"/>
-      <c r="M126" s="20"/>
-      <c r="N126" s="20"/>
-      <c r="O126" s="20"/>
-      <c r="P126" s="20"/>
-      <c r="Q126" s="20"/>
-      <c r="R126" s="20"/>
-      <c r="S126" s="20"/>
-      <c r="T126" s="20"/>
-      <c r="U126" s="20"/>
+      <c r="L126" s="19"/>
+      <c r="M126" s="19"/>
+      <c r="N126" s="19"/>
+      <c r="O126" s="19"/>
+      <c r="P126" s="19"/>
+      <c r="Q126" s="19"/>
+      <c r="R126" s="19"/>
+      <c r="S126" s="19"/>
+      <c r="T126" s="19"/>
+      <c r="U126" s="19"/>
     </row>
     <row r="127" spans="1:21" ht="15.75" customHeight="1">
       <c r="A127" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B127" s="16" t="s">
-        <v>108</v>
+      <c r="B127" s="15" t="s">
+        <v>53</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D127" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E127" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="F127" s="18" t="s">
-        <v>103</v>
+        <v>50</v>
+      </c>
+      <c r="D127" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="F127" s="17" t="s">
+        <v>51</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="H127" s="15">
+        <v>54</v>
+      </c>
+      <c r="H127" s="14">
         <f t="shared" si="0"/>
-        <v>37.799999999999997</v>
-      </c>
-      <c r="I127" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="J127" s="19">
+        <v>3.5</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J127" s="18">
         <v>30</v>
       </c>
-      <c r="K127" s="20">
+      <c r="K127" s="19">
         <v>1</v>
       </c>
-      <c r="L127" s="20"/>
-      <c r="M127" s="20"/>
-      <c r="N127" s="20"/>
-      <c r="O127" s="20"/>
-      <c r="P127" s="20"/>
-      <c r="Q127" s="20"/>
-      <c r="R127" s="20"/>
-      <c r="S127" s="20"/>
-      <c r="T127" s="20"/>
-      <c r="U127" s="20"/>
+      <c r="L127" s="19"/>
+      <c r="M127" s="19"/>
+      <c r="N127" s="19"/>
+      <c r="O127" s="19"/>
+      <c r="P127" s="19"/>
+      <c r="Q127" s="19"/>
+      <c r="R127" s="19"/>
+      <c r="S127" s="19"/>
+      <c r="T127" s="19"/>
+      <c r="U127" s="19"/>
     </row>
     <row r="128" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A128" s="25" t="s">
-        <v>114</v>
+      <c r="A128" s="24" t="s">
+        <v>55</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F128" s="23"/>
+        <v>82</v>
+      </c>
+      <c r="F128" s="22"/>
       <c r="H128" s="9">
         <f t="shared" ref="H128:H131" si="7">I128*((100-J128)/100)</f>
-        <v>3.0352396694214878</v>
-      </c>
-      <c r="I128" s="23">
-        <f>3.68/1.21</f>
-        <v>3.0413223140495869</v>
-      </c>
-      <c r="J128" s="24">
+        <v>4.99</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J128" s="23">
         <v>0.2</v>
       </c>
-      <c r="K128" s="20"/>
+      <c r="K128" s="19"/>
     </row>
     <row r="129" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A129" s="25" t="s">
-        <v>114</v>
+      <c r="A129" s="24" t="s">
+        <v>55</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F129" s="23"/>
+        <v>80</v>
+      </c>
+      <c r="F129" s="22"/>
       <c r="H129" s="9">
         <v>1</v>
       </c>
-      <c r="I129" s="23">
-        <v>1</v>
-      </c>
-      <c r="J129" s="24">
+      <c r="I129" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J129" s="23">
         <v>0.2</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A130" s="25" t="s">
-        <v>114</v>
+      <c r="A130" s="24" t="s">
+        <v>55</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F130" s="23"/>
+        <v>81</v>
+      </c>
+      <c r="F130" s="22"/>
       <c r="H130" s="9">
         <v>1</v>
       </c>
-      <c r="I130" s="23">
-        <v>1.2</v>
-      </c>
-      <c r="J130" s="24"/>
-      <c r="L130" s="26"/>
+      <c r="I130" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J130" s="23"/>
+      <c r="L130" s="25"/>
     </row>
     <row r="131" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A131" s="25" t="s">
-        <v>114</v>
+      <c r="A131" s="24" t="s">
+        <v>55</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="F131" s="21"/>
+        <v>79</v>
+      </c>
+      <c r="F131" s="20"/>
       <c r="H131" s="9">
         <f t="shared" si="7"/>
-        <v>3.992</v>
-      </c>
-      <c r="I131" s="21">
-        <v>4</v>
-      </c>
-      <c r="J131" s="24">
+        <v>4.99</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J131" s="23">
         <v>0.2</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B132" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C132" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D132" s="21">
+        <v>56</v>
+      </c>
+      <c r="B132" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C132" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D132" s="20">
         <v>698</v>
       </c>
-      <c r="E132" s="21">
+      <c r="E132" s="20">
         <v>147</v>
       </c>
-      <c r="F132" s="21"/>
-      <c r="G132" s="22" t="s">
-        <v>117</v>
+      <c r="F132" s="20"/>
+      <c r="G132" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H132" s="9">
         <f t="shared" ref="H132:H146" si="8">I132*((100-J132)/100)</f>
-        <v>700</v>
-      </c>
-      <c r="I132" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J132" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J132" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B133" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="C133" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D133" s="21">
+        <v>56</v>
+      </c>
+      <c r="B133" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C133" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D133" s="20">
         <v>698</v>
       </c>
-      <c r="E133" s="21">
+      <c r="E133" s="20">
         <v>297</v>
       </c>
-      <c r="F133" s="21"/>
-      <c r="G133" s="22" t="s">
-        <v>117</v>
+      <c r="F133" s="20"/>
+      <c r="G133" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H133" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I133" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J133" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J133" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B134" s="22" t="s">
-        <v>120</v>
-      </c>
-      <c r="C134" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D134" s="21">
+        <v>56</v>
+      </c>
+      <c r="B134" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C134" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D134" s="20">
         <v>698</v>
       </c>
-      <c r="E134" s="21">
+      <c r="E134" s="20">
         <v>347</v>
       </c>
-      <c r="F134" s="21"/>
-      <c r="G134" s="22" t="s">
-        <v>117</v>
+      <c r="F134" s="20"/>
+      <c r="G134" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H134" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I134" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J134" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J134" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B135" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="C135" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D135" s="21">
+        <v>56</v>
+      </c>
+      <c r="B135" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C135" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D135" s="20">
         <v>698</v>
       </c>
-      <c r="E135" s="21">
+      <c r="E135" s="20">
         <v>397</v>
       </c>
-      <c r="F135" s="21"/>
-      <c r="G135" s="22" t="s">
-        <v>117</v>
+      <c r="F135" s="20"/>
+      <c r="G135" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H135" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I135" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J135" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J135" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B136" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C136" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D136" s="21">
+        <v>56</v>
+      </c>
+      <c r="B136" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C136" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D136" s="20">
         <v>698</v>
       </c>
-      <c r="E136" s="21">
+      <c r="E136" s="20">
         <v>447</v>
       </c>
-      <c r="F136" s="21"/>
-      <c r="G136" s="22" t="s">
-        <v>117</v>
+      <c r="F136" s="20"/>
+      <c r="G136" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H136" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I136" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J136" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J136" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B137" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C137" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D137" s="21">
+        <v>56</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C137" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D137" s="20">
         <v>698</v>
       </c>
-      <c r="E137" s="21">
+      <c r="E137" s="20">
         <v>497</v>
       </c>
-      <c r="F137" s="21"/>
-      <c r="G137" s="22" t="s">
-        <v>117</v>
+      <c r="F137" s="20"/>
+      <c r="G137" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H137" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I137" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J137" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J137" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B138" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C138" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D138" s="21">
+        <v>56</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C138" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D138" s="20">
         <v>698</v>
       </c>
-      <c r="E138" s="21">
+      <c r="E138" s="20">
         <v>597</v>
       </c>
-      <c r="F138" s="21"/>
-      <c r="G138" s="22" t="s">
-        <v>117</v>
+      <c r="F138" s="20"/>
+      <c r="G138" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H138" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I138" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J138" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J138" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B139" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="C139" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D139" s="21">
+        <v>56</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D139" s="20">
         <v>798</v>
       </c>
-      <c r="E139" s="21">
+      <c r="E139" s="20">
         <v>147</v>
       </c>
-      <c r="F139" s="21"/>
-      <c r="G139" s="22" t="s">
-        <v>117</v>
+      <c r="F139" s="20"/>
+      <c r="G139" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H139" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I139" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J139" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J139" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B140" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C140" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D140" s="21">
+        <v>56</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C140" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D140" s="20">
         <v>798</v>
       </c>
-      <c r="E140" s="21">
+      <c r="E140" s="20">
         <v>297</v>
       </c>
-      <c r="F140" s="21"/>
-      <c r="G140" s="22" t="s">
-        <v>117</v>
+      <c r="F140" s="20"/>
+      <c r="G140" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H140" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I140" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J140" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J140" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B141" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="C141" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D141" s="21">
+        <v>56</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C141" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D141" s="20">
         <v>798</v>
       </c>
-      <c r="E141" s="21">
+      <c r="E141" s="20">
         <v>347</v>
       </c>
-      <c r="F141" s="21"/>
-      <c r="G141" s="22" t="s">
-        <v>117</v>
+      <c r="F141" s="20"/>
+      <c r="G141" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H141" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I141" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J141" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I141" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J141" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B142" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C142" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D142" s="21">
+        <v>56</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C142" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D142" s="20">
         <v>798</v>
       </c>
-      <c r="E142" s="21">
+      <c r="E142" s="20">
         <v>397</v>
       </c>
-      <c r="F142" s="21"/>
-      <c r="G142" s="22" t="s">
-        <v>117</v>
+      <c r="F142" s="20"/>
+      <c r="G142" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H142" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I142" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J142" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J142" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B143" s="22" t="s">
-        <v>129</v>
-      </c>
-      <c r="C143" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D143" s="21">
+        <v>56</v>
+      </c>
+      <c r="B143" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C143" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D143" s="20">
         <v>798</v>
       </c>
-      <c r="E143" s="21">
+      <c r="E143" s="20">
         <v>447</v>
       </c>
-      <c r="F143" s="21"/>
-      <c r="G143" s="22" t="s">
-        <v>117</v>
+      <c r="F143" s="20"/>
+      <c r="G143" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H143" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I143" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J143" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J143" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B144" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C144" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D144" s="21">
+        <v>56</v>
+      </c>
+      <c r="B144" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C144" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D144" s="20">
         <v>798</v>
       </c>
-      <c r="E144" s="21">
+      <c r="E144" s="20">
         <v>497</v>
       </c>
-      <c r="F144" s="21"/>
-      <c r="G144" s="22" t="s">
-        <v>117</v>
+      <c r="F144" s="20"/>
+      <c r="G144" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H144" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I144" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J144" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J144" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="145" spans="1:21" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B145" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="C145" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D145" s="21">
+        <v>56</v>
+      </c>
+      <c r="B145" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C145" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D145" s="20">
         <v>798</v>
       </c>
-      <c r="E145" s="21">
+      <c r="E145" s="20">
         <v>597</v>
       </c>
-      <c r="F145" s="21"/>
-      <c r="G145" s="22" t="s">
-        <v>117</v>
+      <c r="F145" s="20"/>
+      <c r="G145" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H145" s="9">
         <f t="shared" si="8"/>
-        <v>700</v>
-      </c>
-      <c r="I145" s="21">
-        <v>1000</v>
-      </c>
-      <c r="J145" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J145" s="20">
         <v>30</v>
       </c>
     </row>
     <row r="146" spans="1:21" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B146" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="C146" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D146" s="21">
+        <v>56</v>
+      </c>
+      <c r="B146" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C146" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D146" s="20">
         <v>1098</v>
       </c>
-      <c r="E146" s="21">
+      <c r="E146" s="20">
         <v>397</v>
       </c>
-      <c r="F146" s="21"/>
-      <c r="G146" s="22" t="s">
-        <v>117</v>
+      <c r="F146" s="20"/>
+      <c r="G146" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H146" s="9">
         <f t="shared" si="8"/>
-        <v>1639.3999999999999</v>
-      </c>
-      <c r="I146" s="21">
-        <v>2342</v>
-      </c>
-      <c r="J146" s="21">
+        <v>3.5</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J146" s="20">
         <v>30</v>
       </c>
       <c r="K146" s="10"/>
@@ -7262,45 +7074,45 @@
     </row>
     <row r="147" spans="1:21" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B147" s="22" t="s">
-        <v>132</v>
-      </c>
-      <c r="C147" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D147" s="23">
+        <v>56</v>
+      </c>
+      <c r="B147" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C147" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D147" s="22">
         <v>1098</v>
       </c>
-      <c r="E147" s="23">
+      <c r="E147" s="22">
         <v>597</v>
       </c>
-      <c r="F147" s="23"/>
-      <c r="G147" s="22" t="s">
-        <v>117</v>
+      <c r="F147" s="22"/>
+      <c r="G147" s="21" t="s">
+        <v>58</v>
       </c>
       <c r="H147" s="9">
         <f t="shared" ref="H147" si="9">I147*((100-J147)/100)</f>
-        <v>16396.099999999999</v>
-      </c>
-      <c r="I147" s="23">
-        <v>23423</v>
-      </c>
-      <c r="J147" s="23">
+        <v>3.5</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J147" s="22">
         <v>30</v>
       </c>
-      <c r="K147" s="23"/>
-      <c r="L147" s="23"/>
-      <c r="M147" s="23"/>
-      <c r="N147" s="23"/>
-      <c r="O147" s="23"/>
-      <c r="P147" s="23"/>
-      <c r="Q147" s="23"/>
-      <c r="R147" s="23"/>
-      <c r="S147" s="23"/>
-      <c r="T147" s="23"/>
-      <c r="U147" s="23"/>
+      <c r="K147" s="22"/>
+      <c r="L147" s="22"/>
+      <c r="M147" s="22"/>
+      <c r="N147" s="22"/>
+      <c r="O147" s="22"/>
+      <c r="P147" s="22"/>
+      <c r="Q147" s="22"/>
+      <c r="R147" s="22"/>
+      <c r="S147" s="22"/>
+      <c r="T147" s="22"/>
+      <c r="U147" s="22"/>
     </row>
     <row r="148" spans="1:21" ht="15.75" customHeight="1">
       <c r="A148" s="10"/>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="86">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -6526,6 +6526,9 @@
       <c r="A128" s="24" t="s">
         <v>55</v>
       </c>
+      <c r="B128" s="15" t="s">
+        <v>82</v>
+      </c>
       <c r="C128" s="7" t="s">
         <v>82</v>
       </c>
@@ -6546,6 +6549,9 @@
       <c r="A129" s="24" t="s">
         <v>55</v>
       </c>
+      <c r="B129" s="15" t="s">
+        <v>80</v>
+      </c>
       <c r="C129" s="7" t="s">
         <v>80</v>
       </c>
@@ -6564,6 +6570,9 @@
       <c r="A130" s="24" t="s">
         <v>55</v>
       </c>
+      <c r="B130" s="15" t="s">
+        <v>81</v>
+      </c>
       <c r="C130" s="7" t="s">
         <v>81</v>
       </c>
@@ -6580,6 +6589,9 @@
     <row r="131" spans="1:12" ht="15.75" customHeight="1">
       <c r="A131" s="24" t="s">
         <v>55</v>
+      </c>
+      <c r="B131" s="15" t="s">
+        <v>79</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>79</v>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -254,9 +254,6 @@
     <t>110_40</t>
   </si>
   <si>
-    <t>Colgador mueble alto</t>
-  </si>
-  <si>
     <t>PATA_H10</t>
   </si>
   <si>
@@ -273,6 +270,9 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>Colgador</t>
   </si>
 </sst>
 </file>
@@ -719,7 +719,7 @@
         <v>3.5</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J2" s="9">
         <v>30</v>
@@ -771,7 +771,7 @@
         <v>3.5</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J3" s="9">
         <v>30</v>
@@ -823,7 +823,7 @@
         <v>3.5</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J4" s="9">
         <v>30</v>
@@ -875,7 +875,7 @@
         <v>3.5</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J5" s="9">
         <v>30</v>
@@ -927,7 +927,7 @@
         <v>3.5</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
@@ -979,7 +979,7 @@
         <v>3.5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J7" s="9">
         <v>30</v>
@@ -1031,7 +1031,7 @@
         <v>3.5</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J8" s="9">
         <v>30</v>
@@ -1083,7 +1083,7 @@
         <v>3.5</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J9" s="9">
         <v>30</v>
@@ -1129,7 +1129,7 @@
         <v>3.5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J10" s="9">
         <v>30</v>
@@ -1175,7 +1175,7 @@
         <v>3.5</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J11" s="9">
         <v>30</v>
@@ -1221,7 +1221,7 @@
         <v>3.5</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J12" s="9">
         <v>30</v>
@@ -1267,7 +1267,7 @@
         <v>3.5</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J13" s="9">
         <v>30</v>
@@ -1313,7 +1313,7 @@
         <v>3.5</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J14" s="9">
         <v>30</v>
@@ -1359,7 +1359,7 @@
         <v>3.5</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J15" s="9">
         <v>30</v>
@@ -1405,7 +1405,7 @@
         <v>3.5</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J16" s="9">
         <v>30</v>
@@ -1451,7 +1451,7 @@
         <v>3.5</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J17" s="9">
         <v>30</v>
@@ -1497,7 +1497,7 @@
         <v>3.5</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J18" s="9">
         <v>30</v>
@@ -1543,7 +1543,7 @@
         <v>3.5</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J19" s="9">
         <v>30</v>
@@ -1589,7 +1589,7 @@
         <v>3.5</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J20" s="9">
         <v>30</v>
@@ -1635,7 +1635,7 @@
         <v>3.5</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J21" s="9">
         <v>30</v>
@@ -1681,7 +1681,7 @@
         <v>3.5</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J22" s="9">
         <v>30</v>
@@ -1727,7 +1727,7 @@
         <v>3.5</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J23" s="9">
         <v>30</v>
@@ -1773,7 +1773,7 @@
         <v>3.5</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J24" s="9">
         <v>30</v>
@@ -1819,7 +1819,7 @@
         <v>3.5</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J25" s="9">
         <v>30</v>
@@ -1865,7 +1865,7 @@
         <v>3.5</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J26" s="9">
         <v>30</v>
@@ -1911,7 +1911,7 @@
         <v>3.5</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J27" s="9">
         <v>30</v>
@@ -1957,7 +1957,7 @@
         <v>3.5</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J28" s="9">
         <v>30</v>
@@ -2003,7 +2003,7 @@
         <v>3.5</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J29" s="9">
         <v>30</v>
@@ -2049,7 +2049,7 @@
         <v>3.5</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J30" s="9">
         <v>30</v>
@@ -2095,7 +2095,7 @@
         <v>3.5</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2141,7 +2141,7 @@
         <v>3.5</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J32" s="9">
         <v>30</v>
@@ -2187,7 +2187,7 @@
         <v>3.5</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J33" s="9">
         <v>30</v>
@@ -2233,7 +2233,7 @@
         <v>3.5</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J34" s="9">
         <v>30</v>
@@ -2279,7 +2279,7 @@
         <v>3.5</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J35" s="9">
         <v>30</v>
@@ -2325,7 +2325,7 @@
         <v>3.5</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J36" s="9">
         <v>30</v>
@@ -2371,7 +2371,7 @@
         <v>3.5</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J37" s="9">
         <v>30</v>
@@ -2417,7 +2417,7 @@
         <v>3.5</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J38" s="9">
         <v>30</v>
@@ -2463,7 +2463,7 @@
         <v>3.5</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J39" s="9">
         <v>30</v>
@@ -2509,7 +2509,7 @@
         <v>3.5</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J40" s="9">
         <v>30</v>
@@ -2555,7 +2555,7 @@
         <v>3.5</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J41" s="9">
         <v>30</v>
@@ -2601,7 +2601,7 @@
         <v>3.5</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J42" s="9">
         <v>30</v>
@@ -2647,7 +2647,7 @@
         <v>3.5</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J43" s="9">
         <v>30</v>
@@ -2693,7 +2693,7 @@
         <v>3.5</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J44" s="9">
         <v>30</v>
@@ -2739,7 +2739,7 @@
         <v>3.5</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J45" s="9">
         <v>30</v>
@@ -2785,7 +2785,7 @@
         <v>3.5</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J46" s="9">
         <v>30</v>
@@ -2831,7 +2831,7 @@
         <v>3.5</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J47" s="9">
         <v>30</v>
@@ -2877,7 +2877,7 @@
         <v>3.5</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J48" s="9">
         <v>30</v>
@@ -2923,7 +2923,7 @@
         <v>3.5</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J49" s="9">
         <v>30</v>
@@ -2967,7 +2967,7 @@
         <v>3.5</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J50" s="9">
         <v>30</v>
@@ -3009,7 +3009,7 @@
         <v>3.5</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J51" s="9">
         <v>30</v>
@@ -3053,7 +3053,7 @@
         <v>3.5</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J52" s="9">
         <v>30</v>
@@ -3099,7 +3099,7 @@
         <v>3.5</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J53" s="9">
         <v>30</v>
@@ -3126,7 +3126,7 @@
         <v>45</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>35</v>
@@ -3145,7 +3145,7 @@
         <v>3.5</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J54" s="9">
         <v>30</v>
@@ -3191,7 +3191,7 @@
         <v>3.5</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J55" s="9">
         <v>30</v>
@@ -3237,7 +3237,7 @@
         <v>3.5</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J56" s="9">
         <v>30</v>
@@ -3283,7 +3283,7 @@
         <v>3.5</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J57" s="9">
         <v>30</v>
@@ -3329,7 +3329,7 @@
         <v>3.5</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J58" s="9">
         <v>30</v>
@@ -3375,7 +3375,7 @@
         <v>3.5</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J59" s="9">
         <v>30</v>
@@ -3421,7 +3421,7 @@
         <v>3.5</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J60" s="9">
         <v>30</v>
@@ -3467,7 +3467,7 @@
         <v>3.5</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J61" s="9">
         <v>30</v>
@@ -3513,7 +3513,7 @@
         <v>3.5</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J62" s="9">
         <v>30</v>
@@ -3559,7 +3559,7 @@
         <v>3.5</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J63" s="9">
         <v>30</v>
@@ -3605,7 +3605,7 @@
         <v>3.5</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J64" s="9">
         <v>30</v>
@@ -3651,7 +3651,7 @@
         <v>3.5</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J65" s="9">
         <v>30</v>
@@ -3697,7 +3697,7 @@
         <v>3.5</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J66" s="9">
         <v>30</v>
@@ -3743,13 +3743,13 @@
         <v>3.5</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J67" s="9">
         <v>30</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -3789,7 +3789,7 @@
         <v>3.5</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J68" s="9">
         <v>30</v>
@@ -3835,7 +3835,7 @@
         <v>3.5</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J69" s="9">
         <v>30</v>
@@ -3881,7 +3881,7 @@
         <v>3.5</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J70" s="9">
         <v>30</v>
@@ -3927,7 +3927,7 @@
         <v>3.5</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J71" s="9">
         <v>30</v>
@@ -3973,7 +3973,7 @@
         <v>3.5</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J72" s="9">
         <v>30</v>
@@ -4019,7 +4019,7 @@
         <v>3.5</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J73" s="9">
         <v>30</v>
@@ -4065,7 +4065,7 @@
         <v>3.5</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J74" s="9">
         <v>30</v>
@@ -4111,7 +4111,7 @@
         <v>3.5</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J75" s="9">
         <v>30</v>
@@ -4157,7 +4157,7 @@
         <v>3.5</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J76" s="9">
         <v>30</v>
@@ -4203,7 +4203,7 @@
         <v>3.5</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J77" s="9">
         <v>30</v>
@@ -4249,7 +4249,7 @@
         <v>3.5</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J78" s="9">
         <v>30</v>
@@ -4295,7 +4295,7 @@
         <v>3.5</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J79" s="9">
         <v>30</v>
@@ -4341,13 +4341,13 @@
         <v>3.5</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J80" s="9">
         <v>30</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -4387,7 +4387,7 @@
         <v>3.5</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J81" s="9">
         <v>30</v>
@@ -4433,7 +4433,7 @@
         <v>3.5</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J82" s="9">
         <v>30</v>
@@ -4479,7 +4479,7 @@
         <v>3.5</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J83" s="9">
         <v>30</v>
@@ -4525,7 +4525,7 @@
         <v>3.5</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J84" s="9">
         <v>30</v>
@@ -4571,7 +4571,7 @@
         <v>3.5</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J85" s="9">
         <v>30</v>
@@ -4617,7 +4617,7 @@
         <v>3.5</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J86" s="9">
         <v>30</v>
@@ -4663,7 +4663,7 @@
         <v>3.5</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J87" s="9">
         <v>30</v>
@@ -4709,7 +4709,7 @@
         <v>3.5</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J88" s="9">
         <v>30</v>
@@ -4755,7 +4755,7 @@
         <v>3.5</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J89" s="9">
         <v>30</v>
@@ -4801,7 +4801,7 @@
         <v>3.5</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J90" s="9">
         <v>30</v>
@@ -4847,7 +4847,7 @@
         <v>3.5</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J91" s="9">
         <v>30</v>
@@ -4893,7 +4893,7 @@
         <v>3.5</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J92" s="9">
         <v>30</v>
@@ -4939,7 +4939,7 @@
         <v>3.5</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J93" s="9">
         <v>30</v>
@@ -4985,7 +4985,7 @@
         <v>3.5</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J94" s="9">
         <v>30</v>
@@ -5031,7 +5031,7 @@
         <v>3.5</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J95" s="9">
         <v>30</v>
@@ -5077,7 +5077,7 @@
         <v>3.5</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J96" s="9">
         <v>30</v>
@@ -5123,7 +5123,7 @@
         <v>3.5</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J97" s="9">
         <v>30</v>
@@ -5169,7 +5169,7 @@
         <v>3.5</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J98" s="9">
         <v>30</v>
@@ -5215,7 +5215,7 @@
         <v>3.5</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J99" s="9">
         <v>30</v>
@@ -5261,7 +5261,7 @@
         <v>3.5</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J100" s="9">
         <v>30</v>
@@ -5307,7 +5307,7 @@
         <v>3.5</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J101" s="9">
         <v>30</v>
@@ -5353,7 +5353,7 @@
         <v>3.5</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J102" s="9">
         <v>30</v>
@@ -5399,7 +5399,7 @@
         <v>3.5</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J103" s="9">
         <v>30</v>
@@ -5445,7 +5445,7 @@
         <v>3.5</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J104" s="9">
         <v>30</v>
@@ -5491,7 +5491,7 @@
         <v>3.5</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J105" s="9">
         <v>30</v>
@@ -5537,7 +5537,7 @@
         <v>3.5</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J106" s="9">
         <v>30</v>
@@ -5583,7 +5583,7 @@
         <v>3.5</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J107" s="9">
         <v>30</v>
@@ -5629,7 +5629,7 @@
         <v>3.5</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J108" s="9">
         <v>30</v>
@@ -5675,7 +5675,7 @@
         <v>3.5</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J109" s="9">
         <v>30</v>
@@ -5721,7 +5721,7 @@
         <v>3.5</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J110" s="9">
         <v>30</v>
@@ -5767,7 +5767,7 @@
         <v>3.5</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J111" s="9">
         <v>30</v>
@@ -5813,7 +5813,7 @@
         <v>3.5</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J112" s="9">
         <v>30</v>
@@ -5859,7 +5859,7 @@
         <v>3.5</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J113" s="9">
         <v>30</v>
@@ -5905,7 +5905,7 @@
         <v>3.5</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J114" s="9">
         <v>30</v>
@@ -5951,7 +5951,7 @@
         <v>3.5</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J115" s="9">
         <v>30</v>
@@ -5997,7 +5997,7 @@
         <v>3.5</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J116" s="9">
         <v>30</v>
@@ -6043,7 +6043,7 @@
         <v>3.5</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J117" s="9">
         <v>30</v>
@@ -6089,7 +6089,7 @@
         <v>3.5</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J118" s="9">
         <v>30</v>
@@ -6135,7 +6135,7 @@
         <v>3.5</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J119" s="18">
         <v>30</v>
@@ -6181,7 +6181,7 @@
         <v>3.5</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J120" s="18">
         <v>30</v>
@@ -6227,7 +6227,7 @@
         <v>3.5</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J121" s="18">
         <v>30</v>
@@ -6273,7 +6273,7 @@
         <v>3.5</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J122" s="18">
         <v>30</v>
@@ -6319,7 +6319,7 @@
         <v>3.5</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J123" s="18">
         <v>30</v>
@@ -6365,7 +6365,7 @@
         <v>3.5</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J124" s="18">
         <v>30</v>
@@ -6411,7 +6411,7 @@
         <v>3.5</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J125" s="18">
         <v>30</v>
@@ -6457,7 +6457,7 @@
         <v>3.5</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J126" s="18">
         <v>30</v>
@@ -6503,7 +6503,7 @@
         <v>3.5</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J127" s="18">
         <v>30</v>
@@ -6527,10 +6527,10 @@
         <v>55</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F128" s="22"/>
       <c r="H128" s="9">
@@ -6538,7 +6538,7 @@
         <v>4.99</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J128" s="23">
         <v>0.2</v>
@@ -6550,17 +6550,17 @@
         <v>55</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F129" s="22"/>
       <c r="H129" s="9">
         <v>1</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J129" s="23">
         <v>0.2</v>
@@ -6571,17 +6571,17 @@
         <v>55</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F130" s="22"/>
       <c r="H130" s="9">
         <v>1</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J130" s="23"/>
       <c r="L130" s="25"/>
@@ -6591,10 +6591,10 @@
         <v>55</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F131" s="20"/>
       <c r="H131" s="9">
@@ -6602,7 +6602,7 @@
         <v>4.99</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J131" s="23">
         <v>0.2</v>
@@ -6633,7 +6633,7 @@
         <v>3.5</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J132" s="20">
         <v>30</v>
@@ -6664,7 +6664,7 @@
         <v>3.5</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J133" s="20">
         <v>30</v>
@@ -6695,7 +6695,7 @@
         <v>3.5</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J134" s="20">
         <v>30</v>
@@ -6726,7 +6726,7 @@
         <v>3.5</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J135" s="20">
         <v>30</v>
@@ -6757,7 +6757,7 @@
         <v>3.5</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J136" s="20">
         <v>30</v>
@@ -6788,7 +6788,7 @@
         <v>3.5</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J137" s="20">
         <v>30</v>
@@ -6819,7 +6819,7 @@
         <v>3.5</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J138" s="20">
         <v>30</v>
@@ -6850,7 +6850,7 @@
         <v>3.5</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J139" s="20">
         <v>30</v>
@@ -6881,7 +6881,7 @@
         <v>3.5</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J140" s="20">
         <v>30</v>
@@ -6912,7 +6912,7 @@
         <v>3.5</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J141" s="20">
         <v>30</v>
@@ -6943,7 +6943,7 @@
         <v>3.5</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J142" s="20">
         <v>30</v>
@@ -6974,7 +6974,7 @@
         <v>3.5</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J143" s="20">
         <v>30</v>
@@ -7005,7 +7005,7 @@
         <v>3.5</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J144" s="20">
         <v>30</v>
@@ -7036,7 +7036,7 @@
         <v>3.5</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J145" s="20">
         <v>30</v>
@@ -7067,7 +7067,7 @@
         <v>3.5</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J146" s="20">
         <v>30</v>
@@ -7109,7 +7109,7 @@
         <v>3.5</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J147" s="22">
         <v>30</v>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="87">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -191,9 +191,6 @@
     <t>Puerta</t>
   </si>
   <si>
-    <t>blanco mate pem060</t>
-  </si>
-  <si>
     <t>70_15</t>
   </si>
   <si>
@@ -273,6 +270,12 @@
   </si>
   <si>
     <t>Colgador</t>
+  </si>
+  <si>
+    <t>tamesis_color</t>
+  </si>
+  <si>
+    <t>cloe</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -662,7 +665,7 @@
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="11" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -675,13 +678,13 @@
         <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>75</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>76</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -719,7 +722,7 @@
         <v>3.5</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J2" s="9">
         <v>30</v>
@@ -771,7 +774,7 @@
         <v>3.5</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J3" s="9">
         <v>30</v>
@@ -823,7 +826,7 @@
         <v>3.5</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J4" s="9">
         <v>30</v>
@@ -875,7 +878,7 @@
         <v>3.5</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J5" s="9">
         <v>30</v>
@@ -927,7 +930,7 @@
         <v>3.5</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
@@ -979,7 +982,7 @@
         <v>3.5</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J7" s="9">
         <v>30</v>
@@ -1031,7 +1034,7 @@
         <v>3.5</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J8" s="9">
         <v>30</v>
@@ -1083,7 +1086,7 @@
         <v>3.5</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J9" s="9">
         <v>30</v>
@@ -1129,7 +1132,7 @@
         <v>3.5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J10" s="9">
         <v>30</v>
@@ -1175,7 +1178,7 @@
         <v>3.5</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J11" s="9">
         <v>30</v>
@@ -1221,7 +1224,7 @@
         <v>3.5</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J12" s="9">
         <v>30</v>
@@ -1267,7 +1270,7 @@
         <v>3.5</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J13" s="9">
         <v>30</v>
@@ -1313,7 +1316,7 @@
         <v>3.5</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J14" s="9">
         <v>30</v>
@@ -1359,7 +1362,7 @@
         <v>3.5</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J15" s="9">
         <v>30</v>
@@ -1405,7 +1408,7 @@
         <v>3.5</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J16" s="9">
         <v>30</v>
@@ -1451,7 +1454,7 @@
         <v>3.5</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J17" s="9">
         <v>30</v>
@@ -1497,7 +1500,7 @@
         <v>3.5</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J18" s="9">
         <v>30</v>
@@ -1543,7 +1546,7 @@
         <v>3.5</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J19" s="9">
         <v>30</v>
@@ -1589,7 +1592,7 @@
         <v>3.5</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J20" s="9">
         <v>30</v>
@@ -1635,7 +1638,7 @@
         <v>3.5</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J21" s="9">
         <v>30</v>
@@ -1681,7 +1684,7 @@
         <v>3.5</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J22" s="9">
         <v>30</v>
@@ -1727,7 +1730,7 @@
         <v>3.5</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J23" s="9">
         <v>30</v>
@@ -1773,7 +1776,7 @@
         <v>3.5</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J24" s="9">
         <v>30</v>
@@ -1819,7 +1822,7 @@
         <v>3.5</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J25" s="9">
         <v>30</v>
@@ -1865,7 +1868,7 @@
         <v>3.5</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J26" s="9">
         <v>30</v>
@@ -1911,7 +1914,7 @@
         <v>3.5</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J27" s="9">
         <v>30</v>
@@ -1957,7 +1960,7 @@
         <v>3.5</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J28" s="9">
         <v>30</v>
@@ -2003,7 +2006,7 @@
         <v>3.5</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J29" s="9">
         <v>30</v>
@@ -2049,7 +2052,7 @@
         <v>3.5</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J30" s="9">
         <v>30</v>
@@ -2095,7 +2098,7 @@
         <v>3.5</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2141,7 +2144,7 @@
         <v>3.5</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J32" s="9">
         <v>30</v>
@@ -2187,7 +2190,7 @@
         <v>3.5</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J33" s="9">
         <v>30</v>
@@ -2233,7 +2236,7 @@
         <v>3.5</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J34" s="9">
         <v>30</v>
@@ -2279,7 +2282,7 @@
         <v>3.5</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J35" s="9">
         <v>30</v>
@@ -2325,7 +2328,7 @@
         <v>3.5</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J36" s="9">
         <v>30</v>
@@ -2371,7 +2374,7 @@
         <v>3.5</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J37" s="9">
         <v>30</v>
@@ -2417,7 +2420,7 @@
         <v>3.5</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J38" s="9">
         <v>30</v>
@@ -2463,7 +2466,7 @@
         <v>3.5</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J39" s="9">
         <v>30</v>
@@ -2509,7 +2512,7 @@
         <v>3.5</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J40" s="9">
         <v>30</v>
@@ -2555,7 +2558,7 @@
         <v>3.5</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J41" s="9">
         <v>30</v>
@@ -2601,7 +2604,7 @@
         <v>3.5</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J42" s="9">
         <v>30</v>
@@ -2647,7 +2650,7 @@
         <v>3.5</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J43" s="9">
         <v>30</v>
@@ -2693,7 +2696,7 @@
         <v>3.5</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J44" s="9">
         <v>30</v>
@@ -2739,7 +2742,7 @@
         <v>3.5</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J45" s="9">
         <v>30</v>
@@ -2785,7 +2788,7 @@
         <v>3.5</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J46" s="9">
         <v>30</v>
@@ -2831,7 +2834,7 @@
         <v>3.5</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J47" s="9">
         <v>30</v>
@@ -2877,7 +2880,7 @@
         <v>3.5</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J48" s="9">
         <v>30</v>
@@ -2923,7 +2926,7 @@
         <v>3.5</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J49" s="9">
         <v>30</v>
@@ -2967,7 +2970,7 @@
         <v>3.5</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J50" s="9">
         <v>30</v>
@@ -3009,7 +3012,7 @@
         <v>3.5</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J51" s="9">
         <v>30</v>
@@ -3053,7 +3056,7 @@
         <v>3.5</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J52" s="9">
         <v>30</v>
@@ -3099,7 +3102,7 @@
         <v>3.5</v>
       </c>
       <c r="I53" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J53" s="9">
         <v>30</v>
@@ -3126,7 +3129,7 @@
         <v>45</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>35</v>
@@ -3145,7 +3148,7 @@
         <v>3.5</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J54" s="9">
         <v>30</v>
@@ -3191,7 +3194,7 @@
         <v>3.5</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J55" s="9">
         <v>30</v>
@@ -3237,7 +3240,7 @@
         <v>3.5</v>
       </c>
       <c r="I56" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J56" s="9">
         <v>30</v>
@@ -3283,7 +3286,7 @@
         <v>3.5</v>
       </c>
       <c r="I57" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J57" s="9">
         <v>30</v>
@@ -3329,7 +3332,7 @@
         <v>3.5</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J58" s="9">
         <v>30</v>
@@ -3375,7 +3378,7 @@
         <v>3.5</v>
       </c>
       <c r="I59" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J59" s="9">
         <v>30</v>
@@ -3421,7 +3424,7 @@
         <v>3.5</v>
       </c>
       <c r="I60" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J60" s="9">
         <v>30</v>
@@ -3467,7 +3470,7 @@
         <v>3.5</v>
       </c>
       <c r="I61" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J61" s="9">
         <v>30</v>
@@ -3513,7 +3516,7 @@
         <v>3.5</v>
       </c>
       <c r="I62" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J62" s="9">
         <v>30</v>
@@ -3559,7 +3562,7 @@
         <v>3.5</v>
       </c>
       <c r="I63" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J63" s="9">
         <v>30</v>
@@ -3605,7 +3608,7 @@
         <v>3.5</v>
       </c>
       <c r="I64" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J64" s="9">
         <v>30</v>
@@ -3651,7 +3654,7 @@
         <v>3.5</v>
       </c>
       <c r="I65" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J65" s="9">
         <v>30</v>
@@ -3697,7 +3700,7 @@
         <v>3.5</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J66" s="9">
         <v>30</v>
@@ -3743,13 +3746,13 @@
         <v>3.5</v>
       </c>
       <c r="I67" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J67" s="9">
         <v>30</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -3789,7 +3792,7 @@
         <v>3.5</v>
       </c>
       <c r="I68" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J68" s="9">
         <v>30</v>
@@ -3835,7 +3838,7 @@
         <v>3.5</v>
       </c>
       <c r="I69" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J69" s="9">
         <v>30</v>
@@ -3881,7 +3884,7 @@
         <v>3.5</v>
       </c>
       <c r="I70" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J70" s="9">
         <v>30</v>
@@ -3927,7 +3930,7 @@
         <v>3.5</v>
       </c>
       <c r="I71" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J71" s="9">
         <v>30</v>
@@ -3973,7 +3976,7 @@
         <v>3.5</v>
       </c>
       <c r="I72" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J72" s="9">
         <v>30</v>
@@ -4019,7 +4022,7 @@
         <v>3.5</v>
       </c>
       <c r="I73" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J73" s="9">
         <v>30</v>
@@ -4065,7 +4068,7 @@
         <v>3.5</v>
       </c>
       <c r="I74" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J74" s="9">
         <v>30</v>
@@ -4111,7 +4114,7 @@
         <v>3.5</v>
       </c>
       <c r="I75" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J75" s="9">
         <v>30</v>
@@ -4157,7 +4160,7 @@
         <v>3.5</v>
       </c>
       <c r="I76" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J76" s="9">
         <v>30</v>
@@ -4203,7 +4206,7 @@
         <v>3.5</v>
       </c>
       <c r="I77" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J77" s="9">
         <v>30</v>
@@ -4249,7 +4252,7 @@
         <v>3.5</v>
       </c>
       <c r="I78" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J78" s="9">
         <v>30</v>
@@ -4295,7 +4298,7 @@
         <v>3.5</v>
       </c>
       <c r="I79" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J79" s="9">
         <v>30</v>
@@ -4341,13 +4344,13 @@
         <v>3.5</v>
       </c>
       <c r="I80" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J80" s="9">
         <v>30</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -4387,7 +4390,7 @@
         <v>3.5</v>
       </c>
       <c r="I81" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J81" s="9">
         <v>30</v>
@@ -4433,7 +4436,7 @@
         <v>3.5</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J82" s="9">
         <v>30</v>
@@ -4479,7 +4482,7 @@
         <v>3.5</v>
       </c>
       <c r="I83" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J83" s="9">
         <v>30</v>
@@ -4525,7 +4528,7 @@
         <v>3.5</v>
       </c>
       <c r="I84" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J84" s="9">
         <v>30</v>
@@ -4571,7 +4574,7 @@
         <v>3.5</v>
       </c>
       <c r="I85" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J85" s="9">
         <v>30</v>
@@ -4617,7 +4620,7 @@
         <v>3.5</v>
       </c>
       <c r="I86" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J86" s="9">
         <v>30</v>
@@ -4663,7 +4666,7 @@
         <v>3.5</v>
       </c>
       <c r="I87" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J87" s="9">
         <v>30</v>
@@ -4709,7 +4712,7 @@
         <v>3.5</v>
       </c>
       <c r="I88" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J88" s="9">
         <v>30</v>
@@ -4755,7 +4758,7 @@
         <v>3.5</v>
       </c>
       <c r="I89" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J89" s="9">
         <v>30</v>
@@ -4801,7 +4804,7 @@
         <v>3.5</v>
       </c>
       <c r="I90" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J90" s="9">
         <v>30</v>
@@ -4847,7 +4850,7 @@
         <v>3.5</v>
       </c>
       <c r="I91" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J91" s="9">
         <v>30</v>
@@ -4893,7 +4896,7 @@
         <v>3.5</v>
       </c>
       <c r="I92" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J92" s="9">
         <v>30</v>
@@ -4939,7 +4942,7 @@
         <v>3.5</v>
       </c>
       <c r="I93" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J93" s="9">
         <v>30</v>
@@ -4985,7 +4988,7 @@
         <v>3.5</v>
       </c>
       <c r="I94" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J94" s="9">
         <v>30</v>
@@ -5031,7 +5034,7 @@
         <v>3.5</v>
       </c>
       <c r="I95" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J95" s="9">
         <v>30</v>
@@ -5077,7 +5080,7 @@
         <v>3.5</v>
       </c>
       <c r="I96" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J96" s="9">
         <v>30</v>
@@ -5123,7 +5126,7 @@
         <v>3.5</v>
       </c>
       <c r="I97" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J97" s="9">
         <v>30</v>
@@ -5169,7 +5172,7 @@
         <v>3.5</v>
       </c>
       <c r="I98" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J98" s="9">
         <v>30</v>
@@ -5215,7 +5218,7 @@
         <v>3.5</v>
       </c>
       <c r="I99" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J99" s="9">
         <v>30</v>
@@ -5261,7 +5264,7 @@
         <v>3.5</v>
       </c>
       <c r="I100" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J100" s="9">
         <v>30</v>
@@ -5307,7 +5310,7 @@
         <v>3.5</v>
       </c>
       <c r="I101" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J101" s="9">
         <v>30</v>
@@ -5353,7 +5356,7 @@
         <v>3.5</v>
       </c>
       <c r="I102" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J102" s="9">
         <v>30</v>
@@ -5399,7 +5402,7 @@
         <v>3.5</v>
       </c>
       <c r="I103" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J103" s="9">
         <v>30</v>
@@ -5445,7 +5448,7 @@
         <v>3.5</v>
       </c>
       <c r="I104" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J104" s="9">
         <v>30</v>
@@ -5491,7 +5494,7 @@
         <v>3.5</v>
       </c>
       <c r="I105" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J105" s="9">
         <v>30</v>
@@ -5537,7 +5540,7 @@
         <v>3.5</v>
       </c>
       <c r="I106" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J106" s="9">
         <v>30</v>
@@ -5583,7 +5586,7 @@
         <v>3.5</v>
       </c>
       <c r="I107" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J107" s="9">
         <v>30</v>
@@ -5629,7 +5632,7 @@
         <v>3.5</v>
       </c>
       <c r="I108" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J108" s="9">
         <v>30</v>
@@ -5675,7 +5678,7 @@
         <v>3.5</v>
       </c>
       <c r="I109" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J109" s="9">
         <v>30</v>
@@ -5721,7 +5724,7 @@
         <v>3.5</v>
       </c>
       <c r="I110" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J110" s="9">
         <v>30</v>
@@ -5767,7 +5770,7 @@
         <v>3.5</v>
       </c>
       <c r="I111" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J111" s="9">
         <v>30</v>
@@ -5813,7 +5816,7 @@
         <v>3.5</v>
       </c>
       <c r="I112" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J112" s="9">
         <v>30</v>
@@ -5859,7 +5862,7 @@
         <v>3.5</v>
       </c>
       <c r="I113" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J113" s="9">
         <v>30</v>
@@ -5905,7 +5908,7 @@
         <v>3.5</v>
       </c>
       <c r="I114" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J114" s="9">
         <v>30</v>
@@ -5951,7 +5954,7 @@
         <v>3.5</v>
       </c>
       <c r="I115" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J115" s="9">
         <v>30</v>
@@ -5997,7 +6000,7 @@
         <v>3.5</v>
       </c>
       <c r="I116" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J116" s="9">
         <v>30</v>
@@ -6043,7 +6046,7 @@
         <v>3.5</v>
       </c>
       <c r="I117" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J117" s="9">
         <v>30</v>
@@ -6089,7 +6092,7 @@
         <v>3.5</v>
       </c>
       <c r="I118" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J118" s="9">
         <v>30</v>
@@ -6135,7 +6138,7 @@
         <v>3.5</v>
       </c>
       <c r="I119" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J119" s="18">
         <v>30</v>
@@ -6181,7 +6184,7 @@
         <v>3.5</v>
       </c>
       <c r="I120" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J120" s="18">
         <v>30</v>
@@ -6227,7 +6230,7 @@
         <v>3.5</v>
       </c>
       <c r="I121" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J121" s="18">
         <v>30</v>
@@ -6273,7 +6276,7 @@
         <v>3.5</v>
       </c>
       <c r="I122" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J122" s="18">
         <v>30</v>
@@ -6319,7 +6322,7 @@
         <v>3.5</v>
       </c>
       <c r="I123" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J123" s="18">
         <v>30</v>
@@ -6365,7 +6368,7 @@
         <v>3.5</v>
       </c>
       <c r="I124" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J124" s="18">
         <v>30</v>
@@ -6411,7 +6414,7 @@
         <v>3.5</v>
       </c>
       <c r="I125" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J125" s="18">
         <v>30</v>
@@ -6457,7 +6460,7 @@
         <v>3.5</v>
       </c>
       <c r="I126" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J126" s="18">
         <v>30</v>
@@ -6503,7 +6506,7 @@
         <v>3.5</v>
       </c>
       <c r="I127" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J127" s="18">
         <v>30</v>
@@ -6527,10 +6530,10 @@
         <v>55</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F128" s="22"/>
       <c r="H128" s="9">
@@ -6538,7 +6541,7 @@
         <v>4.99</v>
       </c>
       <c r="I128" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J128" s="23">
         <v>0.2</v>
@@ -6550,17 +6553,17 @@
         <v>55</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F129" s="22"/>
       <c r="H129" s="9">
         <v>1</v>
       </c>
       <c r="I129" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J129" s="23">
         <v>0.2</v>
@@ -6571,17 +6574,17 @@
         <v>55</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F130" s="22"/>
       <c r="H130" s="9">
         <v>1</v>
       </c>
       <c r="I130" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J130" s="23"/>
       <c r="L130" s="25"/>
@@ -6591,10 +6594,10 @@
         <v>55</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F131" s="20"/>
       <c r="H131" s="9">
@@ -6602,7 +6605,7 @@
         <v>4.99</v>
       </c>
       <c r="I131" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J131" s="23">
         <v>0.2</v>
@@ -6613,7 +6616,7 @@
         <v>56</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C132" s="21" t="s">
         <v>57</v>
@@ -6626,14 +6629,14 @@
       </c>
       <c r="F132" s="20"/>
       <c r="G132" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H132" s="9">
         <f t="shared" ref="H132:H146" si="8">I132*((100-J132)/100)</f>
         <v>3.5</v>
       </c>
       <c r="I132" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J132" s="20">
         <v>30</v>
@@ -6644,7 +6647,7 @@
         <v>56</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C133" s="21" t="s">
         <v>57</v>
@@ -6657,14 +6660,14 @@
       </c>
       <c r="F133" s="20"/>
       <c r="G133" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H133" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I133" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J133" s="20">
         <v>30</v>
@@ -6675,7 +6678,7 @@
         <v>56</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C134" s="21" t="s">
         <v>57</v>
@@ -6688,14 +6691,14 @@
       </c>
       <c r="F134" s="20"/>
       <c r="G134" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H134" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I134" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J134" s="20">
         <v>30</v>
@@ -6706,7 +6709,7 @@
         <v>56</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C135" s="21" t="s">
         <v>57</v>
@@ -6719,14 +6722,14 @@
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H135" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I135" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J135" s="20">
         <v>30</v>
@@ -6737,7 +6740,7 @@
         <v>56</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C136" s="21" t="s">
         <v>57</v>
@@ -6750,14 +6753,14 @@
       </c>
       <c r="F136" s="20"/>
       <c r="G136" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H136" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I136" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J136" s="20">
         <v>30</v>
@@ -6768,7 +6771,7 @@
         <v>56</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C137" s="21" t="s">
         <v>57</v>
@@ -6781,14 +6784,14 @@
       </c>
       <c r="F137" s="20"/>
       <c r="G137" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H137" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I137" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J137" s="20">
         <v>30</v>
@@ -6799,7 +6802,7 @@
         <v>56</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C138" s="21" t="s">
         <v>57</v>
@@ -6812,14 +6815,14 @@
       </c>
       <c r="F138" s="20"/>
       <c r="G138" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H138" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I138" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J138" s="20">
         <v>30</v>
@@ -6830,7 +6833,7 @@
         <v>56</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C139" s="21" t="s">
         <v>57</v>
@@ -6843,14 +6846,14 @@
       </c>
       <c r="F139" s="20"/>
       <c r="G139" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H139" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I139" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J139" s="20">
         <v>30</v>
@@ -6861,7 +6864,7 @@
         <v>56</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C140" s="21" t="s">
         <v>57</v>
@@ -6874,14 +6877,14 @@
       </c>
       <c r="F140" s="20"/>
       <c r="G140" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H140" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I140" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J140" s="20">
         <v>30</v>
@@ -6892,7 +6895,7 @@
         <v>56</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C141" s="21" t="s">
         <v>57</v>
@@ -6905,14 +6908,14 @@
       </c>
       <c r="F141" s="20"/>
       <c r="G141" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H141" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I141" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J141" s="20">
         <v>30</v>
@@ -6923,7 +6926,7 @@
         <v>56</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C142" s="21" t="s">
         <v>57</v>
@@ -6936,14 +6939,14 @@
       </c>
       <c r="F142" s="20"/>
       <c r="G142" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H142" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I142" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J142" s="20">
         <v>30</v>
@@ -6954,7 +6957,7 @@
         <v>56</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C143" s="21" t="s">
         <v>57</v>
@@ -6967,14 +6970,14 @@
       </c>
       <c r="F143" s="20"/>
       <c r="G143" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H143" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I143" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J143" s="20">
         <v>30</v>
@@ -6985,7 +6988,7 @@
         <v>56</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C144" s="21" t="s">
         <v>57</v>
@@ -6998,14 +7001,14 @@
       </c>
       <c r="F144" s="20"/>
       <c r="G144" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H144" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I144" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J144" s="20">
         <v>30</v>
@@ -7016,7 +7019,7 @@
         <v>56</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C145" s="21" t="s">
         <v>57</v>
@@ -7029,14 +7032,14 @@
       </c>
       <c r="F145" s="20"/>
       <c r="G145" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H145" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I145" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J145" s="20">
         <v>30</v>
@@ -7047,7 +7050,7 @@
         <v>56</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C146" s="21" t="s">
         <v>57</v>
@@ -7060,14 +7063,14 @@
       </c>
       <c r="F146" s="20"/>
       <c r="G146" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H146" s="9">
         <f t="shared" si="8"/>
         <v>3.5</v>
       </c>
       <c r="I146" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J146" s="20">
         <v>30</v>
@@ -7089,7 +7092,7 @@
         <v>56</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C147" s="21" t="s">
         <v>57</v>
@@ -7102,14 +7105,14 @@
       </c>
       <c r="F147" s="22"/>
       <c r="G147" s="21" t="s">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="H147" s="9">
         <f t="shared" ref="H147" si="9">I147*((100-J147)/100)</f>
         <v>3.5</v>
       </c>
       <c r="I147" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J147" s="22">
         <v>30</v>
@@ -7127,16 +7130,34 @@
       <c r="U147" s="22"/>
     </row>
     <row r="148" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A148" s="10"/>
-      <c r="B148" s="10"/>
-      <c r="C148" s="10"/>
-      <c r="D148" s="10"/>
-      <c r="E148" s="10"/>
-      <c r="F148" s="10"/>
-      <c r="G148" s="10"/>
-      <c r="H148" s="10"/>
-      <c r="I148" s="10"/>
-      <c r="J148" s="10"/>
+      <c r="A148" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B148" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C148" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D148" s="22">
+        <v>698</v>
+      </c>
+      <c r="E148" s="22">
+        <v>147</v>
+      </c>
+      <c r="F148" s="22"/>
+      <c r="G148" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H148" s="9">
+        <v>7</v>
+      </c>
+      <c r="I148" s="9">
+        <v>7</v>
+      </c>
+      <c r="J148" s="22">
+        <v>30</v>
+      </c>
       <c r="K148" s="10"/>
       <c r="L148" s="10"/>
       <c r="M148" s="10"/>
@@ -7150,16 +7171,34 @@
       <c r="U148" s="10"/>
     </row>
     <row r="149" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A149" s="10"/>
-      <c r="B149" s="10"/>
-      <c r="C149" s="10"/>
-      <c r="D149" s="10"/>
-      <c r="E149" s="10"/>
-      <c r="F149" s="10"/>
-      <c r="G149" s="10"/>
-      <c r="H149" s="10"/>
-      <c r="I149" s="10"/>
-      <c r="J149" s="10"/>
+      <c r="A149" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C149" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D149" s="22">
+        <v>698</v>
+      </c>
+      <c r="E149" s="22">
+        <v>297</v>
+      </c>
+      <c r="F149" s="22"/>
+      <c r="G149" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H149" s="9">
+        <v>7</v>
+      </c>
+      <c r="I149" s="9">
+        <v>7</v>
+      </c>
+      <c r="J149" s="22">
+        <v>30</v>
+      </c>
       <c r="K149" s="10"/>
       <c r="L149" s="10"/>
       <c r="M149" s="10"/>
@@ -7173,16 +7212,34 @@
       <c r="U149" s="10"/>
     </row>
     <row r="150" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A150" s="10"/>
-      <c r="B150" s="10"/>
-      <c r="C150" s="10"/>
-      <c r="D150" s="10"/>
-      <c r="E150" s="10"/>
-      <c r="F150" s="10"/>
-      <c r="G150" s="10"/>
-      <c r="H150" s="10"/>
-      <c r="I150" s="10"/>
-      <c r="J150" s="10"/>
+      <c r="A150" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B150" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C150" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D150" s="22">
+        <v>698</v>
+      </c>
+      <c r="E150" s="22">
+        <v>347</v>
+      </c>
+      <c r="F150" s="22"/>
+      <c r="G150" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H150" s="9">
+        <v>7</v>
+      </c>
+      <c r="I150" s="9">
+        <v>7</v>
+      </c>
+      <c r="J150" s="22">
+        <v>30</v>
+      </c>
       <c r="K150" s="10"/>
       <c r="L150" s="10"/>
       <c r="M150" s="10"/>
@@ -7196,16 +7253,34 @@
       <c r="U150" s="10"/>
     </row>
     <row r="151" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A151" s="10"/>
-      <c r="B151" s="10"/>
-      <c r="C151" s="10"/>
-      <c r="D151" s="10"/>
-      <c r="E151" s="10"/>
-      <c r="F151" s="10"/>
-      <c r="G151" s="10"/>
-      <c r="H151" s="10"/>
-      <c r="I151" s="10"/>
-      <c r="J151" s="10"/>
+      <c r="A151" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B151" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C151" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D151" s="22">
+        <v>698</v>
+      </c>
+      <c r="E151" s="22">
+        <v>397</v>
+      </c>
+      <c r="F151" s="22"/>
+      <c r="G151" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H151" s="9">
+        <v>7</v>
+      </c>
+      <c r="I151" s="9">
+        <v>7</v>
+      </c>
+      <c r="J151" s="22">
+        <v>30</v>
+      </c>
       <c r="K151" s="10"/>
       <c r="L151" s="10"/>
       <c r="M151" s="10"/>
@@ -7219,16 +7294,34 @@
       <c r="U151" s="10"/>
     </row>
     <row r="152" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A152" s="10"/>
-      <c r="B152" s="10"/>
-      <c r="C152" s="10"/>
-      <c r="D152" s="10"/>
-      <c r="E152" s="10"/>
-      <c r="F152" s="10"/>
-      <c r="G152" s="10"/>
-      <c r="H152" s="10"/>
-      <c r="I152" s="10"/>
-      <c r="J152" s="10"/>
+      <c r="A152" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B152" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C152" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D152" s="22">
+        <v>698</v>
+      </c>
+      <c r="E152" s="22">
+        <v>447</v>
+      </c>
+      <c r="F152" s="22"/>
+      <c r="G152" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H152" s="9">
+        <v>7</v>
+      </c>
+      <c r="I152" s="9">
+        <v>7</v>
+      </c>
+      <c r="J152" s="22">
+        <v>30</v>
+      </c>
       <c r="K152" s="10"/>
       <c r="L152" s="10"/>
       <c r="M152" s="10"/>
@@ -7242,16 +7335,34 @@
       <c r="U152" s="10"/>
     </row>
     <row r="153" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A153" s="10"/>
-      <c r="B153" s="10"/>
-      <c r="C153" s="10"/>
-      <c r="D153" s="10"/>
-      <c r="E153" s="10"/>
-      <c r="F153" s="10"/>
-      <c r="G153" s="10"/>
-      <c r="H153" s="10"/>
-      <c r="I153" s="10"/>
-      <c r="J153" s="10"/>
+      <c r="A153" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C153" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D153" s="22">
+        <v>698</v>
+      </c>
+      <c r="E153" s="22">
+        <v>497</v>
+      </c>
+      <c r="F153" s="22"/>
+      <c r="G153" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H153" s="9">
+        <v>7</v>
+      </c>
+      <c r="I153" s="9">
+        <v>7</v>
+      </c>
+      <c r="J153" s="22">
+        <v>30</v>
+      </c>
       <c r="K153" s="10"/>
       <c r="L153" s="10"/>
       <c r="M153" s="10"/>
@@ -7265,16 +7376,34 @@
       <c r="U153" s="10"/>
     </row>
     <row r="154" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A154" s="10"/>
-      <c r="B154" s="10"/>
-      <c r="C154" s="10"/>
-      <c r="D154" s="10"/>
-      <c r="E154" s="10"/>
-      <c r="F154" s="10"/>
-      <c r="G154" s="10"/>
-      <c r="H154" s="10"/>
-      <c r="I154" s="10"/>
-      <c r="J154" s="10"/>
+      <c r="A154" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C154" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D154" s="22">
+        <v>698</v>
+      </c>
+      <c r="E154" s="22">
+        <v>597</v>
+      </c>
+      <c r="F154" s="22"/>
+      <c r="G154" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H154" s="9">
+        <v>7</v>
+      </c>
+      <c r="I154" s="9">
+        <v>7</v>
+      </c>
+      <c r="J154" s="22">
+        <v>30</v>
+      </c>
       <c r="K154" s="10"/>
       <c r="L154" s="10"/>
       <c r="M154" s="10"/>
@@ -7288,16 +7417,34 @@
       <c r="U154" s="10"/>
     </row>
     <row r="155" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A155" s="10"/>
-      <c r="B155" s="10"/>
-      <c r="C155" s="10"/>
-      <c r="D155" s="10"/>
-      <c r="E155" s="10"/>
-      <c r="F155" s="10"/>
-      <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
-      <c r="I155" s="10"/>
-      <c r="J155" s="10"/>
+      <c r="A155" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B155" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C155" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D155" s="22">
+        <v>798</v>
+      </c>
+      <c r="E155" s="22">
+        <v>147</v>
+      </c>
+      <c r="F155" s="22"/>
+      <c r="G155" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H155" s="9">
+        <v>7</v>
+      </c>
+      <c r="I155" s="9">
+        <v>7</v>
+      </c>
+      <c r="J155" s="22">
+        <v>30</v>
+      </c>
       <c r="K155" s="10"/>
       <c r="L155" s="10"/>
       <c r="M155" s="10"/>
@@ -7311,16 +7458,34 @@
       <c r="U155" s="10"/>
     </row>
     <row r="156" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A156" s="10"/>
-      <c r="B156" s="10"/>
-      <c r="C156" s="10"/>
-      <c r="D156" s="10"/>
-      <c r="E156" s="10"/>
-      <c r="F156" s="10"/>
-      <c r="G156" s="10"/>
-      <c r="H156" s="10"/>
-      <c r="I156" s="10"/>
-      <c r="J156" s="10"/>
+      <c r="A156" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B156" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C156" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D156" s="22">
+        <v>798</v>
+      </c>
+      <c r="E156" s="22">
+        <v>297</v>
+      </c>
+      <c r="F156" s="22"/>
+      <c r="G156" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H156" s="9">
+        <v>7</v>
+      </c>
+      <c r="I156" s="9">
+        <v>7</v>
+      </c>
+      <c r="J156" s="22">
+        <v>30</v>
+      </c>
       <c r="K156" s="10"/>
       <c r="L156" s="10"/>
       <c r="M156" s="10"/>
@@ -7334,16 +7499,34 @@
       <c r="U156" s="10"/>
     </row>
     <row r="157" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A157" s="10"/>
-      <c r="B157" s="10"/>
-      <c r="C157" s="10"/>
-      <c r="D157" s="10"/>
-      <c r="E157" s="10"/>
-      <c r="F157" s="10"/>
-      <c r="G157" s="10"/>
-      <c r="H157" s="10"/>
-      <c r="I157" s="10"/>
-      <c r="J157" s="10"/>
+      <c r="A157" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C157" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D157" s="22">
+        <v>798</v>
+      </c>
+      <c r="E157" s="22">
+        <v>347</v>
+      </c>
+      <c r="F157" s="22"/>
+      <c r="G157" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H157" s="9">
+        <v>7</v>
+      </c>
+      <c r="I157" s="9">
+        <v>7</v>
+      </c>
+      <c r="J157" s="22">
+        <v>30</v>
+      </c>
       <c r="K157" s="10"/>
       <c r="L157" s="10"/>
       <c r="M157" s="10"/>
@@ -7357,16 +7540,34 @@
       <c r="U157" s="10"/>
     </row>
     <row r="158" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A158" s="10"/>
-      <c r="B158" s="10"/>
-      <c r="C158" s="10"/>
-      <c r="D158" s="10"/>
-      <c r="E158" s="10"/>
-      <c r="F158" s="10"/>
-      <c r="G158" s="10"/>
-      <c r="H158" s="10"/>
-      <c r="I158" s="10"/>
-      <c r="J158" s="10"/>
+      <c r="A158" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B158" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C158" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D158" s="22">
+        <v>798</v>
+      </c>
+      <c r="E158" s="22">
+        <v>397</v>
+      </c>
+      <c r="F158" s="22"/>
+      <c r="G158" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H158" s="9">
+        <v>7</v>
+      </c>
+      <c r="I158" s="9">
+        <v>7</v>
+      </c>
+      <c r="J158" s="22">
+        <v>30</v>
+      </c>
       <c r="K158" s="10"/>
       <c r="L158" s="10"/>
       <c r="M158" s="10"/>
@@ -7380,16 +7581,34 @@
       <c r="U158" s="10"/>
     </row>
     <row r="159" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A159" s="10"/>
-      <c r="B159" s="10"/>
-      <c r="C159" s="10"/>
-      <c r="D159" s="10"/>
-      <c r="E159" s="10"/>
-      <c r="F159" s="10"/>
-      <c r="G159" s="10"/>
-      <c r="H159" s="10"/>
-      <c r="I159" s="10"/>
-      <c r="J159" s="10"/>
+      <c r="A159" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C159" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D159" s="22">
+        <v>798</v>
+      </c>
+      <c r="E159" s="22">
+        <v>447</v>
+      </c>
+      <c r="F159" s="22"/>
+      <c r="G159" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H159" s="9">
+        <v>7</v>
+      </c>
+      <c r="I159" s="9">
+        <v>7</v>
+      </c>
+      <c r="J159" s="22">
+        <v>30</v>
+      </c>
       <c r="K159" s="10"/>
       <c r="L159" s="10"/>
       <c r="M159" s="10"/>
@@ -7403,16 +7622,34 @@
       <c r="U159" s="10"/>
     </row>
     <row r="160" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A160" s="10"/>
-      <c r="B160" s="10"/>
-      <c r="C160" s="10"/>
-      <c r="D160" s="10"/>
-      <c r="E160" s="10"/>
-      <c r="F160" s="10"/>
-      <c r="G160" s="10"/>
-      <c r="H160" s="10"/>
-      <c r="I160" s="10"/>
-      <c r="J160" s="10"/>
+      <c r="A160" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D160" s="22">
+        <v>798</v>
+      </c>
+      <c r="E160" s="22">
+        <v>497</v>
+      </c>
+      <c r="F160" s="22"/>
+      <c r="G160" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H160" s="9">
+        <v>7</v>
+      </c>
+      <c r="I160" s="9">
+        <v>7</v>
+      </c>
+      <c r="J160" s="22">
+        <v>30</v>
+      </c>
       <c r="K160" s="10"/>
       <c r="L160" s="10"/>
       <c r="M160" s="10"/>
@@ -7426,16 +7663,34 @@
       <c r="U160" s="10"/>
     </row>
     <row r="161" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A161" s="10"/>
-      <c r="B161" s="10"/>
-      <c r="C161" s="10"/>
-      <c r="D161" s="10"/>
-      <c r="E161" s="10"/>
-      <c r="F161" s="10"/>
-      <c r="G161" s="10"/>
-      <c r="H161" s="10"/>
-      <c r="I161" s="10"/>
-      <c r="J161" s="10"/>
+      <c r="A161" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C161" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D161" s="22">
+        <v>798</v>
+      </c>
+      <c r="E161" s="22">
+        <v>597</v>
+      </c>
+      <c r="F161" s="22"/>
+      <c r="G161" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H161" s="9">
+        <v>7</v>
+      </c>
+      <c r="I161" s="9">
+        <v>7</v>
+      </c>
+      <c r="J161" s="22">
+        <v>30</v>
+      </c>
       <c r="K161" s="10"/>
       <c r="L161" s="10"/>
       <c r="M161" s="10"/>
@@ -7449,16 +7704,34 @@
       <c r="U161" s="10"/>
     </row>
     <row r="162" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A162" s="10"/>
-      <c r="B162" s="10"/>
-      <c r="C162" s="10"/>
-      <c r="D162" s="10"/>
-      <c r="E162" s="10"/>
-      <c r="F162" s="10"/>
-      <c r="G162" s="10"/>
-      <c r="H162" s="10"/>
-      <c r="I162" s="10"/>
-      <c r="J162" s="10"/>
+      <c r="A162" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D162" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E162" s="22">
+        <v>397</v>
+      </c>
+      <c r="F162" s="22"/>
+      <c r="G162" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H162" s="9">
+        <v>7</v>
+      </c>
+      <c r="I162" s="9">
+        <v>7</v>
+      </c>
+      <c r="J162" s="22">
+        <v>30</v>
+      </c>
       <c r="K162" s="10"/>
       <c r="L162" s="10"/>
       <c r="M162" s="10"/>
@@ -7472,16 +7745,34 @@
       <c r="U162" s="10"/>
     </row>
     <row r="163" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A163" s="10"/>
-      <c r="B163" s="10"/>
-      <c r="C163" s="10"/>
-      <c r="D163" s="10"/>
-      <c r="E163" s="10"/>
-      <c r="F163" s="10"/>
-      <c r="G163" s="10"/>
-      <c r="H163" s="10"/>
-      <c r="I163" s="10"/>
-      <c r="J163" s="10"/>
+      <c r="A163" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="D163" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E163" s="22">
+        <v>597</v>
+      </c>
+      <c r="F163" s="22"/>
+      <c r="G163" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="H163" s="9">
+        <v>7</v>
+      </c>
+      <c r="I163" s="9">
+        <v>7</v>
+      </c>
+      <c r="J163" s="22">
+        <v>30</v>
+      </c>
       <c r="K163" s="10"/>
       <c r="L163" s="10"/>
       <c r="M163" s="10"/>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="103">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -188,9 +188,6 @@
     <t>PUERTA</t>
   </si>
   <si>
-    <t>Puerta</t>
-  </si>
-  <si>
     <t>70_15</t>
   </si>
   <si>
@@ -276,6 +273,57 @@
   </si>
   <si>
     <t>cloe</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>blanco mate</t>
+  </si>
+  <si>
+    <t>color solido</t>
   </si>
 </sst>
 </file>
@@ -653,11 +701,11 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -671,20 +719,20 @@
       <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>75</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -717,12 +765,9 @@
       <c r="G2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="9">
-        <f t="shared" ref="H2:H127" si="0">I2*((100-J2)/100)</f>
-        <v>3.5</v>
-      </c>
+      <c r="H2" s="9"/>
       <c r="I2" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J2" s="9">
         <v>30</v>
@@ -769,12 +814,9 @@
       <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H3" s="9"/>
       <c r="I3" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J3" s="9">
         <v>30</v>
@@ -783,11 +825,11 @@
         <v>1</v>
       </c>
       <c r="L3" s="22">
-        <f t="shared" ref="L3:M3" si="1">D133</f>
+        <f t="shared" ref="L3:M3" si="0">D133</f>
         <v>698</v>
       </c>
       <c r="M3" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>297</v>
       </c>
       <c r="N3" s="10"/>
@@ -821,12 +863,9 @@
       <c r="G4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H4" s="9"/>
       <c r="I4" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J4" s="9">
         <v>30</v>
@@ -835,11 +874,11 @@
         <v>1</v>
       </c>
       <c r="L4" s="22">
-        <f t="shared" ref="L4:M4" si="2">D134</f>
+        <f t="shared" ref="L4:M4" si="1">D134</f>
         <v>698</v>
       </c>
       <c r="M4" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>347</v>
       </c>
       <c r="N4" s="10"/>
@@ -873,12 +912,9 @@
       <c r="G5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H5" s="9"/>
       <c r="I5" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J5" s="9">
         <v>30</v>
@@ -887,11 +923,11 @@
         <v>1</v>
       </c>
       <c r="L5" s="22">
-        <f t="shared" ref="L5:M5" si="3">D135</f>
+        <f t="shared" ref="L5:M5" si="2">D135</f>
         <v>698</v>
       </c>
       <c r="M5" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>397</v>
       </c>
       <c r="N5" s="10"/>
@@ -925,12 +961,9 @@
       <c r="G6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H6" s="9"/>
       <c r="I6" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
@@ -939,11 +972,11 @@
         <v>1</v>
       </c>
       <c r="L6" s="22">
-        <f t="shared" ref="L6:M6" si="4">D136</f>
+        <f t="shared" ref="L6:M6" si="3">D136</f>
         <v>698</v>
       </c>
       <c r="M6" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>447</v>
       </c>
       <c r="N6" s="10"/>
@@ -977,12 +1010,9 @@
       <c r="G7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H7" s="9"/>
       <c r="I7" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J7" s="9">
         <v>30</v>
@@ -991,11 +1021,11 @@
         <v>1</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" ref="L7:M7" si="5">D137</f>
+        <f t="shared" ref="L7:M7" si="4">D137</f>
         <v>698</v>
       </c>
       <c r="M7" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>497</v>
       </c>
       <c r="N7" s="10"/>
@@ -1029,12 +1059,9 @@
       <c r="G8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H8" s="9"/>
       <c r="I8" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J8" s="9">
         <v>30</v>
@@ -1043,11 +1070,11 @@
         <v>1</v>
       </c>
       <c r="L8" s="22">
-        <f t="shared" ref="L8:M8" si="6">D138</f>
+        <f t="shared" ref="L8:M8" si="5">D138</f>
         <v>698</v>
       </c>
       <c r="M8" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>597</v>
       </c>
       <c r="N8" s="10"/>
@@ -1081,12 +1108,9 @@
       <c r="G9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H9" s="9"/>
       <c r="I9" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J9" s="9">
         <v>30</v>
@@ -1127,12 +1151,9 @@
       <c r="G10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H10" s="9"/>
       <c r="I10" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J10" s="9">
         <v>30</v>
@@ -1173,12 +1194,9 @@
       <c r="G11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H11" s="9"/>
       <c r="I11" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J11" s="9">
         <v>30</v>
@@ -1219,12 +1237,9 @@
       <c r="G12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H12" s="9"/>
       <c r="I12" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J12" s="9">
         <v>30</v>
@@ -1265,12 +1280,9 @@
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H13" s="9"/>
       <c r="I13" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J13" s="9">
         <v>30</v>
@@ -1311,12 +1323,9 @@
       <c r="G14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H14" s="9"/>
       <c r="I14" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J14" s="9">
         <v>30</v>
@@ -1357,12 +1366,9 @@
       <c r="G15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H15" s="9"/>
       <c r="I15" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J15" s="9">
         <v>30</v>
@@ -1403,12 +1409,9 @@
       <c r="G16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H16" s="9"/>
       <c r="I16" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J16" s="9">
         <v>30</v>
@@ -1449,12 +1452,9 @@
       <c r="G17" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H17" s="9"/>
       <c r="I17" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J17" s="9">
         <v>30</v>
@@ -1495,12 +1495,9 @@
       <c r="G18" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H18" s="9"/>
       <c r="I18" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J18" s="9">
         <v>30</v>
@@ -1541,12 +1538,9 @@
       <c r="G19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H19" s="9"/>
       <c r="I19" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J19" s="9">
         <v>30</v>
@@ -1587,12 +1581,9 @@
       <c r="G20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H20" s="9"/>
       <c r="I20" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J20" s="9">
         <v>30</v>
@@ -1633,12 +1624,9 @@
       <c r="G21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J21" s="9">
         <v>30</v>
@@ -1679,12 +1667,9 @@
       <c r="G22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H22" s="9"/>
       <c r="I22" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J22" s="9">
         <v>30</v>
@@ -1725,12 +1710,9 @@
       <c r="G23" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" s="9">
         <v>30</v>
@@ -1771,12 +1753,9 @@
       <c r="G24" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H24" s="9"/>
       <c r="I24" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" s="9">
         <v>30</v>
@@ -1817,12 +1796,9 @@
       <c r="G25" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H25" s="9"/>
       <c r="I25" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J25" s="9">
         <v>30</v>
@@ -1863,12 +1839,9 @@
       <c r="G26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H26" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H26" s="9"/>
       <c r="I26" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J26" s="9">
         <v>30</v>
@@ -1909,12 +1882,9 @@
       <c r="G27" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H27" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H27" s="9"/>
       <c r="I27" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J27" s="9">
         <v>30</v>
@@ -1955,12 +1925,9 @@
       <c r="G28" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H28" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H28" s="9"/>
       <c r="I28" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J28" s="9">
         <v>30</v>
@@ -2001,12 +1968,9 @@
       <c r="G29" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H29" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J29" s="9">
         <v>30</v>
@@ -2047,12 +2011,9 @@
       <c r="G30" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H30" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H30" s="9"/>
       <c r="I30" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J30" s="9">
         <v>30</v>
@@ -2093,12 +2054,9 @@
       <c r="G31" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H31" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H31" s="9"/>
       <c r="I31" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2139,12 +2097,9 @@
       <c r="G32" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H32" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H32" s="9"/>
       <c r="I32" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J32" s="9">
         <v>30</v>
@@ -2185,12 +2140,9 @@
       <c r="G33" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H33" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H33" s="9"/>
       <c r="I33" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J33" s="9">
         <v>30</v>
@@ -2231,12 +2183,9 @@
       <c r="G34" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H34" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H34" s="9"/>
       <c r="I34" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J34" s="9">
         <v>30</v>
@@ -2277,12 +2226,9 @@
       <c r="G35" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H35" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H35" s="9"/>
       <c r="I35" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J35" s="9">
         <v>30</v>
@@ -2323,12 +2269,9 @@
       <c r="G36" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H36" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H36" s="9"/>
       <c r="I36" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J36" s="9">
         <v>30</v>
@@ -2369,12 +2312,9 @@
       <c r="G37" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H37" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H37" s="9"/>
       <c r="I37" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J37" s="9">
         <v>30</v>
@@ -2415,12 +2355,9 @@
       <c r="G38" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H38" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H38" s="9"/>
       <c r="I38" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J38" s="9">
         <v>30</v>
@@ -2461,12 +2398,9 @@
       <c r="G39" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H39" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H39" s="9"/>
       <c r="I39" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J39" s="9">
         <v>30</v>
@@ -2507,12 +2441,9 @@
       <c r="G40" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H40" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H40" s="9"/>
       <c r="I40" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J40" s="9">
         <v>30</v>
@@ -2553,12 +2484,9 @@
       <c r="G41" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H41" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H41" s="9"/>
       <c r="I41" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J41" s="9">
         <v>30</v>
@@ -2599,12 +2527,9 @@
       <c r="G42" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H42" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H42" s="9"/>
       <c r="I42" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J42" s="9">
         <v>30</v>
@@ -2645,12 +2570,9 @@
       <c r="G43" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H43" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H43" s="9"/>
       <c r="I43" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J43" s="9">
         <v>30</v>
@@ -2691,12 +2613,9 @@
       <c r="G44" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H44" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H44" s="9"/>
       <c r="I44" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J44" s="9">
         <v>30</v>
@@ -2737,12 +2656,9 @@
       <c r="G45" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H45" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H45" s="9"/>
       <c r="I45" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J45" s="9">
         <v>30</v>
@@ -2783,12 +2699,9 @@
       <c r="G46" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H46" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H46" s="9"/>
       <c r="I46" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J46" s="9">
         <v>30</v>
@@ -2829,12 +2742,9 @@
       <c r="G47" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H47" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H47" s="9"/>
       <c r="I47" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J47" s="9">
         <v>30</v>
@@ -2875,12 +2785,9 @@
       <c r="G48" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H48" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H48" s="9"/>
       <c r="I48" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J48" s="9">
         <v>30</v>
@@ -2921,12 +2828,9 @@
       <c r="G49" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H49" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H49" s="9"/>
       <c r="I49" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J49" s="9">
         <v>30</v>
@@ -2965,12 +2869,9 @@
       <c r="G50" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H50" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H50" s="9"/>
       <c r="I50" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J50" s="9">
         <v>30</v>
@@ -3007,12 +2908,9 @@
       <c r="G51" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H51" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H51" s="9"/>
       <c r="I51" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J51" s="9">
         <v>30</v>
@@ -3051,12 +2949,9 @@
       <c r="G52" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H52" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H52" s="9"/>
       <c r="I52" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J52" s="9">
         <v>30</v>
@@ -3097,12 +2992,9 @@
       <c r="G53" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H53" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H53" s="9"/>
       <c r="I53" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J53" s="9">
         <v>30</v>
@@ -3129,7 +3021,7 @@
         <v>45</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>35</v>
@@ -3143,12 +3035,9 @@
       <c r="G54" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H54" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H54" s="9"/>
       <c r="I54" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J54" s="9">
         <v>30</v>
@@ -3189,12 +3078,9 @@
       <c r="G55" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H55" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H55" s="9"/>
       <c r="I55" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J55" s="9">
         <v>30</v>
@@ -3235,12 +3121,9 @@
       <c r="G56" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H56" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H56" s="9"/>
       <c r="I56" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J56" s="9">
         <v>30</v>
@@ -3281,12 +3164,9 @@
       <c r="G57" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H57" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H57" s="9"/>
       <c r="I57" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J57" s="9">
         <v>30</v>
@@ -3327,12 +3207,9 @@
       <c r="G58" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H58" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H58" s="9"/>
       <c r="I58" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J58" s="9">
         <v>30</v>
@@ -3373,12 +3250,9 @@
       <c r="G59" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H59" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H59" s="9"/>
       <c r="I59" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J59" s="9">
         <v>30</v>
@@ -3419,12 +3293,9 @@
       <c r="G60" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H60" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H60" s="9"/>
       <c r="I60" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J60" s="9">
         <v>30</v>
@@ -3465,12 +3336,9 @@
       <c r="G61" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H61" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H61" s="9"/>
       <c r="I61" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J61" s="9">
         <v>30</v>
@@ -3511,12 +3379,9 @@
       <c r="G62" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H62" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H62" s="9"/>
       <c r="I62" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J62" s="9">
         <v>30</v>
@@ -3557,12 +3422,9 @@
       <c r="G63" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H63" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H63" s="9"/>
       <c r="I63" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J63" s="9">
         <v>30</v>
@@ -3603,12 +3465,9 @@
       <c r="G64" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H64" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H64" s="9"/>
       <c r="I64" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J64" s="9">
         <v>30</v>
@@ -3649,12 +3508,9 @@
       <c r="G65" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H65" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H65" s="9"/>
       <c r="I65" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J65" s="9">
         <v>30</v>
@@ -3695,12 +3551,9 @@
       <c r="G66" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H66" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H66" s="9"/>
       <c r="I66" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J66" s="9">
         <v>30</v>
@@ -3741,18 +3594,15 @@
       <c r="G67" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H67" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H67" s="9"/>
       <c r="I67" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J67" s="9">
         <v>30</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -3787,12 +3637,9 @@
       <c r="G68" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H68" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H68" s="9"/>
       <c r="I68" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J68" s="9">
         <v>30</v>
@@ -3833,12 +3680,9 @@
       <c r="G69" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H69" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H69" s="9"/>
       <c r="I69" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J69" s="9">
         <v>30</v>
@@ -3879,12 +3723,9 @@
       <c r="G70" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H70" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H70" s="9"/>
       <c r="I70" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J70" s="9">
         <v>30</v>
@@ -3925,12 +3766,9 @@
       <c r="G71" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H71" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H71" s="9"/>
       <c r="I71" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J71" s="9">
         <v>30</v>
@@ -3971,12 +3809,9 @@
       <c r="G72" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H72" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H72" s="9"/>
       <c r="I72" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J72" s="9">
         <v>30</v>
@@ -4017,12 +3852,9 @@
       <c r="G73" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H73" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H73" s="9"/>
       <c r="I73" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J73" s="9">
         <v>30</v>
@@ -4063,12 +3895,9 @@
       <c r="G74" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H74" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H74" s="9"/>
       <c r="I74" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J74" s="9">
         <v>30</v>
@@ -4109,12 +3938,9 @@
       <c r="G75" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H75" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H75" s="9"/>
       <c r="I75" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J75" s="9">
         <v>30</v>
@@ -4155,12 +3981,9 @@
       <c r="G76" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H76" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H76" s="9"/>
       <c r="I76" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J76" s="9">
         <v>30</v>
@@ -4201,12 +4024,9 @@
       <c r="G77" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H77" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H77" s="9"/>
       <c r="I77" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J77" s="9">
         <v>30</v>
@@ -4247,12 +4067,9 @@
       <c r="G78" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H78" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H78" s="9"/>
       <c r="I78" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J78" s="9">
         <v>30</v>
@@ -4293,12 +4110,9 @@
       <c r="G79" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H79" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H79" s="9"/>
       <c r="I79" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J79" s="9">
         <v>30</v>
@@ -4339,18 +4153,15 @@
       <c r="G80" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H80" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H80" s="9"/>
       <c r="I80" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J80" s="9">
         <v>30</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -4385,12 +4196,9 @@
       <c r="G81" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H81" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H81" s="9"/>
       <c r="I81" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J81" s="9">
         <v>30</v>
@@ -4431,12 +4239,9 @@
       <c r="G82" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H82" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H82" s="9"/>
       <c r="I82" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J82" s="9">
         <v>30</v>
@@ -4477,12 +4282,9 @@
       <c r="G83" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H83" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H83" s="9"/>
       <c r="I83" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J83" s="9">
         <v>30</v>
@@ -4523,12 +4325,9 @@
       <c r="G84" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H84" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H84" s="9"/>
       <c r="I84" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J84" s="9">
         <v>30</v>
@@ -4569,12 +4368,9 @@
       <c r="G85" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H85" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H85" s="9"/>
       <c r="I85" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J85" s="9">
         <v>30</v>
@@ -4615,12 +4411,9 @@
       <c r="G86" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H86" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H86" s="9"/>
       <c r="I86" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J86" s="9">
         <v>30</v>
@@ -4661,12 +4454,9 @@
       <c r="G87" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H87" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H87" s="9"/>
       <c r="I87" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J87" s="9">
         <v>30</v>
@@ -4707,12 +4497,9 @@
       <c r="G88" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H88" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H88" s="9"/>
       <c r="I88" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J88" s="9">
         <v>30</v>
@@ -4753,12 +4540,9 @@
       <c r="G89" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H89" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H89" s="9"/>
       <c r="I89" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J89" s="9">
         <v>30</v>
@@ -4799,12 +4583,9 @@
       <c r="G90" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H90" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H90" s="9"/>
       <c r="I90" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J90" s="9">
         <v>30</v>
@@ -4845,12 +4626,9 @@
       <c r="G91" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H91" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J91" s="9">
         <v>30</v>
@@ -4891,12 +4669,9 @@
       <c r="G92" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H92" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H92" s="9"/>
       <c r="I92" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J92" s="9">
         <v>30</v>
@@ -4937,12 +4712,9 @@
       <c r="G93" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H93" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J93" s="9">
         <v>30</v>
@@ -4983,12 +4755,9 @@
       <c r="G94" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H94" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H94" s="9"/>
       <c r="I94" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J94" s="9">
         <v>30</v>
@@ -5029,12 +4798,9 @@
       <c r="G95" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H95" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J95" s="9">
         <v>30</v>
@@ -5075,12 +4841,9 @@
       <c r="G96" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H96" s="9">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H96" s="9"/>
       <c r="I96" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J96" s="9">
         <v>30</v>
@@ -5121,12 +4884,9 @@
       <c r="G97" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H97" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H97" s="14"/>
       <c r="I97" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J97" s="9">
         <v>30</v>
@@ -5167,12 +4927,9 @@
       <c r="G98" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H98" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H98" s="14"/>
       <c r="I98" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J98" s="9">
         <v>30</v>
@@ -5213,12 +4970,9 @@
       <c r="G99" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H99" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H99" s="14"/>
       <c r="I99" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J99" s="9">
         <v>30</v>
@@ -5259,12 +5013,9 @@
       <c r="G100" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H100" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H100" s="14"/>
       <c r="I100" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J100" s="9">
         <v>30</v>
@@ -5305,12 +5056,9 @@
       <c r="G101" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H101" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H101" s="14"/>
       <c r="I101" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J101" s="9">
         <v>30</v>
@@ -5351,12 +5099,9 @@
       <c r="G102" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H102" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H102" s="14"/>
       <c r="I102" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J102" s="9">
         <v>30</v>
@@ -5397,12 +5142,9 @@
       <c r="G103" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H103" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H103" s="14"/>
       <c r="I103" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J103" s="9">
         <v>30</v>
@@ -5443,12 +5185,9 @@
       <c r="G104" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H104" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H104" s="14"/>
       <c r="I104" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J104" s="9">
         <v>30</v>
@@ -5489,12 +5228,9 @@
       <c r="G105" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H105" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H105" s="14"/>
       <c r="I105" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J105" s="9">
         <v>30</v>
@@ -5535,12 +5271,9 @@
       <c r="G106" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H106" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H106" s="14"/>
       <c r="I106" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J106" s="9">
         <v>30</v>
@@ -5581,12 +5314,9 @@
       <c r="G107" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H107" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H107" s="14"/>
       <c r="I107" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J107" s="9">
         <v>30</v>
@@ -5627,12 +5357,9 @@
       <c r="G108" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H108" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H108" s="14"/>
       <c r="I108" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J108" s="9">
         <v>30</v>
@@ -5673,12 +5400,9 @@
       <c r="G109" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H109" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H109" s="14"/>
       <c r="I109" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J109" s="9">
         <v>30</v>
@@ -5719,12 +5443,9 @@
       <c r="G110" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H110" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H110" s="14"/>
       <c r="I110" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J110" s="9">
         <v>30</v>
@@ -5765,12 +5486,9 @@
       <c r="G111" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H111" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H111" s="14"/>
       <c r="I111" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J111" s="9">
         <v>30</v>
@@ -5811,12 +5529,9 @@
       <c r="G112" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H112" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H112" s="14"/>
       <c r="I112" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J112" s="9">
         <v>30</v>
@@ -5857,12 +5572,9 @@
       <c r="G113" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H113" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H113" s="14"/>
       <c r="I113" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J113" s="9">
         <v>30</v>
@@ -5903,12 +5615,9 @@
       <c r="G114" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H114" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H114" s="14"/>
       <c r="I114" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J114" s="9">
         <v>30</v>
@@ -5949,12 +5658,9 @@
       <c r="G115" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H115" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H115" s="14"/>
       <c r="I115" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J115" s="9">
         <v>30</v>
@@ -5995,12 +5701,9 @@
       <c r="G116" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H116" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H116" s="14"/>
       <c r="I116" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J116" s="9">
         <v>30</v>
@@ -6041,12 +5744,9 @@
       <c r="G117" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H117" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H117" s="14"/>
       <c r="I117" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J117" s="9">
         <v>30</v>
@@ -6087,12 +5787,9 @@
       <c r="G118" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H118" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H118" s="14"/>
       <c r="I118" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J118" s="9">
         <v>30</v>
@@ -6133,12 +5830,9 @@
       <c r="G119" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H119" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H119" s="14"/>
       <c r="I119" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J119" s="18">
         <v>30</v>
@@ -6179,12 +5873,9 @@
       <c r="G120" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H120" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H120" s="14"/>
       <c r="I120" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J120" s="18">
         <v>30</v>
@@ -6225,12 +5916,9 @@
       <c r="G121" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H121" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H121" s="14"/>
       <c r="I121" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J121" s="18">
         <v>30</v>
@@ -6271,12 +5959,9 @@
       <c r="G122" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H122" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H122" s="14"/>
       <c r="I122" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J122" s="18">
         <v>30</v>
@@ -6317,12 +6002,9 @@
       <c r="G123" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H123" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H123" s="14"/>
       <c r="I123" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J123" s="18">
         <v>30</v>
@@ -6363,12 +6045,9 @@
       <c r="G124" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H124" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H124" s="14"/>
       <c r="I124" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J124" s="18">
         <v>30</v>
@@ -6409,12 +6088,9 @@
       <c r="G125" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H125" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H125" s="14"/>
       <c r="I125" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J125" s="18">
         <v>30</v>
@@ -6455,12 +6131,9 @@
       <c r="G126" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H126" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H126" s="14"/>
       <c r="I126" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J126" s="18">
         <v>30</v>
@@ -6501,12 +6174,9 @@
       <c r="G127" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H127" s="14">
-        <f t="shared" si="0"/>
-        <v>3.5</v>
-      </c>
+      <c r="H127" s="14"/>
       <c r="I127" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J127" s="18">
         <v>30</v>
@@ -6530,18 +6200,15 @@
         <v>55</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F128" s="22"/>
-      <c r="H128" s="9">
-        <f t="shared" ref="H128:H131" si="7">I128*((100-J128)/100)</f>
-        <v>4.99</v>
-      </c>
+      <c r="H128" s="9"/>
       <c r="I128" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J128" s="23">
         <v>0.2</v>
@@ -6553,17 +6220,15 @@
         <v>55</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F129" s="22"/>
-      <c r="H129" s="9">
-        <v>1</v>
-      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J129" s="23">
         <v>0.2</v>
@@ -6574,17 +6239,15 @@
         <v>55</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F130" s="22"/>
-      <c r="H130" s="9">
-        <v>1</v>
-      </c>
+      <c r="H130" s="9"/>
       <c r="I130" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J130" s="23"/>
       <c r="L130" s="25"/>
@@ -6594,18 +6257,15 @@
         <v>55</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F131" s="20"/>
-      <c r="H131" s="9">
-        <f t="shared" si="7"/>
-        <v>4.99</v>
-      </c>
+      <c r="H131" s="9"/>
       <c r="I131" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J131" s="23">
         <v>0.2</v>
@@ -6616,10 +6276,10 @@
         <v>56</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D132" s="20">
         <v>698</v>
@@ -6629,14 +6289,11 @@
       </c>
       <c r="F132" s="20"/>
       <c r="G132" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H132" s="9">
-        <f t="shared" ref="H132:H146" si="8">I132*((100-J132)/100)</f>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H132" s="9"/>
       <c r="I132" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J132" s="20">
         <v>30</v>
@@ -6647,10 +6304,10 @@
         <v>56</v>
       </c>
       <c r="B133" s="21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C133" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D133" s="20">
         <v>698</v>
@@ -6660,14 +6317,11 @@
       </c>
       <c r="F133" s="20"/>
       <c r="G133" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="H133" s="9"/>
+      <c r="I133" s="8" t="s">
         <v>86</v>
-      </c>
-      <c r="H133" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
-      <c r="I133" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="J133" s="20">
         <v>30</v>
@@ -6678,10 +6332,10 @@
         <v>56</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D134" s="20">
         <v>698</v>
@@ -6691,14 +6345,11 @@
       </c>
       <c r="F134" s="20"/>
       <c r="G134" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H134" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H134" s="9"/>
       <c r="I134" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J134" s="20">
         <v>30</v>
@@ -6709,10 +6360,10 @@
         <v>56</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D135" s="20">
         <v>698</v>
@@ -6722,14 +6373,11 @@
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H135" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H135" s="9"/>
       <c r="I135" s="8" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J135" s="20">
         <v>30</v>
@@ -6740,10 +6388,10 @@
         <v>56</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D136" s="20">
         <v>698</v>
@@ -6753,14 +6401,11 @@
       </c>
       <c r="F136" s="20"/>
       <c r="G136" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H136" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H136" s="9"/>
       <c r="I136" s="8" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="J136" s="20">
         <v>30</v>
@@ -6771,10 +6416,10 @@
         <v>56</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D137" s="20">
         <v>698</v>
@@ -6784,14 +6429,11 @@
       </c>
       <c r="F137" s="20"/>
       <c r="G137" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H137" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H137" s="9"/>
       <c r="I137" s="8" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="J137" s="20">
         <v>30</v>
@@ -6802,10 +6444,10 @@
         <v>56</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D138" s="20">
         <v>698</v>
@@ -6815,14 +6457,11 @@
       </c>
       <c r="F138" s="20"/>
       <c r="G138" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H138" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H138" s="9"/>
       <c r="I138" s="8" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="J138" s="20">
         <v>30</v>
@@ -6833,10 +6472,10 @@
         <v>56</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D139" s="20">
         <v>798</v>
@@ -6846,14 +6485,11 @@
       </c>
       <c r="F139" s="20"/>
       <c r="G139" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H139" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H139" s="9"/>
       <c r="I139" s="8" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="J139" s="20">
         <v>30</v>
@@ -6864,10 +6500,10 @@
         <v>56</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D140" s="20">
         <v>798</v>
@@ -6877,14 +6513,11 @@
       </c>
       <c r="F140" s="20"/>
       <c r="G140" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H140" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H140" s="9"/>
       <c r="I140" s="8" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J140" s="20">
         <v>30</v>
@@ -6895,10 +6528,10 @@
         <v>56</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D141" s="20">
         <v>798</v>
@@ -6908,14 +6541,11 @@
       </c>
       <c r="F141" s="20"/>
       <c r="G141" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H141" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H141" s="9"/>
       <c r="I141" s="8" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="J141" s="20">
         <v>30</v>
@@ -6926,10 +6556,10 @@
         <v>56</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D142" s="20">
         <v>798</v>
@@ -6939,14 +6569,11 @@
       </c>
       <c r="F142" s="20"/>
       <c r="G142" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H142" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H142" s="9"/>
       <c r="I142" s="8" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J142" s="20">
         <v>30</v>
@@ -6957,10 +6584,10 @@
         <v>56</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D143" s="20">
         <v>798</v>
@@ -6970,14 +6597,11 @@
       </c>
       <c r="F143" s="20"/>
       <c r="G143" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H143" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H143" s="9"/>
       <c r="I143" s="8" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="J143" s="20">
         <v>30</v>
@@ -6988,10 +6612,10 @@
         <v>56</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D144" s="20">
         <v>798</v>
@@ -7001,14 +6625,11 @@
       </c>
       <c r="F144" s="20"/>
       <c r="G144" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H144" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H144" s="9"/>
       <c r="I144" s="8" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="J144" s="20">
         <v>30</v>
@@ -7019,10 +6640,10 @@
         <v>56</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D145" s="20">
         <v>798</v>
@@ -7032,14 +6653,11 @@
       </c>
       <c r="F145" s="20"/>
       <c r="G145" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H145" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H145" s="9"/>
       <c r="I145" s="8" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J145" s="20">
         <v>30</v>
@@ -7050,10 +6668,10 @@
         <v>56</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D146" s="20">
         <v>1098</v>
@@ -7063,14 +6681,11 @@
       </c>
       <c r="F146" s="20"/>
       <c r="G146" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H146" s="9">
-        <f t="shared" si="8"/>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H146" s="9"/>
       <c r="I146" s="8" t="s">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="J146" s="20">
         <v>30</v>
@@ -7092,10 +6707,10 @@
         <v>56</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="D147" s="22">
         <v>1098</v>
@@ -7105,14 +6720,11 @@
       </c>
       <c r="F147" s="22"/>
       <c r="G147" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="H147" s="9">
-        <f t="shared" ref="H147" si="9">I147*((100-J147)/100)</f>
-        <v>3.5</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="H147" s="9"/>
       <c r="I147" s="8" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="J147" s="22">
         <v>30</v>
@@ -7134,10 +6746,10 @@
         <v>56</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C148" s="21" t="s">
         <v>57</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D148" s="22">
         <v>698</v>
@@ -7147,11 +6759,9 @@
       </c>
       <c r="F148" s="22"/>
       <c r="G148" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H148" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H148" s="9"/>
       <c r="I148" s="9">
         <v>7</v>
       </c>
@@ -7175,10 +6785,10 @@
         <v>56</v>
       </c>
       <c r="B149" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C149" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D149" s="22">
         <v>698</v>
@@ -7188,13 +6798,12 @@
       </c>
       <c r="F149" s="22"/>
       <c r="G149" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H149" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H149" s="9"/>
       <c r="I149" s="9">
-        <v>7</v>
+        <f>I148+1</f>
+        <v>8</v>
       </c>
       <c r="J149" s="22">
         <v>30</v>
@@ -7216,10 +6825,10 @@
         <v>56</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C150" s="21" t="s">
-        <v>57</v>
+        <v>59</v>
+      </c>
+      <c r="C150" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D150" s="22">
         <v>698</v>
@@ -7229,13 +6838,12 @@
       </c>
       <c r="F150" s="22"/>
       <c r="G150" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H150" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H150" s="9"/>
       <c r="I150" s="9">
-        <v>7</v>
+        <f t="shared" ref="I150:I163" si="6">I149+1</f>
+        <v>9</v>
       </c>
       <c r="J150" s="22">
         <v>30</v>
@@ -7257,10 +6865,10 @@
         <v>56</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C151" s="21" t="s">
-        <v>57</v>
+        <v>60</v>
+      </c>
+      <c r="C151" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D151" s="22">
         <v>698</v>
@@ -7270,13 +6878,12 @@
       </c>
       <c r="F151" s="22"/>
       <c r="G151" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H151" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H151" s="9"/>
       <c r="I151" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>10</v>
       </c>
       <c r="J151" s="22">
         <v>30</v>
@@ -7298,10 +6905,10 @@
         <v>56</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C152" s="21" t="s">
-        <v>57</v>
+        <v>61</v>
+      </c>
+      <c r="C152" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D152" s="22">
         <v>698</v>
@@ -7311,13 +6918,12 @@
       </c>
       <c r="F152" s="22"/>
       <c r="G152" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H152" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H152" s="9"/>
       <c r="I152" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>11</v>
       </c>
       <c r="J152" s="22">
         <v>30</v>
@@ -7339,10 +6945,10 @@
         <v>56</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C153" s="21" t="s">
-        <v>57</v>
+        <v>62</v>
+      </c>
+      <c r="C153" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D153" s="22">
         <v>698</v>
@@ -7352,13 +6958,12 @@
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H153" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H153" s="9"/>
       <c r="I153" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>12</v>
       </c>
       <c r="J153" s="22">
         <v>30</v>
@@ -7380,10 +6985,10 @@
         <v>56</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C154" s="21" t="s">
-        <v>57</v>
+        <v>63</v>
+      </c>
+      <c r="C154" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D154" s="22">
         <v>698</v>
@@ -7393,13 +6998,12 @@
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H154" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H154" s="9"/>
       <c r="I154" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>13</v>
       </c>
       <c r="J154" s="22">
         <v>30</v>
@@ -7421,10 +7025,10 @@
         <v>56</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C155" s="21" t="s">
-        <v>57</v>
+        <v>64</v>
+      </c>
+      <c r="C155" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D155" s="22">
         <v>798</v>
@@ -7434,13 +7038,12 @@
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H155" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H155" s="9"/>
       <c r="I155" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>14</v>
       </c>
       <c r="J155" s="22">
         <v>30</v>
@@ -7462,10 +7065,10 @@
         <v>56</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C156" s="21" t="s">
-        <v>57</v>
+        <v>65</v>
+      </c>
+      <c r="C156" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D156" s="22">
         <v>798</v>
@@ -7475,13 +7078,12 @@
       </c>
       <c r="F156" s="22"/>
       <c r="G156" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H156" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H156" s="9"/>
       <c r="I156" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>15</v>
       </c>
       <c r="J156" s="22">
         <v>30</v>
@@ -7503,10 +7105,10 @@
         <v>56</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C157" s="21" t="s">
-        <v>57</v>
+        <v>66</v>
+      </c>
+      <c r="C157" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D157" s="22">
         <v>798</v>
@@ -7516,13 +7118,12 @@
       </c>
       <c r="F157" s="22"/>
       <c r="G157" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H157" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H157" s="9"/>
       <c r="I157" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>16</v>
       </c>
       <c r="J157" s="22">
         <v>30</v>
@@ -7544,10 +7145,10 @@
         <v>56</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C158" s="21" t="s">
-        <v>57</v>
+        <v>67</v>
+      </c>
+      <c r="C158" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D158" s="22">
         <v>798</v>
@@ -7557,13 +7158,12 @@
       </c>
       <c r="F158" s="22"/>
       <c r="G158" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H158" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H158" s="9"/>
       <c r="I158" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>17</v>
       </c>
       <c r="J158" s="22">
         <v>30</v>
@@ -7585,10 +7185,10 @@
         <v>56</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C159" s="21" t="s">
-        <v>57</v>
+        <v>68</v>
+      </c>
+      <c r="C159" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D159" s="22">
         <v>798</v>
@@ -7598,13 +7198,12 @@
       </c>
       <c r="F159" s="22"/>
       <c r="G159" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H159" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H159" s="9"/>
       <c r="I159" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>18</v>
       </c>
       <c r="J159" s="22">
         <v>30</v>
@@ -7626,10 +7225,10 @@
         <v>56</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>57</v>
+        <v>69</v>
+      </c>
+      <c r="C160" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D160" s="22">
         <v>798</v>
@@ -7639,13 +7238,12 @@
       </c>
       <c r="F160" s="22"/>
       <c r="G160" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H160" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H160" s="9"/>
       <c r="I160" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>19</v>
       </c>
       <c r="J160" s="22">
         <v>30</v>
@@ -7667,10 +7265,10 @@
         <v>56</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="C161" s="21" t="s">
-        <v>57</v>
+        <v>70</v>
+      </c>
+      <c r="C161" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D161" s="22">
         <v>798</v>
@@ -7680,13 +7278,12 @@
       </c>
       <c r="F161" s="22"/>
       <c r="G161" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H161" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H161" s="9"/>
       <c r="I161" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>20</v>
       </c>
       <c r="J161" s="22">
         <v>30</v>
@@ -7708,10 +7305,10 @@
         <v>56</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C162" s="21" t="s">
-        <v>57</v>
+        <v>76</v>
+      </c>
+      <c r="C162" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D162" s="22">
         <v>1098</v>
@@ -7721,13 +7318,12 @@
       </c>
       <c r="F162" s="22"/>
       <c r="G162" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H162" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H162" s="9"/>
       <c r="I162" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>21</v>
       </c>
       <c r="J162" s="22">
         <v>30</v>
@@ -7749,10 +7345,10 @@
         <v>56</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>57</v>
+        <v>71</v>
+      </c>
+      <c r="C163" s="22" t="s">
+        <v>84</v>
       </c>
       <c r="D163" s="22">
         <v>1098</v>
@@ -7762,13 +7358,12 @@
       </c>
       <c r="F163" s="22"/>
       <c r="G163" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H163" s="9">
-        <v>7</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="H163" s="9"/>
       <c r="I163" s="9">
-        <v>7</v>
+        <f t="shared" si="6"/>
+        <v>22</v>
       </c>
       <c r="J163" s="22">
         <v>30</v>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="104">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -98,13 +98,7 @@
     <t>BAJOS ALMACENAJE altura 80</t>
   </si>
   <si>
-    <t>FREGDERO DE 70</t>
-  </si>
-  <si>
     <t>BAJOS_FREGADERO</t>
-  </si>
-  <si>
-    <t>FREGADEROS 80</t>
   </si>
   <si>
     <t>BAJO RINCON L</t>
@@ -324,6 +318,15 @@
   </si>
   <si>
     <t>color solido</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>FREGADERO Altura 70</t>
+  </si>
+  <si>
+    <t>FREGADERO Altura 80</t>
   </si>
 </sst>
 </file>
@@ -705,7 +708,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>3</v>
@@ -726,13 +729,13 @@
         <v>8</v>
       </c>
       <c r="K1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>72</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>74</v>
       </c>
       <c r="N1" s="5"/>
       <c r="O1" s="5"/>
@@ -767,7 +770,7 @@
       </c>
       <c r="H2" s="9"/>
       <c r="I2" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J2" s="9">
         <v>30</v>
@@ -816,7 +819,7 @@
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J3" s="9">
         <v>30</v>
@@ -865,7 +868,7 @@
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J4" s="9">
         <v>30</v>
@@ -914,7 +917,7 @@
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J5" s="9">
         <v>30</v>
@@ -963,7 +966,7 @@
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J6" s="9">
         <v>30</v>
@@ -1012,7 +1015,7 @@
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J7" s="9">
         <v>30</v>
@@ -1061,7 +1064,7 @@
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J8" s="9">
         <v>30</v>
@@ -1110,7 +1113,7 @@
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J9" s="9">
         <v>30</v>
@@ -1153,7 +1156,7 @@
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J10" s="9">
         <v>30</v>
@@ -1196,7 +1199,7 @@
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J11" s="9">
         <v>30</v>
@@ -1239,7 +1242,7 @@
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J12" s="9">
         <v>30</v>
@@ -1282,7 +1285,7 @@
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="9">
         <v>30</v>
@@ -1325,7 +1328,7 @@
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J14" s="9">
         <v>30</v>
@@ -1368,7 +1371,7 @@
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J15" s="9">
         <v>30</v>
@@ -1411,7 +1414,7 @@
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J16" s="9">
         <v>30</v>
@@ -1454,7 +1457,7 @@
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J17" s="9">
         <v>30</v>
@@ -1497,7 +1500,7 @@
       </c>
       <c r="H18" s="9"/>
       <c r="I18" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J18" s="9">
         <v>30</v>
@@ -1540,7 +1543,7 @@
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J19" s="9">
         <v>30</v>
@@ -1583,7 +1586,7 @@
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J20" s="9">
         <v>30</v>
@@ -1626,7 +1629,7 @@
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J21" s="9">
         <v>30</v>
@@ -1669,7 +1672,7 @@
       </c>
       <c r="H22" s="9"/>
       <c r="I22" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J22" s="9">
         <v>30</v>
@@ -1712,7 +1715,7 @@
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J23" s="9">
         <v>30</v>
@@ -1755,7 +1758,7 @@
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J24" s="9">
         <v>30</v>
@@ -1798,7 +1801,7 @@
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J25" s="9">
         <v>30</v>
@@ -1822,10 +1825,10 @@
         <v>9</v>
       </c>
       <c r="B26" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>12</v>
@@ -1841,7 +1844,7 @@
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J26" s="9">
         <v>30</v>
@@ -1865,10 +1868,10 @@
         <v>9</v>
       </c>
       <c r="B27" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>12</v>
@@ -1884,7 +1887,7 @@
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J27" s="9">
         <v>30</v>
@@ -1908,10 +1911,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>12</v>
@@ -1927,7 +1930,7 @@
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J28" s="9">
         <v>30</v>
@@ -1951,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>12</v>
@@ -1970,7 +1973,7 @@
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J29" s="9">
         <v>30</v>
@@ -1994,10 +1997,10 @@
         <v>9</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>12</v>
@@ -2013,7 +2016,7 @@
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J30" s="9">
         <v>30</v>
@@ -2037,10 +2040,10 @@
         <v>9</v>
       </c>
       <c r="B31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>12</v>
@@ -2056,7 +2059,7 @@
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J31" s="9">
         <v>30</v>
@@ -2080,10 +2083,10 @@
         <v>9</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>12</v>
@@ -2099,7 +2102,7 @@
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J32" s="9">
         <v>30</v>
@@ -2123,10 +2126,10 @@
         <v>9</v>
       </c>
       <c r="B33" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>12</v>
@@ -2142,7 +2145,7 @@
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J33" s="9">
         <v>30</v>
@@ -2166,10 +2169,10 @@
         <v>9</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>22</v>
@@ -2185,7 +2188,7 @@
       </c>
       <c r="H34" s="9"/>
       <c r="I34" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J34" s="9">
         <v>30</v>
@@ -2209,10 +2212,10 @@
         <v>9</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>22</v>
@@ -2228,7 +2231,7 @@
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J35" s="9">
         <v>30</v>
@@ -2252,10 +2255,10 @@
         <v>9</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>22</v>
@@ -2271,7 +2274,7 @@
       </c>
       <c r="H36" s="9"/>
       <c r="I36" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J36" s="9">
         <v>30</v>
@@ -2295,10 +2298,10 @@
         <v>9</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>22</v>
@@ -2314,7 +2317,7 @@
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J37" s="9">
         <v>30</v>
@@ -2338,10 +2341,10 @@
         <v>9</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D38" s="8" t="s">
         <v>22</v>
@@ -2357,7 +2360,7 @@
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J38" s="9">
         <v>30</v>
@@ -2381,10 +2384,10 @@
         <v>9</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>22</v>
@@ -2400,7 +2403,7 @@
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J39" s="9">
         <v>30</v>
@@ -2424,10 +2427,10 @@
         <v>9</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>22</v>
@@ -2443,7 +2446,7 @@
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J40" s="9">
         <v>30</v>
@@ -2467,10 +2470,10 @@
         <v>9</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>22</v>
@@ -2486,7 +2489,7 @@
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J41" s="9">
         <v>30</v>
@@ -2510,16 +2513,16 @@
         <v>9</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F42" s="8" t="s">
         <v>14</v>
@@ -2529,7 +2532,7 @@
       </c>
       <c r="H42" s="9"/>
       <c r="I42" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J42" s="9">
         <v>30</v>
@@ -2553,16 +2556,16 @@
         <v>9</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F43" s="8" t="s">
         <v>14</v>
@@ -2572,7 +2575,7 @@
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J43" s="9">
         <v>30</v>
@@ -2596,13 +2599,13 @@
         <v>9</v>
       </c>
       <c r="B44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>18</v>
@@ -2615,7 +2618,7 @@
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J44" s="9">
         <v>30</v>
@@ -2639,13 +2642,13 @@
         <v>9</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E45" s="8" t="s">
         <v>18</v>
@@ -2658,7 +2661,7 @@
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J45" s="9">
         <v>30</v>
@@ -2682,13 +2685,13 @@
         <v>9</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>18</v>
@@ -2701,7 +2704,7 @@
       </c>
       <c r="H46" s="9"/>
       <c r="I46" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J46" s="9">
         <v>30</v>
@@ -2725,13 +2728,13 @@
         <v>9</v>
       </c>
       <c r="B47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E47" s="8" t="s">
         <v>21</v>
@@ -2744,7 +2747,7 @@
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J47" s="9">
         <v>30</v>
@@ -2768,13 +2771,13 @@
         <v>9</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E48" s="8" t="s">
         <v>21</v>
@@ -2787,7 +2790,7 @@
       </c>
       <c r="H48" s="9"/>
       <c r="I48" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J48" s="9">
         <v>30</v>
@@ -2811,13 +2814,13 @@
         <v>9</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>21</v>
@@ -2830,7 +2833,7 @@
       </c>
       <c r="H49" s="9"/>
       <c r="I49" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J49" s="9">
         <v>30</v>
@@ -2854,10 +2857,10 @@
         <v>9</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8" t="s">
@@ -2871,7 +2874,7 @@
       </c>
       <c r="H50" s="9"/>
       <c r="I50" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J50" s="9">
         <v>30</v>
@@ -2893,10 +2896,10 @@
         <v>9</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8" t="s">
@@ -2910,7 +2913,7 @@
       </c>
       <c r="H51" s="9"/>
       <c r="I51" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J51" s="9">
         <v>30</v>
@@ -2932,10 +2935,10 @@
         <v>9</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>12</v>
@@ -2951,7 +2954,7 @@
       </c>
       <c r="H52" s="9"/>
       <c r="I52" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J52" s="9">
         <v>30</v>
@@ -2975,10 +2978,10 @@
         <v>9</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>22</v>
@@ -2994,7 +2997,7 @@
       </c>
       <c r="H53" s="9"/>
       <c r="I53" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J53" s="9">
         <v>30</v>
@@ -3018,13 +3021,13 @@
         <v>9</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>21</v>
@@ -3037,7 +3040,7 @@
       </c>
       <c r="H54" s="9"/>
       <c r="I54" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J54" s="9">
         <v>30</v>
@@ -3061,13 +3064,13 @@
         <v>9</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>21</v>
@@ -3080,7 +3083,7 @@
       </c>
       <c r="H55" s="9"/>
       <c r="I55" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J55" s="9">
         <v>30</v>
@@ -3104,13 +3107,13 @@
         <v>9</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E56" s="8" t="s">
         <v>21</v>
@@ -3123,7 +3126,7 @@
       </c>
       <c r="H56" s="9"/>
       <c r="I56" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J56" s="9">
         <v>30</v>
@@ -3147,10 +3150,10 @@
         <v>9</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>12</v>
@@ -3159,14 +3162,14 @@
         <v>16</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J57" s="9">
         <v>30</v>
@@ -3190,10 +3193,10 @@
         <v>9</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>12</v>
@@ -3202,14 +3205,14 @@
         <v>19</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H58" s="9"/>
       <c r="I58" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J58" s="9">
         <v>30</v>
@@ -3233,10 +3236,10 @@
         <v>9</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>12</v>
@@ -3245,14 +3248,14 @@
         <v>21</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J59" s="9">
         <v>30</v>
@@ -3276,10 +3279,10 @@
         <v>9</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>22</v>
@@ -3288,14 +3291,14 @@
         <v>16</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H60" s="9"/>
       <c r="I60" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J60" s="9">
         <v>30</v>
@@ -3319,10 +3322,10 @@
         <v>9</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>22</v>
@@ -3331,14 +3334,14 @@
         <v>19</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H61" s="9"/>
       <c r="I61" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J61" s="9">
         <v>30</v>
@@ -3362,10 +3365,10 @@
         <v>9</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>22</v>
@@ -3374,14 +3377,14 @@
         <v>21</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H62" s="9"/>
       <c r="I62" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J62" s="9">
         <v>30</v>
@@ -3405,10 +3408,10 @@
         <v>9</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>23</v>
@@ -3417,14 +3420,14 @@
         <v>16</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H63" s="9"/>
       <c r="I63" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J63" s="9">
         <v>30</v>
@@ -3448,10 +3451,10 @@
         <v>9</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>23</v>
@@ -3460,14 +3463,14 @@
         <v>19</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J64" s="9">
         <v>30</v>
@@ -3491,10 +3494,10 @@
         <v>9</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>23</v>
@@ -3503,14 +3506,14 @@
         <v>21</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>15</v>
       </c>
       <c r="H65" s="9"/>
       <c r="I65" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J65" s="9">
         <v>30</v>
@@ -3549,11 +3552,11 @@
         <v>14</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J66" s="9">
         <v>30</v>
@@ -3592,17 +3595,17 @@
         <v>14</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H67" s="9"/>
       <c r="I67" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J67" s="9">
         <v>30</v>
       </c>
       <c r="K67" s="22" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L67" s="10"/>
       <c r="M67" s="10"/>
@@ -3635,11 +3638,11 @@
         <v>14</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H68" s="9"/>
       <c r="I68" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J68" s="9">
         <v>30</v>
@@ -3678,11 +3681,11 @@
         <v>14</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H69" s="9"/>
       <c r="I69" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J69" s="9">
         <v>30</v>
@@ -3721,11 +3724,11 @@
         <v>14</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H70" s="9"/>
       <c r="I70" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J70" s="9">
         <v>30</v>
@@ -3764,11 +3767,11 @@
         <v>14</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H71" s="9"/>
       <c r="I71" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J71" s="9">
         <v>30</v>
@@ -3807,11 +3810,11 @@
         <v>14</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J72" s="9">
         <v>30</v>
@@ -3850,11 +3853,11 @@
         <v>14</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H73" s="9"/>
       <c r="I73" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J73" s="9">
         <v>30</v>
@@ -3893,11 +3896,11 @@
         <v>14</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H74" s="9"/>
       <c r="I74" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J74" s="9">
         <v>30</v>
@@ -3936,11 +3939,11 @@
         <v>14</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H75" s="9"/>
       <c r="I75" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J75" s="9">
         <v>30</v>
@@ -3979,11 +3982,11 @@
         <v>14</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J76" s="9">
         <v>30</v>
@@ -4022,11 +4025,11 @@
         <v>14</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J77" s="9">
         <v>30</v>
@@ -4065,11 +4068,11 @@
         <v>14</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H78" s="9"/>
       <c r="I78" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J78" s="9">
         <v>30</v>
@@ -4108,11 +4111,11 @@
         <v>14</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J79" s="9">
         <v>30</v>
@@ -4151,17 +4154,17 @@
         <v>14</v>
       </c>
       <c r="G80" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J80" s="9">
         <v>30</v>
       </c>
       <c r="K80" s="22" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L80" s="10"/>
       <c r="M80" s="10"/>
@@ -4194,11 +4197,11 @@
         <v>14</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J81" s="9">
         <v>30</v>
@@ -4237,11 +4240,11 @@
         <v>14</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H82" s="9"/>
       <c r="I82" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J82" s="9">
         <v>30</v>
@@ -4280,11 +4283,11 @@
         <v>14</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J83" s="9">
         <v>30</v>
@@ -4323,11 +4326,11 @@
         <v>14</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H84" s="9"/>
       <c r="I84" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J84" s="9">
         <v>30</v>
@@ -4366,11 +4369,11 @@
         <v>14</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H85" s="9"/>
       <c r="I85" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J85" s="9">
         <v>30</v>
@@ -4409,11 +4412,11 @@
         <v>14</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J86" s="9">
         <v>30</v>
@@ -4452,11 +4455,11 @@
         <v>14</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H87" s="9"/>
       <c r="I87" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J87" s="9">
         <v>30</v>
@@ -4495,11 +4498,11 @@
         <v>14</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H88" s="9"/>
       <c r="I88" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J88" s="9">
         <v>30</v>
@@ -4538,11 +4541,11 @@
         <v>14</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H89" s="9"/>
       <c r="I89" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J89" s="9">
         <v>30</v>
@@ -4566,10 +4569,10 @@
         <v>9</v>
       </c>
       <c r="B90" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C90" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>12</v>
@@ -4581,11 +4584,11 @@
         <v>14</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H90" s="9"/>
       <c r="I90" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J90" s="9">
         <v>30</v>
@@ -4609,10 +4612,10 @@
         <v>9</v>
       </c>
       <c r="B91" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C91" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>12</v>
@@ -4624,11 +4627,11 @@
         <v>14</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H91" s="9"/>
       <c r="I91" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J91" s="9">
         <v>30</v>
@@ -4652,10 +4655,10 @@
         <v>9</v>
       </c>
       <c r="B92" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C92" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>12</v>
@@ -4667,11 +4670,11 @@
         <v>14</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H92" s="9"/>
       <c r="I92" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J92" s="9">
         <v>30</v>
@@ -4695,10 +4698,10 @@
         <v>9</v>
       </c>
       <c r="B93" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>12</v>
@@ -4710,11 +4713,11 @@
         <v>14</v>
       </c>
       <c r="G93" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H93" s="9"/>
       <c r="I93" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J93" s="9">
         <v>30</v>
@@ -4738,10 +4741,10 @@
         <v>9</v>
       </c>
       <c r="B94" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C94" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>12</v>
@@ -4753,11 +4756,11 @@
         <v>14</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H94" s="9"/>
       <c r="I94" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J94" s="9">
         <v>30</v>
@@ -4781,10 +4784,10 @@
         <v>9</v>
       </c>
       <c r="B95" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C95" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>12</v>
@@ -4796,11 +4799,11 @@
         <v>14</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H95" s="9"/>
       <c r="I95" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J95" s="9">
         <v>30</v>
@@ -4824,10 +4827,10 @@
         <v>9</v>
       </c>
       <c r="B96" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C96" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C96" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>12</v>
@@ -4839,11 +4842,11 @@
         <v>14</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J96" s="9">
         <v>30</v>
@@ -4867,10 +4870,10 @@
         <v>9</v>
       </c>
       <c r="B97" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="C97" s="11" t="s">
-        <v>28</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>12</v>
@@ -4882,11 +4885,11 @@
         <v>14</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H97" s="14"/>
       <c r="I97" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J97" s="9">
         <v>30</v>
@@ -4910,10 +4913,10 @@
         <v>9</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>22</v>
@@ -4925,11 +4928,11 @@
         <v>14</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H98" s="14"/>
       <c r="I98" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J98" s="9">
         <v>30</v>
@@ -4953,10 +4956,10 @@
         <v>9</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>22</v>
@@ -4968,11 +4971,11 @@
         <v>14</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H99" s="14"/>
       <c r="I99" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J99" s="9">
         <v>30</v>
@@ -4996,10 +4999,10 @@
         <v>9</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C100" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>22</v>
@@ -5011,11 +5014,11 @@
         <v>14</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H100" s="14"/>
       <c r="I100" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J100" s="9">
         <v>30</v>
@@ -5039,10 +5042,10 @@
         <v>9</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C101" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>22</v>
@@ -5054,11 +5057,11 @@
         <v>14</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H101" s="14"/>
       <c r="I101" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J101" s="9">
         <v>30</v>
@@ -5082,10 +5085,10 @@
         <v>9</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>22</v>
@@ -5097,11 +5100,11 @@
         <v>14</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H102" s="14"/>
       <c r="I102" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J102" s="9">
         <v>30</v>
@@ -5125,10 +5128,10 @@
         <v>9</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C103" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>22</v>
@@ -5140,11 +5143,11 @@
         <v>14</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H103" s="14"/>
       <c r="I103" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J103" s="9">
         <v>30</v>
@@ -5168,10 +5171,10 @@
         <v>9</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>22</v>
@@ -5183,11 +5186,11 @@
         <v>14</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H104" s="14"/>
       <c r="I104" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J104" s="9">
         <v>30</v>
@@ -5211,10 +5214,10 @@
         <v>9</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>29</v>
+        <v>103</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>22</v>
@@ -5226,11 +5229,11 @@
         <v>14</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H105" s="14"/>
       <c r="I105" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J105" s="9">
         <v>30</v>
@@ -5254,26 +5257,26 @@
         <v>9</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C106" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>12</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G106" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H106" s="14"/>
       <c r="I106" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J106" s="9">
         <v>30</v>
@@ -5297,26 +5300,26 @@
         <v>9</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C107" s="11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>22</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G107" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H107" s="14"/>
       <c r="I107" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J107" s="9">
         <v>30</v>
@@ -5340,13 +5343,13 @@
         <v>9</v>
       </c>
       <c r="B108" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D108" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>18</v>
@@ -5355,11 +5358,11 @@
         <v>14</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H108" s="14"/>
       <c r="I108" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J108" s="9">
         <v>30</v>
@@ -5383,13 +5386,13 @@
         <v>9</v>
       </c>
       <c r="B109" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E109" s="8" t="s">
         <v>18</v>
@@ -5398,11 +5401,11 @@
         <v>14</v>
       </c>
       <c r="G109" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H109" s="14"/>
       <c r="I109" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J109" s="9">
         <v>30</v>
@@ -5426,13 +5429,13 @@
         <v>9</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E110" s="8" t="s">
         <v>18</v>
@@ -5441,11 +5444,11 @@
         <v>14</v>
       </c>
       <c r="G110" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H110" s="14"/>
       <c r="I110" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J110" s="9">
         <v>30</v>
@@ -5469,13 +5472,13 @@
         <v>9</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D111" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D111" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="E111" s="8" t="s">
         <v>21</v>
@@ -5484,11 +5487,11 @@
         <v>14</v>
       </c>
       <c r="G111" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H111" s="14"/>
       <c r="I111" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J111" s="9">
         <v>30</v>
@@ -5512,13 +5515,13 @@
         <v>9</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E112" s="8" t="s">
         <v>21</v>
@@ -5527,11 +5530,11 @@
         <v>14</v>
       </c>
       <c r="G112" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H112" s="14"/>
       <c r="I112" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J112" s="9">
         <v>30</v>
@@ -5555,13 +5558,13 @@
         <v>9</v>
       </c>
       <c r="B113" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E113" s="8" t="s">
         <v>21</v>
@@ -5570,11 +5573,11 @@
         <v>14</v>
       </c>
       <c r="G113" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H113" s="14"/>
       <c r="I113" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J113" s="9">
         <v>30</v>
@@ -5598,10 +5601,10 @@
         <v>9</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D114" s="8" t="s">
         <v>12</v>
@@ -5613,11 +5616,11 @@
         <v>14</v>
       </c>
       <c r="G114" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H114" s="14"/>
       <c r="I114" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J114" s="9">
         <v>30</v>
@@ -5641,10 +5644,10 @@
         <v>9</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D115" s="8" t="s">
         <v>22</v>
@@ -5656,11 +5659,11 @@
         <v>14</v>
       </c>
       <c r="G115" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H115" s="14"/>
       <c r="I115" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J115" s="9">
         <v>30</v>
@@ -5684,13 +5687,13 @@
         <v>9</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C116" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E116" s="8" t="s">
         <v>21</v>
@@ -5699,11 +5702,11 @@
         <v>14</v>
       </c>
       <c r="G116" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H116" s="14"/>
       <c r="I116" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J116" s="9">
         <v>30</v>
@@ -5727,13 +5730,13 @@
         <v>9</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E117" s="8" t="s">
         <v>21</v>
@@ -5742,11 +5745,11 @@
         <v>14</v>
       </c>
       <c r="G117" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H117" s="14"/>
       <c r="I117" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J117" s="9">
         <v>30</v>
@@ -5770,13 +5773,13 @@
         <v>9</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C118" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E118" s="8" t="s">
         <v>21</v>
@@ -5785,11 +5788,11 @@
         <v>14</v>
       </c>
       <c r="G118" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H118" s="14"/>
       <c r="I118" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J118" s="9">
         <v>30</v>
@@ -5813,10 +5816,10 @@
         <v>9</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D119" s="16" t="s">
         <v>12</v>
@@ -5825,14 +5828,14 @@
         <v>16</v>
       </c>
       <c r="F119" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G119" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H119" s="14"/>
       <c r="I119" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J119" s="18">
         <v>30</v>
@@ -5856,10 +5859,10 @@
         <v>9</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D120" s="16" t="s">
         <v>12</v>
@@ -5868,14 +5871,14 @@
         <v>19</v>
       </c>
       <c r="F120" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G120" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H120" s="14"/>
       <c r="I120" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J120" s="18">
         <v>30</v>
@@ -5899,10 +5902,10 @@
         <v>9</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D121" s="16" t="s">
         <v>12</v>
@@ -5911,14 +5914,14 @@
         <v>21</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G121" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H121" s="14"/>
       <c r="I121" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J121" s="18">
         <v>30</v>
@@ -5942,10 +5945,10 @@
         <v>9</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D122" s="16" t="s">
         <v>22</v>
@@ -5954,14 +5957,14 @@
         <v>16</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G122" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H122" s="14"/>
       <c r="I122" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J122" s="18">
         <v>30</v>
@@ -5985,10 +5988,10 @@
         <v>9</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D123" s="16" t="s">
         <v>22</v>
@@ -5997,14 +6000,14 @@
         <v>19</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G123" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H123" s="14"/>
       <c r="I123" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J123" s="18">
         <v>30</v>
@@ -6028,10 +6031,10 @@
         <v>9</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D124" s="16" t="s">
         <v>22</v>
@@ -6040,14 +6043,14 @@
         <v>21</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G124" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H124" s="14"/>
       <c r="I124" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J124" s="18">
         <v>30</v>
@@ -6071,10 +6074,10 @@
         <v>9</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D125" s="16" t="s">
         <v>23</v>
@@ -6083,14 +6086,14 @@
         <v>16</v>
       </c>
       <c r="F125" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G125" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H125" s="14"/>
       <c r="I125" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J125" s="18">
         <v>30</v>
@@ -6114,10 +6117,10 @@
         <v>9</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D126" s="16" t="s">
         <v>23</v>
@@ -6126,14 +6129,14 @@
         <v>19</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G126" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H126" s="14"/>
       <c r="I126" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J126" s="18">
         <v>30</v>
@@ -6157,10 +6160,10 @@
         <v>9</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D127" s="16" t="s">
         <v>23</v>
@@ -6169,14 +6172,14 @@
         <v>21</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G127" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H127" s="14"/>
       <c r="I127" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J127" s="18">
         <v>30</v>
@@ -6197,18 +6200,18 @@
     </row>
     <row r="128" spans="1:21" ht="15.75" customHeight="1">
       <c r="A128" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F128" s="22"/>
       <c r="H128" s="9"/>
       <c r="I128" s="8" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="J128" s="23">
         <v>0.2</v>
@@ -6217,18 +6220,18 @@
     </row>
     <row r="129" spans="1:12" ht="15.75" customHeight="1">
       <c r="A129" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F129" s="22"/>
       <c r="H129" s="9"/>
       <c r="I129" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J129" s="23">
         <v>0.2</v>
@@ -6236,36 +6239,36 @@
     </row>
     <row r="130" spans="1:12" ht="15.75" customHeight="1">
       <c r="A130" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F130" s="22"/>
       <c r="H130" s="9"/>
       <c r="I130" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J130" s="23"/>
       <c r="L130" s="25"/>
     </row>
     <row r="131" spans="1:12" ht="15.75" customHeight="1">
       <c r="A131" s="24" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F131" s="20"/>
       <c r="H131" s="9"/>
       <c r="I131" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J131" s="23">
         <v>0.2</v>
@@ -6273,13 +6276,13 @@
     </row>
     <row r="132" spans="1:12" ht="15.75" customHeight="1">
       <c r="A132" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B132" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C132" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D132" s="20">
         <v>698</v>
@@ -6289,11 +6292,11 @@
       </c>
       <c r="F132" s="20"/>
       <c r="G132" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H132" s="9"/>
       <c r="I132" s="8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J132" s="20">
         <v>30</v>
@@ -6301,13 +6304,13 @@
     </row>
     <row r="133" spans="1:12" ht="15.75" customHeight="1">
       <c r="A133" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B133" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B133" s="21" t="s">
-        <v>58</v>
-      </c>
       <c r="C133" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D133" s="20">
         <v>698</v>
@@ -6317,11 +6320,11 @@
       </c>
       <c r="F133" s="20"/>
       <c r="G133" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H133" s="9"/>
       <c r="I133" s="8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J133" s="20">
         <v>30</v>
@@ -6329,13 +6332,13 @@
     </row>
     <row r="134" spans="1:12" ht="15.75" customHeight="1">
       <c r="A134" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B134" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C134" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D134" s="20">
         <v>698</v>
@@ -6345,11 +6348,11 @@
       </c>
       <c r="F134" s="20"/>
       <c r="G134" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H134" s="9"/>
       <c r="I134" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J134" s="20">
         <v>30</v>
@@ -6357,13 +6360,13 @@
     </row>
     <row r="135" spans="1:12" ht="15.75" customHeight="1">
       <c r="A135" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B135" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C135" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D135" s="20">
         <v>698</v>
@@ -6373,11 +6376,11 @@
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H135" s="9"/>
       <c r="I135" s="8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J135" s="20">
         <v>30</v>
@@ -6385,13 +6388,13 @@
     </row>
     <row r="136" spans="1:12" ht="15.75" customHeight="1">
       <c r="A136" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B136" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C136" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D136" s="20">
         <v>698</v>
@@ -6401,11 +6404,11 @@
       </c>
       <c r="F136" s="20"/>
       <c r="G136" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H136" s="9"/>
       <c r="I136" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J136" s="20">
         <v>30</v>
@@ -6413,13 +6416,13 @@
     </row>
     <row r="137" spans="1:12" ht="15.75" customHeight="1">
       <c r="A137" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B137" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C137" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D137" s="20">
         <v>698</v>
@@ -6429,11 +6432,11 @@
       </c>
       <c r="F137" s="20"/>
       <c r="G137" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H137" s="9"/>
       <c r="I137" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J137" s="20">
         <v>30</v>
@@ -6441,13 +6444,13 @@
     </row>
     <row r="138" spans="1:12" ht="15.75" customHeight="1">
       <c r="A138" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B138" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C138" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D138" s="20">
         <v>698</v>
@@ -6457,11 +6460,11 @@
       </c>
       <c r="F138" s="20"/>
       <c r="G138" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H138" s="9"/>
       <c r="I138" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J138" s="20">
         <v>30</v>
@@ -6469,13 +6472,13 @@
     </row>
     <row r="139" spans="1:12" ht="15.75" customHeight="1">
       <c r="A139" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B139" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C139" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D139" s="20">
         <v>798</v>
@@ -6485,11 +6488,11 @@
       </c>
       <c r="F139" s="20"/>
       <c r="G139" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H139" s="9"/>
       <c r="I139" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J139" s="20">
         <v>30</v>
@@ -6497,13 +6500,13 @@
     </row>
     <row r="140" spans="1:12" ht="15.75" customHeight="1">
       <c r="A140" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B140" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C140" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D140" s="20">
         <v>798</v>
@@ -6513,11 +6516,11 @@
       </c>
       <c r="F140" s="20"/>
       <c r="G140" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H140" s="9"/>
       <c r="I140" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="J140" s="20">
         <v>30</v>
@@ -6525,13 +6528,13 @@
     </row>
     <row r="141" spans="1:12" ht="15.75" customHeight="1">
       <c r="A141" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B141" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C141" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D141" s="20">
         <v>798</v>
@@ -6541,11 +6544,11 @@
       </c>
       <c r="F141" s="20"/>
       <c r="G141" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H141" s="9"/>
       <c r="I141" s="8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J141" s="20">
         <v>30</v>
@@ -6553,13 +6556,13 @@
     </row>
     <row r="142" spans="1:12" ht="15.75" customHeight="1">
       <c r="A142" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B142" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C142" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D142" s="20">
         <v>798</v>
@@ -6569,11 +6572,11 @@
       </c>
       <c r="F142" s="20"/>
       <c r="G142" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H142" s="9"/>
       <c r="I142" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J142" s="20">
         <v>30</v>
@@ -6581,13 +6584,13 @@
     </row>
     <row r="143" spans="1:12" ht="15.75" customHeight="1">
       <c r="A143" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B143" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C143" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D143" s="20">
         <v>798</v>
@@ -6597,11 +6600,11 @@
       </c>
       <c r="F143" s="20"/>
       <c r="G143" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H143" s="9"/>
       <c r="I143" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J143" s="20">
         <v>30</v>
@@ -6609,13 +6612,13 @@
     </row>
     <row r="144" spans="1:12" ht="15.75" customHeight="1">
       <c r="A144" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B144" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C144" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D144" s="20">
         <v>798</v>
@@ -6625,11 +6628,11 @@
       </c>
       <c r="F144" s="20"/>
       <c r="G144" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H144" s="9"/>
       <c r="I144" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J144" s="20">
         <v>30</v>
@@ -6637,13 +6640,13 @@
     </row>
     <row r="145" spans="1:21" ht="15.75" customHeight="1">
       <c r="A145" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B145" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C145" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D145" s="20">
         <v>798</v>
@@ -6653,11 +6656,11 @@
       </c>
       <c r="F145" s="20"/>
       <c r="G145" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H145" s="9"/>
       <c r="I145" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J145" s="20">
         <v>30</v>
@@ -6665,13 +6668,13 @@
     </row>
     <row r="146" spans="1:21" ht="15.75" customHeight="1">
       <c r="A146" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B146" s="21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C146" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D146" s="20">
         <v>1098</v>
@@ -6681,11 +6684,11 @@
       </c>
       <c r="F146" s="20"/>
       <c r="G146" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H146" s="9"/>
       <c r="I146" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J146" s="20">
         <v>30</v>
@@ -6704,13 +6707,13 @@
     </row>
     <row r="147" spans="1:21" ht="15.75" customHeight="1">
       <c r="A147" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B147" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C147" s="21" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D147" s="22">
         <v>1098</v>
@@ -6720,11 +6723,11 @@
       </c>
       <c r="F147" s="22"/>
       <c r="G147" s="21" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H147" s="9"/>
       <c r="I147" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J147" s="22">
         <v>30</v>
@@ -6743,13 +6746,13 @@
     </row>
     <row r="148" spans="1:21" ht="15.75" customHeight="1">
       <c r="A148" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B148" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C148" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D148" s="22">
         <v>698</v>
@@ -6759,7 +6762,7 @@
       </c>
       <c r="F148" s="22"/>
       <c r="G148" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H148" s="9"/>
       <c r="I148" s="9">
@@ -6782,13 +6785,13 @@
     </row>
     <row r="149" spans="1:21" ht="15.75" customHeight="1">
       <c r="A149" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B149" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B149" s="21" t="s">
-        <v>58</v>
-      </c>
       <c r="C149" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D149" s="22">
         <v>698</v>
@@ -6798,7 +6801,7 @@
       </c>
       <c r="F149" s="22"/>
       <c r="G149" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H149" s="9"/>
       <c r="I149" s="9">
@@ -6822,13 +6825,13 @@
     </row>
     <row r="150" spans="1:21" ht="15.75" customHeight="1">
       <c r="A150" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B150" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C150" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D150" s="22">
         <v>698</v>
@@ -6838,7 +6841,7 @@
       </c>
       <c r="F150" s="22"/>
       <c r="G150" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H150" s="9"/>
       <c r="I150" s="9">
@@ -6862,13 +6865,13 @@
     </row>
     <row r="151" spans="1:21" ht="15.75" customHeight="1">
       <c r="A151" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B151" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C151" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D151" s="22">
         <v>698</v>
@@ -6878,7 +6881,7 @@
       </c>
       <c r="F151" s="22"/>
       <c r="G151" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H151" s="9"/>
       <c r="I151" s="9">
@@ -6902,13 +6905,13 @@
     </row>
     <row r="152" spans="1:21" ht="15.75" customHeight="1">
       <c r="A152" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B152" s="21" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C152" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D152" s="22">
         <v>698</v>
@@ -6918,7 +6921,7 @@
       </c>
       <c r="F152" s="22"/>
       <c r="G152" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H152" s="9"/>
       <c r="I152" s="9">
@@ -6942,13 +6945,13 @@
     </row>
     <row r="153" spans="1:21" ht="15.75" customHeight="1">
       <c r="A153" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B153" s="21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C153" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D153" s="22">
         <v>698</v>
@@ -6958,7 +6961,7 @@
       </c>
       <c r="F153" s="22"/>
       <c r="G153" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H153" s="9"/>
       <c r="I153" s="9">
@@ -6982,13 +6985,13 @@
     </row>
     <row r="154" spans="1:21" ht="15.75" customHeight="1">
       <c r="A154" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B154" s="21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C154" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D154" s="22">
         <v>698</v>
@@ -6998,7 +7001,7 @@
       </c>
       <c r="F154" s="22"/>
       <c r="G154" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H154" s="9"/>
       <c r="I154" s="9">
@@ -7022,13 +7025,13 @@
     </row>
     <row r="155" spans="1:21" ht="15.75" customHeight="1">
       <c r="A155" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B155" s="21" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C155" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D155" s="22">
         <v>798</v>
@@ -7038,7 +7041,7 @@
       </c>
       <c r="F155" s="22"/>
       <c r="G155" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H155" s="9"/>
       <c r="I155" s="9">
@@ -7062,13 +7065,13 @@
     </row>
     <row r="156" spans="1:21" ht="15.75" customHeight="1">
       <c r="A156" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B156" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C156" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D156" s="22">
         <v>798</v>
@@ -7078,7 +7081,7 @@
       </c>
       <c r="F156" s="22"/>
       <c r="G156" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H156" s="9"/>
       <c r="I156" s="9">
@@ -7102,13 +7105,13 @@
     </row>
     <row r="157" spans="1:21" ht="15.75" customHeight="1">
       <c r="A157" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B157" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C157" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D157" s="22">
         <v>798</v>
@@ -7118,7 +7121,7 @@
       </c>
       <c r="F157" s="22"/>
       <c r="G157" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H157" s="9"/>
       <c r="I157" s="9">
@@ -7142,13 +7145,13 @@
     </row>
     <row r="158" spans="1:21" ht="15.75" customHeight="1">
       <c r="A158" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B158" s="21" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C158" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D158" s="22">
         <v>798</v>
@@ -7158,7 +7161,7 @@
       </c>
       <c r="F158" s="22"/>
       <c r="G158" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H158" s="9"/>
       <c r="I158" s="9">
@@ -7182,13 +7185,13 @@
     </row>
     <row r="159" spans="1:21" ht="15.75" customHeight="1">
       <c r="A159" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B159" s="21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C159" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D159" s="22">
         <v>798</v>
@@ -7198,7 +7201,7 @@
       </c>
       <c r="F159" s="22"/>
       <c r="G159" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H159" s="9"/>
       <c r="I159" s="9">
@@ -7222,13 +7225,13 @@
     </row>
     <row r="160" spans="1:21" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C160" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D160" s="22">
         <v>798</v>
@@ -7238,7 +7241,7 @@
       </c>
       <c r="F160" s="22"/>
       <c r="G160" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H160" s="9"/>
       <c r="I160" s="9">
@@ -7262,13 +7265,13 @@
     </row>
     <row r="161" spans="1:21" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C161" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D161" s="22">
         <v>798</v>
@@ -7278,7 +7281,7 @@
       </c>
       <c r="F161" s="22"/>
       <c r="G161" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H161" s="9"/>
       <c r="I161" s="9">
@@ -7302,13 +7305,13 @@
     </row>
     <row r="162" spans="1:21" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C162" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D162" s="22">
         <v>1098</v>
@@ -7318,7 +7321,7 @@
       </c>
       <c r="F162" s="22"/>
       <c r="G162" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H162" s="9"/>
       <c r="I162" s="9">
@@ -7342,13 +7345,13 @@
     </row>
     <row r="163" spans="1:21" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C163" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D163" s="22">
         <v>1098</v>
@@ -7358,7 +7361,7 @@
       </c>
       <c r="F163" s="22"/>
       <c r="G163" s="22" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H163" s="9"/>
       <c r="I163" s="9">

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="121">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -327,6 +327,57 @@
   </si>
   <si>
     <t>FREGADERO Altura 80</t>
+  </si>
+  <si>
+    <t>BAJOS CACEROLEROS altura 70</t>
+  </si>
+  <si>
+    <t>BAJOS CACEROLEROS altura 80</t>
+  </si>
+  <si>
+    <t>CACEROLEROS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAJÓN </t>
+  </si>
+  <si>
+    <t>CAJÓN HETTICH</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>CACEROLERO</t>
+  </si>
+  <si>
+    <t>CACEROLERO HETTICH</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>BASE</t>
+  </si>
+  <si>
+    <t>HETTICH</t>
+  </si>
+  <si>
+    <t>35_45</t>
+  </si>
+  <si>
+    <t>35_60</t>
+  </si>
+  <si>
+    <t>35_90</t>
+  </si>
+  <si>
+    <t>40_45</t>
+  </si>
+  <si>
+    <t>40_60</t>
+  </si>
+  <si>
+    <t>40_90</t>
   </si>
 </sst>
 </file>
@@ -685,7 +736,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U976"/>
+  <dimension ref="A1:U1012"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.90625" customWidth="1"/>
@@ -779,11 +830,11 @@
         <v>1</v>
       </c>
       <c r="L2" s="10">
-        <f>D132</f>
+        <f>D160</f>
         <v>698</v>
       </c>
       <c r="M2" s="10">
-        <f>E132</f>
+        <f>E160</f>
         <v>147</v>
       </c>
       <c r="N2" s="10"/>
@@ -828,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="22">
-        <f t="shared" ref="L3:M3" si="0">D133</f>
+        <f t="shared" ref="L3:M3" si="0">D161</f>
         <v>698</v>
       </c>
       <c r="M3" s="22">
@@ -877,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="22">
-        <f t="shared" ref="L4:M4" si="1">D134</f>
+        <f t="shared" ref="L4:M4" si="1">D162</f>
         <v>698</v>
       </c>
       <c r="M4" s="22">
@@ -926,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="22">
-        <f t="shared" ref="L5:M5" si="2">D135</f>
+        <f t="shared" ref="L5:M5" si="2">D163</f>
         <v>698</v>
       </c>
       <c r="M5" s="22">
@@ -975,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="22">
-        <f t="shared" ref="L6:M6" si="3">D136</f>
+        <f t="shared" ref="L6:M6" si="3">D164</f>
         <v>698</v>
       </c>
       <c r="M6" s="22">
@@ -1024,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" ref="L7:M7" si="4">D137</f>
+        <f t="shared" ref="L7:M7" si="4">D165</f>
         <v>698</v>
       </c>
       <c r="M7" s="22">
@@ -1073,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="22">
-        <f t="shared" ref="L8:M8" si="5">D138</f>
+        <f t="shared" ref="L8:M8" si="5">D166</f>
         <v>698</v>
       </c>
       <c r="M8" s="22">
@@ -6199,1431 +6250,1358 @@
       <c r="U127" s="19"/>
     </row>
     <row r="128" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A128" s="24" t="s">
+      <c r="A128" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B128" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E128" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" s="10"/>
+      <c r="I128" s="9">
+        <f>J6</f>
+        <v>30</v>
+      </c>
+      <c r="J128" s="10"/>
+      <c r="K128" s="10"/>
+      <c r="L128" s="10"/>
+      <c r="M128" s="10"/>
+      <c r="N128" s="10"/>
+      <c r="O128" s="10"/>
+      <c r="P128" s="10"/>
+      <c r="Q128" s="10"/>
+      <c r="R128" s="10"/>
+      <c r="S128" s="10"/>
+      <c r="T128" s="10"/>
+      <c r="U128" s="10"/>
+    </row>
+    <row r="129" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A129" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B129" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C129" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E129" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="10"/>
+      <c r="I129" s="9">
+        <f>J7</f>
+        <v>30</v>
+      </c>
+      <c r="J129" s="10"/>
+      <c r="K129" s="10"/>
+      <c r="L129" s="10"/>
+      <c r="M129" s="10"/>
+      <c r="N129" s="10"/>
+      <c r="O129" s="10"/>
+      <c r="P129" s="10"/>
+      <c r="Q129" s="10"/>
+      <c r="R129" s="10"/>
+      <c r="S129" s="10"/>
+      <c r="T129" s="10"/>
+      <c r="U129" s="10"/>
+    </row>
+    <row r="130" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A130" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B130" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C130" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D130" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E130" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" s="10"/>
+      <c r="I130" s="9">
+        <f>J8</f>
+        <v>30</v>
+      </c>
+      <c r="J130" s="10"/>
+      <c r="K130" s="10"/>
+      <c r="L130" s="10"/>
+      <c r="M130" s="10"/>
+      <c r="N130" s="10"/>
+      <c r="O130" s="10"/>
+      <c r="P130" s="10"/>
+      <c r="Q130" s="10"/>
+      <c r="R130" s="10"/>
+      <c r="S130" s="10"/>
+      <c r="T130" s="10"/>
+      <c r="U130" s="10"/>
+    </row>
+    <row r="131" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A131" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B131" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C131" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" s="10"/>
+      <c r="I131" s="9">
+        <f>J9</f>
+        <v>30</v>
+      </c>
+      <c r="J131" s="10"/>
+      <c r="K131" s="10"/>
+      <c r="L131" s="10"/>
+      <c r="M131" s="10"/>
+      <c r="N131" s="10"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="10"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
+      <c r="T131" s="10"/>
+      <c r="U131" s="10"/>
+    </row>
+    <row r="132" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A132" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B132" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C132" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="10"/>
+      <c r="I132" s="9">
+        <f>J10</f>
+        <v>30</v>
+      </c>
+      <c r="J132" s="10"/>
+      <c r="K132" s="10"/>
+      <c r="L132" s="10"/>
+      <c r="M132" s="10"/>
+      <c r="N132" s="10"/>
+      <c r="O132" s="10"/>
+      <c r="P132" s="10"/>
+      <c r="Q132" s="10"/>
+      <c r="R132" s="10"/>
+      <c r="S132" s="10"/>
+      <c r="T132" s="10"/>
+      <c r="U132" s="10"/>
+    </row>
+    <row r="133" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A133" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B133" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C133" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D133" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E133" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="10"/>
+      <c r="I133" s="9">
+        <f>J11</f>
+        <v>30</v>
+      </c>
+      <c r="J133" s="10"/>
+      <c r="K133" s="10"/>
+      <c r="L133" s="10"/>
+      <c r="M133" s="10"/>
+      <c r="N133" s="10"/>
+      <c r="O133" s="10"/>
+      <c r="P133" s="10"/>
+      <c r="Q133" s="10"/>
+      <c r="R133" s="10"/>
+      <c r="S133" s="10"/>
+      <c r="T133" s="10"/>
+      <c r="U133" s="10"/>
+    </row>
+    <row r="134" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A134" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B134" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C134" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E134" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" s="10"/>
+      <c r="I134" s="9">
+        <f>J12</f>
+        <v>30</v>
+      </c>
+      <c r="J134" s="10"/>
+      <c r="K134" s="10"/>
+      <c r="L134" s="10"/>
+      <c r="M134" s="10"/>
+      <c r="N134" s="10"/>
+      <c r="O134" s="10"/>
+      <c r="P134" s="10"/>
+      <c r="Q134" s="10"/>
+      <c r="R134" s="10"/>
+      <c r="S134" s="10"/>
+      <c r="T134" s="10"/>
+      <c r="U134" s="10"/>
+    </row>
+    <row r="135" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A135" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B135" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C135" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D135" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E135" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="10"/>
+      <c r="I135" s="9">
+        <f>J18</f>
+        <v>30</v>
+      </c>
+      <c r="J135" s="10"/>
+      <c r="K135" s="10"/>
+      <c r="L135" s="10"/>
+      <c r="M135" s="10"/>
+      <c r="N135" s="10"/>
+      <c r="O135" s="10"/>
+      <c r="P135" s="10"/>
+      <c r="Q135" s="10"/>
+      <c r="R135" s="10"/>
+      <c r="S135" s="10"/>
+      <c r="T135" s="10"/>
+      <c r="U135" s="10"/>
+    </row>
+    <row r="136" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B136" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C136" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E136" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="10"/>
+      <c r="I136" s="9">
+        <f>J19</f>
+        <v>30</v>
+      </c>
+      <c r="J136" s="10"/>
+      <c r="K136" s="10"/>
+      <c r="L136" s="10"/>
+      <c r="M136" s="10"/>
+      <c r="N136" s="10"/>
+      <c r="O136" s="10"/>
+      <c r="P136" s="10"/>
+      <c r="Q136" s="10"/>
+      <c r="R136" s="10"/>
+      <c r="S136" s="10"/>
+      <c r="T136" s="10"/>
+      <c r="U136" s="10"/>
+    </row>
+    <row r="137" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A137" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B137" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C137" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E137" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="10"/>
+      <c r="I137" s="9">
+        <f>J20</f>
+        <v>30</v>
+      </c>
+      <c r="J137" s="10"/>
+      <c r="K137" s="10"/>
+      <c r="L137" s="10"/>
+      <c r="M137" s="10"/>
+      <c r="N137" s="10"/>
+      <c r="O137" s="10"/>
+      <c r="P137" s="10"/>
+      <c r="Q137" s="10"/>
+      <c r="R137" s="10"/>
+      <c r="S137" s="10"/>
+      <c r="T137" s="10"/>
+      <c r="U137" s="10"/>
+    </row>
+    <row r="138" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A138" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C138" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D138" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E138" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="10"/>
+      <c r="I138" s="9">
+        <f>J21</f>
+        <v>30</v>
+      </c>
+      <c r="J138" s="10"/>
+      <c r="K138" s="10"/>
+      <c r="L138" s="10"/>
+      <c r="M138" s="10"/>
+      <c r="N138" s="10"/>
+      <c r="O138" s="10"/>
+      <c r="P138" s="10"/>
+      <c r="Q138" s="10"/>
+      <c r="R138" s="10"/>
+      <c r="S138" s="10"/>
+      <c r="T138" s="10"/>
+      <c r="U138" s="10"/>
+    </row>
+    <row r="139" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A139" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B139" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C139" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="10"/>
+      <c r="I139" s="9">
+        <f>J22</f>
+        <v>30</v>
+      </c>
+      <c r="J139" s="10"/>
+      <c r="K139" s="10"/>
+      <c r="L139" s="10"/>
+      <c r="M139" s="10"/>
+      <c r="N139" s="10"/>
+      <c r="O139" s="10"/>
+      <c r="P139" s="10"/>
+      <c r="Q139" s="10"/>
+      <c r="R139" s="10"/>
+      <c r="S139" s="10"/>
+      <c r="T139" s="10"/>
+      <c r="U139" s="10"/>
+    </row>
+    <row r="140" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A140" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B140" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C140" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="10"/>
+      <c r="I140" s="9">
+        <f>J23</f>
+        <v>30</v>
+      </c>
+      <c r="J140" s="10"/>
+      <c r="K140" s="10"/>
+      <c r="L140" s="10"/>
+      <c r="M140" s="10"/>
+      <c r="N140" s="10"/>
+      <c r="O140" s="10"/>
+      <c r="P140" s="10"/>
+      <c r="Q140" s="10"/>
+      <c r="R140" s="10"/>
+      <c r="S140" s="10"/>
+      <c r="T140" s="10"/>
+      <c r="U140" s="10"/>
+    </row>
+    <row r="141" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A141" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B141" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C141" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E141" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="10"/>
+      <c r="I141" s="9">
+        <f>J24</f>
+        <v>30</v>
+      </c>
+      <c r="J141" s="10"/>
+      <c r="K141" s="10"/>
+      <c r="L141" s="10"/>
+      <c r="M141" s="10"/>
+      <c r="N141" s="10"/>
+      <c r="O141" s="10"/>
+      <c r="P141" s="10"/>
+      <c r="Q141" s="10"/>
+      <c r="R141" s="10"/>
+      <c r="S141" s="10"/>
+      <c r="T141" s="10"/>
+      <c r="U141" s="10"/>
+    </row>
+    <row r="142" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A142" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B128" s="15" t="s">
+      <c r="B142" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C128" s="7" t="s">
+      <c r="C142" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F128" s="22"/>
-      <c r="H128" s="9"/>
-      <c r="I128" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J128" s="23">
-        <v>0.2</v>
-      </c>
-      <c r="K128" s="19"/>
-    </row>
-    <row r="129" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A129" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B129" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C129" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F129" s="22"/>
-      <c r="H129" s="9"/>
-      <c r="I129" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J129" s="23">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A130" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B130" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F130" s="22"/>
-      <c r="H130" s="9"/>
-      <c r="I130" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J130" s="23"/>
-      <c r="L130" s="25"/>
-    </row>
-    <row r="131" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A131" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B131" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F131" s="20"/>
-      <c r="H131" s="9"/>
-      <c r="I131" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J131" s="23">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A132" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B132" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C132" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D132" s="20">
-        <v>698</v>
-      </c>
-      <c r="E132" s="20">
-        <v>147</v>
-      </c>
-      <c r="F132" s="20"/>
-      <c r="G132" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H132" s="9"/>
-      <c r="I132" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J132" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A133" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B133" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C133" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D133" s="20">
-        <v>698</v>
-      </c>
-      <c r="E133" s="20">
-        <v>297</v>
-      </c>
-      <c r="F133" s="20"/>
-      <c r="G133" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H133" s="9"/>
-      <c r="I133" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J133" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A134" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B134" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C134" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D134" s="20">
-        <v>698</v>
-      </c>
-      <c r="E134" s="20">
-        <v>347</v>
-      </c>
-      <c r="F134" s="20"/>
-      <c r="G134" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H134" s="9"/>
-      <c r="I134" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J134" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A135" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B135" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C135" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D135" s="20">
-        <v>698</v>
-      </c>
-      <c r="E135" s="20">
-        <v>397</v>
-      </c>
-      <c r="F135" s="20"/>
-      <c r="G135" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H135" s="9"/>
-      <c r="I135" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="J135" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A136" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B136" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C136" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D136" s="20">
-        <v>698</v>
-      </c>
-      <c r="E136" s="20">
-        <v>447</v>
-      </c>
-      <c r="F136" s="20"/>
-      <c r="G136" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H136" s="9"/>
-      <c r="I136" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J136" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A137" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C137" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D137" s="20">
-        <v>698</v>
-      </c>
-      <c r="E137" s="20">
-        <v>497</v>
-      </c>
-      <c r="F137" s="20"/>
-      <c r="G137" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H137" s="9"/>
-      <c r="I137" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J137" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A138" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B138" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C138" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D138" s="20">
-        <v>698</v>
-      </c>
-      <c r="E138" s="20">
-        <v>597</v>
-      </c>
-      <c r="F138" s="20"/>
-      <c r="G138" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H138" s="9"/>
-      <c r="I138" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="J138" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A139" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B139" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C139" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D139" s="20">
-        <v>798</v>
-      </c>
-      <c r="E139" s="20">
-        <v>147</v>
-      </c>
-      <c r="F139" s="20"/>
-      <c r="G139" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H139" s="9"/>
-      <c r="I139" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J139" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A140" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B140" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C140" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D140" s="20">
-        <v>798</v>
-      </c>
-      <c r="E140" s="20">
-        <v>297</v>
-      </c>
-      <c r="F140" s="20"/>
-      <c r="G140" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H140" s="9"/>
-      <c r="I140" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J140" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A141" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B141" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C141" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D141" s="20">
-        <v>798</v>
-      </c>
-      <c r="E141" s="20">
-        <v>347</v>
-      </c>
-      <c r="F141" s="20"/>
-      <c r="G141" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="H141" s="9"/>
-      <c r="I141" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J141" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A142" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B142" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C142" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D142" s="20">
-        <v>798</v>
-      </c>
-      <c r="E142" s="20">
-        <v>397</v>
-      </c>
-      <c r="F142" s="20"/>
-      <c r="G142" s="21" t="s">
-        <v>99</v>
-      </c>
+      <c r="F142" s="22"/>
       <c r="H142" s="9"/>
       <c r="I142" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J142" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A143" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B143" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C143" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D143" s="20">
-        <v>798</v>
-      </c>
-      <c r="E143" s="20">
-        <v>447</v>
-      </c>
-      <c r="F143" s="20"/>
-      <c r="G143" s="21" t="s">
-        <v>99</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="J142" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="K142" s="19"/>
+    </row>
+    <row r="143" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A143" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B143" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C143" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F143" s="22"/>
       <c r="H143" s="9"/>
       <c r="I143" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J143" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" ht="15.75" customHeight="1">
-      <c r="A144" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B144" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C144" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D144" s="20">
-        <v>798</v>
-      </c>
-      <c r="E144" s="20">
-        <v>497</v>
-      </c>
-      <c r="F144" s="20"/>
-      <c r="G144" s="21" t="s">
-        <v>99</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J143" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A144" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B144" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F144" s="22"/>
       <c r="H144" s="9"/>
       <c r="I144" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="J144" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="145" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A145" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B145" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C145" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D145" s="20">
-        <v>798</v>
-      </c>
-      <c r="E145" s="20">
-        <v>597</v>
+        <v>80</v>
+      </c>
+      <c r="J144" s="23"/>
+      <c r="L144" s="25"/>
+    </row>
+    <row r="145" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A145" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B145" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="F145" s="20"/>
-      <c r="G145" s="21" t="s">
-        <v>99</v>
-      </c>
       <c r="H145" s="9"/>
       <c r="I145" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="J145" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="146" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A146" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B146" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C146" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D146" s="20">
-        <v>1098</v>
-      </c>
-      <c r="E146" s="20">
-        <v>397</v>
-      </c>
-      <c r="F146" s="20"/>
-      <c r="G146" s="21" t="s">
-        <v>99</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="J145" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A146" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B146" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F146" s="22"/>
       <c r="H146" s="9"/>
       <c r="I146" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J146" s="20">
-        <v>30</v>
-      </c>
-      <c r="K146" s="10"/>
-      <c r="L146" s="10"/>
-      <c r="M146" s="10"/>
-      <c r="N146" s="10"/>
-      <c r="O146" s="10"/>
-      <c r="P146" s="10"/>
-      <c r="Q146" s="10"/>
-      <c r="R146" s="10"/>
-      <c r="S146" s="10"/>
-      <c r="T146" s="10"/>
-      <c r="U146" s="10"/>
-    </row>
-    <row r="147" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A147" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B147" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C147" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D147" s="22">
-        <v>1098</v>
-      </c>
-      <c r="E147" s="22">
-        <v>597</v>
+        <v>109</v>
+      </c>
+      <c r="J146" s="23"/>
+    </row>
+    <row r="147" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A147" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="B147" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="F147" s="22"/>
-      <c r="G147" s="21" t="s">
-        <v>99</v>
-      </c>
       <c r="H147" s="9"/>
       <c r="I147" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="J147" s="22">
-        <v>30</v>
-      </c>
-      <c r="K147" s="22"/>
-      <c r="L147" s="22"/>
-      <c r="M147" s="22"/>
-      <c r="N147" s="22"/>
-      <c r="O147" s="22"/>
-      <c r="P147" s="22"/>
-      <c r="Q147" s="22"/>
-      <c r="R147" s="22"/>
-      <c r="S147" s="22"/>
-      <c r="T147" s="22"/>
-      <c r="U147" s="22"/>
-    </row>
-    <row r="148" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A148" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B148" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C148" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D148" s="22">
-        <v>698</v>
-      </c>
-      <c r="E148" s="22">
-        <v>147</v>
-      </c>
-      <c r="F148" s="22"/>
-      <c r="G148" s="22" t="s">
-        <v>100</v>
+        <v>112</v>
+      </c>
+      <c r="J147" s="23"/>
+    </row>
+    <row r="148" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A148" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B148" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E148">
+        <v>450</v>
+      </c>
+      <c r="F148" s="22">
+        <v>500</v>
       </c>
       <c r="H148" s="9"/>
-      <c r="I148" s="9">
-        <v>7</v>
-      </c>
-      <c r="J148" s="22">
-        <v>30</v>
-      </c>
-      <c r="K148" s="10"/>
-      <c r="L148" s="10"/>
-      <c r="M148" s="10"/>
-      <c r="N148" s="10"/>
-      <c r="O148" s="10"/>
-      <c r="P148" s="10"/>
-      <c r="Q148" s="10"/>
-      <c r="R148" s="10"/>
-      <c r="S148" s="10"/>
-      <c r="T148" s="10"/>
-      <c r="U148" s="10"/>
-    </row>
-    <row r="149" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A149" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B149" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C149" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D149" s="22">
-        <v>698</v>
-      </c>
-      <c r="E149" s="22">
-        <v>297</v>
-      </c>
-      <c r="F149" s="22"/>
-      <c r="G149" s="22" t="s">
-        <v>100</v>
+      <c r="I148" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J148" s="23"/>
+    </row>
+    <row r="149" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A149" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B149" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E149">
+        <v>600</v>
+      </c>
+      <c r="F149" s="22">
+        <v>500</v>
       </c>
       <c r="H149" s="9"/>
-      <c r="I149" s="9">
-        <f>I148+1</f>
-        <v>8</v>
-      </c>
-      <c r="J149" s="22">
-        <v>30</v>
-      </c>
-      <c r="K149" s="10"/>
-      <c r="L149" s="10"/>
-      <c r="M149" s="10"/>
-      <c r="N149" s="10"/>
-      <c r="O149" s="10"/>
-      <c r="P149" s="10"/>
-      <c r="Q149" s="10"/>
-      <c r="R149" s="10"/>
-      <c r="S149" s="10"/>
-      <c r="T149" s="10"/>
-      <c r="U149" s="10"/>
-    </row>
-    <row r="150" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A150" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B150" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C150" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D150" s="22">
-        <v>698</v>
-      </c>
-      <c r="E150" s="22">
-        <v>347</v>
-      </c>
-      <c r="F150" s="22"/>
-      <c r="G150" s="22" t="s">
-        <v>100</v>
+      <c r="I149" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J149" s="23"/>
+    </row>
+    <row r="150" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A150" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B150" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E150">
+        <v>700</v>
+      </c>
+      <c r="F150" s="22">
+        <v>500</v>
       </c>
       <c r="H150" s="9"/>
-      <c r="I150" s="9">
-        <f t="shared" ref="I150:I163" si="6">I149+1</f>
-        <v>9</v>
-      </c>
-      <c r="J150" s="22">
-        <v>30</v>
-      </c>
-      <c r="K150" s="10"/>
-      <c r="L150" s="10"/>
-      <c r="M150" s="10"/>
-      <c r="N150" s="10"/>
-      <c r="O150" s="10"/>
-      <c r="P150" s="10"/>
-      <c r="Q150" s="10"/>
-      <c r="R150" s="10"/>
-      <c r="S150" s="10"/>
-      <c r="T150" s="10"/>
-      <c r="U150" s="10"/>
-    </row>
-    <row r="151" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A151" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B151" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C151" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D151" s="22">
-        <v>698</v>
-      </c>
-      <c r="E151" s="22">
-        <v>397</v>
-      </c>
-      <c r="F151" s="22"/>
-      <c r="G151" s="22" t="s">
-        <v>100</v>
+      <c r="I150" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J150" s="23"/>
+    </row>
+    <row r="151" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A151" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B151" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E151">
+        <v>800</v>
+      </c>
+      <c r="F151" s="22">
+        <v>500</v>
       </c>
       <c r="H151" s="9"/>
-      <c r="I151" s="9">
-        <f t="shared" si="6"/>
-        <v>10</v>
-      </c>
-      <c r="J151" s="22">
-        <v>30</v>
-      </c>
-      <c r="K151" s="10"/>
-      <c r="L151" s="10"/>
-      <c r="M151" s="10"/>
-      <c r="N151" s="10"/>
-      <c r="O151" s="10"/>
-      <c r="P151" s="10"/>
-      <c r="Q151" s="10"/>
-      <c r="R151" s="10"/>
-      <c r="S151" s="10"/>
-      <c r="T151" s="10"/>
-      <c r="U151" s="10"/>
-    </row>
-    <row r="152" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A152" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B152" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C152" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D152" s="22">
-        <v>698</v>
-      </c>
-      <c r="E152" s="22">
-        <v>447</v>
-      </c>
-      <c r="F152" s="22"/>
-      <c r="G152" s="22" t="s">
-        <v>100</v>
+      <c r="I151" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J151" s="23"/>
+    </row>
+    <row r="152" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A152" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B152" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E152">
+        <v>900</v>
+      </c>
+      <c r="F152" s="22">
+        <v>500</v>
       </c>
       <c r="H152" s="9"/>
-      <c r="I152" s="9">
-        <f t="shared" si="6"/>
-        <v>11</v>
-      </c>
-      <c r="J152" s="22">
-        <v>30</v>
-      </c>
-      <c r="K152" s="10"/>
-      <c r="L152" s="10"/>
-      <c r="M152" s="10"/>
-      <c r="N152" s="10"/>
-      <c r="O152" s="10"/>
-      <c r="P152" s="10"/>
-      <c r="Q152" s="10"/>
-      <c r="R152" s="10"/>
-      <c r="S152" s="10"/>
-      <c r="T152" s="10"/>
-      <c r="U152" s="10"/>
-    </row>
-    <row r="153" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A153" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B153" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C153" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D153" s="22">
-        <v>698</v>
-      </c>
-      <c r="E153" s="22">
-        <v>497</v>
-      </c>
-      <c r="F153" s="22"/>
-      <c r="G153" s="22" t="s">
-        <v>100</v>
+      <c r="I152" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J152" s="23"/>
+    </row>
+    <row r="153" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A153" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B153" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E153">
+        <v>1000</v>
+      </c>
+      <c r="F153" s="22">
+        <v>500</v>
       </c>
       <c r="H153" s="9"/>
-      <c r="I153" s="9">
-        <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="J153" s="22">
-        <v>30</v>
-      </c>
-      <c r="K153" s="10"/>
-      <c r="L153" s="10"/>
-      <c r="M153" s="10"/>
-      <c r="N153" s="10"/>
-      <c r="O153" s="10"/>
-      <c r="P153" s="10"/>
-      <c r="Q153" s="10"/>
-      <c r="R153" s="10"/>
-      <c r="S153" s="10"/>
-      <c r="T153" s="10"/>
-      <c r="U153" s="10"/>
-    </row>
-    <row r="154" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A154" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C154" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D154" s="22">
-        <v>698</v>
-      </c>
-      <c r="E154" s="22">
-        <v>597</v>
-      </c>
-      <c r="F154" s="22"/>
-      <c r="G154" s="22" t="s">
-        <v>100</v>
+      <c r="I153" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J153" s="23"/>
+    </row>
+    <row r="154" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A154" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B154" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E154">
+        <v>450</v>
+      </c>
+      <c r="F154" s="22">
+        <v>500</v>
       </c>
       <c r="H154" s="9"/>
-      <c r="I154" s="9">
-        <f t="shared" si="6"/>
-        <v>13</v>
-      </c>
-      <c r="J154" s="22">
-        <v>30</v>
-      </c>
-      <c r="K154" s="10"/>
-      <c r="L154" s="10"/>
-      <c r="M154" s="10"/>
-      <c r="N154" s="10"/>
-      <c r="O154" s="10"/>
-      <c r="P154" s="10"/>
-      <c r="Q154" s="10"/>
-      <c r="R154" s="10"/>
-      <c r="S154" s="10"/>
-      <c r="T154" s="10"/>
-      <c r="U154" s="10"/>
-    </row>
-    <row r="155" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A155" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B155" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C155" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D155" s="22">
-        <v>798</v>
-      </c>
-      <c r="E155" s="22">
-        <v>147</v>
-      </c>
-      <c r="F155" s="22"/>
-      <c r="G155" s="22" t="s">
-        <v>100</v>
+      <c r="I154" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J154" s="23"/>
+    </row>
+    <row r="155" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A155" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B155" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E155">
+        <v>600</v>
+      </c>
+      <c r="F155" s="22">
+        <v>500</v>
       </c>
       <c r="H155" s="9"/>
-      <c r="I155" s="9">
-        <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="J155" s="22">
-        <v>30</v>
-      </c>
-      <c r="K155" s="10"/>
-      <c r="L155" s="10"/>
-      <c r="M155" s="10"/>
-      <c r="N155" s="10"/>
-      <c r="O155" s="10"/>
-      <c r="P155" s="10"/>
-      <c r="Q155" s="10"/>
-      <c r="R155" s="10"/>
-      <c r="S155" s="10"/>
-      <c r="T155" s="10"/>
-      <c r="U155" s="10"/>
-    </row>
-    <row r="156" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A156" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B156" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C156" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D156" s="22">
-        <v>798</v>
-      </c>
-      <c r="E156" s="22">
-        <v>297</v>
-      </c>
-      <c r="F156" s="22"/>
-      <c r="G156" s="22" t="s">
-        <v>100</v>
+      <c r="I155" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J155" s="23"/>
+    </row>
+    <row r="156" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A156" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B156" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C156" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E156">
+        <v>700</v>
+      </c>
+      <c r="F156" s="22">
+        <v>500</v>
       </c>
       <c r="H156" s="9"/>
-      <c r="I156" s="9">
-        <f t="shared" si="6"/>
-        <v>15</v>
-      </c>
-      <c r="J156" s="22">
-        <v>30</v>
-      </c>
-      <c r="K156" s="10"/>
-      <c r="L156" s="10"/>
-      <c r="M156" s="10"/>
-      <c r="N156" s="10"/>
-      <c r="O156" s="10"/>
-      <c r="P156" s="10"/>
-      <c r="Q156" s="10"/>
-      <c r="R156" s="10"/>
-      <c r="S156" s="10"/>
-      <c r="T156" s="10"/>
-      <c r="U156" s="10"/>
-    </row>
-    <row r="157" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A157" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C157" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D157" s="22">
-        <v>798</v>
-      </c>
-      <c r="E157" s="22">
-        <v>347</v>
-      </c>
-      <c r="F157" s="22"/>
-      <c r="G157" s="22" t="s">
-        <v>100</v>
+      <c r="I156" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J156" s="23"/>
+    </row>
+    <row r="157" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A157" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B157" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C157" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E157">
+        <v>800</v>
+      </c>
+      <c r="F157" s="22">
+        <v>500</v>
       </c>
       <c r="H157" s="9"/>
-      <c r="I157" s="9">
-        <f t="shared" si="6"/>
-        <v>16</v>
-      </c>
-      <c r="J157" s="22">
-        <v>30</v>
-      </c>
-      <c r="K157" s="10"/>
-      <c r="L157" s="10"/>
-      <c r="M157" s="10"/>
-      <c r="N157" s="10"/>
-      <c r="O157" s="10"/>
-      <c r="P157" s="10"/>
-      <c r="Q157" s="10"/>
-      <c r="R157" s="10"/>
-      <c r="S157" s="10"/>
-      <c r="T157" s="10"/>
-      <c r="U157" s="10"/>
-    </row>
-    <row r="158" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A158" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B158" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C158" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D158" s="22">
-        <v>798</v>
-      </c>
-      <c r="E158" s="22">
-        <v>397</v>
-      </c>
-      <c r="F158" s="22"/>
-      <c r="G158" s="22" t="s">
-        <v>100</v>
+      <c r="I157" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J157" s="23"/>
+    </row>
+    <row r="158" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A158" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E158">
+        <v>900</v>
+      </c>
+      <c r="F158" s="22">
+        <v>500</v>
       </c>
       <c r="H158" s="9"/>
-      <c r="I158" s="9">
-        <f t="shared" si="6"/>
-        <v>17</v>
-      </c>
-      <c r="J158" s="22">
-        <v>30</v>
-      </c>
-      <c r="K158" s="10"/>
-      <c r="L158" s="10"/>
-      <c r="M158" s="10"/>
-      <c r="N158" s="10"/>
-      <c r="O158" s="10"/>
-      <c r="P158" s="10"/>
-      <c r="Q158" s="10"/>
-      <c r="R158" s="10"/>
-      <c r="S158" s="10"/>
-      <c r="T158" s="10"/>
-      <c r="U158" s="10"/>
-    </row>
-    <row r="159" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A159" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B159" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C159" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D159" s="22">
-        <v>798</v>
-      </c>
-      <c r="E159" s="22">
-        <v>447</v>
-      </c>
-      <c r="F159" s="22"/>
-      <c r="G159" s="22" t="s">
-        <v>100</v>
+      <c r="I158" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J158" s="23"/>
+    </row>
+    <row r="159" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A159" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B159" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E159">
+        <v>1000</v>
+      </c>
+      <c r="F159" s="22">
+        <v>500</v>
       </c>
       <c r="H159" s="9"/>
-      <c r="I159" s="9">
-        <f t="shared" si="6"/>
-        <v>18</v>
-      </c>
-      <c r="J159" s="22">
-        <v>30</v>
-      </c>
-      <c r="K159" s="10"/>
-      <c r="L159" s="10"/>
-      <c r="M159" s="10"/>
-      <c r="N159" s="10"/>
-      <c r="O159" s="10"/>
-      <c r="P159" s="10"/>
-      <c r="Q159" s="10"/>
-      <c r="R159" s="10"/>
-      <c r="S159" s="10"/>
-      <c r="T159" s="10"/>
-      <c r="U159" s="10"/>
-    </row>
-    <row r="160" spans="1:21" ht="15.75" customHeight="1">
+      <c r="I159" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J159" s="23"/>
+    </row>
+    <row r="160" spans="1:10" ht="15.75" customHeight="1">
       <c r="A160" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B160" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="C160" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D160" s="22">
-        <v>798</v>
-      </c>
-      <c r="E160" s="22">
-        <v>497</v>
-      </c>
-      <c r="F160" s="22"/>
-      <c r="G160" s="22" t="s">
-        <v>100</v>
+        <v>55</v>
+      </c>
+      <c r="C160" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D160" s="20">
+        <v>698</v>
+      </c>
+      <c r="E160" s="20">
+        <v>147</v>
+      </c>
+      <c r="F160" s="20"/>
+      <c r="G160" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H160" s="9"/>
-      <c r="I160" s="9">
-        <f t="shared" si="6"/>
-        <v>19</v>
-      </c>
-      <c r="J160" s="22">
+      <c r="I160" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J160" s="20">
         <v>30</v>
       </c>
-      <c r="K160" s="10"/>
-      <c r="L160" s="10"/>
-      <c r="M160" s="10"/>
-      <c r="N160" s="10"/>
-      <c r="O160" s="10"/>
-      <c r="P160" s="10"/>
-      <c r="Q160" s="10"/>
-      <c r="R160" s="10"/>
-      <c r="S160" s="10"/>
-      <c r="T160" s="10"/>
-      <c r="U160" s="10"/>
     </row>
     <row r="161" spans="1:21" ht="15.75" customHeight="1">
       <c r="A161" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B161" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C161" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D161" s="22">
-        <v>798</v>
-      </c>
-      <c r="E161" s="22">
-        <v>597</v>
-      </c>
-      <c r="F161" s="22"/>
-      <c r="G161" s="22" t="s">
-        <v>100</v>
+        <v>56</v>
+      </c>
+      <c r="C161" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D161" s="20">
+        <v>698</v>
+      </c>
+      <c r="E161" s="20">
+        <v>297</v>
+      </c>
+      <c r="F161" s="20"/>
+      <c r="G161" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H161" s="9"/>
-      <c r="I161" s="9">
-        <f t="shared" si="6"/>
-        <v>20</v>
-      </c>
-      <c r="J161" s="22">
+      <c r="I161" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J161" s="20">
         <v>30</v>
       </c>
-      <c r="K161" s="10"/>
-      <c r="L161" s="10"/>
-      <c r="M161" s="10"/>
-      <c r="N161" s="10"/>
-      <c r="O161" s="10"/>
-      <c r="P161" s="10"/>
-      <c r="Q161" s="10"/>
-      <c r="R161" s="10"/>
-      <c r="S161" s="10"/>
-      <c r="T161" s="10"/>
-      <c r="U161" s="10"/>
     </row>
     <row r="162" spans="1:21" ht="15.75" customHeight="1">
       <c r="A162" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B162" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="C162" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D162" s="22">
-        <v>1098</v>
-      </c>
-      <c r="E162" s="22">
-        <v>397</v>
-      </c>
-      <c r="F162" s="22"/>
-      <c r="G162" s="22" t="s">
-        <v>100</v>
+        <v>57</v>
+      </c>
+      <c r="C162" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D162" s="20">
+        <v>698</v>
+      </c>
+      <c r="E162" s="20">
+        <v>347</v>
+      </c>
+      <c r="F162" s="20"/>
+      <c r="G162" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H162" s="9"/>
-      <c r="I162" s="9">
-        <f t="shared" si="6"/>
-        <v>21</v>
-      </c>
-      <c r="J162" s="22">
+      <c r="I162" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="J162" s="20">
         <v>30</v>
       </c>
-      <c r="K162" s="10"/>
-      <c r="L162" s="10"/>
-      <c r="M162" s="10"/>
-      <c r="N162" s="10"/>
-      <c r="O162" s="10"/>
-      <c r="P162" s="10"/>
-      <c r="Q162" s="10"/>
-      <c r="R162" s="10"/>
-      <c r="S162" s="10"/>
-      <c r="T162" s="10"/>
-      <c r="U162" s="10"/>
     </row>
     <row r="163" spans="1:21" ht="15.75" customHeight="1">
       <c r="A163" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B163" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C163" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D163" s="22">
+        <v>58</v>
+      </c>
+      <c r="C163" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D163" s="20">
+        <v>698</v>
+      </c>
+      <c r="E163" s="20">
+        <v>397</v>
+      </c>
+      <c r="F163" s="20"/>
+      <c r="G163" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H163" s="9"/>
+      <c r="I163" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="J163" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A164" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C164" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D164" s="20">
+        <v>698</v>
+      </c>
+      <c r="E164" s="20">
+        <v>447</v>
+      </c>
+      <c r="F164" s="20"/>
+      <c r="G164" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H164" s="9"/>
+      <c r="I164" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J164" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="165" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A165" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C165" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D165" s="20">
+        <v>698</v>
+      </c>
+      <c r="E165" s="20">
+        <v>497</v>
+      </c>
+      <c r="F165" s="20"/>
+      <c r="G165" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H165" s="9"/>
+      <c r="I165" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J165" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="166" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A166" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B166" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C166" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D166" s="20">
+        <v>698</v>
+      </c>
+      <c r="E166" s="20">
+        <v>597</v>
+      </c>
+      <c r="F166" s="20"/>
+      <c r="G166" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H166" s="9"/>
+      <c r="I166" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J166" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="167" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A167" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B167" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C167" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D167" s="20">
+        <v>798</v>
+      </c>
+      <c r="E167" s="20">
+        <v>147</v>
+      </c>
+      <c r="F167" s="20"/>
+      <c r="G167" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H167" s="9"/>
+      <c r="I167" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J167" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A168" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C168" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D168" s="20">
+        <v>798</v>
+      </c>
+      <c r="E168" s="20">
+        <v>297</v>
+      </c>
+      <c r="F168" s="20"/>
+      <c r="G168" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H168" s="9"/>
+      <c r="I168" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J168" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="169" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A169" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B169" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C169" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D169" s="20">
+        <v>798</v>
+      </c>
+      <c r="E169" s="20">
+        <v>347</v>
+      </c>
+      <c r="F169" s="20"/>
+      <c r="G169" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H169" s="9"/>
+      <c r="I169" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J169" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="170" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A170" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B170" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C170" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D170" s="20">
+        <v>798</v>
+      </c>
+      <c r="E170" s="20">
+        <v>397</v>
+      </c>
+      <c r="F170" s="20"/>
+      <c r="G170" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H170" s="9"/>
+      <c r="I170" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J170" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A171" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C171" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D171" s="20">
+        <v>798</v>
+      </c>
+      <c r="E171" s="20">
+        <v>447</v>
+      </c>
+      <c r="F171" s="20"/>
+      <c r="G171" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H171" s="9"/>
+      <c r="I171" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J171" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A172" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C172" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D172" s="20">
+        <v>798</v>
+      </c>
+      <c r="E172" s="20">
+        <v>497</v>
+      </c>
+      <c r="F172" s="20"/>
+      <c r="G172" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H172" s="9"/>
+      <c r="I172" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J172" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A173" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B173" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C173" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D173" s="20">
+        <v>798</v>
+      </c>
+      <c r="E173" s="20">
+        <v>597</v>
+      </c>
+      <c r="F173" s="20"/>
+      <c r="G173" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H173" s="9"/>
+      <c r="I173" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J173" s="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A174" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B174" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C174" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D174" s="20">
         <v>1098</v>
       </c>
-      <c r="E163" s="22">
-        <v>597</v>
-      </c>
-      <c r="F163" s="22"/>
-      <c r="G163" s="22" t="s">
-        <v>100</v>
-      </c>
-      <c r="H163" s="9"/>
-      <c r="I163" s="9">
-        <f t="shared" si="6"/>
-        <v>22</v>
-      </c>
-      <c r="J163" s="22">
+      <c r="E174" s="20">
+        <v>397</v>
+      </c>
+      <c r="F174" s="20"/>
+      <c r="G174" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H174" s="9"/>
+      <c r="I174" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J174" s="20">
         <v>30</v>
       </c>
-      <c r="K163" s="10"/>
-      <c r="L163" s="10"/>
-      <c r="M163" s="10"/>
-      <c r="N163" s="10"/>
-      <c r="O163" s="10"/>
-      <c r="P163" s="10"/>
-      <c r="Q163" s="10"/>
-      <c r="R163" s="10"/>
-      <c r="S163" s="10"/>
-      <c r="T163" s="10"/>
-      <c r="U163" s="10"/>
-    </row>
-    <row r="164" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A164" s="10"/>
-      <c r="B164" s="10"/>
-      <c r="C164" s="10"/>
-      <c r="D164" s="10"/>
-      <c r="E164" s="10"/>
-      <c r="F164" s="10"/>
-      <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
-      <c r="I164" s="10"/>
-      <c r="J164" s="10"/>
-      <c r="K164" s="10"/>
-      <c r="L164" s="10"/>
-      <c r="M164" s="10"/>
-      <c r="N164" s="10"/>
-      <c r="O164" s="10"/>
-      <c r="P164" s="10"/>
-      <c r="Q164" s="10"/>
-      <c r="R164" s="10"/>
-      <c r="S164" s="10"/>
-      <c r="T164" s="10"/>
-      <c r="U164" s="10"/>
-    </row>
-    <row r="165" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A165" s="10"/>
-      <c r="B165" s="10"/>
-      <c r="C165" s="10"/>
-      <c r="D165" s="10"/>
-      <c r="E165" s="10"/>
-      <c r="F165" s="10"/>
-      <c r="G165" s="10"/>
-      <c r="H165" s="10"/>
-      <c r="I165" s="10"/>
-      <c r="J165" s="10"/>
-      <c r="K165" s="10"/>
-      <c r="L165" s="10"/>
-      <c r="M165" s="10"/>
-      <c r="N165" s="10"/>
-      <c r="O165" s="10"/>
-      <c r="P165" s="10"/>
-      <c r="Q165" s="10"/>
-      <c r="R165" s="10"/>
-      <c r="S165" s="10"/>
-      <c r="T165" s="10"/>
-      <c r="U165" s="10"/>
-    </row>
-    <row r="166" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A166" s="10"/>
-      <c r="B166" s="10"/>
-      <c r="C166" s="10"/>
-      <c r="D166" s="10"/>
-      <c r="E166" s="10"/>
-      <c r="F166" s="10"/>
-      <c r="G166" s="10"/>
-      <c r="H166" s="10"/>
-      <c r="I166" s="10"/>
-      <c r="J166" s="10"/>
-      <c r="K166" s="10"/>
-      <c r="L166" s="10"/>
-      <c r="M166" s="10"/>
-      <c r="N166" s="10"/>
-      <c r="O166" s="10"/>
-      <c r="P166" s="10"/>
-      <c r="Q166" s="10"/>
-      <c r="R166" s="10"/>
-      <c r="S166" s="10"/>
-      <c r="T166" s="10"/>
-      <c r="U166" s="10"/>
-    </row>
-    <row r="167" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A167" s="10"/>
-      <c r="B167" s="10"/>
-      <c r="C167" s="10"/>
-      <c r="D167" s="10"/>
-      <c r="E167" s="10"/>
-      <c r="F167" s="10"/>
-      <c r="G167" s="10"/>
-      <c r="H167" s="10"/>
-      <c r="I167" s="10"/>
-      <c r="J167" s="10"/>
-      <c r="K167" s="10"/>
-      <c r="L167" s="10"/>
-      <c r="M167" s="10"/>
-      <c r="N167" s="10"/>
-      <c r="O167" s="10"/>
-      <c r="P167" s="10"/>
-      <c r="Q167" s="10"/>
-      <c r="R167" s="10"/>
-      <c r="S167" s="10"/>
-      <c r="T167" s="10"/>
-      <c r="U167" s="10"/>
-    </row>
-    <row r="168" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A168" s="10"/>
-      <c r="B168" s="10"/>
-      <c r="C168" s="10"/>
-      <c r="D168" s="10"/>
-      <c r="E168" s="10"/>
-      <c r="F168" s="10"/>
-      <c r="G168" s="10"/>
-      <c r="H168" s="10"/>
-      <c r="I168" s="10"/>
-      <c r="J168" s="10"/>
-      <c r="K168" s="10"/>
-      <c r="L168" s="10"/>
-      <c r="M168" s="10"/>
-      <c r="N168" s="10"/>
-      <c r="O168" s="10"/>
-      <c r="P168" s="10"/>
-      <c r="Q168" s="10"/>
-      <c r="R168" s="10"/>
-      <c r="S168" s="10"/>
-      <c r="T168" s="10"/>
-      <c r="U168" s="10"/>
-    </row>
-    <row r="169" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A169" s="10"/>
-      <c r="B169" s="10"/>
-      <c r="C169" s="10"/>
-      <c r="D169" s="10"/>
-      <c r="E169" s="10"/>
-      <c r="F169" s="10"/>
-      <c r="G169" s="10"/>
-      <c r="H169" s="10"/>
-      <c r="I169" s="10"/>
-      <c r="J169" s="10"/>
-      <c r="K169" s="10"/>
-      <c r="L169" s="10"/>
-      <c r="M169" s="10"/>
-      <c r="N169" s="10"/>
-      <c r="O169" s="10"/>
-      <c r="P169" s="10"/>
-      <c r="Q169" s="10"/>
-      <c r="R169" s="10"/>
-      <c r="S169" s="10"/>
-      <c r="T169" s="10"/>
-      <c r="U169" s="10"/>
-    </row>
-    <row r="170" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A170" s="10"/>
-      <c r="B170" s="10"/>
-      <c r="C170" s="10"/>
-      <c r="D170" s="10"/>
-      <c r="E170" s="10"/>
-      <c r="F170" s="10"/>
-      <c r="G170" s="10"/>
-      <c r="H170" s="10"/>
-      <c r="I170" s="10"/>
-      <c r="J170" s="10"/>
-      <c r="K170" s="10"/>
-      <c r="L170" s="10"/>
-      <c r="M170" s="10"/>
-      <c r="N170" s="10"/>
-      <c r="O170" s="10"/>
-      <c r="P170" s="10"/>
-      <c r="Q170" s="10"/>
-      <c r="R170" s="10"/>
-      <c r="S170" s="10"/>
-      <c r="T170" s="10"/>
-      <c r="U170" s="10"/>
-    </row>
-    <row r="171" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A171" s="10"/>
-      <c r="B171" s="10"/>
-      <c r="C171" s="10"/>
-      <c r="D171" s="10"/>
-      <c r="E171" s="10"/>
-      <c r="F171" s="10"/>
-      <c r="G171" s="10"/>
-      <c r="H171" s="10"/>
-      <c r="I171" s="10"/>
-      <c r="J171" s="10"/>
-      <c r="K171" s="10"/>
-      <c r="L171" s="10"/>
-      <c r="M171" s="10"/>
-      <c r="N171" s="10"/>
-      <c r="O171" s="10"/>
-      <c r="P171" s="10"/>
-      <c r="Q171" s="10"/>
-      <c r="R171" s="10"/>
-      <c r="S171" s="10"/>
-      <c r="T171" s="10"/>
-      <c r="U171" s="10"/>
-    </row>
-    <row r="172" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A172" s="10"/>
-      <c r="B172" s="10"/>
-      <c r="C172" s="10"/>
-      <c r="D172" s="10"/>
-      <c r="E172" s="10"/>
-      <c r="F172" s="10"/>
-      <c r="G172" s="10"/>
-      <c r="H172" s="10"/>
-      <c r="I172" s="10"/>
-      <c r="J172" s="10"/>
-      <c r="K172" s="10"/>
-      <c r="L172" s="10"/>
-      <c r="M172" s="10"/>
-      <c r="N172" s="10"/>
-      <c r="O172" s="10"/>
-      <c r="P172" s="10"/>
-      <c r="Q172" s="10"/>
-      <c r="R172" s="10"/>
-      <c r="S172" s="10"/>
-      <c r="T172" s="10"/>
-      <c r="U172" s="10"/>
-    </row>
-    <row r="173" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A173" s="10"/>
-      <c r="B173" s="10"/>
-      <c r="C173" s="10"/>
-      <c r="D173" s="10"/>
-      <c r="E173" s="10"/>
-      <c r="F173" s="10"/>
-      <c r="G173" s="10"/>
-      <c r="H173" s="10"/>
-      <c r="I173" s="10"/>
-      <c r="J173" s="10"/>
-      <c r="K173" s="10"/>
-      <c r="L173" s="10"/>
-      <c r="M173" s="10"/>
-      <c r="N173" s="10"/>
-      <c r="O173" s="10"/>
-      <c r="P173" s="10"/>
-      <c r="Q173" s="10"/>
-      <c r="R173" s="10"/>
-      <c r="S173" s="10"/>
-      <c r="T173" s="10"/>
-      <c r="U173" s="10"/>
-    </row>
-    <row r="174" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A174" s="10"/>
-      <c r="B174" s="10"/>
-      <c r="C174" s="10"/>
-      <c r="D174" s="10"/>
-      <c r="E174" s="10"/>
-      <c r="F174" s="10"/>
-      <c r="G174" s="10"/>
-      <c r="H174" s="10"/>
-      <c r="I174" s="10"/>
-      <c r="J174" s="10"/>
       <c r="K174" s="10"/>
       <c r="L174" s="10"/>
       <c r="M174" s="10"/>
@@ -7637,177 +7615,311 @@
       <c r="U174" s="10"/>
     </row>
     <row r="175" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A175" s="10"/>
-      <c r="B175" s="10"/>
-      <c r="C175" s="10"/>
-      <c r="D175" s="10"/>
-      <c r="E175" s="10"/>
-      <c r="F175" s="10"/>
-      <c r="G175" s="10"/>
-      <c r="H175" s="10"/>
-      <c r="I175" s="10"/>
-      <c r="J175" s="10"/>
-      <c r="K175" s="10"/>
-      <c r="L175" s="10"/>
-      <c r="M175" s="10"/>
-      <c r="N175" s="10"/>
-      <c r="O175" s="10"/>
-      <c r="P175" s="10"/>
-      <c r="Q175" s="10"/>
-      <c r="R175" s="10"/>
-      <c r="S175" s="10"/>
-      <c r="T175" s="10"/>
-      <c r="U175" s="10"/>
+      <c r="A175" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B175" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C175" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D175" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E175" s="22">
+        <v>597</v>
+      </c>
+      <c r="F175" s="22"/>
+      <c r="G175" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="H175" s="9"/>
+      <c r="I175" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="J175" s="22">
+        <v>30</v>
+      </c>
+      <c r="K175" s="22"/>
+      <c r="L175" s="22"/>
+      <c r="M175" s="22"/>
+      <c r="N175" s="22"/>
+      <c r="O175" s="22"/>
+      <c r="P175" s="22"/>
+      <c r="Q175" s="22"/>
+      <c r="R175" s="22"/>
+      <c r="S175" s="22"/>
+      <c r="T175" s="22"/>
+      <c r="U175" s="22"/>
     </row>
     <row r="176" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A176" s="10"/>
-      <c r="B176" s="10"/>
-      <c r="C176" s="10"/>
-      <c r="D176" s="10"/>
-      <c r="E176" s="10"/>
-      <c r="F176" s="10"/>
-      <c r="G176" s="10"/>
-      <c r="H176" s="10"/>
-      <c r="I176" s="10"/>
-      <c r="J176" s="10"/>
-      <c r="K176" s="10"/>
-      <c r="L176" s="10"/>
-      <c r="M176" s="10"/>
-      <c r="N176" s="10"/>
-      <c r="O176" s="10"/>
-      <c r="P176" s="10"/>
-      <c r="Q176" s="10"/>
-      <c r="R176" s="10"/>
-      <c r="S176" s="10"/>
-      <c r="T176" s="10"/>
-      <c r="U176" s="10"/>
+      <c r="A176" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C176" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D176" s="22">
+        <v>348</v>
+      </c>
+      <c r="E176" s="22">
+        <v>448</v>
+      </c>
+      <c r="F176" s="22"/>
+      <c r="G176" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H176" s="9"/>
+      <c r="I176" s="9">
+        <f t="shared" ref="I176:I181" si="6">I175+1</f>
+        <v>21</v>
+      </c>
+      <c r="J176" s="22">
+        <v>30</v>
+      </c>
+      <c r="K176" s="22"/>
+      <c r="L176" s="22"/>
+      <c r="M176" s="22"/>
+      <c r="N176" s="22"/>
+      <c r="O176" s="22"/>
+      <c r="P176" s="22"/>
+      <c r="Q176" s="22"/>
+      <c r="R176" s="22"/>
+      <c r="S176" s="22"/>
+      <c r="T176" s="22"/>
+      <c r="U176" s="22"/>
     </row>
     <row r="177" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A177" s="10"/>
-      <c r="B177" s="10"/>
-      <c r="C177" s="10"/>
-      <c r="D177" s="10"/>
-      <c r="E177" s="10"/>
-      <c r="F177" s="10"/>
-      <c r="G177" s="10"/>
-      <c r="H177" s="10"/>
-      <c r="I177" s="10"/>
-      <c r="J177" s="10"/>
-      <c r="K177" s="10"/>
-      <c r="L177" s="10"/>
-      <c r="M177" s="10"/>
-      <c r="N177" s="10"/>
-      <c r="O177" s="10"/>
-      <c r="P177" s="10"/>
-      <c r="Q177" s="10"/>
-      <c r="R177" s="10"/>
-      <c r="S177" s="10"/>
-      <c r="T177" s="10"/>
-      <c r="U177" s="10"/>
+      <c r="A177" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B177" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C177" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D177" s="22">
+        <v>348</v>
+      </c>
+      <c r="E177" s="22">
+        <v>597</v>
+      </c>
+      <c r="F177" s="22"/>
+      <c r="G177" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H177" s="9"/>
+      <c r="I177" s="9">
+        <f t="shared" si="6"/>
+        <v>22</v>
+      </c>
+      <c r="J177" s="22">
+        <v>30</v>
+      </c>
+      <c r="K177" s="22"/>
+      <c r="L177" s="22"/>
+      <c r="M177" s="22"/>
+      <c r="N177" s="22"/>
+      <c r="O177" s="22"/>
+      <c r="P177" s="22"/>
+      <c r="Q177" s="22"/>
+      <c r="R177" s="22"/>
+      <c r="S177" s="22"/>
+      <c r="T177" s="22"/>
+      <c r="U177" s="22"/>
     </row>
     <row r="178" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A178" s="10"/>
-      <c r="B178" s="10"/>
-      <c r="C178" s="10"/>
-      <c r="D178" s="10"/>
-      <c r="E178" s="10"/>
-      <c r="F178" s="10"/>
-      <c r="G178" s="10"/>
-      <c r="H178" s="10"/>
-      <c r="I178" s="10"/>
-      <c r="J178" s="10"/>
-      <c r="K178" s="10"/>
-      <c r="L178" s="10"/>
-      <c r="M178" s="10"/>
-      <c r="N178" s="10"/>
-      <c r="O178" s="10"/>
-      <c r="P178" s="10"/>
-      <c r="Q178" s="10"/>
-      <c r="R178" s="10"/>
-      <c r="S178" s="10"/>
-      <c r="T178" s="10"/>
-      <c r="U178" s="10"/>
+      <c r="A178" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B178" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C178" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D178" s="22">
+        <v>348</v>
+      </c>
+      <c r="E178" s="22">
+        <v>897</v>
+      </c>
+      <c r="F178" s="22"/>
+      <c r="G178" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H178" s="9"/>
+      <c r="I178" s="9">
+        <f t="shared" si="6"/>
+        <v>23</v>
+      </c>
+      <c r="J178" s="22">
+        <v>30</v>
+      </c>
+      <c r="K178" s="22"/>
+      <c r="L178" s="22"/>
+      <c r="M178" s="22"/>
+      <c r="N178" s="22"/>
+      <c r="O178" s="22"/>
+      <c r="P178" s="22"/>
+      <c r="Q178" s="22"/>
+      <c r="R178" s="22"/>
+      <c r="S178" s="22"/>
+      <c r="T178" s="22"/>
+      <c r="U178" s="22"/>
     </row>
     <row r="179" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A179" s="10"/>
-      <c r="B179" s="10"/>
-      <c r="C179" s="10"/>
-      <c r="D179" s="10"/>
-      <c r="E179" s="10"/>
-      <c r="F179" s="10"/>
-      <c r="G179" s="10"/>
-      <c r="H179" s="10"/>
-      <c r="I179" s="10"/>
-      <c r="J179" s="10"/>
-      <c r="K179" s="10"/>
-      <c r="L179" s="10"/>
-      <c r="M179" s="10"/>
-      <c r="N179" s="10"/>
-      <c r="O179" s="10"/>
-      <c r="P179" s="10"/>
-      <c r="Q179" s="10"/>
-      <c r="R179" s="10"/>
-      <c r="S179" s="10"/>
-      <c r="T179" s="10"/>
-      <c r="U179" s="10"/>
+      <c r="A179" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B179" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C179" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D179" s="22">
+        <v>398</v>
+      </c>
+      <c r="E179" s="22">
+        <v>448</v>
+      </c>
+      <c r="F179" s="22"/>
+      <c r="G179" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H179" s="9"/>
+      <c r="I179" s="9">
+        <f t="shared" si="6"/>
+        <v>24</v>
+      </c>
+      <c r="J179" s="22">
+        <v>30</v>
+      </c>
+      <c r="K179" s="22"/>
+      <c r="L179" s="22"/>
+      <c r="M179" s="22"/>
+      <c r="N179" s="22"/>
+      <c r="O179" s="22"/>
+      <c r="P179" s="22"/>
+      <c r="Q179" s="22"/>
+      <c r="R179" s="22"/>
+      <c r="S179" s="22"/>
+      <c r="T179" s="22"/>
+      <c r="U179" s="22"/>
     </row>
     <row r="180" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A180" s="10"/>
-      <c r="B180" s="10"/>
-      <c r="C180" s="10"/>
-      <c r="D180" s="10"/>
-      <c r="E180" s="10"/>
-      <c r="F180" s="10"/>
-      <c r="G180" s="10"/>
-      <c r="H180" s="10"/>
-      <c r="I180" s="10"/>
-      <c r="J180" s="10"/>
-      <c r="K180" s="10"/>
-      <c r="L180" s="10"/>
-      <c r="M180" s="10"/>
-      <c r="N180" s="10"/>
-      <c r="O180" s="10"/>
-      <c r="P180" s="10"/>
-      <c r="Q180" s="10"/>
-      <c r="R180" s="10"/>
-      <c r="S180" s="10"/>
-      <c r="T180" s="10"/>
-      <c r="U180" s="10"/>
+      <c r="A180" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B180" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C180" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D180" s="22">
+        <v>398</v>
+      </c>
+      <c r="E180" s="22">
+        <v>597</v>
+      </c>
+      <c r="F180" s="22"/>
+      <c r="G180" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H180" s="9"/>
+      <c r="I180" s="9">
+        <f t="shared" si="6"/>
+        <v>25</v>
+      </c>
+      <c r="J180" s="22">
+        <v>30</v>
+      </c>
+      <c r="K180" s="22"/>
+      <c r="L180" s="22"/>
+      <c r="M180" s="22"/>
+      <c r="N180" s="22"/>
+      <c r="O180" s="22"/>
+      <c r="P180" s="22"/>
+      <c r="Q180" s="22"/>
+      <c r="R180" s="22"/>
+      <c r="S180" s="22"/>
+      <c r="T180" s="22"/>
+      <c r="U180" s="22"/>
     </row>
     <row r="181" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A181" s="10"/>
-      <c r="B181" s="10"/>
-      <c r="C181" s="10"/>
-      <c r="D181" s="10"/>
-      <c r="E181" s="10"/>
-      <c r="F181" s="10"/>
-      <c r="G181" s="10"/>
-      <c r="H181" s="10"/>
-      <c r="I181" s="10"/>
-      <c r="J181" s="10"/>
-      <c r="K181" s="10"/>
-      <c r="L181" s="10"/>
-      <c r="M181" s="10"/>
-      <c r="N181" s="10"/>
-      <c r="O181" s="10"/>
-      <c r="P181" s="10"/>
-      <c r="Q181" s="10"/>
-      <c r="R181" s="10"/>
-      <c r="S181" s="10"/>
-      <c r="T181" s="10"/>
-      <c r="U181" s="10"/>
+      <c r="A181" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B181" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C181" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D181" s="22">
+        <v>398</v>
+      </c>
+      <c r="E181" s="22">
+        <v>897</v>
+      </c>
+      <c r="F181" s="22"/>
+      <c r="G181" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H181" s="9"/>
+      <c r="I181" s="9">
+        <f t="shared" si="6"/>
+        <v>26</v>
+      </c>
+      <c r="J181" s="22">
+        <v>30</v>
+      </c>
+      <c r="K181" s="22"/>
+      <c r="L181" s="22"/>
+      <c r="M181" s="22"/>
+      <c r="N181" s="22"/>
+      <c r="O181" s="22"/>
+      <c r="P181" s="22"/>
+      <c r="Q181" s="22"/>
+      <c r="R181" s="22"/>
+      <c r="S181" s="22"/>
+      <c r="T181" s="22"/>
+      <c r="U181" s="22"/>
     </row>
     <row r="182" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A182" s="10"/>
-      <c r="B182" s="10"/>
-      <c r="C182" s="10"/>
-      <c r="D182" s="10"/>
-      <c r="E182" s="10"/>
-      <c r="F182" s="10"/>
-      <c r="G182" s="10"/>
-      <c r="H182" s="10"/>
-      <c r="I182" s="10"/>
-      <c r="J182" s="10"/>
+      <c r="A182" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="C182" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D182" s="22">
+        <v>698</v>
+      </c>
+      <c r="E182" s="22">
+        <v>147</v>
+      </c>
+      <c r="F182" s="22"/>
+      <c r="G182" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H182" s="9"/>
+      <c r="I182" s="9">
+        <v>7</v>
+      </c>
+      <c r="J182" s="22">
+        <v>30</v>
+      </c>
       <c r="K182" s="10"/>
       <c r="L182" s="10"/>
       <c r="M182" s="10"/>
@@ -7821,16 +7933,33 @@
       <c r="U182" s="10"/>
     </row>
     <row r="183" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A183" s="10"/>
-      <c r="B183" s="10"/>
-      <c r="C183" s="10"/>
-      <c r="D183" s="10"/>
-      <c r="E183" s="10"/>
-      <c r="F183" s="10"/>
-      <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
-      <c r="I183" s="10"/>
-      <c r="J183" s="10"/>
+      <c r="A183" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B183" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C183" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D183" s="22">
+        <v>698</v>
+      </c>
+      <c r="E183" s="22">
+        <v>297</v>
+      </c>
+      <c r="F183" s="22"/>
+      <c r="G183" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H183" s="9"/>
+      <c r="I183" s="9">
+        <f>I182+1</f>
+        <v>8</v>
+      </c>
+      <c r="J183" s="22">
+        <v>30</v>
+      </c>
       <c r="K183" s="10"/>
       <c r="L183" s="10"/>
       <c r="M183" s="10"/>
@@ -7844,16 +7973,33 @@
       <c r="U183" s="10"/>
     </row>
     <row r="184" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A184" s="10"/>
-      <c r="B184" s="10"/>
-      <c r="C184" s="10"/>
-      <c r="D184" s="10"/>
-      <c r="E184" s="10"/>
-      <c r="F184" s="10"/>
-      <c r="G184" s="10"/>
-      <c r="H184" s="10"/>
-      <c r="I184" s="10"/>
-      <c r="J184" s="10"/>
+      <c r="A184" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B184" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C184" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D184" s="22">
+        <v>698</v>
+      </c>
+      <c r="E184" s="22">
+        <v>347</v>
+      </c>
+      <c r="F184" s="22"/>
+      <c r="G184" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H184" s="9"/>
+      <c r="I184" s="9">
+        <f t="shared" ref="I184:I203" si="7">I183+1</f>
+        <v>9</v>
+      </c>
+      <c r="J184" s="22">
+        <v>30</v>
+      </c>
       <c r="K184" s="10"/>
       <c r="L184" s="10"/>
       <c r="M184" s="10"/>
@@ -7867,16 +8013,33 @@
       <c r="U184" s="10"/>
     </row>
     <row r="185" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A185" s="10"/>
-      <c r="B185" s="10"/>
-      <c r="C185" s="10"/>
-      <c r="D185" s="10"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="10"/>
-      <c r="G185" s="10"/>
-      <c r="H185" s="10"/>
-      <c r="I185" s="10"/>
-      <c r="J185" s="10"/>
+      <c r="A185" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B185" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="C185" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D185" s="22">
+        <v>698</v>
+      </c>
+      <c r="E185" s="22">
+        <v>397</v>
+      </c>
+      <c r="F185" s="22"/>
+      <c r="G185" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H185" s="9"/>
+      <c r="I185" s="9">
+        <f t="shared" si="7"/>
+        <v>10</v>
+      </c>
+      <c r="J185" s="22">
+        <v>30</v>
+      </c>
       <c r="K185" s="10"/>
       <c r="L185" s="10"/>
       <c r="M185" s="10"/>
@@ -7890,16 +8053,33 @@
       <c r="U185" s="10"/>
     </row>
     <row r="186" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A186" s="10"/>
-      <c r="B186" s="10"/>
-      <c r="C186" s="10"/>
-      <c r="D186" s="10"/>
-      <c r="E186" s="10"/>
-      <c r="F186" s="10"/>
-      <c r="G186" s="10"/>
-      <c r="H186" s="10"/>
-      <c r="I186" s="10"/>
-      <c r="J186" s="10"/>
+      <c r="A186" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B186" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C186" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D186" s="22">
+        <v>698</v>
+      </c>
+      <c r="E186" s="22">
+        <v>447</v>
+      </c>
+      <c r="F186" s="22"/>
+      <c r="G186" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H186" s="9"/>
+      <c r="I186" s="9">
+        <f t="shared" si="7"/>
+        <v>11</v>
+      </c>
+      <c r="J186" s="22">
+        <v>30</v>
+      </c>
       <c r="K186" s="10"/>
       <c r="L186" s="10"/>
       <c r="M186" s="10"/>
@@ -7913,16 +8093,33 @@
       <c r="U186" s="10"/>
     </row>
     <row r="187" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A187" s="10"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="10"/>
-      <c r="D187" s="10"/>
-      <c r="E187" s="10"/>
-      <c r="F187" s="10"/>
-      <c r="G187" s="10"/>
-      <c r="H187" s="10"/>
-      <c r="I187" s="10"/>
-      <c r="J187" s="10"/>
+      <c r="A187" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B187" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C187" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D187" s="22">
+        <v>698</v>
+      </c>
+      <c r="E187" s="22">
+        <v>497</v>
+      </c>
+      <c r="F187" s="22"/>
+      <c r="G187" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H187" s="9"/>
+      <c r="I187" s="9">
+        <f t="shared" si="7"/>
+        <v>12</v>
+      </c>
+      <c r="J187" s="22">
+        <v>30</v>
+      </c>
       <c r="K187" s="10"/>
       <c r="L187" s="10"/>
       <c r="M187" s="10"/>
@@ -7936,16 +8133,33 @@
       <c r="U187" s="10"/>
     </row>
     <row r="188" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
-      <c r="G188" s="10"/>
-      <c r="H188" s="10"/>
-      <c r="I188" s="10"/>
-      <c r="J188" s="10"/>
+      <c r="A188" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B188" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="C188" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D188" s="22">
+        <v>698</v>
+      </c>
+      <c r="E188" s="22">
+        <v>597</v>
+      </c>
+      <c r="F188" s="22"/>
+      <c r="G188" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H188" s="9"/>
+      <c r="I188" s="9">
+        <f t="shared" si="7"/>
+        <v>13</v>
+      </c>
+      <c r="J188" s="22">
+        <v>30</v>
+      </c>
       <c r="K188" s="10"/>
       <c r="L188" s="10"/>
       <c r="M188" s="10"/>
@@ -7959,16 +8173,33 @@
       <c r="U188" s="10"/>
     </row>
     <row r="189" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
-      <c r="G189" s="10"/>
-      <c r="H189" s="10"/>
-      <c r="I189" s="10"/>
-      <c r="J189" s="10"/>
+      <c r="A189" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B189" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C189" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D189" s="22">
+        <v>798</v>
+      </c>
+      <c r="E189" s="22">
+        <v>147</v>
+      </c>
+      <c r="F189" s="22"/>
+      <c r="G189" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H189" s="9"/>
+      <c r="I189" s="9">
+        <f t="shared" si="7"/>
+        <v>14</v>
+      </c>
+      <c r="J189" s="22">
+        <v>30</v>
+      </c>
       <c r="K189" s="10"/>
       <c r="L189" s="10"/>
       <c r="M189" s="10"/>
@@ -7982,16 +8213,33 @@
       <c r="U189" s="10"/>
     </row>
     <row r="190" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
-      <c r="G190" s="10"/>
-      <c r="H190" s="10"/>
-      <c r="I190" s="10"/>
-      <c r="J190" s="10"/>
+      <c r="A190" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B190" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C190" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D190" s="22">
+        <v>798</v>
+      </c>
+      <c r="E190" s="22">
+        <v>297</v>
+      </c>
+      <c r="F190" s="22"/>
+      <c r="G190" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H190" s="9"/>
+      <c r="I190" s="9">
+        <f t="shared" si="7"/>
+        <v>15</v>
+      </c>
+      <c r="J190" s="22">
+        <v>30</v>
+      </c>
       <c r="K190" s="10"/>
       <c r="L190" s="10"/>
       <c r="M190" s="10"/>
@@ -8005,16 +8253,33 @@
       <c r="U190" s="10"/>
     </row>
     <row r="191" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10"/>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
-      <c r="G191" s="10"/>
-      <c r="H191" s="10"/>
-      <c r="I191" s="10"/>
-      <c r="J191" s="10"/>
+      <c r="A191" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B191" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C191" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D191" s="22">
+        <v>798</v>
+      </c>
+      <c r="E191" s="22">
+        <v>347</v>
+      </c>
+      <c r="F191" s="22"/>
+      <c r="G191" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H191" s="9"/>
+      <c r="I191" s="9">
+        <f t="shared" si="7"/>
+        <v>16</v>
+      </c>
+      <c r="J191" s="22">
+        <v>30</v>
+      </c>
       <c r="K191" s="10"/>
       <c r="L191" s="10"/>
       <c r="M191" s="10"/>
@@ -8028,16 +8293,33 @@
       <c r="U191" s="10"/>
     </row>
     <row r="192" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A192" s="10"/>
-      <c r="B192" s="10"/>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10"/>
-      <c r="E192" s="10"/>
-      <c r="F192" s="10"/>
-      <c r="G192" s="10"/>
-      <c r="H192" s="10"/>
-      <c r="I192" s="10"/>
-      <c r="J192" s="10"/>
+      <c r="A192" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B192" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C192" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D192" s="22">
+        <v>798</v>
+      </c>
+      <c r="E192" s="22">
+        <v>397</v>
+      </c>
+      <c r="F192" s="22"/>
+      <c r="G192" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H192" s="9"/>
+      <c r="I192" s="9">
+        <f t="shared" si="7"/>
+        <v>17</v>
+      </c>
+      <c r="J192" s="22">
+        <v>30</v>
+      </c>
       <c r="K192" s="10"/>
       <c r="L192" s="10"/>
       <c r="M192" s="10"/>
@@ -8051,16 +8333,33 @@
       <c r="U192" s="10"/>
     </row>
     <row r="193" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A193" s="10"/>
-      <c r="B193" s="10"/>
-      <c r="C193" s="10"/>
-      <c r="D193" s="10"/>
-      <c r="E193" s="10"/>
-      <c r="F193" s="10"/>
-      <c r="G193" s="10"/>
-      <c r="H193" s="10"/>
-      <c r="I193" s="10"/>
-      <c r="J193" s="10"/>
+      <c r="A193" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B193" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C193" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D193" s="22">
+        <v>798</v>
+      </c>
+      <c r="E193" s="22">
+        <v>447</v>
+      </c>
+      <c r="F193" s="22"/>
+      <c r="G193" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H193" s="9"/>
+      <c r="I193" s="9">
+        <f t="shared" si="7"/>
+        <v>18</v>
+      </c>
+      <c r="J193" s="22">
+        <v>30</v>
+      </c>
       <c r="K193" s="10"/>
       <c r="L193" s="10"/>
       <c r="M193" s="10"/>
@@ -8074,16 +8373,33 @@
       <c r="U193" s="10"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A194" s="10"/>
-      <c r="B194" s="10"/>
-      <c r="C194" s="10"/>
-      <c r="D194" s="10"/>
-      <c r="E194" s="10"/>
-      <c r="F194" s="10"/>
-      <c r="G194" s="10"/>
-      <c r="H194" s="10"/>
-      <c r="I194" s="10"/>
-      <c r="J194" s="10"/>
+      <c r="A194" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B194" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C194" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D194" s="22">
+        <v>798</v>
+      </c>
+      <c r="E194" s="22">
+        <v>497</v>
+      </c>
+      <c r="F194" s="22"/>
+      <c r="G194" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H194" s="9"/>
+      <c r="I194" s="9">
+        <f t="shared" si="7"/>
+        <v>19</v>
+      </c>
+      <c r="J194" s="22">
+        <v>30</v>
+      </c>
       <c r="K194" s="10"/>
       <c r="L194" s="10"/>
       <c r="M194" s="10"/>
@@ -8097,16 +8413,33 @@
       <c r="U194" s="10"/>
     </row>
     <row r="195" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A195" s="10"/>
-      <c r="B195" s="10"/>
-      <c r="C195" s="10"/>
-      <c r="D195" s="10"/>
-      <c r="E195" s="10"/>
-      <c r="F195" s="10"/>
-      <c r="G195" s="10"/>
-      <c r="H195" s="10"/>
-      <c r="I195" s="10"/>
-      <c r="J195" s="10"/>
+      <c r="A195" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B195" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C195" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D195" s="22">
+        <v>798</v>
+      </c>
+      <c r="E195" s="22">
+        <v>597</v>
+      </c>
+      <c r="F195" s="22"/>
+      <c r="G195" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H195" s="9"/>
+      <c r="I195" s="9">
+        <f t="shared" si="7"/>
+        <v>20</v>
+      </c>
+      <c r="J195" s="22">
+        <v>30</v>
+      </c>
       <c r="K195" s="10"/>
       <c r="L195" s="10"/>
       <c r="M195" s="10"/>
@@ -8120,16 +8453,33 @@
       <c r="U195" s="10"/>
     </row>
     <row r="196" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
-      <c r="D196" s="10"/>
-      <c r="E196" s="10"/>
-      <c r="F196" s="10"/>
-      <c r="G196" s="10"/>
-      <c r="H196" s="10"/>
-      <c r="I196" s="10"/>
-      <c r="J196" s="10"/>
+      <c r="A196" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B196" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C196" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D196" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E196" s="22">
+        <v>397</v>
+      </c>
+      <c r="F196" s="22"/>
+      <c r="G196" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H196" s="9"/>
+      <c r="I196" s="9">
+        <f t="shared" si="7"/>
+        <v>21</v>
+      </c>
+      <c r="J196" s="22">
+        <v>30</v>
+      </c>
       <c r="K196" s="10"/>
       <c r="L196" s="10"/>
       <c r="M196" s="10"/>
@@ -8143,16 +8493,33 @@
       <c r="U196" s="10"/>
     </row>
     <row r="197" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A197" s="10"/>
-      <c r="B197" s="10"/>
-      <c r="C197" s="10"/>
-      <c r="D197" s="10"/>
-      <c r="E197" s="10"/>
-      <c r="F197" s="10"/>
-      <c r="G197" s="10"/>
-      <c r="H197" s="10"/>
-      <c r="I197" s="10"/>
-      <c r="J197" s="10"/>
+      <c r="A197" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B197" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C197" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D197" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E197" s="22">
+        <v>597</v>
+      </c>
+      <c r="F197" s="22"/>
+      <c r="G197" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H197" s="9"/>
+      <c r="I197" s="9">
+        <f t="shared" si="7"/>
+        <v>22</v>
+      </c>
+      <c r="J197" s="22">
+        <v>30</v>
+      </c>
       <c r="K197" s="10"/>
       <c r="L197" s="10"/>
       <c r="M197" s="10"/>
@@ -8166,464 +8533,244 @@
       <c r="U197" s="10"/>
     </row>
     <row r="198" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A198" s="10"/>
-      <c r="B198" s="10"/>
-      <c r="C198" s="10"/>
-      <c r="D198" s="10"/>
-      <c r="E198" s="10"/>
-      <c r="F198" s="10"/>
-      <c r="G198" s="10"/>
-      <c r="H198" s="10"/>
-      <c r="I198" s="10"/>
-      <c r="J198" s="10"/>
-      <c r="K198" s="10"/>
-      <c r="L198" s="10"/>
-      <c r="M198" s="10"/>
-      <c r="N198" s="10"/>
-      <c r="O198" s="10"/>
-      <c r="P198" s="10"/>
-      <c r="Q198" s="10"/>
-      <c r="R198" s="10"/>
-      <c r="S198" s="10"/>
-      <c r="T198" s="10"/>
-      <c r="U198" s="10"/>
+      <c r="A198" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B198" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C198" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D198" s="22">
+        <v>348</v>
+      </c>
+      <c r="E198" s="22">
+        <v>448</v>
+      </c>
+      <c r="F198" s="22"/>
+      <c r="G198" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H198" s="9"/>
+      <c r="I198" s="9">
+        <f t="shared" si="7"/>
+        <v>23</v>
+      </c>
+      <c r="J198" s="22">
+        <v>30</v>
+      </c>
+      <c r="K198" s="22"/>
+      <c r="L198" s="22"/>
+      <c r="M198" s="22"/>
+      <c r="N198" s="22"/>
+      <c r="O198" s="22"/>
+      <c r="P198" s="22"/>
+      <c r="Q198" s="22"/>
+      <c r="R198" s="22"/>
+      <c r="S198" s="22"/>
+      <c r="T198" s="22"/>
+      <c r="U198" s="22"/>
     </row>
     <row r="199" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A199" s="10"/>
-      <c r="B199" s="10"/>
-      <c r="C199" s="10"/>
-      <c r="D199" s="10"/>
-      <c r="E199" s="10"/>
-      <c r="F199" s="10"/>
-      <c r="G199" s="10"/>
-      <c r="H199" s="10"/>
-      <c r="I199" s="10"/>
-      <c r="J199" s="10"/>
-      <c r="K199" s="10"/>
-      <c r="L199" s="10"/>
-      <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="10"/>
-      <c r="P199" s="10"/>
-      <c r="Q199" s="10"/>
-      <c r="R199" s="10"/>
-      <c r="S199" s="10"/>
-      <c r="T199" s="10"/>
-      <c r="U199" s="10"/>
+      <c r="A199" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B199" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C199" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D199" s="22">
+        <v>348</v>
+      </c>
+      <c r="E199" s="22">
+        <v>597</v>
+      </c>
+      <c r="F199" s="22"/>
+      <c r="G199" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H199" s="9"/>
+      <c r="I199" s="9">
+        <f t="shared" si="7"/>
+        <v>24</v>
+      </c>
+      <c r="J199" s="22">
+        <v>30</v>
+      </c>
+      <c r="K199" s="22"/>
+      <c r="L199" s="22"/>
+      <c r="M199" s="22"/>
+      <c r="N199" s="22"/>
+      <c r="O199" s="22"/>
+      <c r="P199" s="22"/>
+      <c r="Q199" s="22"/>
+      <c r="R199" s="22"/>
+      <c r="S199" s="22"/>
+      <c r="T199" s="22"/>
+      <c r="U199" s="22"/>
     </row>
     <row r="200" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A200" s="10"/>
-      <c r="B200" s="10"/>
-      <c r="C200" s="10"/>
-      <c r="D200" s="10"/>
-      <c r="E200" s="10"/>
-      <c r="F200" s="10"/>
-      <c r="G200" s="10"/>
-      <c r="H200" s="10"/>
-      <c r="I200" s="10"/>
-      <c r="J200" s="10"/>
-      <c r="K200" s="10"/>
-      <c r="L200" s="10"/>
-      <c r="M200" s="10"/>
-      <c r="N200" s="10"/>
-      <c r="O200" s="10"/>
-      <c r="P200" s="10"/>
-      <c r="Q200" s="10"/>
-      <c r="R200" s="10"/>
-      <c r="S200" s="10"/>
-      <c r="T200" s="10"/>
-      <c r="U200" s="10"/>
+      <c r="A200" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B200" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C200" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D200" s="22">
+        <v>348</v>
+      </c>
+      <c r="E200" s="22">
+        <v>897</v>
+      </c>
+      <c r="F200" s="22"/>
+      <c r="G200" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H200" s="9"/>
+      <c r="I200" s="9">
+        <f t="shared" si="7"/>
+        <v>25</v>
+      </c>
+      <c r="J200" s="22">
+        <v>30</v>
+      </c>
+      <c r="K200" s="22"/>
+      <c r="L200" s="22"/>
+      <c r="M200" s="22"/>
+      <c r="N200" s="22"/>
+      <c r="O200" s="22"/>
+      <c r="P200" s="22"/>
+      <c r="Q200" s="22"/>
+      <c r="R200" s="22"/>
+      <c r="S200" s="22"/>
+      <c r="T200" s="22"/>
+      <c r="U200" s="22"/>
     </row>
     <row r="201" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10"/>
-      <c r="E201" s="10"/>
-      <c r="F201" s="10"/>
-      <c r="G201" s="10"/>
-      <c r="H201" s="10"/>
-      <c r="I201" s="10"/>
-      <c r="J201" s="10"/>
-      <c r="K201" s="10"/>
-      <c r="L201" s="10"/>
-      <c r="M201" s="10"/>
-      <c r="N201" s="10"/>
-      <c r="O201" s="10"/>
-      <c r="P201" s="10"/>
-      <c r="Q201" s="10"/>
-      <c r="R201" s="10"/>
-      <c r="S201" s="10"/>
-      <c r="T201" s="10"/>
-      <c r="U201" s="10"/>
+      <c r="A201" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B201" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C201" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D201" s="22">
+        <v>398</v>
+      </c>
+      <c r="E201" s="22">
+        <v>448</v>
+      </c>
+      <c r="F201" s="22"/>
+      <c r="G201" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H201" s="9"/>
+      <c r="I201" s="9">
+        <f t="shared" si="7"/>
+        <v>26</v>
+      </c>
+      <c r="J201" s="22">
+        <v>30</v>
+      </c>
+      <c r="K201" s="22"/>
+      <c r="L201" s="22"/>
+      <c r="M201" s="22"/>
+      <c r="N201" s="22"/>
+      <c r="O201" s="22"/>
+      <c r="P201" s="22"/>
+      <c r="Q201" s="22"/>
+      <c r="R201" s="22"/>
+      <c r="S201" s="22"/>
+      <c r="T201" s="22"/>
+      <c r="U201" s="22"/>
     </row>
     <row r="202" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A202" s="10"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10"/>
-      <c r="E202" s="10"/>
-      <c r="F202" s="10"/>
-      <c r="G202" s="10"/>
-      <c r="H202" s="10"/>
-      <c r="I202" s="10"/>
-      <c r="J202" s="10"/>
-      <c r="K202" s="10"/>
-      <c r="L202" s="10"/>
-      <c r="M202" s="10"/>
-      <c r="N202" s="10"/>
-      <c r="O202" s="10"/>
-      <c r="P202" s="10"/>
-      <c r="Q202" s="10"/>
-      <c r="R202" s="10"/>
-      <c r="S202" s="10"/>
-      <c r="T202" s="10"/>
-      <c r="U202" s="10"/>
+      <c r="A202" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B202" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C202" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D202" s="22">
+        <v>398</v>
+      </c>
+      <c r="E202" s="22">
+        <v>597</v>
+      </c>
+      <c r="F202" s="22"/>
+      <c r="G202" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H202" s="9"/>
+      <c r="I202" s="9">
+        <f t="shared" si="7"/>
+        <v>27</v>
+      </c>
+      <c r="J202" s="22">
+        <v>30</v>
+      </c>
+      <c r="K202" s="22"/>
+      <c r="L202" s="22"/>
+      <c r="M202" s="22"/>
+      <c r="N202" s="22"/>
+      <c r="O202" s="22"/>
+      <c r="P202" s="22"/>
+      <c r="Q202" s="22"/>
+      <c r="R202" s="22"/>
+      <c r="S202" s="22"/>
+      <c r="T202" s="22"/>
+      <c r="U202" s="22"/>
     </row>
     <row r="203" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A203" s="10"/>
-      <c r="B203" s="10"/>
-      <c r="C203" s="10"/>
-      <c r="D203" s="10"/>
-      <c r="E203" s="10"/>
-      <c r="F203" s="10"/>
-      <c r="G203" s="10"/>
-      <c r="H203" s="10"/>
-      <c r="I203" s="10"/>
-      <c r="J203" s="10"/>
-      <c r="K203" s="10"/>
-      <c r="L203" s="10"/>
-      <c r="M203" s="10"/>
-      <c r="N203" s="10"/>
-      <c r="O203" s="10"/>
-      <c r="P203" s="10"/>
-      <c r="Q203" s="10"/>
-      <c r="R203" s="10"/>
-      <c r="S203" s="10"/>
-      <c r="T203" s="10"/>
-      <c r="U203" s="10"/>
-    </row>
-    <row r="204" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A204" s="10"/>
-      <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10"/>
-      <c r="G204" s="10"/>
-      <c r="H204" s="10"/>
-      <c r="I204" s="10"/>
-      <c r="J204" s="10"/>
-      <c r="K204" s="10"/>
-      <c r="L204" s="10"/>
-      <c r="M204" s="10"/>
-      <c r="N204" s="10"/>
-      <c r="O204" s="10"/>
-      <c r="P204" s="10"/>
-      <c r="Q204" s="10"/>
-      <c r="R204" s="10"/>
-      <c r="S204" s="10"/>
-      <c r="T204" s="10"/>
-      <c r="U204" s="10"/>
-    </row>
-    <row r="205" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A205" s="10"/>
-      <c r="B205" s="10"/>
-      <c r="C205" s="10"/>
-      <c r="D205" s="10"/>
-      <c r="E205" s="10"/>
-      <c r="F205" s="10"/>
-      <c r="G205" s="10"/>
-      <c r="H205" s="10"/>
-      <c r="I205" s="10"/>
-      <c r="J205" s="10"/>
-      <c r="K205" s="10"/>
-      <c r="L205" s="10"/>
-      <c r="M205" s="10"/>
-      <c r="N205" s="10"/>
-      <c r="O205" s="10"/>
-      <c r="P205" s="10"/>
-      <c r="Q205" s="10"/>
-      <c r="R205" s="10"/>
-      <c r="S205" s="10"/>
-      <c r="T205" s="10"/>
-      <c r="U205" s="10"/>
-    </row>
-    <row r="206" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10"/>
-      <c r="E206" s="10"/>
-      <c r="F206" s="10"/>
-      <c r="G206" s="10"/>
-      <c r="H206" s="10"/>
-      <c r="I206" s="10"/>
-      <c r="J206" s="10"/>
-      <c r="K206" s="10"/>
-      <c r="L206" s="10"/>
-      <c r="M206" s="10"/>
-      <c r="N206" s="10"/>
-      <c r="O206" s="10"/>
-      <c r="P206" s="10"/>
-      <c r="Q206" s="10"/>
-      <c r="R206" s="10"/>
-      <c r="S206" s="10"/>
-      <c r="T206" s="10"/>
-      <c r="U206" s="10"/>
-    </row>
-    <row r="207" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A207" s="10"/>
-      <c r="B207" s="10"/>
-      <c r="C207" s="10"/>
-      <c r="D207" s="10"/>
-      <c r="E207" s="10"/>
-      <c r="F207" s="10"/>
-      <c r="G207" s="10"/>
-      <c r="H207" s="10"/>
-      <c r="I207" s="10"/>
-      <c r="J207" s="10"/>
-      <c r="K207" s="10"/>
-      <c r="L207" s="10"/>
-      <c r="M207" s="10"/>
-      <c r="N207" s="10"/>
-      <c r="O207" s="10"/>
-      <c r="P207" s="10"/>
-      <c r="Q207" s="10"/>
-      <c r="R207" s="10"/>
-      <c r="S207" s="10"/>
-      <c r="T207" s="10"/>
-      <c r="U207" s="10"/>
-    </row>
-    <row r="208" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A208" s="10"/>
-      <c r="B208" s="10"/>
-      <c r="C208" s="10"/>
-      <c r="D208" s="10"/>
-      <c r="E208" s="10"/>
-      <c r="F208" s="10"/>
-      <c r="G208" s="10"/>
-      <c r="H208" s="10"/>
-      <c r="I208" s="10"/>
-      <c r="J208" s="10"/>
-      <c r="K208" s="10"/>
-      <c r="L208" s="10"/>
-      <c r="M208" s="10"/>
-      <c r="N208" s="10"/>
-      <c r="O208" s="10"/>
-      <c r="P208" s="10"/>
-      <c r="Q208" s="10"/>
-      <c r="R208" s="10"/>
-      <c r="S208" s="10"/>
-      <c r="T208" s="10"/>
-      <c r="U208" s="10"/>
-    </row>
-    <row r="209" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A209" s="10"/>
-      <c r="B209" s="10"/>
-      <c r="C209" s="10"/>
-      <c r="D209" s="10"/>
-      <c r="E209" s="10"/>
-      <c r="F209" s="10"/>
-      <c r="G209" s="10"/>
-      <c r="H209" s="10"/>
-      <c r="I209" s="10"/>
-      <c r="J209" s="10"/>
-      <c r="K209" s="10"/>
-      <c r="L209" s="10"/>
-      <c r="M209" s="10"/>
-      <c r="N209" s="10"/>
-      <c r="O209" s="10"/>
-      <c r="P209" s="10"/>
-      <c r="Q209" s="10"/>
-      <c r="R209" s="10"/>
-      <c r="S209" s="10"/>
-      <c r="T209" s="10"/>
-      <c r="U209" s="10"/>
-    </row>
-    <row r="210" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A210" s="10"/>
-      <c r="B210" s="10"/>
-      <c r="C210" s="10"/>
-      <c r="D210" s="10"/>
-      <c r="E210" s="10"/>
-      <c r="F210" s="10"/>
-      <c r="G210" s="10"/>
-      <c r="H210" s="10"/>
-      <c r="I210" s="10"/>
-      <c r="J210" s="10"/>
-      <c r="K210" s="10"/>
-      <c r="L210" s="10"/>
-      <c r="M210" s="10"/>
-      <c r="N210" s="10"/>
-      <c r="O210" s="10"/>
-      <c r="P210" s="10"/>
-      <c r="Q210" s="10"/>
-      <c r="R210" s="10"/>
-      <c r="S210" s="10"/>
-      <c r="T210" s="10"/>
-      <c r="U210" s="10"/>
-    </row>
-    <row r="211" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A211" s="10"/>
-      <c r="B211" s="10"/>
-      <c r="C211" s="10"/>
-      <c r="D211" s="10"/>
-      <c r="E211" s="10"/>
-      <c r="F211" s="10"/>
-      <c r="G211" s="10"/>
-      <c r="H211" s="10"/>
-      <c r="I211" s="10"/>
-      <c r="J211" s="10"/>
-      <c r="K211" s="10"/>
-      <c r="L211" s="10"/>
-      <c r="M211" s="10"/>
-      <c r="N211" s="10"/>
-      <c r="O211" s="10"/>
-      <c r="P211" s="10"/>
-      <c r="Q211" s="10"/>
-      <c r="R211" s="10"/>
-      <c r="S211" s="10"/>
-      <c r="T211" s="10"/>
-      <c r="U211" s="10"/>
-    </row>
-    <row r="212" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A212" s="10"/>
-      <c r="B212" s="10"/>
-      <c r="C212" s="10"/>
-      <c r="D212" s="10"/>
-      <c r="E212" s="10"/>
-      <c r="F212" s="10"/>
-      <c r="G212" s="10"/>
-      <c r="H212" s="10"/>
-      <c r="I212" s="10"/>
-      <c r="J212" s="10"/>
-      <c r="K212" s="10"/>
-      <c r="L212" s="10"/>
-      <c r="M212" s="10"/>
-      <c r="N212" s="10"/>
-      <c r="O212" s="10"/>
-      <c r="P212" s="10"/>
-      <c r="Q212" s="10"/>
-      <c r="R212" s="10"/>
-      <c r="S212" s="10"/>
-      <c r="T212" s="10"/>
-      <c r="U212" s="10"/>
-    </row>
-    <row r="213" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A213" s="10"/>
-      <c r="B213" s="10"/>
-      <c r="C213" s="10"/>
-      <c r="D213" s="10"/>
-      <c r="E213" s="10"/>
-      <c r="F213" s="10"/>
-      <c r="G213" s="10"/>
-      <c r="H213" s="10"/>
-      <c r="I213" s="10"/>
-      <c r="J213" s="10"/>
-      <c r="K213" s="10"/>
-      <c r="L213" s="10"/>
-      <c r="M213" s="10"/>
-      <c r="N213" s="10"/>
-      <c r="O213" s="10"/>
-      <c r="P213" s="10"/>
-      <c r="Q213" s="10"/>
-      <c r="R213" s="10"/>
-      <c r="S213" s="10"/>
-      <c r="T213" s="10"/>
-      <c r="U213" s="10"/>
-    </row>
-    <row r="214" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A214" s="10"/>
-      <c r="B214" s="10"/>
-      <c r="C214" s="10"/>
-      <c r="D214" s="10"/>
-      <c r="E214" s="10"/>
-      <c r="F214" s="10"/>
-      <c r="G214" s="10"/>
-      <c r="H214" s="10"/>
-      <c r="I214" s="10"/>
-      <c r="J214" s="10"/>
-      <c r="K214" s="10"/>
-      <c r="L214" s="10"/>
-      <c r="M214" s="10"/>
-      <c r="N214" s="10"/>
-      <c r="O214" s="10"/>
-      <c r="P214" s="10"/>
-      <c r="Q214" s="10"/>
-      <c r="R214" s="10"/>
-      <c r="S214" s="10"/>
-      <c r="T214" s="10"/>
-      <c r="U214" s="10"/>
-    </row>
-    <row r="215" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A215" s="10"/>
-      <c r="B215" s="10"/>
-      <c r="C215" s="10"/>
-      <c r="D215" s="10"/>
-      <c r="E215" s="10"/>
-      <c r="F215" s="10"/>
-      <c r="G215" s="10"/>
-      <c r="H215" s="10"/>
-      <c r="I215" s="10"/>
-      <c r="J215" s="10"/>
-      <c r="K215" s="10"/>
-      <c r="L215" s="10"/>
-      <c r="M215" s="10"/>
-      <c r="N215" s="10"/>
-      <c r="O215" s="10"/>
-      <c r="P215" s="10"/>
-      <c r="Q215" s="10"/>
-      <c r="R215" s="10"/>
-      <c r="S215" s="10"/>
-      <c r="T215" s="10"/>
-      <c r="U215" s="10"/>
-    </row>
-    <row r="216" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A216" s="10"/>
-      <c r="B216" s="10"/>
-      <c r="C216" s="10"/>
-      <c r="D216" s="10"/>
-      <c r="E216" s="10"/>
-      <c r="F216" s="10"/>
-      <c r="G216" s="10"/>
-      <c r="H216" s="10"/>
-      <c r="I216" s="10"/>
-      <c r="J216" s="10"/>
-      <c r="K216" s="10"/>
-      <c r="L216" s="10"/>
-      <c r="M216" s="10"/>
-      <c r="N216" s="10"/>
-      <c r="O216" s="10"/>
-      <c r="P216" s="10"/>
-      <c r="Q216" s="10"/>
-      <c r="R216" s="10"/>
-      <c r="S216" s="10"/>
-      <c r="T216" s="10"/>
-      <c r="U216" s="10"/>
-    </row>
-    <row r="217" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A217" s="10"/>
-      <c r="B217" s="10"/>
-      <c r="C217" s="10"/>
-      <c r="D217" s="10"/>
-      <c r="E217" s="10"/>
-      <c r="F217" s="10"/>
-      <c r="G217" s="10"/>
-      <c r="H217" s="10"/>
-      <c r="I217" s="10"/>
-      <c r="J217" s="10"/>
-      <c r="K217" s="10"/>
-      <c r="L217" s="10"/>
-      <c r="M217" s="10"/>
-      <c r="N217" s="10"/>
-      <c r="O217" s="10"/>
-      <c r="P217" s="10"/>
-      <c r="Q217" s="10"/>
-      <c r="R217" s="10"/>
-      <c r="S217" s="10"/>
-      <c r="T217" s="10"/>
-      <c r="U217" s="10"/>
+      <c r="A203" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B203" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C203" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D203" s="22">
+        <v>398</v>
+      </c>
+      <c r="E203" s="22">
+        <v>897</v>
+      </c>
+      <c r="F203" s="22"/>
+      <c r="G203" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H203" s="9"/>
+      <c r="I203" s="9">
+        <f t="shared" si="7"/>
+        <v>28</v>
+      </c>
+      <c r="J203" s="22">
+        <v>30</v>
+      </c>
+      <c r="K203" s="22"/>
+      <c r="L203" s="22"/>
+      <c r="M203" s="22"/>
+      <c r="N203" s="22"/>
+      <c r="O203" s="22"/>
+      <c r="P203" s="22"/>
+      <c r="Q203" s="22"/>
+      <c r="R203" s="22"/>
+      <c r="S203" s="22"/>
+      <c r="T203" s="22"/>
+      <c r="U203" s="22"/>
     </row>
     <row r="218" spans="1:21" ht="15.75" customHeight="1">
       <c r="A218" s="10"/>
@@ -26082,6 +26229,834 @@
       <c r="T976" s="10"/>
       <c r="U976" s="10"/>
     </row>
+    <row r="977" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A977" s="10"/>
+      <c r="B977" s="10"/>
+      <c r="C977" s="10"/>
+      <c r="D977" s="10"/>
+      <c r="E977" s="10"/>
+      <c r="F977" s="10"/>
+      <c r="G977" s="10"/>
+      <c r="H977" s="10"/>
+      <c r="I977" s="10"/>
+      <c r="J977" s="10"/>
+      <c r="K977" s="10"/>
+      <c r="L977" s="10"/>
+      <c r="M977" s="10"/>
+      <c r="N977" s="10"/>
+      <c r="O977" s="10"/>
+      <c r="P977" s="10"/>
+      <c r="Q977" s="10"/>
+      <c r="R977" s="10"/>
+      <c r="S977" s="10"/>
+      <c r="T977" s="10"/>
+      <c r="U977" s="10"/>
+    </row>
+    <row r="978" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A978" s="10"/>
+      <c r="B978" s="10"/>
+      <c r="C978" s="10"/>
+      <c r="D978" s="10"/>
+      <c r="E978" s="10"/>
+      <c r="F978" s="10"/>
+      <c r="G978" s="10"/>
+      <c r="H978" s="10"/>
+      <c r="I978" s="10"/>
+      <c r="J978" s="10"/>
+      <c r="K978" s="10"/>
+      <c r="L978" s="10"/>
+      <c r="M978" s="10"/>
+      <c r="N978" s="10"/>
+      <c r="O978" s="10"/>
+      <c r="P978" s="10"/>
+      <c r="Q978" s="10"/>
+      <c r="R978" s="10"/>
+      <c r="S978" s="10"/>
+      <c r="T978" s="10"/>
+      <c r="U978" s="10"/>
+    </row>
+    <row r="979" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A979" s="10"/>
+      <c r="B979" s="10"/>
+      <c r="C979" s="10"/>
+      <c r="D979" s="10"/>
+      <c r="E979" s="10"/>
+      <c r="F979" s="10"/>
+      <c r="G979" s="10"/>
+      <c r="H979" s="10"/>
+      <c r="I979" s="10"/>
+      <c r="J979" s="10"/>
+      <c r="K979" s="10"/>
+      <c r="L979" s="10"/>
+      <c r="M979" s="10"/>
+      <c r="N979" s="10"/>
+      <c r="O979" s="10"/>
+      <c r="P979" s="10"/>
+      <c r="Q979" s="10"/>
+      <c r="R979" s="10"/>
+      <c r="S979" s="10"/>
+      <c r="T979" s="10"/>
+      <c r="U979" s="10"/>
+    </row>
+    <row r="980" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A980" s="10"/>
+      <c r="B980" s="10"/>
+      <c r="C980" s="10"/>
+      <c r="D980" s="10"/>
+      <c r="E980" s="10"/>
+      <c r="F980" s="10"/>
+      <c r="G980" s="10"/>
+      <c r="H980" s="10"/>
+      <c r="I980" s="10"/>
+      <c r="J980" s="10"/>
+      <c r="K980" s="10"/>
+      <c r="L980" s="10"/>
+      <c r="M980" s="10"/>
+      <c r="N980" s="10"/>
+      <c r="O980" s="10"/>
+      <c r="P980" s="10"/>
+      <c r="Q980" s="10"/>
+      <c r="R980" s="10"/>
+      <c r="S980" s="10"/>
+      <c r="T980" s="10"/>
+      <c r="U980" s="10"/>
+    </row>
+    <row r="981" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A981" s="10"/>
+      <c r="B981" s="10"/>
+      <c r="C981" s="10"/>
+      <c r="D981" s="10"/>
+      <c r="E981" s="10"/>
+      <c r="F981" s="10"/>
+      <c r="G981" s="10"/>
+      <c r="H981" s="10"/>
+      <c r="I981" s="10"/>
+      <c r="J981" s="10"/>
+      <c r="K981" s="10"/>
+      <c r="L981" s="10"/>
+      <c r="M981" s="10"/>
+      <c r="N981" s="10"/>
+      <c r="O981" s="10"/>
+      <c r="P981" s="10"/>
+      <c r="Q981" s="10"/>
+      <c r="R981" s="10"/>
+      <c r="S981" s="10"/>
+      <c r="T981" s="10"/>
+      <c r="U981" s="10"/>
+    </row>
+    <row r="982" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A982" s="10"/>
+      <c r="B982" s="10"/>
+      <c r="C982" s="10"/>
+      <c r="D982" s="10"/>
+      <c r="E982" s="10"/>
+      <c r="F982" s="10"/>
+      <c r="G982" s="10"/>
+      <c r="H982" s="10"/>
+      <c r="I982" s="10"/>
+      <c r="J982" s="10"/>
+      <c r="K982" s="10"/>
+      <c r="L982" s="10"/>
+      <c r="M982" s="10"/>
+      <c r="N982" s="10"/>
+      <c r="O982" s="10"/>
+      <c r="P982" s="10"/>
+      <c r="Q982" s="10"/>
+      <c r="R982" s="10"/>
+      <c r="S982" s="10"/>
+      <c r="T982" s="10"/>
+      <c r="U982" s="10"/>
+    </row>
+    <row r="983" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A983" s="10"/>
+      <c r="B983" s="10"/>
+      <c r="C983" s="10"/>
+      <c r="D983" s="10"/>
+      <c r="E983" s="10"/>
+      <c r="F983" s="10"/>
+      <c r="G983" s="10"/>
+      <c r="H983" s="10"/>
+      <c r="I983" s="10"/>
+      <c r="J983" s="10"/>
+      <c r="K983" s="10"/>
+      <c r="L983" s="10"/>
+      <c r="M983" s="10"/>
+      <c r="N983" s="10"/>
+      <c r="O983" s="10"/>
+      <c r="P983" s="10"/>
+      <c r="Q983" s="10"/>
+      <c r="R983" s="10"/>
+      <c r="S983" s="10"/>
+      <c r="T983" s="10"/>
+      <c r="U983" s="10"/>
+    </row>
+    <row r="984" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A984" s="10"/>
+      <c r="B984" s="10"/>
+      <c r="C984" s="10"/>
+      <c r="D984" s="10"/>
+      <c r="E984" s="10"/>
+      <c r="F984" s="10"/>
+      <c r="G984" s="10"/>
+      <c r="H984" s="10"/>
+      <c r="I984" s="10"/>
+      <c r="J984" s="10"/>
+      <c r="K984" s="10"/>
+      <c r="L984" s="10"/>
+      <c r="M984" s="10"/>
+      <c r="N984" s="10"/>
+      <c r="O984" s="10"/>
+      <c r="P984" s="10"/>
+      <c r="Q984" s="10"/>
+      <c r="R984" s="10"/>
+      <c r="S984" s="10"/>
+      <c r="T984" s="10"/>
+      <c r="U984" s="10"/>
+    </row>
+    <row r="985" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A985" s="10"/>
+      <c r="B985" s="10"/>
+      <c r="C985" s="10"/>
+      <c r="D985" s="10"/>
+      <c r="E985" s="10"/>
+      <c r="F985" s="10"/>
+      <c r="G985" s="10"/>
+      <c r="H985" s="10"/>
+      <c r="I985" s="10"/>
+      <c r="J985" s="10"/>
+      <c r="K985" s="10"/>
+      <c r="L985" s="10"/>
+      <c r="M985" s="10"/>
+      <c r="N985" s="10"/>
+      <c r="O985" s="10"/>
+      <c r="P985" s="10"/>
+      <c r="Q985" s="10"/>
+      <c r="R985" s="10"/>
+      <c r="S985" s="10"/>
+      <c r="T985" s="10"/>
+      <c r="U985" s="10"/>
+    </row>
+    <row r="986" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A986" s="10"/>
+      <c r="B986" s="10"/>
+      <c r="C986" s="10"/>
+      <c r="D986" s="10"/>
+      <c r="E986" s="10"/>
+      <c r="F986" s="10"/>
+      <c r="G986" s="10"/>
+      <c r="H986" s="10"/>
+      <c r="I986" s="10"/>
+      <c r="J986" s="10"/>
+      <c r="K986" s="10"/>
+      <c r="L986" s="10"/>
+      <c r="M986" s="10"/>
+      <c r="N986" s="10"/>
+      <c r="O986" s="10"/>
+      <c r="P986" s="10"/>
+      <c r="Q986" s="10"/>
+      <c r="R986" s="10"/>
+      <c r="S986" s="10"/>
+      <c r="T986" s="10"/>
+      <c r="U986" s="10"/>
+    </row>
+    <row r="987" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A987" s="10"/>
+      <c r="B987" s="10"/>
+      <c r="C987" s="10"/>
+      <c r="D987" s="10"/>
+      <c r="E987" s="10"/>
+      <c r="F987" s="10"/>
+      <c r="G987" s="10"/>
+      <c r="H987" s="10"/>
+      <c r="I987" s="10"/>
+      <c r="J987" s="10"/>
+      <c r="K987" s="10"/>
+      <c r="L987" s="10"/>
+      <c r="M987" s="10"/>
+      <c r="N987" s="10"/>
+      <c r="O987" s="10"/>
+      <c r="P987" s="10"/>
+      <c r="Q987" s="10"/>
+      <c r="R987" s="10"/>
+      <c r="S987" s="10"/>
+      <c r="T987" s="10"/>
+      <c r="U987" s="10"/>
+    </row>
+    <row r="988" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A988" s="10"/>
+      <c r="B988" s="10"/>
+      <c r="C988" s="10"/>
+      <c r="D988" s="10"/>
+      <c r="E988" s="10"/>
+      <c r="F988" s="10"/>
+      <c r="G988" s="10"/>
+      <c r="H988" s="10"/>
+      <c r="I988" s="10"/>
+      <c r="J988" s="10"/>
+      <c r="K988" s="10"/>
+      <c r="L988" s="10"/>
+      <c r="M988" s="10"/>
+      <c r="N988" s="10"/>
+      <c r="O988" s="10"/>
+      <c r="P988" s="10"/>
+      <c r="Q988" s="10"/>
+      <c r="R988" s="10"/>
+      <c r="S988" s="10"/>
+      <c r="T988" s="10"/>
+      <c r="U988" s="10"/>
+    </row>
+    <row r="989" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A989" s="10"/>
+      <c r="B989" s="10"/>
+      <c r="C989" s="10"/>
+      <c r="D989" s="10"/>
+      <c r="E989" s="10"/>
+      <c r="F989" s="10"/>
+      <c r="G989" s="10"/>
+      <c r="H989" s="10"/>
+      <c r="I989" s="10"/>
+      <c r="J989" s="10"/>
+      <c r="K989" s="10"/>
+      <c r="L989" s="10"/>
+      <c r="M989" s="10"/>
+      <c r="N989" s="10"/>
+      <c r="O989" s="10"/>
+      <c r="P989" s="10"/>
+      <c r="Q989" s="10"/>
+      <c r="R989" s="10"/>
+      <c r="S989" s="10"/>
+      <c r="T989" s="10"/>
+      <c r="U989" s="10"/>
+    </row>
+    <row r="990" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A990" s="10"/>
+      <c r="B990" s="10"/>
+      <c r="C990" s="10"/>
+      <c r="D990" s="10"/>
+      <c r="E990" s="10"/>
+      <c r="F990" s="10"/>
+      <c r="G990" s="10"/>
+      <c r="H990" s="10"/>
+      <c r="I990" s="10"/>
+      <c r="J990" s="10"/>
+      <c r="K990" s="10"/>
+      <c r="L990" s="10"/>
+      <c r="M990" s="10"/>
+      <c r="N990" s="10"/>
+      <c r="O990" s="10"/>
+      <c r="P990" s="10"/>
+      <c r="Q990" s="10"/>
+      <c r="R990" s="10"/>
+      <c r="S990" s="10"/>
+      <c r="T990" s="10"/>
+      <c r="U990" s="10"/>
+    </row>
+    <row r="991" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A991" s="10"/>
+      <c r="B991" s="10"/>
+      <c r="C991" s="10"/>
+      <c r="D991" s="10"/>
+      <c r="E991" s="10"/>
+      <c r="F991" s="10"/>
+      <c r="G991" s="10"/>
+      <c r="H991" s="10"/>
+      <c r="I991" s="10"/>
+      <c r="J991" s="10"/>
+      <c r="K991" s="10"/>
+      <c r="L991" s="10"/>
+      <c r="M991" s="10"/>
+      <c r="N991" s="10"/>
+      <c r="O991" s="10"/>
+      <c r="P991" s="10"/>
+      <c r="Q991" s="10"/>
+      <c r="R991" s="10"/>
+      <c r="S991" s="10"/>
+      <c r="T991" s="10"/>
+      <c r="U991" s="10"/>
+    </row>
+    <row r="992" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A992" s="10"/>
+      <c r="B992" s="10"/>
+      <c r="C992" s="10"/>
+      <c r="D992" s="10"/>
+      <c r="E992" s="10"/>
+      <c r="F992" s="10"/>
+      <c r="G992" s="10"/>
+      <c r="H992" s="10"/>
+      <c r="I992" s="10"/>
+      <c r="J992" s="10"/>
+      <c r="K992" s="10"/>
+      <c r="L992" s="10"/>
+      <c r="M992" s="10"/>
+      <c r="N992" s="10"/>
+      <c r="O992" s="10"/>
+      <c r="P992" s="10"/>
+      <c r="Q992" s="10"/>
+      <c r="R992" s="10"/>
+      <c r="S992" s="10"/>
+      <c r="T992" s="10"/>
+      <c r="U992" s="10"/>
+    </row>
+    <row r="993" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A993" s="10"/>
+      <c r="B993" s="10"/>
+      <c r="C993" s="10"/>
+      <c r="D993" s="10"/>
+      <c r="E993" s="10"/>
+      <c r="F993" s="10"/>
+      <c r="G993" s="10"/>
+      <c r="H993" s="10"/>
+      <c r="I993" s="10"/>
+      <c r="J993" s="10"/>
+      <c r="K993" s="10"/>
+      <c r="L993" s="10"/>
+      <c r="M993" s="10"/>
+      <c r="N993" s="10"/>
+      <c r="O993" s="10"/>
+      <c r="P993" s="10"/>
+      <c r="Q993" s="10"/>
+      <c r="R993" s="10"/>
+      <c r="S993" s="10"/>
+      <c r="T993" s="10"/>
+      <c r="U993" s="10"/>
+    </row>
+    <row r="994" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A994" s="10"/>
+      <c r="B994" s="10"/>
+      <c r="C994" s="10"/>
+      <c r="D994" s="10"/>
+      <c r="E994" s="10"/>
+      <c r="F994" s="10"/>
+      <c r="G994" s="10"/>
+      <c r="H994" s="10"/>
+      <c r="I994" s="10"/>
+      <c r="J994" s="10"/>
+      <c r="K994" s="10"/>
+      <c r="L994" s="10"/>
+      <c r="M994" s="10"/>
+      <c r="N994" s="10"/>
+      <c r="O994" s="10"/>
+      <c r="P994" s="10"/>
+      <c r="Q994" s="10"/>
+      <c r="R994" s="10"/>
+      <c r="S994" s="10"/>
+      <c r="T994" s="10"/>
+      <c r="U994" s="10"/>
+    </row>
+    <row r="995" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A995" s="10"/>
+      <c r="B995" s="10"/>
+      <c r="C995" s="10"/>
+      <c r="D995" s="10"/>
+      <c r="E995" s="10"/>
+      <c r="F995" s="10"/>
+      <c r="G995" s="10"/>
+      <c r="H995" s="10"/>
+      <c r="I995" s="10"/>
+      <c r="J995" s="10"/>
+      <c r="K995" s="10"/>
+      <c r="L995" s="10"/>
+      <c r="M995" s="10"/>
+      <c r="N995" s="10"/>
+      <c r="O995" s="10"/>
+      <c r="P995" s="10"/>
+      <c r="Q995" s="10"/>
+      <c r="R995" s="10"/>
+      <c r="S995" s="10"/>
+      <c r="T995" s="10"/>
+      <c r="U995" s="10"/>
+    </row>
+    <row r="996" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A996" s="10"/>
+      <c r="B996" s="10"/>
+      <c r="C996" s="10"/>
+      <c r="D996" s="10"/>
+      <c r="E996" s="10"/>
+      <c r="F996" s="10"/>
+      <c r="G996" s="10"/>
+      <c r="H996" s="10"/>
+      <c r="I996" s="10"/>
+      <c r="J996" s="10"/>
+      <c r="K996" s="10"/>
+      <c r="L996" s="10"/>
+      <c r="M996" s="10"/>
+      <c r="N996" s="10"/>
+      <c r="O996" s="10"/>
+      <c r="P996" s="10"/>
+      <c r="Q996" s="10"/>
+      <c r="R996" s="10"/>
+      <c r="S996" s="10"/>
+      <c r="T996" s="10"/>
+      <c r="U996" s="10"/>
+    </row>
+    <row r="997" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A997" s="10"/>
+      <c r="B997" s="10"/>
+      <c r="C997" s="10"/>
+      <c r="D997" s="10"/>
+      <c r="E997" s="10"/>
+      <c r="F997" s="10"/>
+      <c r="G997" s="10"/>
+      <c r="H997" s="10"/>
+      <c r="I997" s="10"/>
+      <c r="J997" s="10"/>
+      <c r="K997" s="10"/>
+      <c r="L997" s="10"/>
+      <c r="M997" s="10"/>
+      <c r="N997" s="10"/>
+      <c r="O997" s="10"/>
+      <c r="P997" s="10"/>
+      <c r="Q997" s="10"/>
+      <c r="R997" s="10"/>
+      <c r="S997" s="10"/>
+      <c r="T997" s="10"/>
+      <c r="U997" s="10"/>
+    </row>
+    <row r="998" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A998" s="10"/>
+      <c r="B998" s="10"/>
+      <c r="C998" s="10"/>
+      <c r="D998" s="10"/>
+      <c r="E998" s="10"/>
+      <c r="F998" s="10"/>
+      <c r="G998" s="10"/>
+      <c r="H998" s="10"/>
+      <c r="I998" s="10"/>
+      <c r="J998" s="10"/>
+      <c r="K998" s="10"/>
+      <c r="L998" s="10"/>
+      <c r="M998" s="10"/>
+      <c r="N998" s="10"/>
+      <c r="O998" s="10"/>
+      <c r="P998" s="10"/>
+      <c r="Q998" s="10"/>
+      <c r="R998" s="10"/>
+      <c r="S998" s="10"/>
+      <c r="T998" s="10"/>
+      <c r="U998" s="10"/>
+    </row>
+    <row r="999" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A999" s="10"/>
+      <c r="B999" s="10"/>
+      <c r="C999" s="10"/>
+      <c r="D999" s="10"/>
+      <c r="E999" s="10"/>
+      <c r="F999" s="10"/>
+      <c r="G999" s="10"/>
+      <c r="H999" s="10"/>
+      <c r="I999" s="10"/>
+      <c r="J999" s="10"/>
+      <c r="K999" s="10"/>
+      <c r="L999" s="10"/>
+      <c r="M999" s="10"/>
+      <c r="N999" s="10"/>
+      <c r="O999" s="10"/>
+      <c r="P999" s="10"/>
+      <c r="Q999" s="10"/>
+      <c r="R999" s="10"/>
+      <c r="S999" s="10"/>
+      <c r="T999" s="10"/>
+      <c r="U999" s="10"/>
+    </row>
+    <row r="1000" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1000" s="10"/>
+      <c r="B1000" s="10"/>
+      <c r="C1000" s="10"/>
+      <c r="D1000" s="10"/>
+      <c r="E1000" s="10"/>
+      <c r="F1000" s="10"/>
+      <c r="G1000" s="10"/>
+      <c r="H1000" s="10"/>
+      <c r="I1000" s="10"/>
+      <c r="J1000" s="10"/>
+      <c r="K1000" s="10"/>
+      <c r="L1000" s="10"/>
+      <c r="M1000" s="10"/>
+      <c r="N1000" s="10"/>
+      <c r="O1000" s="10"/>
+      <c r="P1000" s="10"/>
+      <c r="Q1000" s="10"/>
+      <c r="R1000" s="10"/>
+      <c r="S1000" s="10"/>
+      <c r="T1000" s="10"/>
+      <c r="U1000" s="10"/>
+    </row>
+    <row r="1001" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1001" s="10"/>
+      <c r="B1001" s="10"/>
+      <c r="C1001" s="10"/>
+      <c r="D1001" s="10"/>
+      <c r="E1001" s="10"/>
+      <c r="F1001" s="10"/>
+      <c r="G1001" s="10"/>
+      <c r="H1001" s="10"/>
+      <c r="I1001" s="10"/>
+      <c r="J1001" s="10"/>
+      <c r="K1001" s="10"/>
+      <c r="L1001" s="10"/>
+      <c r="M1001" s="10"/>
+      <c r="N1001" s="10"/>
+      <c r="O1001" s="10"/>
+      <c r="P1001" s="10"/>
+      <c r="Q1001" s="10"/>
+      <c r="R1001" s="10"/>
+      <c r="S1001" s="10"/>
+      <c r="T1001" s="10"/>
+      <c r="U1001" s="10"/>
+    </row>
+    <row r="1002" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1002" s="10"/>
+      <c r="B1002" s="10"/>
+      <c r="C1002" s="10"/>
+      <c r="D1002" s="10"/>
+      <c r="E1002" s="10"/>
+      <c r="F1002" s="10"/>
+      <c r="G1002" s="10"/>
+      <c r="H1002" s="10"/>
+      <c r="I1002" s="10"/>
+      <c r="J1002" s="10"/>
+      <c r="K1002" s="10"/>
+      <c r="L1002" s="10"/>
+      <c r="M1002" s="10"/>
+      <c r="N1002" s="10"/>
+      <c r="O1002" s="10"/>
+      <c r="P1002" s="10"/>
+      <c r="Q1002" s="10"/>
+      <c r="R1002" s="10"/>
+      <c r="S1002" s="10"/>
+      <c r="T1002" s="10"/>
+      <c r="U1002" s="10"/>
+    </row>
+    <row r="1003" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1003" s="10"/>
+      <c r="B1003" s="10"/>
+      <c r="C1003" s="10"/>
+      <c r="D1003" s="10"/>
+      <c r="E1003" s="10"/>
+      <c r="F1003" s="10"/>
+      <c r="G1003" s="10"/>
+      <c r="H1003" s="10"/>
+      <c r="I1003" s="10"/>
+      <c r="J1003" s="10"/>
+      <c r="K1003" s="10"/>
+      <c r="L1003" s="10"/>
+      <c r="M1003" s="10"/>
+      <c r="N1003" s="10"/>
+      <c r="O1003" s="10"/>
+      <c r="P1003" s="10"/>
+      <c r="Q1003" s="10"/>
+      <c r="R1003" s="10"/>
+      <c r="S1003" s="10"/>
+      <c r="T1003" s="10"/>
+      <c r="U1003" s="10"/>
+    </row>
+    <row r="1004" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1004" s="10"/>
+      <c r="B1004" s="10"/>
+      <c r="C1004" s="10"/>
+      <c r="D1004" s="10"/>
+      <c r="E1004" s="10"/>
+      <c r="F1004" s="10"/>
+      <c r="G1004" s="10"/>
+      <c r="H1004" s="10"/>
+      <c r="I1004" s="10"/>
+      <c r="J1004" s="10"/>
+      <c r="K1004" s="10"/>
+      <c r="L1004" s="10"/>
+      <c r="M1004" s="10"/>
+      <c r="N1004" s="10"/>
+      <c r="O1004" s="10"/>
+      <c r="P1004" s="10"/>
+      <c r="Q1004" s="10"/>
+      <c r="R1004" s="10"/>
+      <c r="S1004" s="10"/>
+      <c r="T1004" s="10"/>
+      <c r="U1004" s="10"/>
+    </row>
+    <row r="1005" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1005" s="10"/>
+      <c r="B1005" s="10"/>
+      <c r="C1005" s="10"/>
+      <c r="D1005" s="10"/>
+      <c r="E1005" s="10"/>
+      <c r="F1005" s="10"/>
+      <c r="G1005" s="10"/>
+      <c r="H1005" s="10"/>
+      <c r="I1005" s="10"/>
+      <c r="J1005" s="10"/>
+      <c r="K1005" s="10"/>
+      <c r="L1005" s="10"/>
+      <c r="M1005" s="10"/>
+      <c r="N1005" s="10"/>
+      <c r="O1005" s="10"/>
+      <c r="P1005" s="10"/>
+      <c r="Q1005" s="10"/>
+      <c r="R1005" s="10"/>
+      <c r="S1005" s="10"/>
+      <c r="T1005" s="10"/>
+      <c r="U1005" s="10"/>
+    </row>
+    <row r="1006" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1006" s="10"/>
+      <c r="B1006" s="10"/>
+      <c r="C1006" s="10"/>
+      <c r="D1006" s="10"/>
+      <c r="E1006" s="10"/>
+      <c r="F1006" s="10"/>
+      <c r="G1006" s="10"/>
+      <c r="H1006" s="10"/>
+      <c r="I1006" s="10"/>
+      <c r="J1006" s="10"/>
+      <c r="K1006" s="10"/>
+      <c r="L1006" s="10"/>
+      <c r="M1006" s="10"/>
+      <c r="N1006" s="10"/>
+      <c r="O1006" s="10"/>
+      <c r="P1006" s="10"/>
+      <c r="Q1006" s="10"/>
+      <c r="R1006" s="10"/>
+      <c r="S1006" s="10"/>
+      <c r="T1006" s="10"/>
+      <c r="U1006" s="10"/>
+    </row>
+    <row r="1007" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1007" s="10"/>
+      <c r="B1007" s="10"/>
+      <c r="C1007" s="10"/>
+      <c r="D1007" s="10"/>
+      <c r="E1007" s="10"/>
+      <c r="F1007" s="10"/>
+      <c r="G1007" s="10"/>
+      <c r="H1007" s="10"/>
+      <c r="I1007" s="10"/>
+      <c r="J1007" s="10"/>
+      <c r="K1007" s="10"/>
+      <c r="L1007" s="10"/>
+      <c r="M1007" s="10"/>
+      <c r="N1007" s="10"/>
+      <c r="O1007" s="10"/>
+      <c r="P1007" s="10"/>
+      <c r="Q1007" s="10"/>
+      <c r="R1007" s="10"/>
+      <c r="S1007" s="10"/>
+      <c r="T1007" s="10"/>
+      <c r="U1007" s="10"/>
+    </row>
+    <row r="1008" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1008" s="10"/>
+      <c r="B1008" s="10"/>
+      <c r="C1008" s="10"/>
+      <c r="D1008" s="10"/>
+      <c r="E1008" s="10"/>
+      <c r="F1008" s="10"/>
+      <c r="G1008" s="10"/>
+      <c r="H1008" s="10"/>
+      <c r="I1008" s="10"/>
+      <c r="J1008" s="10"/>
+      <c r="K1008" s="10"/>
+      <c r="L1008" s="10"/>
+      <c r="M1008" s="10"/>
+      <c r="N1008" s="10"/>
+      <c r="O1008" s="10"/>
+      <c r="P1008" s="10"/>
+      <c r="Q1008" s="10"/>
+      <c r="R1008" s="10"/>
+      <c r="S1008" s="10"/>
+      <c r="T1008" s="10"/>
+      <c r="U1008" s="10"/>
+    </row>
+    <row r="1009" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1009" s="10"/>
+      <c r="B1009" s="10"/>
+      <c r="C1009" s="10"/>
+      <c r="D1009" s="10"/>
+      <c r="E1009" s="10"/>
+      <c r="F1009" s="10"/>
+      <c r="G1009" s="10"/>
+      <c r="H1009" s="10"/>
+      <c r="I1009" s="10"/>
+      <c r="J1009" s="10"/>
+      <c r="K1009" s="10"/>
+      <c r="L1009" s="10"/>
+      <c r="M1009" s="10"/>
+      <c r="N1009" s="10"/>
+      <c r="O1009" s="10"/>
+      <c r="P1009" s="10"/>
+      <c r="Q1009" s="10"/>
+      <c r="R1009" s="10"/>
+      <c r="S1009" s="10"/>
+      <c r="T1009" s="10"/>
+      <c r="U1009" s="10"/>
+    </row>
+    <row r="1010" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1010" s="10"/>
+      <c r="B1010" s="10"/>
+      <c r="C1010" s="10"/>
+      <c r="D1010" s="10"/>
+      <c r="E1010" s="10"/>
+      <c r="F1010" s="10"/>
+      <c r="G1010" s="10"/>
+      <c r="H1010" s="10"/>
+      <c r="I1010" s="10"/>
+      <c r="J1010" s="10"/>
+      <c r="K1010" s="10"/>
+      <c r="L1010" s="10"/>
+      <c r="M1010" s="10"/>
+      <c r="N1010" s="10"/>
+      <c r="O1010" s="10"/>
+      <c r="P1010" s="10"/>
+      <c r="Q1010" s="10"/>
+      <c r="R1010" s="10"/>
+      <c r="S1010" s="10"/>
+      <c r="T1010" s="10"/>
+      <c r="U1010" s="10"/>
+    </row>
+    <row r="1011" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1011" s="10"/>
+      <c r="B1011" s="10"/>
+      <c r="C1011" s="10"/>
+      <c r="D1011" s="10"/>
+      <c r="E1011" s="10"/>
+      <c r="F1011" s="10"/>
+      <c r="G1011" s="10"/>
+      <c r="H1011" s="10"/>
+      <c r="I1011" s="10"/>
+      <c r="J1011" s="10"/>
+      <c r="K1011" s="10"/>
+      <c r="L1011" s="10"/>
+      <c r="M1011" s="10"/>
+      <c r="N1011" s="10"/>
+      <c r="O1011" s="10"/>
+      <c r="P1011" s="10"/>
+      <c r="Q1011" s="10"/>
+      <c r="R1011" s="10"/>
+      <c r="S1011" s="10"/>
+      <c r="T1011" s="10"/>
+      <c r="U1011" s="10"/>
+    </row>
+    <row r="1012" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1012" s="10"/>
+      <c r="B1012" s="10"/>
+      <c r="C1012" s="10"/>
+      <c r="D1012" s="10"/>
+      <c r="E1012" s="10"/>
+      <c r="F1012" s="10"/>
+      <c r="G1012" s="10"/>
+      <c r="H1012" s="10"/>
+      <c r="I1012" s="10"/>
+      <c r="J1012" s="10"/>
+      <c r="K1012" s="10"/>
+      <c r="L1012" s="10"/>
+      <c r="M1012" s="10"/>
+      <c r="N1012" s="10"/>
+      <c r="O1012" s="10"/>
+      <c r="P1012" s="10"/>
+      <c r="Q1012" s="10"/>
+      <c r="R1012" s="10"/>
+      <c r="S1012" s="10"/>
+      <c r="T1012" s="10"/>
+      <c r="U1012" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H128" s="10"/>
       <c r="I128" s="9">
-        <f>J6</f>
+        <f t="shared" ref="I128:I134" si="6">J6</f>
         <v>30</v>
       </c>
       <c r="J128" s="10"/>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="H129" s="10"/>
       <c r="I129" s="9">
-        <f>J7</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J129" s="10"/>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="H130" s="10"/>
       <c r="I130" s="9">
-        <f>J8</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J130" s="10"/>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="H131" s="10"/>
       <c r="I131" s="9">
-        <f>J9</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J131" s="10"/>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="H132" s="10"/>
       <c r="I132" s="9">
-        <f>J10</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J132" s="10"/>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="H133" s="10"/>
       <c r="I133" s="9">
-        <f>J11</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J133" s="10"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="H134" s="10"/>
       <c r="I134" s="9">
-        <f>J12</f>
+        <f t="shared" si="6"/>
         <v>30</v>
       </c>
       <c r="J134" s="10"/>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H135" s="10"/>
       <c r="I135" s="9">
-        <f>J18</f>
+        <f t="shared" ref="I135:I141" si="7">J18</f>
         <v>30</v>
       </c>
       <c r="J135" s="10"/>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="H136" s="10"/>
       <c r="I136" s="9">
-        <f>J19</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J136" s="10"/>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="H137" s="10"/>
       <c r="I137" s="9">
-        <f>J20</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J137" s="10"/>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="H138" s="10"/>
       <c r="I138" s="9">
-        <f>J21</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J138" s="10"/>
@@ -6713,7 +6713,7 @@
       </c>
       <c r="H139" s="10"/>
       <c r="I139" s="9">
-        <f>J22</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J139" s="10"/>
@@ -6753,7 +6753,7 @@
       </c>
       <c r="H140" s="10"/>
       <c r="I140" s="9">
-        <f>J23</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J140" s="10"/>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="H141" s="10"/>
       <c r="I141" s="9">
-        <f>J24</f>
+        <f t="shared" si="7"/>
         <v>30</v>
       </c>
       <c r="J141" s="10"/>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="H176" s="9"/>
       <c r="I176" s="9">
-        <f t="shared" ref="I176:I181" si="6">I175+1</f>
+        <f t="shared" ref="I176:I181" si="8">I175+1</f>
         <v>21</v>
       </c>
       <c r="J176" s="22">
@@ -7715,7 +7715,7 @@
       </c>
       <c r="H177" s="9"/>
       <c r="I177" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>22</v>
       </c>
       <c r="J177" s="22">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="H178" s="9"/>
       <c r="I178" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>23</v>
       </c>
       <c r="J178" s="22">
@@ -7795,7 +7795,7 @@
       </c>
       <c r="H179" s="9"/>
       <c r="I179" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>24</v>
       </c>
       <c r="J179" s="22">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="H180" s="9"/>
       <c r="I180" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>25</v>
       </c>
       <c r="J180" s="22">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="H181" s="9"/>
       <c r="I181" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>26</v>
       </c>
       <c r="J181" s="22">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="H184" s="9"/>
       <c r="I184" s="9">
-        <f t="shared" ref="I184:I203" si="7">I183+1</f>
+        <f t="shared" ref="I184:I203" si="9">I183+1</f>
         <v>9</v>
       </c>
       <c r="J184" s="22">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="H185" s="9"/>
       <c r="I185" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
       <c r="J185" s="22">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="H186" s="9"/>
       <c r="I186" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
       <c r="J186" s="22">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="H187" s="9"/>
       <c r="I187" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
       <c r="J187" s="22">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H188" s="9"/>
       <c r="I188" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
       <c r="J188" s="22">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="H189" s="9"/>
       <c r="I189" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
       <c r="J189" s="22">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="H190" s="9"/>
       <c r="I190" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
       <c r="J190" s="22">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="H191" s="9"/>
       <c r="I191" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
       <c r="J191" s="22">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="H192" s="9"/>
       <c r="I192" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>17</v>
       </c>
       <c r="J192" s="22">
@@ -8354,7 +8354,7 @@
       </c>
       <c r="H193" s="9"/>
       <c r="I193" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>18</v>
       </c>
       <c r="J193" s="22">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="H194" s="9"/>
       <c r="I194" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
       <c r="J194" s="22">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="H195" s="9"/>
       <c r="I195" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>20</v>
       </c>
       <c r="J195" s="22">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="H196" s="9"/>
       <c r="I196" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>21</v>
       </c>
       <c r="J196" s="22">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="H197" s="9"/>
       <c r="I197" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>22</v>
       </c>
       <c r="J197" s="22">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="H198" s="9"/>
       <c r="I198" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>23</v>
       </c>
       <c r="J198" s="22">
@@ -8594,7 +8594,7 @@
       </c>
       <c r="H199" s="9"/>
       <c r="I199" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>24</v>
       </c>
       <c r="J199" s="22">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="H200" s="9"/>
       <c r="I200" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>25</v>
       </c>
       <c r="J200" s="22">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="H201" s="9"/>
       <c r="I201" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>26</v>
       </c>
       <c r="J201" s="22">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H202" s="9"/>
       <c r="I202" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>27</v>
       </c>
       <c r="J202" s="22">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="H203" s="9"/>
       <c r="I203" s="9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
       <c r="J203" s="22">

--- a/modulos.xlsx
+++ b/modulos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1383" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="121">
   <si>
     <t xml:space="preserve">
 cod</t>
@@ -736,7 +736,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:U1012"/>
+  <dimension ref="A1:U1024"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.90625" customWidth="1"/>
@@ -830,11 +830,11 @@
         <v>1</v>
       </c>
       <c r="L2" s="10">
-        <f>D160</f>
+        <f>D172</f>
         <v>698</v>
       </c>
       <c r="M2" s="10">
-        <f>E160</f>
+        <f>E172</f>
         <v>147</v>
       </c>
       <c r="N2" s="10"/>
@@ -879,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="L3" s="22">
-        <f t="shared" ref="L3:M3" si="0">D161</f>
+        <f t="shared" ref="L3:M3" si="0">D173</f>
         <v>698</v>
       </c>
       <c r="M3" s="22">
@@ -928,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="L4" s="22">
-        <f t="shared" ref="L4:M4" si="1">D162</f>
+        <f t="shared" ref="L4:M4" si="1">D174</f>
         <v>698</v>
       </c>
       <c r="M4" s="22">
@@ -977,7 +977,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="22">
-        <f t="shared" ref="L5:M5" si="2">D163</f>
+        <f t="shared" ref="L5:M5" si="2">D175</f>
         <v>698</v>
       </c>
       <c r="M5" s="22">
@@ -1026,7 +1026,7 @@
         <v>1</v>
       </c>
       <c r="L6" s="22">
-        <f t="shared" ref="L6:M6" si="3">D164</f>
+        <f t="shared" ref="L6:M6" si="3">D176</f>
         <v>698</v>
       </c>
       <c r="M6" s="22">
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="L7" s="22">
-        <f t="shared" ref="L7:M7" si="4">D165</f>
+        <f t="shared" ref="L7:M7" si="4">D177</f>
         <v>698</v>
       </c>
       <c r="M7" s="22">
@@ -1124,7 +1124,7 @@
         <v>1</v>
       </c>
       <c r="L8" s="22">
-        <f t="shared" ref="L8:M8" si="5">D166</f>
+        <f t="shared" ref="L8:M8" si="5">D178</f>
         <v>698</v>
       </c>
       <c r="M8" s="22">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H135" s="10"/>
       <c r="I135" s="9">
-        <f t="shared" ref="I135:I141" si="7">J18</f>
+        <f t="shared" ref="I135:I140" si="7">J18</f>
         <v>30</v>
       </c>
       <c r="J135" s="10"/>
@@ -6774,766 +6774,897 @@
         <v>9</v>
       </c>
       <c r="B141" s="22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C141" s="22" t="s">
         <v>106</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F141" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G141" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H141" s="10"/>
+        <v>52</v>
+      </c>
+      <c r="H141" s="22"/>
       <c r="I141" s="9">
-        <f t="shared" si="7"/>
-        <v>30</v>
-      </c>
-      <c r="J141" s="10"/>
-      <c r="K141" s="10"/>
-      <c r="L141" s="10"/>
-      <c r="M141" s="10"/>
-      <c r="N141" s="10"/>
-      <c r="O141" s="10"/>
-      <c r="P141" s="10"/>
-      <c r="Q141" s="10"/>
-      <c r="R141" s="10"/>
-      <c r="S141" s="10"/>
-      <c r="T141" s="10"/>
-      <c r="U141" s="10"/>
+        <v>41</v>
+      </c>
+      <c r="J141" s="22"/>
+      <c r="K141" s="22"/>
+      <c r="L141" s="22"/>
+      <c r="M141" s="22"/>
+      <c r="N141" s="22"/>
+      <c r="O141" s="22"/>
+      <c r="P141" s="22"/>
+      <c r="Q141" s="22"/>
+      <c r="R141" s="22"/>
+      <c r="S141" s="22"/>
+      <c r="T141" s="22"/>
+      <c r="U141" s="22"/>
     </row>
     <row r="142" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A142" s="24" t="s">
+      <c r="A142" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B142" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C142" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H142" s="22"/>
+      <c r="I142" s="9">
+        <v>41</v>
+      </c>
+      <c r="J142" s="22"/>
+      <c r="K142" s="22"/>
+      <c r="L142" s="22"/>
+      <c r="M142" s="22"/>
+      <c r="N142" s="22"/>
+      <c r="O142" s="22"/>
+      <c r="P142" s="22"/>
+      <c r="Q142" s="22"/>
+      <c r="R142" s="22"/>
+      <c r="S142" s="22"/>
+      <c r="T142" s="22"/>
+      <c r="U142" s="22"/>
+    </row>
+    <row r="143" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A143" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B143" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H143" s="22"/>
+      <c r="I143" s="9">
+        <v>41</v>
+      </c>
+      <c r="J143" s="22"/>
+      <c r="K143" s="22"/>
+      <c r="L143" s="22"/>
+      <c r="M143" s="22"/>
+      <c r="N143" s="22"/>
+      <c r="O143" s="22"/>
+      <c r="P143" s="22"/>
+      <c r="Q143" s="22"/>
+      <c r="R143" s="22"/>
+      <c r="S143" s="22"/>
+      <c r="T143" s="22"/>
+      <c r="U143" s="22"/>
+    </row>
+    <row r="144" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A144" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B144" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C144" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H144" s="22"/>
+      <c r="I144" s="9">
+        <v>41</v>
+      </c>
+      <c r="J144" s="22"/>
+      <c r="K144" s="22"/>
+      <c r="L144" s="22"/>
+      <c r="M144" s="22"/>
+      <c r="N144" s="22"/>
+      <c r="O144" s="22"/>
+      <c r="P144" s="22"/>
+      <c r="Q144" s="22"/>
+      <c r="R144" s="22"/>
+      <c r="S144" s="22"/>
+      <c r="T144" s="22"/>
+      <c r="U144" s="22"/>
+    </row>
+    <row r="145" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A145" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C145" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H145" s="22"/>
+      <c r="I145" s="9">
+        <v>41</v>
+      </c>
+      <c r="J145" s="22"/>
+      <c r="K145" s="22"/>
+      <c r="L145" s="22"/>
+      <c r="M145" s="22"/>
+      <c r="N145" s="22"/>
+      <c r="O145" s="22"/>
+      <c r="P145" s="22"/>
+      <c r="Q145" s="22"/>
+      <c r="R145" s="22"/>
+      <c r="S145" s="22"/>
+      <c r="T145" s="22"/>
+      <c r="U145" s="22"/>
+    </row>
+    <row r="146" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A146" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B146" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C146" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H146" s="22"/>
+      <c r="I146" s="9">
+        <v>41</v>
+      </c>
+      <c r="J146" s="22"/>
+      <c r="K146" s="22"/>
+      <c r="L146" s="22"/>
+      <c r="M146" s="22"/>
+      <c r="N146" s="22"/>
+      <c r="O146" s="22"/>
+      <c r="P146" s="22"/>
+      <c r="Q146" s="22"/>
+      <c r="R146" s="22"/>
+      <c r="S146" s="22"/>
+      <c r="T146" s="22"/>
+      <c r="U146" s="22"/>
+    </row>
+    <row r="147" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A147" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H147" s="22"/>
+      <c r="I147" s="9">
+        <v>41</v>
+      </c>
+      <c r="J147" s="22"/>
+      <c r="K147" s="22"/>
+      <c r="L147" s="22"/>
+      <c r="M147" s="22"/>
+      <c r="N147" s="22"/>
+      <c r="O147" s="22"/>
+      <c r="P147" s="22"/>
+      <c r="Q147" s="22"/>
+      <c r="R147" s="22"/>
+      <c r="S147" s="22"/>
+      <c r="T147" s="22"/>
+      <c r="U147" s="22"/>
+    </row>
+    <row r="148" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A148" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B148" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C148" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H148" s="22"/>
+      <c r="I148" s="9">
+        <v>41</v>
+      </c>
+      <c r="J148" s="22"/>
+      <c r="K148" s="22"/>
+      <c r="L148" s="22"/>
+      <c r="M148" s="22"/>
+      <c r="N148" s="22"/>
+      <c r="O148" s="22"/>
+      <c r="P148" s="22"/>
+      <c r="Q148" s="22"/>
+      <c r="R148" s="22"/>
+      <c r="S148" s="22"/>
+      <c r="T148" s="22"/>
+      <c r="U148" s="22"/>
+    </row>
+    <row r="149" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A149" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B149" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H149" s="22"/>
+      <c r="I149" s="9">
+        <v>41</v>
+      </c>
+      <c r="J149" s="22"/>
+      <c r="K149" s="22"/>
+      <c r="L149" s="22"/>
+      <c r="M149" s="22"/>
+      <c r="N149" s="22"/>
+      <c r="O149" s="22"/>
+      <c r="P149" s="22"/>
+      <c r="Q149" s="22"/>
+      <c r="R149" s="22"/>
+      <c r="S149" s="22"/>
+      <c r="T149" s="22"/>
+      <c r="U149" s="22"/>
+    </row>
+    <row r="150" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A150" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B150" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C150" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H150" s="22"/>
+      <c r="I150" s="9">
+        <v>41</v>
+      </c>
+      <c r="J150" s="22"/>
+      <c r="K150" s="22"/>
+      <c r="L150" s="22"/>
+      <c r="M150" s="22"/>
+      <c r="N150" s="22"/>
+      <c r="O150" s="22"/>
+      <c r="P150" s="22"/>
+      <c r="Q150" s="22"/>
+      <c r="R150" s="22"/>
+      <c r="S150" s="22"/>
+      <c r="T150" s="22"/>
+      <c r="U150" s="22"/>
+    </row>
+    <row r="151" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A151" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C151" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H151" s="22"/>
+      <c r="I151" s="9">
+        <v>41</v>
+      </c>
+      <c r="J151" s="22"/>
+      <c r="K151" s="22"/>
+      <c r="L151" s="22"/>
+      <c r="M151" s="22"/>
+      <c r="N151" s="22"/>
+      <c r="O151" s="22"/>
+      <c r="P151" s="22"/>
+      <c r="Q151" s="22"/>
+      <c r="R151" s="22"/>
+      <c r="S151" s="22"/>
+      <c r="T151" s="22"/>
+      <c r="U151" s="22"/>
+    </row>
+    <row r="152" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A152" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B152" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C152" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H152" s="22"/>
+      <c r="I152" s="9">
+        <v>41</v>
+      </c>
+      <c r="J152" s="22"/>
+      <c r="K152" s="22"/>
+      <c r="L152" s="22"/>
+      <c r="M152" s="22"/>
+      <c r="N152" s="22"/>
+      <c r="O152" s="22"/>
+      <c r="P152" s="22"/>
+      <c r="Q152" s="22"/>
+      <c r="R152" s="22"/>
+      <c r="S152" s="22"/>
+      <c r="T152" s="22"/>
+      <c r="U152" s="22"/>
+    </row>
+    <row r="153" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A153" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B153" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="C153" s="22" t="s">
+        <v>106</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H153" s="22"/>
+      <c r="I153" s="9">
+        <v>41</v>
+      </c>
+      <c r="J153" s="22"/>
+      <c r="K153" s="22"/>
+      <c r="L153" s="22"/>
+      <c r="M153" s="22"/>
+      <c r="N153" s="22"/>
+      <c r="O153" s="22"/>
+      <c r="P153" s="22"/>
+      <c r="Q153" s="22"/>
+      <c r="R153" s="22"/>
+      <c r="S153" s="22"/>
+      <c r="T153" s="22"/>
+      <c r="U153" s="22"/>
+    </row>
+    <row r="154" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A154" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B142" s="15" t="s">
+      <c r="B154" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C142" s="7" t="s">
+      <c r="C154" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F142" s="22"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J142" s="23">
-        <v>0.2</v>
-      </c>
-      <c r="K142" s="19"/>
-    </row>
-    <row r="143" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A143" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B143" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C143" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="F143" s="22"/>
-      <c r="H143" s="9"/>
-      <c r="I143" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J143" s="23">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A144" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B144" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="F144" s="22"/>
-      <c r="H144" s="9"/>
-      <c r="I144" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J144" s="23"/>
-      <c r="L144" s="25"/>
-    </row>
-    <row r="145" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A145" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B145" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F145" s="20"/>
-      <c r="H145" s="9"/>
-      <c r="I145" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J145" s="23">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A146" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B146" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="F146" s="22"/>
-      <c r="H146" s="9"/>
-      <c r="I146" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J146" s="23"/>
-    </row>
-    <row r="147" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A147" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="B147" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="F147" s="22"/>
-      <c r="H147" s="9"/>
-      <c r="I147" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="J147" s="23"/>
-    </row>
-    <row r="148" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A148" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B148" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E148">
-        <v>450</v>
-      </c>
-      <c r="F148" s="22">
-        <v>500</v>
-      </c>
-      <c r="H148" s="9"/>
-      <c r="I148" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J148" s="23"/>
-    </row>
-    <row r="149" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A149" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B149" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C149" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E149">
-        <v>600</v>
-      </c>
-      <c r="F149" s="22">
-        <v>500</v>
-      </c>
-      <c r="H149" s="9"/>
-      <c r="I149" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J149" s="23"/>
-    </row>
-    <row r="150" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A150" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B150" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C150" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E150">
-        <v>700</v>
-      </c>
-      <c r="F150" s="22">
-        <v>500</v>
-      </c>
-      <c r="H150" s="9"/>
-      <c r="I150" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J150" s="23"/>
-    </row>
-    <row r="151" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A151" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B151" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C151" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E151">
-        <v>800</v>
-      </c>
-      <c r="F151" s="22">
-        <v>500</v>
-      </c>
-      <c r="H151" s="9"/>
-      <c r="I151" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J151" s="23"/>
-    </row>
-    <row r="152" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A152" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B152" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C152" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E152">
-        <v>900</v>
-      </c>
-      <c r="F152" s="22">
-        <v>500</v>
-      </c>
-      <c r="H152" s="9"/>
-      <c r="I152" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J152" s="23"/>
-    </row>
-    <row r="153" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A153" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B153" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C153" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E153">
-        <v>1000</v>
-      </c>
-      <c r="F153" s="22">
-        <v>500</v>
-      </c>
-      <c r="H153" s="9"/>
-      <c r="I153" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J153" s="23"/>
-    </row>
-    <row r="154" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A154" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B154" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C154" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E154">
-        <v>450</v>
-      </c>
-      <c r="F154" s="22">
-        <v>500</v>
-      </c>
+      <c r="F154" s="22"/>
       <c r="H154" s="9"/>
       <c r="I154" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J154" s="23"/>
-    </row>
-    <row r="155" spans="1:10" ht="15.75" customHeight="1">
+        <v>101</v>
+      </c>
+      <c r="J154" s="23">
+        <v>0.2</v>
+      </c>
+      <c r="K154" s="19"/>
+    </row>
+    <row r="155" spans="1:21" ht="15.75" customHeight="1">
       <c r="A155" s="24" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B155" s="15" t="s">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E155">
-        <v>600</v>
-      </c>
-      <c r="F155" s="22">
-        <v>500</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F155" s="22"/>
       <c r="H155" s="9"/>
       <c r="I155" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J155" s="23"/>
-    </row>
-    <row r="156" spans="1:10" ht="15.75" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="J155" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" ht="15.75" customHeight="1">
       <c r="A156" s="24" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B156" s="15" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E156">
-        <v>700</v>
-      </c>
-      <c r="F156" s="22">
-        <v>500</v>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="F156" s="22"/>
       <c r="H156" s="9"/>
       <c r="I156" s="8" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J156" s="23"/>
-    </row>
-    <row r="157" spans="1:10" ht="15.75" customHeight="1">
+      <c r="L156" s="25"/>
+    </row>
+    <row r="157" spans="1:21" ht="15.75" customHeight="1">
       <c r="A157" s="24" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B157" s="15" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E157">
-        <v>800</v>
-      </c>
-      <c r="F157" s="22">
-        <v>500</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="F157" s="20"/>
       <c r="H157" s="9"/>
       <c r="I157" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="J157" s="23"/>
-    </row>
-    <row r="158" spans="1:10" ht="15.75" customHeight="1">
+        <v>80</v>
+      </c>
+      <c r="J157" s="23">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" ht="15.75" customHeight="1">
       <c r="A158" s="24" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E158">
-        <v>900</v>
-      </c>
-      <c r="F158" s="22">
-        <v>500</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="F158" s="22"/>
       <c r="H158" s="9"/>
       <c r="I158" s="8" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="J158" s="23"/>
     </row>
-    <row r="159" spans="1:10" ht="15.75" customHeight="1">
+    <row r="159" spans="1:21" ht="15.75" customHeight="1">
       <c r="A159" s="24" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="B159" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E159">
-        <v>1000</v>
-      </c>
-      <c r="F159" s="22">
-        <v>500</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="F159" s="22"/>
       <c r="H159" s="9"/>
       <c r="I159" s="8" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="J159" s="23"/>
     </row>
-    <row r="160" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A160" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D160" s="20">
-        <v>698</v>
-      </c>
-      <c r="E160" s="20">
-        <v>147</v>
-      </c>
-      <c r="F160" s="20"/>
-      <c r="G160" s="21" t="s">
-        <v>99</v>
+    <row r="160" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A160" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B160" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E160">
+        <v>450</v>
+      </c>
+      <c r="F160" s="22">
+        <v>500</v>
       </c>
       <c r="H160" s="9"/>
       <c r="I160" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J160" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="161" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A161" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B161" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C161" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D161" s="20">
-        <v>698</v>
-      </c>
-      <c r="E161" s="20">
-        <v>297</v>
-      </c>
-      <c r="F161" s="20"/>
-      <c r="G161" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J160" s="23"/>
+    </row>
+    <row r="161" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A161" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B161" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E161">
+        <v>600</v>
+      </c>
+      <c r="F161" s="22">
+        <v>500</v>
       </c>
       <c r="H161" s="9"/>
       <c r="I161" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J161" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="162" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A162" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B162" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C162" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D162" s="20">
-        <v>698</v>
-      </c>
-      <c r="E162" s="20">
-        <v>347</v>
-      </c>
-      <c r="F162" s="20"/>
-      <c r="G162" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J161" s="23"/>
+    </row>
+    <row r="162" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A162" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B162" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E162">
+        <v>700</v>
+      </c>
+      <c r="F162" s="22">
+        <v>500</v>
       </c>
       <c r="H162" s="9"/>
       <c r="I162" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="J162" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="163" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A163" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D163" s="20">
-        <v>698</v>
-      </c>
-      <c r="E163" s="20">
-        <v>397</v>
-      </c>
-      <c r="F163" s="20"/>
-      <c r="G163" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J162" s="23"/>
+    </row>
+    <row r="163" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A163" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B163" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E163">
+        <v>800</v>
+      </c>
+      <c r="F163" s="22">
+        <v>500</v>
       </c>
       <c r="H163" s="9"/>
       <c r="I163" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="J163" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="164" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A164" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B164" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C164" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D164" s="20">
-        <v>698</v>
-      </c>
-      <c r="E164" s="20">
-        <v>447</v>
-      </c>
-      <c r="F164" s="20"/>
-      <c r="G164" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J163" s="23"/>
+    </row>
+    <row r="164" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A164" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C164" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E164">
+        <v>900</v>
+      </c>
+      <c r="F164" s="22">
+        <v>500</v>
       </c>
       <c r="H164" s="9"/>
       <c r="I164" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="J164" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="165" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A165" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B165" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C165" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D165" s="20">
-        <v>698</v>
-      </c>
-      <c r="E165" s="20">
-        <v>497</v>
-      </c>
-      <c r="F165" s="20"/>
-      <c r="G165" s="21" t="s">
-        <v>99</v>
+      <c r="J164" s="23"/>
+    </row>
+    <row r="165" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A165" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B165" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E165">
+        <v>1000</v>
+      </c>
+      <c r="F165" s="22">
+        <v>500</v>
       </c>
       <c r="H165" s="9"/>
       <c r="I165" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J165" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="166" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A166" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B166" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C166" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D166" s="20">
-        <v>698</v>
-      </c>
-      <c r="E166" s="20">
-        <v>597</v>
-      </c>
-      <c r="F166" s="20"/>
-      <c r="G166" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J165" s="23"/>
+    </row>
+    <row r="166" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A166" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B166" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E166">
+        <v>450</v>
+      </c>
+      <c r="F166" s="22">
+        <v>500</v>
       </c>
       <c r="H166" s="9"/>
       <c r="I166" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="J166" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="167" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A167" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B167" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C167" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D167" s="20">
-        <v>798</v>
-      </c>
-      <c r="E167" s="20">
-        <v>147</v>
-      </c>
-      <c r="F167" s="20"/>
-      <c r="G167" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J166" s="23"/>
+    </row>
+    <row r="167" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A167" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B167" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E167">
+        <v>600</v>
+      </c>
+      <c r="F167" s="22">
+        <v>500</v>
       </c>
       <c r="H167" s="9"/>
       <c r="I167" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="J167" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="168" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A168" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B168" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C168" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D168" s="20">
-        <v>798</v>
-      </c>
-      <c r="E168" s="20">
-        <v>297</v>
-      </c>
-      <c r="F168" s="20"/>
-      <c r="G168" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J167" s="23"/>
+    </row>
+    <row r="168" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A168" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B168" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E168">
+        <v>700</v>
+      </c>
+      <c r="F168" s="22">
+        <v>500</v>
       </c>
       <c r="H168" s="9"/>
       <c r="I168" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="J168" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="169" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A169" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B169" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C169" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D169" s="20">
-        <v>798</v>
-      </c>
-      <c r="E169" s="20">
-        <v>347</v>
-      </c>
-      <c r="F169" s="20"/>
-      <c r="G169" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J168" s="23"/>
+    </row>
+    <row r="169" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A169" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B169" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E169">
+        <v>800</v>
+      </c>
+      <c r="F169" s="22">
+        <v>500</v>
       </c>
       <c r="H169" s="9"/>
       <c r="I169" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="J169" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="170" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A170" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B170" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C170" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D170" s="20">
-        <v>798</v>
-      </c>
-      <c r="E170" s="20">
-        <v>397</v>
-      </c>
-      <c r="F170" s="20"/>
-      <c r="G170" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J169" s="23"/>
+    </row>
+    <row r="170" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A170" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B170" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E170">
+        <v>900</v>
+      </c>
+      <c r="F170" s="22">
+        <v>500</v>
       </c>
       <c r="H170" s="9"/>
       <c r="I170" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J170" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="171" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A171" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B171" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C171" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D171" s="20">
-        <v>798</v>
-      </c>
-      <c r="E171" s="20">
-        <v>447</v>
-      </c>
-      <c r="F171" s="20"/>
-      <c r="G171" s="21" t="s">
-        <v>99</v>
+        <v>87</v>
+      </c>
+      <c r="J170" s="23"/>
+    </row>
+    <row r="171" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A171" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="B171" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E171">
+        <v>1000</v>
+      </c>
+      <c r="F171" s="22">
+        <v>500</v>
       </c>
       <c r="H171" s="9"/>
       <c r="I171" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="J171" s="20">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="172" spans="1:21" ht="15.75" customHeight="1">
+        <v>87</v>
+      </c>
+      <c r="J171" s="23"/>
+    </row>
+    <row r="172" spans="1:10" ht="15.75" customHeight="1">
       <c r="A172" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B172" s="21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C172" s="21" t="s">
         <v>83</v>
       </c>
       <c r="D172" s="20">
-        <v>798</v>
+        <v>698</v>
       </c>
       <c r="E172" s="20">
-        <v>497</v>
+        <v>147</v>
       </c>
       <c r="F172" s="20"/>
       <c r="G172" s="21" t="s">
@@ -7541,27 +7672,27 @@
       </c>
       <c r="H172" s="9"/>
       <c r="I172" s="8" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J172" s="20">
         <v>30</v>
       </c>
     </row>
-    <row r="173" spans="1:21" ht="15.75" customHeight="1">
+    <row r="173" spans="1:10" ht="15.75" customHeight="1">
       <c r="A173" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B173" s="21" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C173" s="21" t="s">
         <v>83</v>
       </c>
       <c r="D173" s="20">
-        <v>798</v>
+        <v>698</v>
       </c>
       <c r="E173" s="20">
-        <v>597</v>
+        <v>297</v>
       </c>
       <c r="F173" s="20"/>
       <c r="G173" s="21" t="s">
@@ -7569,27 +7700,27 @@
       </c>
       <c r="H173" s="9"/>
       <c r="I173" s="8" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J173" s="20">
         <v>30</v>
       </c>
     </row>
-    <row r="174" spans="1:21" ht="15.75" customHeight="1">
+    <row r="174" spans="1:10" ht="15.75" customHeight="1">
       <c r="A174" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B174" s="21" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C174" s="21" t="s">
         <v>83</v>
       </c>
       <c r="D174" s="20">
-        <v>1098</v>
+        <v>698</v>
       </c>
       <c r="E174" s="20">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="F174" s="20"/>
       <c r="G174" s="21" t="s">
@@ -7597,487 +7728,345 @@
       </c>
       <c r="H174" s="9"/>
       <c r="I174" s="8" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="J174" s="20">
         <v>30</v>
       </c>
-      <c r="K174" s="10"/>
-      <c r="L174" s="10"/>
-      <c r="M174" s="10"/>
-      <c r="N174" s="10"/>
-      <c r="O174" s="10"/>
-      <c r="P174" s="10"/>
-      <c r="Q174" s="10"/>
-      <c r="R174" s="10"/>
-      <c r="S174" s="10"/>
-      <c r="T174" s="10"/>
-      <c r="U174" s="10"/>
-    </row>
-    <row r="175" spans="1:21" ht="15.75" customHeight="1">
+    </row>
+    <row r="175" spans="1:10" ht="15.75" customHeight="1">
       <c r="A175" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B175" s="21" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C175" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D175" s="22">
-        <v>1098</v>
-      </c>
-      <c r="E175" s="22">
-        <v>597</v>
-      </c>
-      <c r="F175" s="22"/>
+      <c r="D175" s="20">
+        <v>698</v>
+      </c>
+      <c r="E175" s="20">
+        <v>397</v>
+      </c>
+      <c r="F175" s="20"/>
       <c r="G175" s="21" t="s">
         <v>99</v>
       </c>
       <c r="H175" s="9"/>
       <c r="I175" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="J175" s="22">
+        <v>86</v>
+      </c>
+      <c r="J175" s="20">
         <v>30</v>
       </c>
-      <c r="K175" s="22"/>
-      <c r="L175" s="22"/>
-      <c r="M175" s="22"/>
-      <c r="N175" s="22"/>
-      <c r="O175" s="22"/>
-      <c r="P175" s="22"/>
-      <c r="Q175" s="22"/>
-      <c r="R175" s="22"/>
-      <c r="S175" s="22"/>
-      <c r="T175" s="22"/>
-      <c r="U175" s="22"/>
-    </row>
-    <row r="176" spans="1:21" ht="15.75" customHeight="1">
+    </row>
+    <row r="176" spans="1:10" ht="15.75" customHeight="1">
       <c r="A176" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B176" s="21" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C176" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D176" s="22">
-        <v>348</v>
-      </c>
-      <c r="E176" s="22">
-        <v>448</v>
-      </c>
-      <c r="F176" s="22"/>
-      <c r="G176" s="22" t="s">
-        <v>100</v>
+      <c r="D176" s="20">
+        <v>698</v>
+      </c>
+      <c r="E176" s="20">
+        <v>447</v>
+      </c>
+      <c r="F176" s="20"/>
+      <c r="G176" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H176" s="9"/>
-      <c r="I176" s="9">
-        <f t="shared" ref="I176:I181" si="8">I175+1</f>
-        <v>21</v>
-      </c>
-      <c r="J176" s="22">
+      <c r="I176" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="J176" s="20">
         <v>30</v>
       </c>
-      <c r="K176" s="22"/>
-      <c r="L176" s="22"/>
-      <c r="M176" s="22"/>
-      <c r="N176" s="22"/>
-      <c r="O176" s="22"/>
-      <c r="P176" s="22"/>
-      <c r="Q176" s="22"/>
-      <c r="R176" s="22"/>
-      <c r="S176" s="22"/>
-      <c r="T176" s="22"/>
-      <c r="U176" s="22"/>
     </row>
     <row r="177" spans="1:21" ht="15.75" customHeight="1">
       <c r="A177" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B177" s="21" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C177" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D177" s="22">
-        <v>348</v>
-      </c>
-      <c r="E177" s="22">
-        <v>597</v>
-      </c>
-      <c r="F177" s="22"/>
-      <c r="G177" s="22" t="s">
-        <v>100</v>
+      <c r="D177" s="20">
+        <v>698</v>
+      </c>
+      <c r="E177" s="20">
+        <v>497</v>
+      </c>
+      <c r="F177" s="20"/>
+      <c r="G177" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H177" s="9"/>
-      <c r="I177" s="9">
-        <f t="shared" si="8"/>
-        <v>22</v>
-      </c>
-      <c r="J177" s="22">
+      <c r="I177" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J177" s="20">
         <v>30</v>
       </c>
-      <c r="K177" s="22"/>
-      <c r="L177" s="22"/>
-      <c r="M177" s="22"/>
-      <c r="N177" s="22"/>
-      <c r="O177" s="22"/>
-      <c r="P177" s="22"/>
-      <c r="Q177" s="22"/>
-      <c r="R177" s="22"/>
-      <c r="S177" s="22"/>
-      <c r="T177" s="22"/>
-      <c r="U177" s="22"/>
     </row>
     <row r="178" spans="1:21" ht="15.75" customHeight="1">
       <c r="A178" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B178" s="21" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="C178" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D178" s="22">
-        <v>348</v>
-      </c>
-      <c r="E178" s="22">
-        <v>897</v>
-      </c>
-      <c r="F178" s="22"/>
-      <c r="G178" s="22" t="s">
-        <v>100</v>
+      <c r="D178" s="20">
+        <v>698</v>
+      </c>
+      <c r="E178" s="20">
+        <v>597</v>
+      </c>
+      <c r="F178" s="20"/>
+      <c r="G178" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H178" s="9"/>
-      <c r="I178" s="9">
-        <f t="shared" si="8"/>
-        <v>23</v>
-      </c>
-      <c r="J178" s="22">
+      <c r="I178" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="J178" s="20">
         <v>30</v>
       </c>
-      <c r="K178" s="22"/>
-      <c r="L178" s="22"/>
-      <c r="M178" s="22"/>
-      <c r="N178" s="22"/>
-      <c r="O178" s="22"/>
-      <c r="P178" s="22"/>
-      <c r="Q178" s="22"/>
-      <c r="R178" s="22"/>
-      <c r="S178" s="22"/>
-      <c r="T178" s="22"/>
-      <c r="U178" s="22"/>
     </row>
     <row r="179" spans="1:21" ht="15.75" customHeight="1">
       <c r="A179" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B179" s="21" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="C179" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D179" s="22">
-        <v>398</v>
-      </c>
-      <c r="E179" s="22">
-        <v>448</v>
-      </c>
-      <c r="F179" s="22"/>
-      <c r="G179" s="22" t="s">
-        <v>100</v>
+      <c r="D179" s="20">
+        <v>798</v>
+      </c>
+      <c r="E179" s="20">
+        <v>147</v>
+      </c>
+      <c r="F179" s="20"/>
+      <c r="G179" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H179" s="9"/>
-      <c r="I179" s="9">
-        <f t="shared" si="8"/>
-        <v>24</v>
-      </c>
-      <c r="J179" s="22">
+      <c r="I179" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J179" s="20">
         <v>30</v>
       </c>
-      <c r="K179" s="22"/>
-      <c r="L179" s="22"/>
-      <c r="M179" s="22"/>
-      <c r="N179" s="22"/>
-      <c r="O179" s="22"/>
-      <c r="P179" s="22"/>
-      <c r="Q179" s="22"/>
-      <c r="R179" s="22"/>
-      <c r="S179" s="22"/>
-      <c r="T179" s="22"/>
-      <c r="U179" s="22"/>
     </row>
     <row r="180" spans="1:21" ht="15.75" customHeight="1">
       <c r="A180" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B180" s="21" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="C180" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D180" s="22">
-        <v>398</v>
-      </c>
-      <c r="E180" s="22">
-        <v>597</v>
-      </c>
-      <c r="F180" s="22"/>
-      <c r="G180" s="22" t="s">
-        <v>100</v>
+      <c r="D180" s="20">
+        <v>798</v>
+      </c>
+      <c r="E180" s="20">
+        <v>297</v>
+      </c>
+      <c r="F180" s="20"/>
+      <c r="G180" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H180" s="9"/>
-      <c r="I180" s="9">
-        <f t="shared" si="8"/>
-        <v>25</v>
-      </c>
-      <c r="J180" s="22">
+      <c r="I180" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="J180" s="20">
         <v>30</v>
       </c>
-      <c r="K180" s="22"/>
-      <c r="L180" s="22"/>
-      <c r="M180" s="22"/>
-      <c r="N180" s="22"/>
-      <c r="O180" s="22"/>
-      <c r="P180" s="22"/>
-      <c r="Q180" s="22"/>
-      <c r="R180" s="22"/>
-      <c r="S180" s="22"/>
-      <c r="T180" s="22"/>
-      <c r="U180" s="22"/>
     </row>
     <row r="181" spans="1:21" ht="15.75" customHeight="1">
       <c r="A181" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B181" s="21" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C181" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="D181" s="22">
-        <v>398</v>
-      </c>
-      <c r="E181" s="22">
-        <v>897</v>
-      </c>
-      <c r="F181" s="22"/>
-      <c r="G181" s="22" t="s">
-        <v>100</v>
+      <c r="D181" s="20">
+        <v>798</v>
+      </c>
+      <c r="E181" s="20">
+        <v>347</v>
+      </c>
+      <c r="F181" s="20"/>
+      <c r="G181" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H181" s="9"/>
-      <c r="I181" s="9">
-        <f t="shared" si="8"/>
-        <v>26</v>
-      </c>
-      <c r="J181" s="22">
+      <c r="I181" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="J181" s="20">
         <v>30</v>
       </c>
-      <c r="K181" s="22"/>
-      <c r="L181" s="22"/>
-      <c r="M181" s="22"/>
-      <c r="N181" s="22"/>
-      <c r="O181" s="22"/>
-      <c r="P181" s="22"/>
-      <c r="Q181" s="22"/>
-      <c r="R181" s="22"/>
-      <c r="S181" s="22"/>
-      <c r="T181" s="22"/>
-      <c r="U181" s="22"/>
     </row>
     <row r="182" spans="1:21" ht="15.75" customHeight="1">
       <c r="A182" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B182" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C182" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D182" s="22">
-        <v>698</v>
-      </c>
-      <c r="E182" s="22">
-        <v>147</v>
-      </c>
-      <c r="F182" s="22"/>
-      <c r="G182" s="22" t="s">
-        <v>100</v>
+        <v>65</v>
+      </c>
+      <c r="C182" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D182" s="20">
+        <v>798</v>
+      </c>
+      <c r="E182" s="20">
+        <v>397</v>
+      </c>
+      <c r="F182" s="20"/>
+      <c r="G182" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H182" s="9"/>
-      <c r="I182" s="9">
-        <v>7</v>
-      </c>
-      <c r="J182" s="22">
+      <c r="I182" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J182" s="20">
         <v>30</v>
       </c>
-      <c r="K182" s="10"/>
-      <c r="L182" s="10"/>
-      <c r="M182" s="10"/>
-      <c r="N182" s="10"/>
-      <c r="O182" s="10"/>
-      <c r="P182" s="10"/>
-      <c r="Q182" s="10"/>
-      <c r="R182" s="10"/>
-      <c r="S182" s="10"/>
-      <c r="T182" s="10"/>
-      <c r="U182" s="10"/>
     </row>
     <row r="183" spans="1:21" ht="15.75" customHeight="1">
       <c r="A183" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B183" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C183" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D183" s="22">
-        <v>698</v>
-      </c>
-      <c r="E183" s="22">
-        <v>297</v>
-      </c>
-      <c r="F183" s="22"/>
-      <c r="G183" s="22" t="s">
-        <v>100</v>
+        <v>66</v>
+      </c>
+      <c r="C183" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D183" s="20">
+        <v>798</v>
+      </c>
+      <c r="E183" s="20">
+        <v>447</v>
+      </c>
+      <c r="F183" s="20"/>
+      <c r="G183" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H183" s="9"/>
-      <c r="I183" s="9">
-        <f>I182+1</f>
-        <v>8</v>
-      </c>
-      <c r="J183" s="22">
+      <c r="I183" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="J183" s="20">
         <v>30</v>
       </c>
-      <c r="K183" s="10"/>
-      <c r="L183" s="10"/>
-      <c r="M183" s="10"/>
-      <c r="N183" s="10"/>
-      <c r="O183" s="10"/>
-      <c r="P183" s="10"/>
-      <c r="Q183" s="10"/>
-      <c r="R183" s="10"/>
-      <c r="S183" s="10"/>
-      <c r="T183" s="10"/>
-      <c r="U183" s="10"/>
     </row>
     <row r="184" spans="1:21" ht="15.75" customHeight="1">
       <c r="A184" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B184" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="C184" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D184" s="22">
-        <v>698</v>
-      </c>
-      <c r="E184" s="22">
-        <v>347</v>
-      </c>
-      <c r="F184" s="22"/>
-      <c r="G184" s="22" t="s">
-        <v>100</v>
+        <v>67</v>
+      </c>
+      <c r="C184" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D184" s="20">
+        <v>798</v>
+      </c>
+      <c r="E184" s="20">
+        <v>497</v>
+      </c>
+      <c r="F184" s="20"/>
+      <c r="G184" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H184" s="9"/>
-      <c r="I184" s="9">
-        <f t="shared" ref="I184:I203" si="9">I183+1</f>
-        <v>9</v>
-      </c>
-      <c r="J184" s="22">
+      <c r="I184" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="J184" s="20">
         <v>30</v>
       </c>
-      <c r="K184" s="10"/>
-      <c r="L184" s="10"/>
-      <c r="M184" s="10"/>
-      <c r="N184" s="10"/>
-      <c r="O184" s="10"/>
-      <c r="P184" s="10"/>
-      <c r="Q184" s="10"/>
-      <c r="R184" s="10"/>
-      <c r="S184" s="10"/>
-      <c r="T184" s="10"/>
-      <c r="U184" s="10"/>
     </row>
     <row r="185" spans="1:21" ht="15.75" customHeight="1">
       <c r="A185" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B185" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C185" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D185" s="22">
-        <v>698</v>
-      </c>
-      <c r="E185" s="22">
-        <v>397</v>
-      </c>
-      <c r="F185" s="22"/>
-      <c r="G185" s="22" t="s">
-        <v>100</v>
+        <v>68</v>
+      </c>
+      <c r="C185" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D185" s="20">
+        <v>798</v>
+      </c>
+      <c r="E185" s="20">
+        <v>597</v>
+      </c>
+      <c r="F185" s="20"/>
+      <c r="G185" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H185" s="9"/>
-      <c r="I185" s="9">
-        <f t="shared" si="9"/>
-        <v>10</v>
-      </c>
-      <c r="J185" s="22">
+      <c r="I185" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J185" s="20">
         <v>30</v>
       </c>
-      <c r="K185" s="10"/>
-      <c r="L185" s="10"/>
-      <c r="M185" s="10"/>
-      <c r="N185" s="10"/>
-      <c r="O185" s="10"/>
-      <c r="P185" s="10"/>
-      <c r="Q185" s="10"/>
-      <c r="R185" s="10"/>
-      <c r="S185" s="10"/>
-      <c r="T185" s="10"/>
-      <c r="U185" s="10"/>
     </row>
     <row r="186" spans="1:21" ht="15.75" customHeight="1">
       <c r="A186" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B186" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C186" s="22" t="s">
-        <v>82</v>
-      </c>
-      <c r="D186" s="22">
-        <v>698</v>
-      </c>
-      <c r="E186" s="22">
-        <v>447</v>
-      </c>
-      <c r="F186" s="22"/>
-      <c r="G186" s="22" t="s">
-        <v>100</v>
+        <v>74</v>
+      </c>
+      <c r="C186" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D186" s="20">
+        <v>1098</v>
+      </c>
+      <c r="E186" s="20">
+        <v>397</v>
+      </c>
+      <c r="F186" s="20"/>
+      <c r="G186" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H186" s="9"/>
-      <c r="I186" s="9">
-        <f t="shared" si="9"/>
-        <v>11</v>
-      </c>
-      <c r="J186" s="22">
+      <c r="I186" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="J186" s="20">
         <v>30</v>
       </c>
       <c r="K186" s="10"/>
@@ -8097,56 +8086,55 @@
         <v>54</v>
       </c>
       <c r="B187" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="C187" s="22" t="s">
-        <v>82</v>
+        <v>69</v>
+      </c>
+      <c r="C187" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D187" s="22">
-        <v>698</v>
+        <v>1098</v>
       </c>
       <c r="E187" s="22">
-        <v>497</v>
+        <v>597</v>
       </c>
       <c r="F187" s="22"/>
-      <c r="G187" s="22" t="s">
-        <v>100</v>
+      <c r="G187" s="21" t="s">
+        <v>99</v>
       </c>
       <c r="H187" s="9"/>
-      <c r="I187" s="9">
-        <f t="shared" si="9"/>
-        <v>12</v>
+      <c r="I187" s="8" t="s">
+        <v>98</v>
       </c>
       <c r="J187" s="22">
         <v>30</v>
       </c>
-      <c r="K187" s="10"/>
-      <c r="L187" s="10"/>
-      <c r="M187" s="10"/>
-      <c r="N187" s="10"/>
-      <c r="O187" s="10"/>
-      <c r="P187" s="10"/>
-      <c r="Q187" s="10"/>
-      <c r="R187" s="10"/>
-      <c r="S187" s="10"/>
-      <c r="T187" s="10"/>
-      <c r="U187" s="10"/>
+      <c r="K187" s="22"/>
+      <c r="L187" s="22"/>
+      <c r="M187" s="22"/>
+      <c r="N187" s="22"/>
+      <c r="O187" s="22"/>
+      <c r="P187" s="22"/>
+      <c r="Q187" s="22"/>
+      <c r="R187" s="22"/>
+      <c r="S187" s="22"/>
+      <c r="T187" s="22"/>
+      <c r="U187" s="22"/>
     </row>
     <row r="188" spans="1:21" ht="15.75" customHeight="1">
       <c r="A188" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B188" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="C188" s="22" t="s">
-        <v>82</v>
+        <v>115</v>
+      </c>
+      <c r="C188" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D188" s="22">
-        <v>698</v>
+        <v>348</v>
       </c>
       <c r="E188" s="22">
-        <v>597</v>
+        <v>448</v>
       </c>
       <c r="F188" s="22"/>
       <c r="G188" s="22" t="s">
@@ -8154,39 +8142,39 @@
       </c>
       <c r="H188" s="9"/>
       <c r="I188" s="9">
-        <f t="shared" si="9"/>
-        <v>13</v>
+        <f t="shared" ref="I188:I193" si="8">I187+1</f>
+        <v>21</v>
       </c>
       <c r="J188" s="22">
         <v>30</v>
       </c>
-      <c r="K188" s="10"/>
-      <c r="L188" s="10"/>
-      <c r="M188" s="10"/>
-      <c r="N188" s="10"/>
-      <c r="O188" s="10"/>
-      <c r="P188" s="10"/>
-      <c r="Q188" s="10"/>
-      <c r="R188" s="10"/>
-      <c r="S188" s="10"/>
-      <c r="T188" s="10"/>
-      <c r="U188" s="10"/>
+      <c r="K188" s="22"/>
+      <c r="L188" s="22"/>
+      <c r="M188" s="22"/>
+      <c r="N188" s="22"/>
+      <c r="O188" s="22"/>
+      <c r="P188" s="22"/>
+      <c r="Q188" s="22"/>
+      <c r="R188" s="22"/>
+      <c r="S188" s="22"/>
+      <c r="T188" s="22"/>
+      <c r="U188" s="22"/>
     </row>
     <row r="189" spans="1:21" ht="15.75" customHeight="1">
       <c r="A189" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B189" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C189" s="22" t="s">
-        <v>82</v>
+        <v>116</v>
+      </c>
+      <c r="C189" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D189" s="22">
-        <v>798</v>
+        <v>348</v>
       </c>
       <c r="E189" s="22">
-        <v>147</v>
+        <v>597</v>
       </c>
       <c r="F189" s="22"/>
       <c r="G189" s="22" t="s">
@@ -8194,39 +8182,39 @@
       </c>
       <c r="H189" s="9"/>
       <c r="I189" s="9">
-        <f t="shared" si="9"/>
-        <v>14</v>
+        <f t="shared" si="8"/>
+        <v>22</v>
       </c>
       <c r="J189" s="22">
         <v>30</v>
       </c>
-      <c r="K189" s="10"/>
-      <c r="L189" s="10"/>
-      <c r="M189" s="10"/>
-      <c r="N189" s="10"/>
-      <c r="O189" s="10"/>
-      <c r="P189" s="10"/>
-      <c r="Q189" s="10"/>
-      <c r="R189" s="10"/>
-      <c r="S189" s="10"/>
-      <c r="T189" s="10"/>
-      <c r="U189" s="10"/>
+      <c r="K189" s="22"/>
+      <c r="L189" s="22"/>
+      <c r="M189" s="22"/>
+      <c r="N189" s="22"/>
+      <c r="O189" s="22"/>
+      <c r="P189" s="22"/>
+      <c r="Q189" s="22"/>
+      <c r="R189" s="22"/>
+      <c r="S189" s="22"/>
+      <c r="T189" s="22"/>
+      <c r="U189" s="22"/>
     </row>
     <row r="190" spans="1:21" ht="15.75" customHeight="1">
       <c r="A190" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B190" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C190" s="22" t="s">
-        <v>82</v>
+        <v>117</v>
+      </c>
+      <c r="C190" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D190" s="22">
-        <v>798</v>
+        <v>348</v>
       </c>
       <c r="E190" s="22">
-        <v>297</v>
+        <v>897</v>
       </c>
       <c r="F190" s="22"/>
       <c r="G190" s="22" t="s">
@@ -8234,39 +8222,39 @@
       </c>
       <c r="H190" s="9"/>
       <c r="I190" s="9">
-        <f t="shared" si="9"/>
-        <v>15</v>
+        <f t="shared" si="8"/>
+        <v>23</v>
       </c>
       <c r="J190" s="22">
         <v>30</v>
       </c>
-      <c r="K190" s="10"/>
-      <c r="L190" s="10"/>
-      <c r="M190" s="10"/>
-      <c r="N190" s="10"/>
-      <c r="O190" s="10"/>
-      <c r="P190" s="10"/>
-      <c r="Q190" s="10"/>
-      <c r="R190" s="10"/>
-      <c r="S190" s="10"/>
-      <c r="T190" s="10"/>
-      <c r="U190" s="10"/>
+      <c r="K190" s="22"/>
+      <c r="L190" s="22"/>
+      <c r="M190" s="22"/>
+      <c r="N190" s="22"/>
+      <c r="O190" s="22"/>
+      <c r="P190" s="22"/>
+      <c r="Q190" s="22"/>
+      <c r="R190" s="22"/>
+      <c r="S190" s="22"/>
+      <c r="T190" s="22"/>
+      <c r="U190" s="22"/>
     </row>
     <row r="191" spans="1:21" ht="15.75" customHeight="1">
       <c r="A191" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B191" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="C191" s="22" t="s">
-        <v>82</v>
+        <v>118</v>
+      </c>
+      <c r="C191" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D191" s="22">
-        <v>798</v>
+        <v>398</v>
       </c>
       <c r="E191" s="22">
-        <v>347</v>
+        <v>448</v>
       </c>
       <c r="F191" s="22"/>
       <c r="G191" s="22" t="s">
@@ -8274,39 +8262,39 @@
       </c>
       <c r="H191" s="9"/>
       <c r="I191" s="9">
-        <f t="shared" si="9"/>
-        <v>16</v>
+        <f t="shared" si="8"/>
+        <v>24</v>
       </c>
       <c r="J191" s="22">
         <v>30</v>
       </c>
-      <c r="K191" s="10"/>
-      <c r="L191" s="10"/>
-      <c r="M191" s="10"/>
-      <c r="N191" s="10"/>
-      <c r="O191" s="10"/>
-      <c r="P191" s="10"/>
-      <c r="Q191" s="10"/>
-      <c r="R191" s="10"/>
-      <c r="S191" s="10"/>
-      <c r="T191" s="10"/>
-      <c r="U191" s="10"/>
+      <c r="K191" s="22"/>
+      <c r="L191" s="22"/>
+      <c r="M191" s="22"/>
+      <c r="N191" s="22"/>
+      <c r="O191" s="22"/>
+      <c r="P191" s="22"/>
+      <c r="Q191" s="22"/>
+      <c r="R191" s="22"/>
+      <c r="S191" s="22"/>
+      <c r="T191" s="22"/>
+      <c r="U191" s="22"/>
     </row>
     <row r="192" spans="1:21" ht="15.75" customHeight="1">
       <c r="A192" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B192" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C192" s="22" t="s">
-        <v>82</v>
+        <v>119</v>
+      </c>
+      <c r="C192" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D192" s="22">
-        <v>798</v>
+        <v>398</v>
       </c>
       <c r="E192" s="22">
-        <v>397</v>
+        <v>597</v>
       </c>
       <c r="F192" s="22"/>
       <c r="G192" s="22" t="s">
@@ -8314,39 +8302,39 @@
       </c>
       <c r="H192" s="9"/>
       <c r="I192" s="9">
-        <f t="shared" si="9"/>
-        <v>17</v>
+        <f t="shared" si="8"/>
+        <v>25</v>
       </c>
       <c r="J192" s="22">
         <v>30</v>
       </c>
-      <c r="K192" s="10"/>
-      <c r="L192" s="10"/>
-      <c r="M192" s="10"/>
-      <c r="N192" s="10"/>
-      <c r="O192" s="10"/>
-      <c r="P192" s="10"/>
-      <c r="Q192" s="10"/>
-      <c r="R192" s="10"/>
-      <c r="S192" s="10"/>
-      <c r="T192" s="10"/>
-      <c r="U192" s="10"/>
+      <c r="K192" s="22"/>
+      <c r="L192" s="22"/>
+      <c r="M192" s="22"/>
+      <c r="N192" s="22"/>
+      <c r="O192" s="22"/>
+      <c r="P192" s="22"/>
+      <c r="Q192" s="22"/>
+      <c r="R192" s="22"/>
+      <c r="S192" s="22"/>
+      <c r="T192" s="22"/>
+      <c r="U192" s="22"/>
     </row>
     <row r="193" spans="1:21" ht="15.75" customHeight="1">
       <c r="A193" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B193" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C193" s="22" t="s">
-        <v>82</v>
+        <v>120</v>
+      </c>
+      <c r="C193" s="21" t="s">
+        <v>83</v>
       </c>
       <c r="D193" s="22">
-        <v>798</v>
+        <v>398</v>
       </c>
       <c r="E193" s="22">
-        <v>447</v>
+        <v>897</v>
       </c>
       <c r="F193" s="22"/>
       <c r="G193" s="22" t="s">
@@ -8354,39 +8342,39 @@
       </c>
       <c r="H193" s="9"/>
       <c r="I193" s="9">
-        <f t="shared" si="9"/>
-        <v>18</v>
+        <f t="shared" si="8"/>
+        <v>26</v>
       </c>
       <c r="J193" s="22">
         <v>30</v>
       </c>
-      <c r="K193" s="10"/>
-      <c r="L193" s="10"/>
-      <c r="M193" s="10"/>
-      <c r="N193" s="10"/>
-      <c r="O193" s="10"/>
-      <c r="P193" s="10"/>
-      <c r="Q193" s="10"/>
-      <c r="R193" s="10"/>
-      <c r="S193" s="10"/>
-      <c r="T193" s="10"/>
-      <c r="U193" s="10"/>
+      <c r="K193" s="22"/>
+      <c r="L193" s="22"/>
+      <c r="M193" s="22"/>
+      <c r="N193" s="22"/>
+      <c r="O193" s="22"/>
+      <c r="P193" s="22"/>
+      <c r="Q193" s="22"/>
+      <c r="R193" s="22"/>
+      <c r="S193" s="22"/>
+      <c r="T193" s="22"/>
+      <c r="U193" s="22"/>
     </row>
     <row r="194" spans="1:21" ht="15.75" customHeight="1">
       <c r="A194" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B194" s="21" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C194" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D194" s="22">
-        <v>798</v>
+        <v>698</v>
       </c>
       <c r="E194" s="22">
-        <v>497</v>
+        <v>147</v>
       </c>
       <c r="F194" s="22"/>
       <c r="G194" s="22" t="s">
@@ -8394,8 +8382,7 @@
       </c>
       <c r="H194" s="9"/>
       <c r="I194" s="9">
-        <f t="shared" si="9"/>
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J194" s="22">
         <v>30</v>
@@ -8417,16 +8404,16 @@
         <v>54</v>
       </c>
       <c r="B195" s="21" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="C195" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D195" s="22">
-        <v>798</v>
+        <v>698</v>
       </c>
       <c r="E195" s="22">
-        <v>597</v>
+        <v>297</v>
       </c>
       <c r="F195" s="22"/>
       <c r="G195" s="22" t="s">
@@ -8434,8 +8421,8 @@
       </c>
       <c r="H195" s="9"/>
       <c r="I195" s="9">
-        <f t="shared" si="9"/>
-        <v>20</v>
+        <f>I194+1</f>
+        <v>8</v>
       </c>
       <c r="J195" s="22">
         <v>30</v>
@@ -8457,16 +8444,16 @@
         <v>54</v>
       </c>
       <c r="B196" s="21" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C196" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D196" s="22">
-        <v>1098</v>
+        <v>698</v>
       </c>
       <c r="E196" s="22">
-        <v>397</v>
+        <v>347</v>
       </c>
       <c r="F196" s="22"/>
       <c r="G196" s="22" t="s">
@@ -8474,8 +8461,8 @@
       </c>
       <c r="H196" s="9"/>
       <c r="I196" s="9">
-        <f t="shared" si="9"/>
-        <v>21</v>
+        <f t="shared" ref="I196:I215" si="9">I195+1</f>
+        <v>9</v>
       </c>
       <c r="J196" s="22">
         <v>30</v>
@@ -8497,16 +8484,16 @@
         <v>54</v>
       </c>
       <c r="B197" s="21" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C197" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D197" s="22">
-        <v>1098</v>
+        <v>698</v>
       </c>
       <c r="E197" s="22">
-        <v>597</v>
+        <v>397</v>
       </c>
       <c r="F197" s="22"/>
       <c r="G197" s="22" t="s">
@@ -8515,7 +8502,7 @@
       <c r="H197" s="9"/>
       <c r="I197" s="9">
         <f t="shared" si="9"/>
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J197" s="22">
         <v>30</v>
@@ -8537,16 +8524,16 @@
         <v>54</v>
       </c>
       <c r="B198" s="21" t="s">
-        <v>115</v>
+        <v>59</v>
       </c>
       <c r="C198" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D198" s="22">
-        <v>348</v>
+        <v>698</v>
       </c>
       <c r="E198" s="22">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F198" s="22"/>
       <c r="G198" s="22" t="s">
@@ -8555,38 +8542,38 @@
       <c r="H198" s="9"/>
       <c r="I198" s="9">
         <f t="shared" si="9"/>
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="J198" s="22">
         <v>30</v>
       </c>
-      <c r="K198" s="22"/>
-      <c r="L198" s="22"/>
-      <c r="M198" s="22"/>
-      <c r="N198" s="22"/>
-      <c r="O198" s="22"/>
-      <c r="P198" s="22"/>
-      <c r="Q198" s="22"/>
-      <c r="R198" s="22"/>
-      <c r="S198" s="22"/>
-      <c r="T198" s="22"/>
-      <c r="U198" s="22"/>
+      <c r="K198" s="10"/>
+      <c r="L198" s="10"/>
+      <c r="M198" s="10"/>
+      <c r="N198" s="10"/>
+      <c r="O198" s="10"/>
+      <c r="P198" s="10"/>
+      <c r="Q198" s="10"/>
+      <c r="R198" s="10"/>
+      <c r="S198" s="10"/>
+      <c r="T198" s="10"/>
+      <c r="U198" s="10"/>
     </row>
     <row r="199" spans="1:21" ht="15.75" customHeight="1">
       <c r="A199" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B199" s="21" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
       <c r="C199" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D199" s="22">
-        <v>348</v>
+        <v>698</v>
       </c>
       <c r="E199" s="22">
-        <v>597</v>
+        <v>497</v>
       </c>
       <c r="F199" s="22"/>
       <c r="G199" s="22" t="s">
@@ -8595,38 +8582,38 @@
       <c r="H199" s="9"/>
       <c r="I199" s="9">
         <f t="shared" si="9"/>
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="J199" s="22">
         <v>30</v>
       </c>
-      <c r="K199" s="22"/>
-      <c r="L199" s="22"/>
-      <c r="M199" s="22"/>
-      <c r="N199" s="22"/>
-      <c r="O199" s="22"/>
-      <c r="P199" s="22"/>
-      <c r="Q199" s="22"/>
-      <c r="R199" s="22"/>
-      <c r="S199" s="22"/>
-      <c r="T199" s="22"/>
-      <c r="U199" s="22"/>
+      <c r="K199" s="10"/>
+      <c r="L199" s="10"/>
+      <c r="M199" s="10"/>
+      <c r="N199" s="10"/>
+      <c r="O199" s="10"/>
+      <c r="P199" s="10"/>
+      <c r="Q199" s="10"/>
+      <c r="R199" s="10"/>
+      <c r="S199" s="10"/>
+      <c r="T199" s="10"/>
+      <c r="U199" s="10"/>
     </row>
     <row r="200" spans="1:21" ht="15.75" customHeight="1">
       <c r="A200" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B200" s="21" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="C200" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D200" s="22">
-        <v>348</v>
+        <v>698</v>
       </c>
       <c r="E200" s="22">
-        <v>897</v>
+        <v>597</v>
       </c>
       <c r="F200" s="22"/>
       <c r="G200" s="22" t="s">
@@ -8635,38 +8622,38 @@
       <c r="H200" s="9"/>
       <c r="I200" s="9">
         <f t="shared" si="9"/>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="J200" s="22">
         <v>30</v>
       </c>
-      <c r="K200" s="22"/>
-      <c r="L200" s="22"/>
-      <c r="M200" s="22"/>
-      <c r="N200" s="22"/>
-      <c r="O200" s="22"/>
-      <c r="P200" s="22"/>
-      <c r="Q200" s="22"/>
-      <c r="R200" s="22"/>
-      <c r="S200" s="22"/>
-      <c r="T200" s="22"/>
-      <c r="U200" s="22"/>
+      <c r="K200" s="10"/>
+      <c r="L200" s="10"/>
+      <c r="M200" s="10"/>
+      <c r="N200" s="10"/>
+      <c r="O200" s="10"/>
+      <c r="P200" s="10"/>
+      <c r="Q200" s="10"/>
+      <c r="R200" s="10"/>
+      <c r="S200" s="10"/>
+      <c r="T200" s="10"/>
+      <c r="U200" s="10"/>
     </row>
     <row r="201" spans="1:21" ht="15.75" customHeight="1">
       <c r="A201" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B201" s="21" t="s">
-        <v>118</v>
+        <v>62</v>
       </c>
       <c r="C201" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D201" s="22">
-        <v>398</v>
+        <v>798</v>
       </c>
       <c r="E201" s="22">
-        <v>448</v>
+        <v>147</v>
       </c>
       <c r="F201" s="22"/>
       <c r="G201" s="22" t="s">
@@ -8675,38 +8662,38 @@
       <c r="H201" s="9"/>
       <c r="I201" s="9">
         <f t="shared" si="9"/>
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J201" s="22">
         <v>30</v>
       </c>
-      <c r="K201" s="22"/>
-      <c r="L201" s="22"/>
-      <c r="M201" s="22"/>
-      <c r="N201" s="22"/>
-      <c r="O201" s="22"/>
-      <c r="P201" s="22"/>
-      <c r="Q201" s="22"/>
-      <c r="R201" s="22"/>
-      <c r="S201" s="22"/>
-      <c r="T201" s="22"/>
-      <c r="U201" s="22"/>
+      <c r="K201" s="10"/>
+      <c r="L201" s="10"/>
+      <c r="M201" s="10"/>
+      <c r="N201" s="10"/>
+      <c r="O201" s="10"/>
+      <c r="P201" s="10"/>
+      <c r="Q201" s="10"/>
+      <c r="R201" s="10"/>
+      <c r="S201" s="10"/>
+      <c r="T201" s="10"/>
+      <c r="U201" s="10"/>
     </row>
     <row r="202" spans="1:21" ht="15.75" customHeight="1">
       <c r="A202" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B202" s="21" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="C202" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D202" s="22">
-        <v>398</v>
+        <v>798</v>
       </c>
       <c r="E202" s="22">
-        <v>597</v>
+        <v>297</v>
       </c>
       <c r="F202" s="22"/>
       <c r="G202" s="22" t="s">
@@ -8715,38 +8702,38 @@
       <c r="H202" s="9"/>
       <c r="I202" s="9">
         <f t="shared" si="9"/>
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J202" s="22">
         <v>30</v>
       </c>
-      <c r="K202" s="22"/>
-      <c r="L202" s="22"/>
-      <c r="M202" s="22"/>
-      <c r="N202" s="22"/>
-      <c r="O202" s="22"/>
-      <c r="P202" s="22"/>
-      <c r="Q202" s="22"/>
-      <c r="R202" s="22"/>
-      <c r="S202" s="22"/>
-      <c r="T202" s="22"/>
-      <c r="U202" s="22"/>
+      <c r="K202" s="10"/>
+      <c r="L202" s="10"/>
+      <c r="M202" s="10"/>
+      <c r="N202" s="10"/>
+      <c r="O202" s="10"/>
+      <c r="P202" s="10"/>
+      <c r="Q202" s="10"/>
+      <c r="R202" s="10"/>
+      <c r="S202" s="10"/>
+      <c r="T202" s="10"/>
+      <c r="U202" s="10"/>
     </row>
     <row r="203" spans="1:21" ht="15.75" customHeight="1">
       <c r="A203" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B203" s="21" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="C203" s="22" t="s">
         <v>82</v>
       </c>
       <c r="D203" s="22">
-        <v>398</v>
+        <v>798</v>
       </c>
       <c r="E203" s="22">
-        <v>897</v>
+        <v>347</v>
       </c>
       <c r="F203" s="22"/>
       <c r="G203" s="22" t="s">
@@ -8755,298 +8742,502 @@
       <c r="H203" s="9"/>
       <c r="I203" s="9">
         <f t="shared" si="9"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J203" s="22">
         <v>30</v>
       </c>
-      <c r="K203" s="22"/>
-      <c r="L203" s="22"/>
-      <c r="M203" s="22"/>
-      <c r="N203" s="22"/>
-      <c r="O203" s="22"/>
-      <c r="P203" s="22"/>
-      <c r="Q203" s="22"/>
-      <c r="R203" s="22"/>
-      <c r="S203" s="22"/>
-      <c r="T203" s="22"/>
-      <c r="U203" s="22"/>
-    </row>
-    <row r="218" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A218" s="10"/>
-      <c r="B218" s="10"/>
-      <c r="C218" s="10"/>
-      <c r="D218" s="10"/>
-      <c r="E218" s="10"/>
-      <c r="F218" s="10"/>
-      <c r="G218" s="10"/>
-      <c r="H218" s="10"/>
-      <c r="I218" s="10"/>
-      <c r="J218" s="10"/>
-      <c r="K218" s="10"/>
-      <c r="L218" s="10"/>
-      <c r="M218" s="10"/>
-      <c r="N218" s="10"/>
-      <c r="O218" s="10"/>
-      <c r="P218" s="10"/>
-      <c r="Q218" s="10"/>
-      <c r="R218" s="10"/>
-      <c r="S218" s="10"/>
-      <c r="T218" s="10"/>
-      <c r="U218" s="10"/>
-    </row>
-    <row r="219" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A219" s="10"/>
-      <c r="B219" s="10"/>
-      <c r="C219" s="10"/>
-      <c r="D219" s="10"/>
-      <c r="E219" s="10"/>
-      <c r="F219" s="10"/>
-      <c r="G219" s="10"/>
-      <c r="H219" s="10"/>
-      <c r="I219" s="10"/>
-      <c r="J219" s="10"/>
-      <c r="K219" s="10"/>
-      <c r="L219" s="10"/>
-      <c r="M219" s="10"/>
-      <c r="N219" s="10"/>
-      <c r="O219" s="10"/>
-      <c r="P219" s="10"/>
-      <c r="Q219" s="10"/>
-      <c r="R219" s="10"/>
-      <c r="S219" s="10"/>
-      <c r="T219" s="10"/>
-      <c r="U219" s="10"/>
-    </row>
-    <row r="220" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A220" s="10"/>
-      <c r="B220" s="10"/>
-      <c r="C220" s="10"/>
-      <c r="D220" s="10"/>
-      <c r="E220" s="10"/>
-      <c r="F220" s="10"/>
-      <c r="G220" s="10"/>
-      <c r="H220" s="10"/>
-      <c r="I220" s="10"/>
-      <c r="J220" s="10"/>
-      <c r="K220" s="10"/>
-      <c r="L220" s="10"/>
-      <c r="M220" s="10"/>
-      <c r="N220" s="10"/>
-      <c r="O220" s="10"/>
-      <c r="P220" s="10"/>
-      <c r="Q220" s="10"/>
-      <c r="R220" s="10"/>
-      <c r="S220" s="10"/>
-      <c r="T220" s="10"/>
-      <c r="U220" s="10"/>
-    </row>
-    <row r="221" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A221" s="10"/>
-      <c r="B221" s="10"/>
-      <c r="C221" s="10"/>
-      <c r="D221" s="10"/>
-      <c r="E221" s="10"/>
-      <c r="F221" s="10"/>
-      <c r="G221" s="10"/>
-      <c r="H221" s="10"/>
-      <c r="I221" s="10"/>
-      <c r="J221" s="10"/>
-      <c r="K221" s="10"/>
-      <c r="L221" s="10"/>
-      <c r="M221" s="10"/>
-      <c r="N221" s="10"/>
-      <c r="O221" s="10"/>
-      <c r="P221" s="10"/>
-      <c r="Q221" s="10"/>
-      <c r="R221" s="10"/>
-      <c r="S221" s="10"/>
-      <c r="T221" s="10"/>
-      <c r="U221" s="10"/>
-    </row>
-    <row r="222" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A222" s="10"/>
-      <c r="B222" s="10"/>
-      <c r="C222" s="10"/>
-      <c r="D222" s="10"/>
-      <c r="E222" s="10"/>
-      <c r="F222" s="10"/>
-      <c r="G222" s="10"/>
-      <c r="H222" s="10"/>
-      <c r="I222" s="10"/>
-      <c r="J222" s="10"/>
-      <c r="K222" s="10"/>
-      <c r="L222" s="10"/>
-      <c r="M222" s="10"/>
-      <c r="N222" s="10"/>
-      <c r="O222" s="10"/>
-      <c r="P222" s="10"/>
-      <c r="Q222" s="10"/>
-      <c r="R222" s="10"/>
-      <c r="S222" s="10"/>
-      <c r="T222" s="10"/>
-      <c r="U222" s="10"/>
-    </row>
-    <row r="223" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A223" s="10"/>
-      <c r="B223" s="10"/>
-      <c r="C223" s="10"/>
-      <c r="D223" s="10"/>
-      <c r="E223" s="10"/>
-      <c r="F223" s="10"/>
-      <c r="G223" s="10"/>
-      <c r="H223" s="10"/>
-      <c r="I223" s="10"/>
-      <c r="J223" s="10"/>
-      <c r="K223" s="10"/>
-      <c r="L223" s="10"/>
-      <c r="M223" s="10"/>
-      <c r="N223" s="10"/>
-      <c r="O223" s="10"/>
-      <c r="P223" s="10"/>
-      <c r="Q223" s="10"/>
-      <c r="R223" s="10"/>
-      <c r="S223" s="10"/>
-      <c r="T223" s="10"/>
-      <c r="U223" s="10"/>
-    </row>
-    <row r="224" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A224" s="10"/>
-      <c r="B224" s="10"/>
-      <c r="C224" s="10"/>
-      <c r="D224" s="10"/>
-      <c r="E224" s="10"/>
-      <c r="F224" s="10"/>
-      <c r="G224" s="10"/>
-      <c r="H224" s="10"/>
-      <c r="I224" s="10"/>
-      <c r="J224" s="10"/>
-      <c r="K224" s="10"/>
-      <c r="L224" s="10"/>
-      <c r="M224" s="10"/>
-      <c r="N224" s="10"/>
-      <c r="O224" s="10"/>
-      <c r="P224" s="10"/>
-      <c r="Q224" s="10"/>
-      <c r="R224" s="10"/>
-      <c r="S224" s="10"/>
-      <c r="T224" s="10"/>
-      <c r="U224" s="10"/>
-    </row>
-    <row r="225" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A225" s="10"/>
-      <c r="B225" s="10"/>
-      <c r="C225" s="10"/>
-      <c r="D225" s="10"/>
-      <c r="E225" s="10"/>
-      <c r="F225" s="10"/>
-      <c r="G225" s="10"/>
-      <c r="H225" s="10"/>
-      <c r="I225" s="10"/>
-      <c r="J225" s="10"/>
-      <c r="K225" s="10"/>
-      <c r="L225" s="10"/>
-      <c r="M225" s="10"/>
-      <c r="N225" s="10"/>
-      <c r="O225" s="10"/>
-      <c r="P225" s="10"/>
-      <c r="Q225" s="10"/>
-      <c r="R225" s="10"/>
-      <c r="S225" s="10"/>
-      <c r="T225" s="10"/>
-      <c r="U225" s="10"/>
-    </row>
-    <row r="226" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A226" s="10"/>
-      <c r="B226" s="10"/>
-      <c r="C226" s="10"/>
-      <c r="D226" s="10"/>
-      <c r="E226" s="10"/>
-      <c r="F226" s="10"/>
-      <c r="G226" s="10"/>
-      <c r="H226" s="10"/>
-      <c r="I226" s="10"/>
-      <c r="J226" s="10"/>
-      <c r="K226" s="10"/>
-      <c r="L226" s="10"/>
-      <c r="M226" s="10"/>
-      <c r="N226" s="10"/>
-      <c r="O226" s="10"/>
-      <c r="P226" s="10"/>
-      <c r="Q226" s="10"/>
-      <c r="R226" s="10"/>
-      <c r="S226" s="10"/>
-      <c r="T226" s="10"/>
-      <c r="U226" s="10"/>
-    </row>
-    <row r="227" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A227" s="10"/>
-      <c r="B227" s="10"/>
-      <c r="C227" s="10"/>
-      <c r="D227" s="10"/>
-      <c r="E227" s="10"/>
-      <c r="F227" s="10"/>
-      <c r="G227" s="10"/>
-      <c r="H227" s="10"/>
-      <c r="I227" s="10"/>
-      <c r="J227" s="10"/>
-      <c r="K227" s="10"/>
-      <c r="L227" s="10"/>
-      <c r="M227" s="10"/>
-      <c r="N227" s="10"/>
-      <c r="O227" s="10"/>
-      <c r="P227" s="10"/>
-      <c r="Q227" s="10"/>
-      <c r="R227" s="10"/>
-      <c r="S227" s="10"/>
-      <c r="T227" s="10"/>
-      <c r="U227" s="10"/>
-    </row>
-    <row r="228" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A228" s="10"/>
-      <c r="B228" s="10"/>
-      <c r="C228" s="10"/>
-      <c r="D228" s="10"/>
-      <c r="E228" s="10"/>
-      <c r="F228" s="10"/>
-      <c r="G228" s="10"/>
-      <c r="H228" s="10"/>
-      <c r="I228" s="10"/>
-      <c r="J228" s="10"/>
-      <c r="K228" s="10"/>
-      <c r="L228" s="10"/>
-      <c r="M228" s="10"/>
-      <c r="N228" s="10"/>
-      <c r="O228" s="10"/>
-      <c r="P228" s="10"/>
-      <c r="Q228" s="10"/>
-      <c r="R228" s="10"/>
-      <c r="S228" s="10"/>
-      <c r="T228" s="10"/>
-      <c r="U228" s="10"/>
-    </row>
-    <row r="229" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A229" s="10"/>
-      <c r="B229" s="10"/>
-      <c r="C229" s="10"/>
-      <c r="D229" s="10"/>
-      <c r="E229" s="10"/>
-      <c r="F229" s="10"/>
-      <c r="G229" s="10"/>
-      <c r="H229" s="10"/>
-      <c r="I229" s="10"/>
-      <c r="J229" s="10"/>
-      <c r="K229" s="10"/>
-      <c r="L229" s="10"/>
-      <c r="M229" s="10"/>
-      <c r="N229" s="10"/>
-      <c r="O229" s="10"/>
-      <c r="P229" s="10"/>
-      <c r="Q229" s="10"/>
-      <c r="R229" s="10"/>
-      <c r="S229" s="10"/>
-      <c r="T229" s="10"/>
-      <c r="U229" s="10"/>
+      <c r="K203" s="10"/>
+      <c r="L203" s="10"/>
+      <c r="M203" s="10"/>
+      <c r="N203" s="10"/>
+      <c r="O203" s="10"/>
+      <c r="P203" s="10"/>
+      <c r="Q203" s="10"/>
+      <c r="R203" s="10"/>
+      <c r="S203" s="10"/>
+      <c r="T203" s="10"/>
+      <c r="U203" s="10"/>
+    </row>
+    <row r="204" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A204" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B204" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C204" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D204" s="22">
+        <v>798</v>
+      </c>
+      <c r="E204" s="22">
+        <v>397</v>
+      </c>
+      <c r="F204" s="22"/>
+      <c r="G204" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H204" s="9"/>
+      <c r="I204" s="9">
+        <f t="shared" si="9"/>
+        <v>17</v>
+      </c>
+      <c r="J204" s="22">
+        <v>30</v>
+      </c>
+      <c r="K204" s="10"/>
+      <c r="L204" s="10"/>
+      <c r="M204" s="10"/>
+      <c r="N204" s="10"/>
+      <c r="O204" s="10"/>
+      <c r="P204" s="10"/>
+      <c r="Q204" s="10"/>
+      <c r="R204" s="10"/>
+      <c r="S204" s="10"/>
+      <c r="T204" s="10"/>
+      <c r="U204" s="10"/>
+    </row>
+    <row r="205" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A205" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B205" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="C205" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D205" s="22">
+        <v>798</v>
+      </c>
+      <c r="E205" s="22">
+        <v>447</v>
+      </c>
+      <c r="F205" s="22"/>
+      <c r="G205" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H205" s="9"/>
+      <c r="I205" s="9">
+        <f t="shared" si="9"/>
+        <v>18</v>
+      </c>
+      <c r="J205" s="22">
+        <v>30</v>
+      </c>
+      <c r="K205" s="10"/>
+      <c r="L205" s="10"/>
+      <c r="M205" s="10"/>
+      <c r="N205" s="10"/>
+      <c r="O205" s="10"/>
+      <c r="P205" s="10"/>
+      <c r="Q205" s="10"/>
+      <c r="R205" s="10"/>
+      <c r="S205" s="10"/>
+      <c r="T205" s="10"/>
+      <c r="U205" s="10"/>
+    </row>
+    <row r="206" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A206" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B206" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C206" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D206" s="22">
+        <v>798</v>
+      </c>
+      <c r="E206" s="22">
+        <v>497</v>
+      </c>
+      <c r="F206" s="22"/>
+      <c r="G206" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H206" s="9"/>
+      <c r="I206" s="9">
+        <f t="shared" si="9"/>
+        <v>19</v>
+      </c>
+      <c r="J206" s="22">
+        <v>30</v>
+      </c>
+      <c r="K206" s="10"/>
+      <c r="L206" s="10"/>
+      <c r="M206" s="10"/>
+      <c r="N206" s="10"/>
+      <c r="O206" s="10"/>
+      <c r="P206" s="10"/>
+      <c r="Q206" s="10"/>
+      <c r="R206" s="10"/>
+      <c r="S206" s="10"/>
+      <c r="T206" s="10"/>
+      <c r="U206" s="10"/>
+    </row>
+    <row r="207" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A207" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C207" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D207" s="22">
+        <v>798</v>
+      </c>
+      <c r="E207" s="22">
+        <v>597</v>
+      </c>
+      <c r="F207" s="22"/>
+      <c r="G207" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H207" s="9"/>
+      <c r="I207" s="9">
+        <f t="shared" si="9"/>
+        <v>20</v>
+      </c>
+      <c r="J207" s="22">
+        <v>30</v>
+      </c>
+      <c r="K207" s="10"/>
+      <c r="L207" s="10"/>
+      <c r="M207" s="10"/>
+      <c r="N207" s="10"/>
+      <c r="O207" s="10"/>
+      <c r="P207" s="10"/>
+      <c r="Q207" s="10"/>
+      <c r="R207" s="10"/>
+      <c r="S207" s="10"/>
+      <c r="T207" s="10"/>
+      <c r="U207" s="10"/>
+    </row>
+    <row r="208" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A208" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B208" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C208" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D208" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E208" s="22">
+        <v>397</v>
+      </c>
+      <c r="F208" s="22"/>
+      <c r="G208" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H208" s="9"/>
+      <c r="I208" s="9">
+        <f t="shared" si="9"/>
+        <v>21</v>
+      </c>
+      <c r="J208" s="22">
+        <v>30</v>
+      </c>
+      <c r="K208" s="10"/>
+      <c r="L208" s="10"/>
+      <c r="M208" s="10"/>
+      <c r="N208" s="10"/>
+      <c r="O208" s="10"/>
+      <c r="P208" s="10"/>
+      <c r="Q208" s="10"/>
+      <c r="R208" s="10"/>
+      <c r="S208" s="10"/>
+      <c r="T208" s="10"/>
+      <c r="U208" s="10"/>
+    </row>
+    <row r="209" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A209" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B209" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C209" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D209" s="22">
+        <v>1098</v>
+      </c>
+      <c r="E209" s="22">
+        <v>597</v>
+      </c>
+      <c r="F209" s="22"/>
+      <c r="G209" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H209" s="9"/>
+      <c r="I209" s="9">
+        <f t="shared" si="9"/>
+        <v>22</v>
+      </c>
+      <c r="J209" s="22">
+        <v>30</v>
+      </c>
+      <c r="K209" s="10"/>
+      <c r="L209" s="10"/>
+      <c r="M209" s="10"/>
+      <c r="N209" s="10"/>
+      <c r="O209" s="10"/>
+      <c r="P209" s="10"/>
+      <c r="Q209" s="10"/>
+      <c r="R209" s="10"/>
+      <c r="S209" s="10"/>
+      <c r="T209" s="10"/>
+      <c r="U209" s="10"/>
+    </row>
+    <row r="210" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A210" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B210" s="21" t="s">
+        <v>115</v>
+      </c>
+      <c r="C210" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D210" s="22">
+        <v>348</v>
+      </c>
+      <c r="E210" s="22">
+        <v>448</v>
+      </c>
+      <c r="F210" s="22"/>
+      <c r="G210" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H210" s="9"/>
+      <c r="I210" s="9">
+        <f t="shared" si="9"/>
+        <v>23</v>
+      </c>
+      <c r="J210" s="22">
+        <v>30</v>
+      </c>
+      <c r="K210" s="22"/>
+      <c r="L210" s="22"/>
+      <c r="M210" s="22"/>
+      <c r="N210" s="22"/>
+      <c r="O210" s="22"/>
+      <c r="P210" s="22"/>
+      <c r="Q210" s="22"/>
+      <c r="R210" s="22"/>
+      <c r="S210" s="22"/>
+      <c r="T210" s="22"/>
+      <c r="U210" s="22"/>
+    </row>
+    <row r="211" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A211" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B211" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="C211" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D211" s="22">
+        <v>348</v>
+      </c>
+      <c r="E211" s="22">
+        <v>597</v>
+      </c>
+      <c r="F211" s="22"/>
+      <c r="G211" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H211" s="9"/>
+      <c r="I211" s="9">
+        <f t="shared" si="9"/>
+        <v>24</v>
+      </c>
+      <c r="J211" s="22">
+        <v>30</v>
+      </c>
+      <c r="K211" s="22"/>
+      <c r="L211" s="22"/>
+      <c r="M211" s="22"/>
+      <c r="N211" s="22"/>
+      <c r="O211" s="22"/>
+      <c r="P211" s="22"/>
+      <c r="Q211" s="22"/>
+      <c r="R211" s="22"/>
+      <c r="S211" s="22"/>
+      <c r="T211" s="22"/>
+      <c r="U211" s="22"/>
+    </row>
+    <row r="212" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A212" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B212" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="C212" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D212" s="22">
+        <v>348</v>
+      </c>
+      <c r="E212" s="22">
+        <v>897</v>
+      </c>
+      <c r="F212" s="22"/>
+      <c r="G212" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H212" s="9"/>
+      <c r="I212" s="9">
+        <f t="shared" si="9"/>
+        <v>25</v>
+      </c>
+      <c r="J212" s="22">
+        <v>30</v>
+      </c>
+      <c r="K212" s="22"/>
+      <c r="L212" s="22"/>
+      <c r="M212" s="22"/>
+      <c r="N212" s="22"/>
+      <c r="O212" s="22"/>
+      <c r="P212" s="22"/>
+      <c r="Q212" s="22"/>
+      <c r="R212" s="22"/>
+      <c r="S212" s="22"/>
+      <c r="T212" s="22"/>
+      <c r="U212" s="22"/>
+    </row>
+    <row r="213" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A213" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B213" s="21" t="s">
+        <v>118</v>
+      </c>
+      <c r="C213" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D213" s="22">
+        <v>398</v>
+      </c>
+      <c r="E213" s="22">
+        <v>448</v>
+      </c>
+      <c r="F213" s="22"/>
+      <c r="G213" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H213" s="9"/>
+      <c r="I213" s="9">
+        <f t="shared" si="9"/>
+        <v>26</v>
+      </c>
+      <c r="J213" s="22">
+        <v>30</v>
+      </c>
+      <c r="K213" s="22"/>
+      <c r="L213" s="22"/>
+      <c r="M213" s="22"/>
+      <c r="N213" s="22"/>
+      <c r="O213" s="22"/>
+      <c r="P213" s="22"/>
+      <c r="Q213" s="22"/>
+      <c r="R213" s="22"/>
+      <c r="S213" s="22"/>
+      <c r="T213" s="22"/>
+      <c r="U213" s="22"/>
+    </row>
+    <row r="214" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A214" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B214" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C214" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D214" s="22">
+        <v>398</v>
+      </c>
+      <c r="E214" s="22">
+        <v>597</v>
+      </c>
+      <c r="F214" s="22"/>
+      <c r="G214" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H214" s="9"/>
+      <c r="I214" s="9">
+        <f t="shared" si="9"/>
+        <v>27</v>
+      </c>
+      <c r="J214" s="22">
+        <v>30</v>
+      </c>
+      <c r="K214" s="22"/>
+      <c r="L214" s="22"/>
+      <c r="M214" s="22"/>
+      <c r="N214" s="22"/>
+      <c r="O214" s="22"/>
+      <c r="P214" s="22"/>
+      <c r="Q214" s="22"/>
+      <c r="R214" s="22"/>
+      <c r="S214" s="22"/>
+      <c r="T214" s="22"/>
+      <c r="U214" s="22"/>
+    </row>
+    <row r="215" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A215" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B215" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C215" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D215" s="22">
+        <v>398</v>
+      </c>
+      <c r="E215" s="22">
+        <v>897</v>
+      </c>
+      <c r="F215" s="22"/>
+      <c r="G215" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="H215" s="9"/>
+      <c r="I215" s="9">
+        <f t="shared" si="9"/>
+        <v>28</v>
+      </c>
+      <c r="J215" s="22">
+        <v>30</v>
+      </c>
+      <c r="K215" s="22"/>
+      <c r="L215" s="22"/>
+      <c r="M215" s="22"/>
+      <c r="N215" s="22"/>
+      <c r="O215" s="22"/>
+      <c r="P215" s="22"/>
+      <c r="Q215" s="22"/>
+      <c r="R215" s="22"/>
+      <c r="S215" s="22"/>
+      <c r="T215" s="22"/>
+      <c r="U215" s="22"/>
     </row>
     <row r="230" spans="1:21" ht="15.75" customHeight="1">
       <c r="A230" s="10"/>
@@ -27057,6 +27248,282 @@
       <c r="T1012" s="10"/>
       <c r="U1012" s="10"/>
     </row>
+    <row r="1013" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1013" s="10"/>
+      <c r="B1013" s="10"/>
+      <c r="C1013" s="10"/>
+      <c r="D1013" s="10"/>
+      <c r="E1013" s="10"/>
+      <c r="F1013" s="10"/>
+      <c r="G1013" s="10"/>
+      <c r="H1013" s="10"/>
+      <c r="I1013" s="10"/>
+      <c r="J1013" s="10"/>
+      <c r="K1013" s="10"/>
+      <c r="L1013" s="10"/>
+      <c r="M1013" s="10"/>
+      <c r="N1013" s="10"/>
+      <c r="O1013" s="10"/>
+      <c r="P1013" s="10"/>
+      <c r="Q1013" s="10"/>
+      <c r="R1013" s="10"/>
+      <c r="S1013" s="10"/>
+      <c r="T1013" s="10"/>
+      <c r="U1013" s="10"/>
+    </row>
+    <row r="1014" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1014" s="10"/>
+      <c r="B1014" s="10"/>
+      <c r="C1014" s="10"/>
+      <c r="D1014" s="10"/>
+      <c r="E1014" s="10"/>
+      <c r="F1014" s="10"/>
+      <c r="G1014" s="10"/>
+      <c r="H1014" s="10"/>
+      <c r="I1014" s="10"/>
+      <c r="J1014" s="10"/>
+      <c r="K1014" s="10"/>
+      <c r="L1014" s="10"/>
+      <c r="M1014" s="10"/>
+      <c r="N1014" s="10"/>
+      <c r="O1014" s="10"/>
+      <c r="P1014" s="10"/>
+      <c r="Q1014" s="10"/>
+      <c r="R1014" s="10"/>
+      <c r="S1014" s="10"/>
+      <c r="T1014" s="10"/>
+      <c r="U1014" s="10"/>
+    </row>
+    <row r="1015" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1015" s="10"/>
+      <c r="B1015" s="10"/>
+      <c r="C1015" s="10"/>
+      <c r="D1015" s="10"/>
+      <c r="E1015" s="10"/>
+      <c r="F1015" s="10"/>
+      <c r="G1015" s="10"/>
+      <c r="H1015" s="10"/>
+      <c r="I1015" s="10"/>
+      <c r="J1015" s="10"/>
+      <c r="K1015" s="10"/>
+      <c r="L1015" s="10"/>
+      <c r="M1015" s="10"/>
+      <c r="N1015" s="10"/>
+      <c r="O1015" s="10"/>
+      <c r="P1015" s="10"/>
+      <c r="Q1015" s="10"/>
+      <c r="R1015" s="10"/>
+      <c r="S1015" s="10"/>
+      <c r="T1015" s="10"/>
+      <c r="U1015" s="10"/>
+    </row>
+    <row r="1016" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1016" s="10"/>
+      <c r="B1016" s="10"/>
+      <c r="C1016" s="10"/>
+      <c r="D1016" s="10"/>
+      <c r="E1016" s="10"/>
+      <c r="F1016" s="10"/>
+      <c r="G1016" s="10"/>
+      <c r="H1016" s="10"/>
+      <c r="I1016" s="10"/>
+      <c r="J1016" s="10"/>
+      <c r="K1016" s="10"/>
+      <c r="L1016" s="10"/>
+      <c r="M1016" s="10"/>
+      <c r="N1016" s="10"/>
+      <c r="O1016" s="10"/>
+      <c r="P1016" s="10"/>
+      <c r="Q1016" s="10"/>
+      <c r="R1016" s="10"/>
+      <c r="S1016" s="10"/>
+      <c r="T1016" s="10"/>
+      <c r="U1016" s="10"/>
+    </row>
+    <row r="1017" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1017" s="10"/>
+      <c r="B1017" s="10"/>
+      <c r="C1017" s="10"/>
+      <c r="D1017" s="10"/>
+      <c r="E1017" s="10"/>
+      <c r="F1017" s="10"/>
+      <c r="G1017" s="10"/>
+      <c r="H1017" s="10"/>
+      <c r="I1017" s="10"/>
+      <c r="J1017" s="10"/>
+      <c r="K1017" s="10"/>
+      <c r="L1017" s="10"/>
+      <c r="M1017" s="10"/>
+      <c r="N1017" s="10"/>
+      <c r="O1017" s="10"/>
+      <c r="P1017" s="10"/>
+      <c r="Q1017" s="10"/>
+      <c r="R1017" s="10"/>
+      <c r="S1017" s="10"/>
+      <c r="T1017" s="10"/>
+      <c r="U1017" s="10"/>
+    </row>
+    <row r="1018" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1018" s="10"/>
+      <c r="B1018" s="10"/>
+      <c r="C1018" s="10"/>
+      <c r="D1018" s="10"/>
+      <c r="E1018" s="10"/>
+      <c r="F1018" s="10"/>
+      <c r="G1018" s="10"/>
+      <c r="H1018" s="10"/>
+      <c r="I1018" s="10"/>
+      <c r="J1018" s="10"/>
+      <c r="K1018" s="10"/>
+      <c r="L1018" s="10"/>
+      <c r="M1018" s="10"/>
+      <c r="N1018" s="10"/>
+      <c r="O1018" s="10"/>
+      <c r="P1018" s="10"/>
+      <c r="Q1018" s="10"/>
+      <c r="R1018" s="10"/>
+      <c r="S1018" s="10"/>
+      <c r="T1018" s="10"/>
+      <c r="U1018" s="10"/>
+    </row>
+    <row r="1019" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1019" s="10"/>
+      <c r="B1019" s="10"/>
+      <c r="C1019" s="10"/>
+      <c r="D1019" s="10"/>
+      <c r="E1019" s="10"/>
+      <c r="F1019" s="10"/>
+      <c r="G1019" s="10"/>
+      <c r="H1019" s="10"/>
+      <c r="I1019" s="10"/>
+      <c r="J1019" s="10"/>
+      <c r="K1019" s="10"/>
+      <c r="L1019" s="10"/>
+      <c r="M1019" s="10"/>
+      <c r="N1019" s="10"/>
+      <c r="O1019" s="10"/>
+      <c r="P1019" s="10"/>
+      <c r="Q1019" s="10"/>
+      <c r="R1019" s="10"/>
+      <c r="S1019" s="10"/>
+      <c r="T1019" s="10"/>
+      <c r="U1019" s="10"/>
+    </row>
+    <row r="1020" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1020" s="10"/>
+      <c r="B1020" s="10"/>
+      <c r="C1020" s="10"/>
+      <c r="D1020" s="10"/>
+      <c r="E1020" s="10"/>
+      <c r="F1020" s="10"/>
+      <c r="G1020" s="10"/>
+      <c r="H1020" s="10"/>
+      <c r="I1020" s="10"/>
+      <c r="J1020" s="10"/>
+      <c r="K1020" s="10"/>
+      <c r="L1020" s="10"/>
+      <c r="M1020" s="10"/>
+      <c r="N1020" s="10"/>
+      <c r="O1020" s="10"/>
+      <c r="P1020" s="10"/>
+      <c r="Q1020" s="10"/>
+      <c r="R1020" s="10"/>
+      <c r="S1020" s="10"/>
+      <c r="T1020" s="10"/>
+      <c r="U1020" s="10"/>
+    </row>
+    <row r="1021" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1021" s="10"/>
+      <c r="B1021" s="10"/>
+      <c r="C1021" s="10"/>
+      <c r="D1021" s="10"/>
+      <c r="E1021" s="10"/>
+      <c r="F1021" s="10"/>
+      <c r="G1021" s="10"/>
+      <c r="H1021" s="10"/>
+      <c r="I1021" s="10"/>
+      <c r="J1021" s="10"/>
+      <c r="K1021" s="10"/>
+      <c r="L1021" s="10"/>
+      <c r="M1021" s="10"/>
+      <c r="N1021" s="10"/>
+      <c r="O1021" s="10"/>
+      <c r="P1021" s="10"/>
+      <c r="Q1021" s="10"/>
+      <c r="R1021" s="10"/>
+      <c r="S1021" s="10"/>
+      <c r="T1021" s="10"/>
+      <c r="U1021" s="10"/>
+    </row>
+    <row r="1022" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1022" s="10"/>
+      <c r="B1022" s="10"/>
+      <c r="C1022" s="10"/>
+      <c r="D1022" s="10"/>
+      <c r="E1022" s="10"/>
+      <c r="F1022" s="10"/>
+      <c r="G1022" s="10"/>
+      <c r="H1022" s="10"/>
+      <c r="I1022" s="10"/>
+      <c r="J1022" s="10"/>
+      <c r="K1022" s="10"/>
+      <c r="L1022" s="10"/>
+      <c r="M1022" s="10"/>
+      <c r="N1022" s="10"/>
+      <c r="O1022" s="10"/>
+      <c r="P1022" s="10"/>
+      <c r="Q1022" s="10"/>
+      <c r="R1022" s="10"/>
+      <c r="S1022" s="10"/>
+      <c r="T1022" s="10"/>
+      <c r="U1022" s="10"/>
+    </row>
+    <row r="1023" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1023" s="10"/>
+      <c r="B1023" s="10"/>
+      <c r="C1023" s="10"/>
+      <c r="D1023" s="10"/>
+      <c r="E1023" s="10"/>
+      <c r="F1023" s="10"/>
+      <c r="G1023" s="10"/>
+      <c r="H1023" s="10"/>
+      <c r="I1023" s="10"/>
+      <c r="J1023" s="10"/>
+      <c r="K1023" s="10"/>
+      <c r="L1023" s="10"/>
+      <c r="M1023" s="10"/>
+      <c r="N1023" s="10"/>
+      <c r="O1023" s="10"/>
+      <c r="P1023" s="10"/>
+      <c r="Q1023" s="10"/>
+      <c r="R1023" s="10"/>
+      <c r="S1023" s="10"/>
+      <c r="T1023" s="10"/>
+      <c r="U1023" s="10"/>
+    </row>
+    <row r="1024" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A1024" s="10"/>
+      <c r="B1024" s="10"/>
+      <c r="C1024" s="10"/>
+      <c r="D1024" s="10"/>
+      <c r="E1024" s="10"/>
+      <c r="F1024" s="10"/>
+      <c r="G1024" s="10"/>
+      <c r="H1024" s="10"/>
+      <c r="I1024" s="10"/>
+      <c r="J1024" s="10"/>
+      <c r="K1024" s="10"/>
+      <c r="L1024" s="10"/>
+      <c r="M1024" s="10"/>
+      <c r="N1024" s="10"/>
+      <c r="O1024" s="10"/>
+      <c r="P1024" s="10"/>
+      <c r="Q1024" s="10"/>
+      <c r="R1024" s="10"/>
+      <c r="S1024" s="10"/>
+      <c r="T1024" s="10"/>
+      <c r="U1024" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
